--- a/input/ES/reg_income.xlsx
+++ b/input/ES/reg_income.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="158" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="166" uniqueCount="68">
   <si>
     <t>Description</t>
   </si>
@@ -57,7 +57,7 @@
     <t>OLS regression estimates (ihs) capital income amount -  who receive capital income</t>
   </si>
   <si>
-    <t>Regions: ES1 =  Noroeste , ES2 = Noreste , ES3 = Madrid , ES4 =  Centro , ES5 = Este , ES5 =  Sur , ES5 = ,  Canarias.</t>
+    <t>Regions: ES1 =  Noroeste , ES2 = Noreste , ES3 = Madrid , ES4 =  Centro , ES5 = Este , ES6=  Sur , ES7 = ,  Canarias.</t>
   </si>
   <si>
     <t>Goodnessoffit</t>
@@ -195,6 +195,12 @@
     <t>Year_transformed</t>
   </si>
   <si>
+    <t>Y2020</t>
+  </si>
+  <si>
+    <t>Y2021</t>
+  </si>
+  <si>
     <t>Constant</t>
   </si>
   <si>
@@ -383,7 +389,7 @@
         <v>16</v>
       </c>
       <c r="B7">
-        <v>0.31876298588660379</v>
+        <v>0.32020493334424105</v>
       </c>
       <c r="C7"/>
       <c r="D7"/>
@@ -391,7 +397,7 @@
         <v>24</v>
       </c>
       <c r="F7">
-        <v>15028.617817897248</v>
+        <v>15106.424510469089</v>
       </c>
     </row>
     <row r="8">
@@ -407,7 +413,7 @@
         <v>25</v>
       </c>
       <c r="F8">
-        <v>-97623386.28692469</v>
+        <v>-97416839.566960737</v>
       </c>
     </row>
     <row r="9">
@@ -442,7 +448,7 @@
         <v>19</v>
       </c>
       <c r="B13">
-        <v>0.63339424295572866</v>
+        <v>0.54353966627829697</v>
       </c>
       <c r="C13"/>
       <c r="D13"/>
@@ -453,7 +459,7 @@
         <v>17</v>
       </c>
       <c r="B14">
-        <v>53223</v>
+        <v>52275</v>
       </c>
       <c r="C14"/>
       <c r="D14"/>
@@ -465,7 +471,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AH33"/>
+  <dimension ref="A1:AJ35"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -473,7 +479,7 @@
         <v>27</v>
       </c>
       <c r="B1" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C1" t="s">
         <v>28</v>
@@ -570,6 +576,12 @@
       </c>
       <c r="AH1" t="s">
         <v>59</v>
+      </c>
+      <c r="AI1" t="s">
+        <v>60</v>
+      </c>
+      <c r="AJ1" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="2">
@@ -577,103 +589,109 @@
         <v>28</v>
       </c>
       <c r="B2">
-        <v>-0.049454691310732921</v>
+        <v>-0.049047819627476584</v>
       </c>
       <c r="C2">
-        <v>0.00043173714771216039</v>
+        <v>0.00043189762075675279</v>
       </c>
       <c r="D2">
-        <v>-6.6266535941864502e-07</v>
+        <v>-7.1937156704148443e-07</v>
       </c>
       <c r="E2">
-        <v>3.3265319739136057e-08</v>
+        <v>3.3578253004639401e-08</v>
       </c>
       <c r="F2">
-        <v>-6.0959814604424941e-06</v>
+        <v>-8.241966738302059e-06</v>
       </c>
       <c r="G2">
-        <v>1.9222037769233948e-05</v>
+        <v>1.855934931981686e-05</v>
       </c>
       <c r="H2">
-        <v>3.3616512975651253e-07</v>
+        <v>-1.6690760842623853e-08</v>
       </c>
       <c r="I2">
-        <v>-9.4071768424800991e-07</v>
+        <v>-7.3914409938055097e-07</v>
       </c>
       <c r="J2">
-        <v>1.9342654812550678e-06</v>
+        <v>1.6071703646335672e-06</v>
       </c>
       <c r="K2">
-        <v>-5.7624821228866908e-05</v>
+        <v>-5.7547310330336932e-05</v>
       </c>
       <c r="L2">
-        <v>-5.718589117759293e-06</v>
+        <v>-5.6414867353351785e-06</v>
       </c>
       <c r="M2">
-        <v>-9.3407144047405155e-07</v>
+        <v>-8.3731349492827086e-07</v>
       </c>
       <c r="N2">
-        <v>-0.00042433242154412705</v>
+        <v>-0.00042477101755662413</v>
       </c>
       <c r="O2">
-        <v>9.1092695125573891e-08</v>
+        <v>9.0939883462974436e-08</v>
       </c>
       <c r="P2">
-        <v>-6.9630187884068893e-07</v>
+        <v>-5.5365494455151705e-07</v>
       </c>
       <c r="Q2">
-        <v>-4.4291088169017185e-06</v>
+        <v>-4.4643412823985004e-06</v>
       </c>
       <c r="R2">
-        <v>-0.00020488441457322765</v>
+        <v>-0.00020276970545396434</v>
       </c>
       <c r="S2">
-        <v>-0.00018583290833420433</v>
+        <v>-0.00018457906641151828</v>
       </c>
       <c r="T2">
-        <v>-0.0001437379964723695</v>
+        <v>-0.00014230107507940196</v>
       </c>
       <c r="U2">
-        <v>-0.00043025157219142519</v>
+        <v>-0.00042824173032764926</v>
       </c>
       <c r="V2">
-        <v>-0.00038948152581626505</v>
+        <v>-0.00038901432655613779</v>
       </c>
       <c r="W2">
-        <v>-0.00054368934856143479</v>
+        <v>-0.00054219627613523783</v>
       </c>
       <c r="X2">
-        <v>3.2875115851226283e-05</v>
+        <v>3.2606815590782098e-05</v>
       </c>
       <c r="Y2">
-        <v>1.2960937229377916e-05</v>
+        <v>1.2507353626023731e-05</v>
       </c>
       <c r="Z2">
-        <v>0.00010968366927055643</v>
+        <v>0.00010919930756859229</v>
       </c>
       <c r="AA2">
-        <v>2.2234755090753911e-05</v>
+        <v>2.008944525785602e-05</v>
       </c>
       <c r="AB2">
-        <v>3.2851493319003622e-05</v>
+        <v>3.0620277680629821e-05</v>
       </c>
       <c r="AC2">
-        <v>1.9518044904853678e-05</v>
+        <v>1.737095255270012e-05</v>
       </c>
       <c r="AD2">
-        <v>1.186426867075995e-05</v>
+        <v>9.9550358277092029e-06</v>
       </c>
       <c r="AE2">
-        <v>2.0848925512747659e-05</v>
+        <v>1.8740201872788885e-05</v>
       </c>
       <c r="AF2">
-        <v>1.8016048059746909e-05</v>
+        <v>1.6236824556625044e-05</v>
       </c>
       <c r="AG2">
-        <v>3.2427673415165035e-07</v>
+        <v>4.5706930769845149e-07</v>
       </c>
       <c r="AH2">
-        <v>0.00034613295039739823</v>
+        <v>-1.1395694809765368e-05</v>
+      </c>
+      <c r="AI2">
+        <v>7.7841352484640314e-07</v>
+      </c>
+      <c r="AJ2">
+        <v>0.00034627450460851311</v>
       </c>
     </row>
     <row r="3">
@@ -681,103 +699,109 @@
         <v>29</v>
       </c>
       <c r="B3">
-        <v>-0.022431504360503968</v>
+        <v>-0.022291752349886996</v>
       </c>
       <c r="C3">
-        <v>-6.6266535941864502e-07</v>
+        <v>-7.1937156704148443e-07</v>
       </c>
       <c r="D3">
-        <v>1.8012752795665159e-05</v>
+        <v>1.8125442436254629e-05</v>
       </c>
       <c r="E3">
-        <v>-1.6785502349928611e-07</v>
+        <v>-1.6888010944626742e-07</v>
       </c>
       <c r="F3">
-        <v>3.8715113795570241e-06</v>
+        <v>3.7800642651957662e-06</v>
       </c>
       <c r="G3">
-        <v>-9.5020304315485756e-06</v>
+        <v>-9.4488630177101824e-06</v>
       </c>
       <c r="H3">
-        <v>-1.4180418073471551e-05</v>
+        <v>-1.4270496977472148e-05</v>
       </c>
       <c r="I3">
-        <v>-1.2255673480901987e-05</v>
+        <v>-1.2432825514939752e-05</v>
       </c>
       <c r="J3">
-        <v>-9.864825399419761e-07</v>
+        <v>-9.6927094243349794e-07</v>
       </c>
       <c r="K3">
-        <v>-1.0834928015026822e-06</v>
+        <v>-9.6672651619156798e-07</v>
       </c>
       <c r="L3">
-        <v>-2.6060318885225805e-06</v>
+        <v>-2.6211966690228471e-06</v>
       </c>
       <c r="M3">
-        <v>-3.1338989980077789e-07</v>
+        <v>-2.8019044137940674e-07</v>
       </c>
       <c r="N3">
-        <v>8.2333549944939496e-07</v>
+        <v>8.6552023993750523e-07</v>
       </c>
       <c r="O3">
-        <v>-2.8773079103080056e-07</v>
+        <v>-2.8893583893147131e-07</v>
       </c>
       <c r="P3">
-        <v>2.8529170781301794e-07</v>
+        <v>3.1809939197751243e-07</v>
       </c>
       <c r="Q3">
-        <v>-2.88184855673491e-08</v>
+        <v>-9.2049423138635105e-08</v>
       </c>
       <c r="R3">
-        <v>-0.00013289368719563159</v>
+        <v>-0.00013339923347572137</v>
       </c>
       <c r="S3">
-        <v>-0.00013909063257459549</v>
+        <v>-0.00013984982154221666</v>
       </c>
       <c r="T3">
-        <v>-0.00013915259142187336</v>
+        <v>-0.00013983667603342863</v>
       </c>
       <c r="U3">
-        <v>9.2835608810035983e-05</v>
+        <v>9.4556681224327444e-05</v>
       </c>
       <c r="V3">
-        <v>-1.8199907419089623e-05</v>
+        <v>-1.7461056325237417e-05</v>
       </c>
       <c r="W3">
-        <v>3.4184986662915199e-05</v>
+        <v>3.4993562997956667e-05</v>
       </c>
       <c r="X3">
-        <v>7.0596743197700326e-06</v>
+        <v>7.0259324899972927e-06</v>
       </c>
       <c r="Y3">
-        <v>3.3498853011830892e-05</v>
+        <v>3.3636494439989339e-05</v>
       </c>
       <c r="Z3">
-        <v>1.2459658143304568e-05</v>
+        <v>1.2068406259105221e-05</v>
       </c>
       <c r="AA3">
-        <v>-2.8963431150097192e-07</v>
+        <v>-5.6742895563629365e-08</v>
       </c>
       <c r="AB3">
-        <v>2.9920934160534854e-06</v>
+        <v>3.1955560987219204e-06</v>
       </c>
       <c r="AC3">
-        <v>-7.7616755457745891e-07</v>
+        <v>-6.8472474563408703e-07</v>
       </c>
       <c r="AD3">
-        <v>2.9705298366321492e-06</v>
+        <v>3.2431857514446849e-06</v>
       </c>
       <c r="AE3">
-        <v>-7.6108715431803884e-07</v>
+        <v>-8.2469178198846168e-07</v>
       </c>
       <c r="AF3">
-        <v>-9.9309227653372669e-07</v>
+        <v>-1.0605696990893357e-06</v>
       </c>
       <c r="AG3">
-        <v>-7.3688707800804895e-08</v>
+        <v>-1.2611444277851479e-08</v>
       </c>
       <c r="AH3">
-        <v>-0.00028780368450828913</v>
+        <v>-1.7413413081221549e-06</v>
+      </c>
+      <c r="AI3">
+        <v>-5.8608815061820762e-06</v>
+      </c>
+      <c r="AJ3">
+        <v>-0.00029159833162855969</v>
       </c>
     </row>
     <row r="4">
@@ -785,103 +809,109 @@
         <v>30</v>
       </c>
       <c r="B4">
-        <v>0.00022222907925898292</v>
+        <v>0.0002226663494288233</v>
       </c>
       <c r="C4">
-        <v>3.3265319739136057e-08</v>
+        <v>3.3578253004639401e-08</v>
       </c>
       <c r="D4">
-        <v>-1.6785502349928611e-07</v>
+        <v>-1.6888010944626742e-07</v>
       </c>
       <c r="E4">
-        <v>1.663087318900021e-09</v>
+        <v>1.6727282583411538e-09</v>
       </c>
       <c r="F4">
-        <v>-1.0846835246964713e-07</v>
+        <v>-1.070237855945143e-07</v>
       </c>
       <c r="G4">
-        <v>1.1824028152076093e-08</v>
+        <v>1.0273546572809171e-08</v>
       </c>
       <c r="H4">
-        <v>6.6593286774008528e-08</v>
+        <v>6.671136080329205e-08</v>
       </c>
       <c r="I4">
-        <v>8.9202116180281253e-08</v>
+        <v>9.081154328071772e-08</v>
       </c>
       <c r="J4">
-        <v>7.9365608593560513e-09</v>
+        <v>7.7275767180458687e-09</v>
       </c>
       <c r="K4">
-        <v>-1.3769748027964034e-08</v>
+        <v>-1.4816671349479194e-08</v>
       </c>
       <c r="L4">
-        <v>2.4353636414914117e-08</v>
+        <v>2.4445942903902144e-08</v>
       </c>
       <c r="M4">
-        <v>-4.1022173935000866e-10</v>
+        <v>-7.2624813416632366e-10</v>
       </c>
       <c r="N4">
-        <v>-3.9222811388244211e-08</v>
+        <v>-3.958036537029314e-08</v>
       </c>
       <c r="O4">
-        <v>2.6493330990526786e-09</v>
+        <v>2.6591359089132346e-09</v>
       </c>
       <c r="P4">
-        <v>-6.538111937488371e-10</v>
+        <v>-9.4327821682507526e-10</v>
       </c>
       <c r="Q4">
-        <v>2.275567861549283e-09</v>
+        <v>2.9432057953050599e-09</v>
       </c>
       <c r="R4">
-        <v>1.1737753706095371e-06</v>
+        <v>1.178256127163396e-06</v>
       </c>
       <c r="S4">
-        <v>1.2684298192710072e-06</v>
+        <v>1.2750902600667099e-06</v>
       </c>
       <c r="T4">
-        <v>1.2844227315813218e-06</v>
+        <v>1.2905328601471298e-06</v>
       </c>
       <c r="U4">
-        <v>-9.0644583065478604e-07</v>
+        <v>-9.2138299886223013e-07</v>
       </c>
       <c r="V4">
-        <v>-2.5301988561612497e-08</v>
+        <v>-3.196357144212363e-08</v>
       </c>
       <c r="W4">
-        <v>-7.94541009372632e-07</v>
+        <v>-8.0194097487419187e-07</v>
       </c>
       <c r="X4">
-        <v>1.9096019429329625e-09</v>
+        <v>2.4718955330417382e-09</v>
       </c>
       <c r="Y4">
-        <v>-2.6422740261230321e-07</v>
+        <v>-2.6520618624859582e-07</v>
       </c>
       <c r="Z4">
-        <v>-2.3703806077740918e-08</v>
+        <v>-2.019680137828838e-08</v>
       </c>
       <c r="AA4">
-        <v>-4.3415141386539307e-09</v>
+        <v>-6.8232360607243115e-09</v>
       </c>
       <c r="AB4">
-        <v>-3.2763529015902064e-08</v>
+        <v>-3.4670737634483481e-08</v>
       </c>
       <c r="AC4">
-        <v>-9.6861377565618268e-09</v>
+        <v>-1.0666190224700449e-08</v>
       </c>
       <c r="AD4">
-        <v>-3.5228759364842849e-08</v>
+        <v>-3.7838868997234808e-08</v>
       </c>
       <c r="AE4">
-        <v>4.83441720118436e-09</v>
+        <v>5.3965842930057215e-09</v>
       </c>
       <c r="AF4">
-        <v>-8.1460225145584858e-10</v>
+        <v>-7.9962469026845007e-10</v>
       </c>
       <c r="AG4">
-        <v>-1.7697718347875624e-09</v>
+        <v>-2.1088776176912062e-09</v>
       </c>
       <c r="AH4">
-        <v>2.7132771203039535e-06</v>
+        <v>2.52249146753247e-10</v>
+      </c>
+      <c r="AI4">
+        <v>5.1451634562556878e-08</v>
+      </c>
+      <c r="AJ4">
+        <v>2.7453203057273422e-06</v>
       </c>
     </row>
     <row r="5">
@@ -889,103 +919,109 @@
         <v>31</v>
       </c>
       <c r="B5">
-        <v>-0.11894398478598062</v>
+        <v>-0.1272697368254139</v>
       </c>
       <c r="C5">
-        <v>-6.0959814604424941e-06</v>
+        <v>-8.241966738302059e-06</v>
       </c>
       <c r="D5">
-        <v>3.8715113795570241e-06</v>
+        <v>3.7800642651957662e-06</v>
       </c>
       <c r="E5">
-        <v>-1.0846835246964713e-07</v>
+        <v>-1.070237855945143e-07</v>
       </c>
       <c r="F5">
-        <v>0.0069030181106416464</v>
+        <v>0.0070011271870271284</v>
       </c>
       <c r="G5">
-        <v>0.00089303193385478796</v>
+        <v>0.00089594544329824652</v>
       </c>
       <c r="H5">
-        <v>0.00074938583118323615</v>
+        <v>0.00075579857920740439</v>
       </c>
       <c r="I5">
-        <v>0.00058724131331214192</v>
+        <v>0.00059028655789596291</v>
       </c>
       <c r="J5">
-        <v>5.9629134612511602e-06</v>
+        <v>6.0484794832162373e-06</v>
       </c>
       <c r="K5">
-        <v>1.8915300501936842e-06</v>
+        <v>4.7606042383823601e-06</v>
       </c>
       <c r="L5">
-        <v>7.2551501351288175e-07</v>
+        <v>3.9998818759418743e-07</v>
       </c>
       <c r="M5">
-        <v>-1.0193228779546308e-05</v>
+        <v>-1.1265379461933814e-05</v>
       </c>
       <c r="N5">
-        <v>7.9664515972540967e-05</v>
+        <v>8.3427250543406401e-05</v>
       </c>
       <c r="O5">
-        <v>-1.7589163526709101e-07</v>
+        <v>-1.9504447077157633e-07</v>
       </c>
       <c r="P5">
-        <v>-6.0548709677588065e-06</v>
+        <v>-7.6681099742058539e-06</v>
       </c>
       <c r="Q5">
-        <v>8.2143268312577867e-06</v>
+        <v>9.5385467637937026e-06</v>
       </c>
       <c r="R5">
-        <v>-8.4748861329416817e-05</v>
+        <v>-8.6934742314077697e-05</v>
       </c>
       <c r="S5">
-        <v>-8.4694143457047713e-05</v>
+        <v>-9.0659463184927195e-05</v>
       </c>
       <c r="T5">
-        <v>-3.2755991009762988e-05</v>
+        <v>-3.7183345565693071e-05</v>
       </c>
       <c r="U5">
-        <v>5.4172295235524297e-05</v>
+        <v>7.3814813121306189e-05</v>
       </c>
       <c r="V5">
-        <v>-8.1881973549052258e-05</v>
+        <v>-6.1034824572332952e-05</v>
       </c>
       <c r="W5">
-        <v>-8.626780096255036e-05</v>
+        <v>-7.2887149255579191e-05</v>
       </c>
       <c r="X5">
-        <v>4.0877533799368282e-05</v>
+        <v>4.4439057352386403e-05</v>
       </c>
       <c r="Y5">
-        <v>5.0404522487951546e-05</v>
+        <v>5.7182990474016758e-05</v>
       </c>
       <c r="Z5">
-        <v>2.6840814959948789e-06</v>
+        <v>7.3325191904736575e-06</v>
       </c>
       <c r="AA5">
-        <v>-0.00035665476068260933</v>
+        <v>-0.0003879657408031901</v>
       </c>
       <c r="AB5">
-        <v>-0.00031278162733416247</v>
+        <v>-0.0003438759676396907</v>
       </c>
       <c r="AC5">
-        <v>-0.00029149891908651052</v>
+        <v>-0.00032144368232211009</v>
       </c>
       <c r="AD5">
-        <v>-0.00030614056520443549</v>
+        <v>-0.00033621321242632862</v>
       </c>
       <c r="AE5">
-        <v>-0.00030570504301377589</v>
+        <v>-0.00033238896329270599</v>
       </c>
       <c r="AF5">
-        <v>-0.00030864186912341182</v>
+        <v>-0.00033821930018997277</v>
       </c>
       <c r="AG5">
-        <v>1.312790935562137e-06</v>
+        <v>-1.0847629299590987e-06</v>
       </c>
       <c r="AH5">
-        <v>-0.00015056543033221308</v>
+        <v>0.0001415248638067281</v>
+      </c>
+      <c r="AI5">
+        <v>9.6796122039921882e-05</v>
+      </c>
+      <c r="AJ5">
+        <v>-0.00011587260424335971</v>
       </c>
     </row>
     <row r="6">
@@ -993,103 +1029,109 @@
         <v>32</v>
       </c>
       <c r="B6">
-        <v>-0.15799272093562175</v>
+        <v>-0.1688379343589245</v>
       </c>
       <c r="C6">
-        <v>1.9222037769233948e-05</v>
+        <v>1.855934931981686e-05</v>
       </c>
       <c r="D6">
-        <v>-9.5020304315485756e-06</v>
+        <v>-9.4488630177101824e-06</v>
       </c>
       <c r="E6">
-        <v>1.1824028152076093e-08</v>
+        <v>1.0273546572809171e-08</v>
       </c>
       <c r="F6">
-        <v>0.00089303193385478796</v>
+        <v>0.00089594544329824652</v>
       </c>
       <c r="G6">
-        <v>0.0023015634132054329</v>
+        <v>0.0023041814130098995</v>
       </c>
       <c r="H6">
-        <v>0.00077781750078962937</v>
+        <v>0.00077996021318262672</v>
       </c>
       <c r="I6">
-        <v>0.0005934377547757696</v>
+        <v>0.0005952103883234025</v>
       </c>
       <c r="J6">
-        <v>8.796549220679139e-06</v>
+        <v>7.7739891524872083e-06</v>
       </c>
       <c r="K6">
-        <v>1.1849337779196809e-05</v>
+        <v>1.2262476722449255e-05</v>
       </c>
       <c r="L6">
-        <v>3.0704944980222247e-06</v>
+        <v>2.8329295447831688e-06</v>
       </c>
       <c r="M6">
-        <v>-9.9612791581779276e-06</v>
+        <v>-9.8463402691600676e-06</v>
       </c>
       <c r="N6">
-        <v>4.7684286516681535e-05</v>
+        <v>5.25249177570374e-05</v>
       </c>
       <c r="O6">
-        <v>1.0792745720968088e-07</v>
+        <v>1.002143807837706e-07</v>
       </c>
       <c r="P6">
-        <v>-8.5154949488814529e-06</v>
+        <v>-8.8487608585180564e-06</v>
       </c>
       <c r="Q6">
-        <v>1.1073215599314283e-05</v>
+        <v>1.159891588002625e-05</v>
       </c>
       <c r="R6">
-        <v>-1.2104100224375977e-05</v>
+        <v>-9.9597856857855599e-06</v>
       </c>
       <c r="S6">
-        <v>5.7740975907146489e-05</v>
+        <v>5.8883803869194855e-05</v>
       </c>
       <c r="T6">
-        <v>8.5622407482293853e-05</v>
+        <v>8.8132520044139427e-05</v>
       </c>
       <c r="U6">
-        <v>8.3036332029209447e-05</v>
+        <v>8.5320300293013223e-05</v>
       </c>
       <c r="V6">
-        <v>1.6375039565686615e-05</v>
+        <v>1.7200407890189924e-05</v>
       </c>
       <c r="W6">
-        <v>7.0723872223454209e-05</v>
+        <v>7.3103565255648747e-05</v>
       </c>
       <c r="X6">
-        <v>3.497730833551634e-05</v>
+        <v>3.3090857626206661e-05</v>
       </c>
       <c r="Y6">
-        <v>-1.8459387842582608e-06</v>
+        <v>-3.0687237558719e-06</v>
       </c>
       <c r="Z6">
-        <v>0.00010042887687203324</v>
+        <v>0.00010496985164197403</v>
       </c>
       <c r="AA6">
-        <v>-3.9753025021668992e-07</v>
+        <v>-7.4596915694141459e-06</v>
       </c>
       <c r="AB6">
-        <v>6.2341965845422702e-05</v>
+        <v>5.4673612840301764e-05</v>
       </c>
       <c r="AC6">
-        <v>5.4421947256034584e-05</v>
+        <v>4.9310795184917987e-05</v>
       </c>
       <c r="AD6">
-        <v>5.3714956046137257e-05</v>
+        <v>4.5919926953411143e-05</v>
       </c>
       <c r="AE6">
-        <v>6.5974288557758365e-05</v>
+        <v>6.1274752174575741e-05</v>
       </c>
       <c r="AF6">
-        <v>6.9240617735101252e-05</v>
+        <v>6.3162003885449379e-05</v>
       </c>
       <c r="AG6">
-        <v>-9.143016305353215e-07</v>
+        <v>-7.7394332615398398e-07</v>
       </c>
       <c r="AH6">
-        <v>-0.00034746826021087105</v>
+        <v>-2.2030612711127417e-05</v>
+      </c>
+      <c r="AI6">
+        <v>3.1578757810894997e-05</v>
+      </c>
+      <c r="AJ6">
+        <v>-0.00034392369399797193</v>
       </c>
     </row>
     <row r="7">
@@ -1097,103 +1139,109 @@
         <v>33</v>
       </c>
       <c r="B7">
-        <v>-0.09000199343080241</v>
+        <v>-0.098748510927967229</v>
       </c>
       <c r="C7">
-        <v>3.3616512975651253e-07</v>
+        <v>-1.6690760842623853e-08</v>
       </c>
       <c r="D7">
-        <v>-1.4180418073471551e-05</v>
+        <v>-1.4270496977472148e-05</v>
       </c>
       <c r="E7">
-        <v>6.6593286774008528e-08</v>
+        <v>6.671136080329205e-08</v>
       </c>
       <c r="F7">
-        <v>0.00074938583118323615</v>
+        <v>0.00075579857920740439</v>
       </c>
       <c r="G7">
-        <v>0.00077781750078962937</v>
+        <v>0.00077996021318262672</v>
       </c>
       <c r="H7">
-        <v>0.0011315053642052654</v>
+        <v>0.0011315132796168752</v>
       </c>
       <c r="I7">
-        <v>0.0005878337582678391</v>
+        <v>0.00058888876881138085</v>
       </c>
       <c r="J7">
-        <v>4.2357679139632553e-06</v>
+        <v>3.2360955125311024e-06</v>
       </c>
       <c r="K7">
-        <v>2.0786111657702558e-05</v>
+        <v>2.0982357384107968e-05</v>
       </c>
       <c r="L7">
-        <v>2.0729995756803925e-06</v>
+        <v>1.9737877711997582e-06</v>
       </c>
       <c r="M7">
-        <v>-2.898844185125591e-06</v>
+        <v>-2.542223090869507e-06</v>
       </c>
       <c r="N7">
-        <v>6.7351037229235766e-05</v>
+        <v>7.054752164711747e-05</v>
       </c>
       <c r="O7">
-        <v>1.6384444896190105e-07</v>
+        <v>1.4424970242157938e-07</v>
       </c>
       <c r="P7">
-        <v>-6.5998867637764146e-06</v>
+        <v>-6.6178325936134106e-06</v>
       </c>
       <c r="Q7">
-        <v>5.9116496688289687e-06</v>
+        <v>6.7493930827819065e-06</v>
       </c>
       <c r="R7">
-        <v>5.4293659110573666e-05</v>
+        <v>5.1677075663596421e-05</v>
       </c>
       <c r="S7">
-        <v>7.7710050512130055e-05</v>
+        <v>7.3886624544214119e-05</v>
       </c>
       <c r="T7">
-        <v>0.00012302769918354166</v>
+        <v>0.00012020170536684142</v>
       </c>
       <c r="U7">
-        <v>0.00014629105508320726</v>
+        <v>0.00014718677037586051</v>
       </c>
       <c r="V7">
-        <v>0.00011471605355682865</v>
+        <v>0.00011459949982876333</v>
       </c>
       <c r="W7">
-        <v>0.00014042705096554026</v>
+        <v>0.00014111864591351823</v>
       </c>
       <c r="X7">
-        <v>2.7588099927021692e-05</v>
+        <v>2.723835413366407e-05</v>
       </c>
       <c r="Y7">
-        <v>-9.6900770293089894e-06</v>
+        <v>-9.4038118989487331e-06</v>
       </c>
       <c r="Z7">
-        <v>2.2871316319884326e-05</v>
+        <v>3.5154995881514023e-05</v>
       </c>
       <c r="AA7">
-        <v>1.1202492387732697e-05</v>
+        <v>-3.0570556696946517e-07</v>
       </c>
       <c r="AB7">
-        <v>4.0732752038115892e-05</v>
+        <v>2.9363457396843162e-05</v>
       </c>
       <c r="AC7">
-        <v>4.2613918864713538e-05</v>
+        <v>3.4039029180815849e-05</v>
       </c>
       <c r="AD7">
-        <v>4.362694109231747e-05</v>
+        <v>3.1579243025551076e-05</v>
       </c>
       <c r="AE7">
-        <v>6.1628326391954697e-05</v>
+        <v>5.5209910383559709e-05</v>
       </c>
       <c r="AF7">
-        <v>4.9979475708497805e-05</v>
+        <v>4.0949210002263745e-05</v>
       </c>
       <c r="AG7">
-        <v>-4.1721118033656768e-06</v>
+        <v>-3.6728508684652067e-06</v>
       </c>
       <c r="AH7">
-        <v>-0.0002912081307662889</v>
+        <v>-2.6350577141604002e-06</v>
+      </c>
+      <c r="AI7">
+        <v>1.7121646091136532e-05</v>
+      </c>
+      <c r="AJ7">
+        <v>-0.00028215220952928924</v>
       </c>
     </row>
     <row r="8">
@@ -1201,103 +1249,109 @@
         <v>34</v>
       </c>
       <c r="B8">
-        <v>-0.035237987944406982</v>
+        <v>-0.040879888998375774</v>
       </c>
       <c r="C8">
-        <v>-9.4071768424800991e-07</v>
+        <v>-7.3914409938055097e-07</v>
       </c>
       <c r="D8">
-        <v>-1.2255673480901987e-05</v>
+        <v>-1.2432825514939752e-05</v>
       </c>
       <c r="E8">
-        <v>8.9202116180281253e-08</v>
+        <v>9.081154328071772e-08</v>
       </c>
       <c r="F8">
-        <v>0.00058724131331214192</v>
+        <v>0.00059028655789596291</v>
       </c>
       <c r="G8">
-        <v>0.0005934377547757696</v>
+        <v>0.0005952103883234025</v>
       </c>
       <c r="H8">
-        <v>0.0005878337582678391</v>
+        <v>0.00058888876881138085</v>
       </c>
       <c r="I8">
-        <v>0.00068931284603347936</v>
+        <v>0.00069174820066388628</v>
       </c>
       <c r="J8">
-        <v>2.6417807943617867e-06</v>
+        <v>2.0368523341756255e-06</v>
       </c>
       <c r="K8">
-        <v>2.5238308197965248e-06</v>
+        <v>2.5789119911564537e-06</v>
       </c>
       <c r="L8">
-        <v>9.0660575383667505e-08</v>
+        <v>5.5289611406675109e-08</v>
       </c>
       <c r="M8">
-        <v>-4.7982660206105442e-06</v>
+        <v>-4.3570862052101599e-06</v>
       </c>
       <c r="N8">
-        <v>8.2170133663235178e-05</v>
+        <v>8.6852708167312485e-05</v>
       </c>
       <c r="O8">
-        <v>-3.469218407606828e-08</v>
+        <v>-3.5753092428886456e-08</v>
       </c>
       <c r="P8">
-        <v>-4.6355220483620501e-06</v>
+        <v>-5.4800625058765496e-06</v>
       </c>
       <c r="Q8">
-        <v>6.1050641238750348e-06</v>
+        <v>6.5896982252864441e-06</v>
       </c>
       <c r="R8">
-        <v>-1.370963977263276e-05</v>
+        <v>-9.9348736545875816e-06</v>
       </c>
       <c r="S8">
-        <v>-1.2827912515240126e-05</v>
+        <v>-1.0058234629685758e-05</v>
       </c>
       <c r="T8">
-        <v>1.6990177490073276e-05</v>
+        <v>2.1311724134353537e-05</v>
       </c>
       <c r="U8">
-        <v>1.0929610966390181e-05</v>
+        <v>1.1399888685241705e-05</v>
       </c>
       <c r="V8">
-        <v>1.3374220194669543e-05</v>
+        <v>1.307100996085454e-05</v>
       </c>
       <c r="W8">
-        <v>2.1542359730252847e-05</v>
+        <v>2.0899714964468818e-05</v>
       </c>
       <c r="X8">
-        <v>1.2382438929014677e-05</v>
+        <v>1.1635607613298661e-05</v>
       </c>
       <c r="Y8">
-        <v>7.2643634315007145e-06</v>
+        <v>7.0885674723720956e-06</v>
       </c>
       <c r="Z8">
-        <v>2.0656766935375653e-05</v>
+        <v>2.3598843092312557e-05</v>
       </c>
       <c r="AA8">
-        <v>-3.2349431402661517e-05</v>
+        <v>-3.490996641805142e-05</v>
       </c>
       <c r="AB8">
-        <v>-1.7887042008131091e-05</v>
+        <v>-2.0527092432584375e-05</v>
       </c>
       <c r="AC8">
-        <v>-5.894578668109681e-06</v>
+        <v>-7.3287296165411089e-06</v>
       </c>
       <c r="AD8">
-        <v>-1.3738714630288901e-05</v>
+        <v>-1.6400313896113033e-05</v>
       </c>
       <c r="AE8">
-        <v>1.6392407808113615e-06</v>
+        <v>7.8808003916201817e-07</v>
       </c>
       <c r="AF8">
-        <v>-7.9407637682717063e-06</v>
+        <v>-1.0023184592857515e-05</v>
       </c>
       <c r="AG8">
-        <v>-2.6956156767708938e-06</v>
+        <v>-2.2712442873387257e-06</v>
       </c>
       <c r="AH8">
-        <v>-0.00013817329010755008</v>
+        <v>-2.4612296879961913e-05</v>
+      </c>
+      <c r="AI8">
+        <v>3.2512755883705105e-06</v>
+      </c>
+      <c r="AJ8">
+        <v>-0.00014186833008786152</v>
       </c>
     </row>
     <row r="9">
@@ -1305,103 +1359,109 @@
         <v>35</v>
       </c>
       <c r="B9">
-        <v>0.52094305766110649</v>
+        <v>0.52230224930162195</v>
       </c>
       <c r="C9">
-        <v>1.9342654812550678e-06</v>
+        <v>1.6071703646335672e-06</v>
       </c>
       <c r="D9">
-        <v>-9.864825399419761e-07</v>
+        <v>-9.6927094243349794e-07</v>
       </c>
       <c r="E9">
-        <v>7.9365608593560513e-09</v>
+        <v>7.7275767180458687e-09</v>
       </c>
       <c r="F9">
-        <v>5.9629134612511602e-06</v>
+        <v>6.0484794832162373e-06</v>
       </c>
       <c r="G9">
-        <v>8.796549220679139e-06</v>
+        <v>7.7739891524872083e-06</v>
       </c>
       <c r="H9">
-        <v>4.2357679139632553e-06</v>
+        <v>3.2360955125311024e-06</v>
       </c>
       <c r="I9">
-        <v>2.6417807943617867e-06</v>
+        <v>2.0368523341756255e-06</v>
       </c>
       <c r="J9">
-        <v>5.4298826176083947e-05</v>
+        <v>5.4637988424876221e-05</v>
       </c>
       <c r="K9">
-        <v>-6.2722499326892359e-06</v>
+        <v>-6.589703952821758e-06</v>
       </c>
       <c r="L9">
-        <v>6.517558633111074e-07</v>
+        <v>6.727853820748999e-07</v>
       </c>
       <c r="M9">
-        <v>-2.1006686263617072e-05</v>
+        <v>-2.1129394291012563e-05</v>
       </c>
       <c r="N9">
-        <v>-1.6125883602401086e-06</v>
+        <v>-1.5943984269933549e-06</v>
       </c>
       <c r="O9">
-        <v>1.5347041682199427e-08</v>
+        <v>1.3473076405657386e-08</v>
       </c>
       <c r="P9">
-        <v>-5.5559429458063994e-05</v>
+        <v>-5.5738154889283928e-05</v>
       </c>
       <c r="Q9">
-        <v>2.1856245634203768e-05</v>
+        <v>2.2172052801245286e-05</v>
       </c>
       <c r="R9">
-        <v>-1.4587525947807571e-05</v>
+        <v>-1.4521490597421205e-05</v>
       </c>
       <c r="S9">
-        <v>-1.5959082681540526e-05</v>
+        <v>-1.6105590771735326e-05</v>
       </c>
       <c r="T9">
-        <v>-1.8387298203976624e-05</v>
+        <v>-1.8653698068622268e-05</v>
       </c>
       <c r="U9">
-        <v>-5.0935754477921896e-05</v>
+        <v>-5.3257989886495712e-05</v>
       </c>
       <c r="V9">
-        <v>-4.9516874433796827e-05</v>
+        <v>-5.1986896564435784e-05</v>
       </c>
       <c r="W9">
-        <v>-5.6314680192282662e-05</v>
+        <v>-5.8470650969077207e-05</v>
       </c>
       <c r="X9">
-        <v>1.598184924259426e-06</v>
+        <v>1.9745750342813263e-06</v>
       </c>
       <c r="Y9">
-        <v>-5.5936669005860406e-07</v>
+        <v>-9.8666629231824524e-08</v>
       </c>
       <c r="Z9">
-        <v>1.0739068533409171e-05</v>
+        <v>1.1311372692250869e-05</v>
       </c>
       <c r="AA9">
-        <v>6.7777764299665312e-06</v>
+        <v>4.8588571204757222e-06</v>
       </c>
       <c r="AB9">
-        <v>7.7405084287827147e-06</v>
+        <v>5.9795931515586247e-06</v>
       </c>
       <c r="AC9">
-        <v>5.1500515317105544e-06</v>
+        <v>3.8411332852990127e-06</v>
       </c>
       <c r="AD9">
-        <v>2.1048768021260701e-06</v>
+        <v>3.582330656313413e-07</v>
       </c>
       <c r="AE9">
-        <v>7.0349394531768444e-06</v>
+        <v>5.711689207059639e-06</v>
       </c>
       <c r="AF9">
-        <v>1.4171980792534952e-05</v>
+        <v>1.2897999056349304e-05</v>
       </c>
       <c r="AG9">
-        <v>7.1113663786945166e-07</v>
+        <v>9.7116927496613578e-07</v>
       </c>
       <c r="AH9">
-        <v>3.8241408493853369e-05</v>
+        <v>-1.5609354672070172e-06</v>
+      </c>
+      <c r="AI9">
+        <v>-1.3730403899072507e-05</v>
+      </c>
+      <c r="AJ9">
+        <v>3.89467405004832e-05</v>
       </c>
     </row>
     <row r="10">
@@ -1409,103 +1469,109 @@
         <v>36</v>
       </c>
       <c r="B10">
-        <v>0.12169763432759727</v>
+        <v>0.11838812140458939</v>
       </c>
       <c r="C10">
-        <v>-5.7624821228866908e-05</v>
+        <v>-5.7547310330336932e-05</v>
       </c>
       <c r="D10">
-        <v>-1.0834928015026822e-06</v>
+        <v>-9.6672651619156798e-07</v>
       </c>
       <c r="E10">
-        <v>-1.3769748027964034e-08</v>
+        <v>-1.4816671349479194e-08</v>
       </c>
       <c r="F10">
-        <v>1.8915300501936842e-06</v>
+        <v>4.7606042383823601e-06</v>
       </c>
       <c r="G10">
-        <v>1.1849337779196809e-05</v>
+        <v>1.2262476722449255e-05</v>
       </c>
       <c r="H10">
-        <v>2.0786111657702558e-05</v>
+        <v>2.0982357384107968e-05</v>
       </c>
       <c r="I10">
-        <v>2.5238308197965248e-06</v>
+        <v>2.5789119911564537e-06</v>
       </c>
       <c r="J10">
-        <v>-6.2722499326892359e-06</v>
+        <v>-6.589703952821758e-06</v>
       </c>
       <c r="K10">
-        <v>0.00040318265792177037</v>
+        <v>0.00040416536467221626</v>
       </c>
       <c r="L10">
-        <v>-2.444351813277091e-05</v>
+        <v>-2.46725333418743e-05</v>
       </c>
       <c r="M10">
-        <v>-2.105745013406545e-07</v>
+        <v>-1.4549384709005733e-07</v>
       </c>
       <c r="N10">
-        <v>5.7188767927676616e-05</v>
+        <v>5.794569055239447e-05</v>
       </c>
       <c r="O10">
-        <v>-3.57267789138076e-08</v>
+        <v>-4.2195512494135536e-08</v>
       </c>
       <c r="P10">
-        <v>4.9742589554302227e-06</v>
+        <v>5.259438075629881e-06</v>
       </c>
       <c r="Q10">
-        <v>1.6116678415521154e-06</v>
+        <v>1.5325239321903013e-06</v>
       </c>
       <c r="R10">
-        <v>7.5268081404743865e-05</v>
+        <v>7.2942141221193967e-05</v>
       </c>
       <c r="S10">
-        <v>4.1560520250256858e-05</v>
+        <v>3.8903304867473406e-05</v>
       </c>
       <c r="T10">
-        <v>-4.0093540460861771e-05</v>
+        <v>-4.2076096725377865e-05</v>
       </c>
       <c r="U10">
-        <v>0.0029916827384938714</v>
+        <v>0.002999366440053402</v>
       </c>
       <c r="V10">
-        <v>0.003045095528134539</v>
+        <v>0.003052238522011635</v>
       </c>
       <c r="W10">
-        <v>0.0030868104116333612</v>
+        <v>0.0030930118556961434</v>
       </c>
       <c r="X10">
-        <v>-1.3878111332322801e-05</v>
+        <v>-1.42044052615582e-05</v>
       </c>
       <c r="Y10">
-        <v>1.4850935956310212e-05</v>
+        <v>1.5362234224736333e-05</v>
       </c>
       <c r="Z10">
-        <v>-2.7042754110714645e-05</v>
+        <v>-2.5286700238444392e-05</v>
       </c>
       <c r="AA10">
-        <v>-1.3495049181258111e-05</v>
+        <v>-1.2605071197613945e-05</v>
       </c>
       <c r="AB10">
-        <v>-4.968256124866983e-05</v>
+        <v>-4.8552193531725685e-05</v>
       </c>
       <c r="AC10">
-        <v>-6.5003285620603179e-05</v>
+        <v>-6.3493944229510251e-05</v>
       </c>
       <c r="AD10">
-        <v>-7.6640437867028875e-06</v>
+        <v>-6.7674234959375079e-06</v>
       </c>
       <c r="AE10">
-        <v>-3.3770335514039535e-05</v>
+        <v>-3.2184299087756286e-05</v>
       </c>
       <c r="AF10">
-        <v>-2.860533445252938e-05</v>
+        <v>-2.8043883466234308e-05</v>
       </c>
       <c r="AG10">
-        <v>-6.5742139252626447e-07</v>
+        <v>-5.0741236670478877e-07</v>
       </c>
       <c r="AH10">
-        <v>-0.0029148802844716684</v>
+        <v>-1.4728989282367707e-05</v>
+      </c>
+      <c r="AI10">
+        <v>6.3375947813017154e-06</v>
+      </c>
+      <c r="AJ10">
+        <v>-0.0029244195253660971</v>
       </c>
     </row>
     <row r="11">
@@ -1513,103 +1579,109 @@
         <v>37</v>
       </c>
       <c r="B11">
-        <v>0.013758111123401511</v>
+        <v>0.014659101291421114</v>
       </c>
       <c r="C11">
-        <v>-5.718589117759293e-06</v>
+        <v>-5.6414867353351785e-06</v>
       </c>
       <c r="D11">
-        <v>-2.6060318885225805e-06</v>
+        <v>-2.6211966690228471e-06</v>
       </c>
       <c r="E11">
-        <v>2.4353636414914117e-08</v>
+        <v>2.4445942903902144e-08</v>
       </c>
       <c r="F11">
-        <v>7.2551501351288175e-07</v>
+        <v>3.9998818759418743e-07</v>
       </c>
       <c r="G11">
-        <v>3.0704944980222247e-06</v>
+        <v>2.8329295447831688e-06</v>
       </c>
       <c r="H11">
-        <v>2.0729995756803925e-06</v>
+        <v>1.9737877711997582e-06</v>
       </c>
       <c r="I11">
-        <v>9.0660575383667505e-08</v>
+        <v>5.5289611406675109e-08</v>
       </c>
       <c r="J11">
-        <v>6.517558633111074e-07</v>
+        <v>6.727853820748999e-07</v>
       </c>
       <c r="K11">
-        <v>-2.444351813277091e-05</v>
+        <v>-2.46725333418743e-05</v>
       </c>
       <c r="L11">
-        <v>2.0606350761556701e-05</v>
+        <v>2.0645238593851432e-05</v>
       </c>
       <c r="M11">
-        <v>5.2446366371917843e-07</v>
+        <v>5.1357797594993791e-07</v>
       </c>
       <c r="N11">
-        <v>5.5681979030883015e-06</v>
+        <v>5.4187298588879362e-06</v>
       </c>
       <c r="O11">
-        <v>2.566161407327924e-08</v>
+        <v>2.5109967207929017e-08</v>
       </c>
       <c r="P11">
-        <v>-1.0836245148114824e-06</v>
+        <v>-1.0909205124439425e-06</v>
       </c>
       <c r="Q11">
-        <v>-2.3286269359875828e-07</v>
+        <v>-1.6022301973270842e-07</v>
       </c>
       <c r="R11">
-        <v>9.1571775018034444e-06</v>
+        <v>8.7873443139225703e-06</v>
       </c>
       <c r="S11">
-        <v>6.2764350888560335e-06</v>
+        <v>6.0585243863096099e-06</v>
       </c>
       <c r="T11">
-        <v>2.1260633326848366e-06</v>
+        <v>1.8206085427353066e-06</v>
       </c>
       <c r="U11">
-        <v>-7.5643521075182982e-05</v>
+        <v>-7.7503693165586649e-05</v>
       </c>
       <c r="V11">
-        <v>-7.7127714590427421e-05</v>
+        <v>-7.8663409873098978e-05</v>
       </c>
       <c r="W11">
-        <v>-6.4099077036030045e-05</v>
+        <v>-6.546711117600631e-05</v>
       </c>
       <c r="X11">
-        <v>-3.8179162124950021e-06</v>
+        <v>-3.9028183123111055e-06</v>
       </c>
       <c r="Y11">
-        <v>8.747500839220292e-08</v>
+        <v>1.4581552651866553e-07</v>
       </c>
       <c r="Z11">
-        <v>-1.3947854852402062e-05</v>
+        <v>-1.3796579052501655e-05</v>
       </c>
       <c r="AA11">
-        <v>4.0115925639870137e-06</v>
+        <v>3.617953627115794e-06</v>
       </c>
       <c r="AB11">
-        <v>3.056533745855855e-06</v>
+        <v>2.67415623426097e-06</v>
       </c>
       <c r="AC11">
-        <v>4.1252634444072315e-06</v>
+        <v>3.9441884765833681e-06</v>
       </c>
       <c r="AD11">
-        <v>3.8857613465943921e-06</v>
+        <v>3.5712211650880036e-06</v>
       </c>
       <c r="AE11">
-        <v>3.2539170285022785e-06</v>
+        <v>2.9579091092853315e-06</v>
       </c>
       <c r="AF11">
-        <v>3.3464814574087493e-06</v>
+        <v>3.1652168661934511e-06</v>
       </c>
       <c r="AG11">
-        <v>-2.7301158488969425e-07</v>
+        <v>-2.2299980491866647e-07</v>
       </c>
       <c r="AH11">
-        <v>0.00011060536569436742</v>
+        <v>-1.2428005193927032e-06</v>
+      </c>
+      <c r="AI11">
+        <v>-2.4194662693187976e-06</v>
+      </c>
+      <c r="AJ11">
+        <v>0.00011265633956514313</v>
       </c>
     </row>
     <row r="12">
@@ -1617,103 +1689,109 @@
         <v>38</v>
       </c>
       <c r="B12">
-        <v>0.29249082093949219</v>
+        <v>0.29268427736767672</v>
       </c>
       <c r="C12">
-        <v>-9.3407144047405155e-07</v>
+        <v>-8.3731349492827086e-07</v>
       </c>
       <c r="D12">
-        <v>-3.1338989980077789e-07</v>
+        <v>-2.8019044137940674e-07</v>
       </c>
       <c r="E12">
-        <v>-4.1022173935000866e-10</v>
+        <v>-7.2624813416632366e-10</v>
       </c>
       <c r="F12">
-        <v>-1.0193228779546308e-05</v>
+        <v>-1.1265379461933814e-05</v>
       </c>
       <c r="G12">
-        <v>-9.9612791581779276e-06</v>
+        <v>-9.8463402691600676e-06</v>
       </c>
       <c r="H12">
-        <v>-2.898844185125591e-06</v>
+        <v>-2.542223090869507e-06</v>
       </c>
       <c r="I12">
-        <v>-4.7982660206105442e-06</v>
+        <v>-4.3570862052101599e-06</v>
       </c>
       <c r="J12">
-        <v>-2.1006686263617072e-05</v>
+        <v>-2.1129394291012563e-05</v>
       </c>
       <c r="K12">
-        <v>-2.105745013406545e-07</v>
+        <v>-1.4549384709005733e-07</v>
       </c>
       <c r="L12">
-        <v>5.2446366371917843e-07</v>
+        <v>5.1357797594993791e-07</v>
       </c>
       <c r="M12">
-        <v>4.1543895088285499e-05</v>
+        <v>4.1741776084694758e-05</v>
       </c>
       <c r="N12">
-        <v>3.0348697276402229e-07</v>
+        <v>9.082504181894794e-08</v>
       </c>
       <c r="O12">
-        <v>6.4978665811687819e-09</v>
+        <v>5.6320424013921407e-09</v>
       </c>
       <c r="P12">
-        <v>2.4102036469438977e-05</v>
+        <v>2.4114701378240636e-05</v>
       </c>
       <c r="Q12">
-        <v>-4.2024789614385775e-05</v>
+        <v>-4.2136373622518569e-05</v>
       </c>
       <c r="R12">
-        <v>2.5659523892040982e-07</v>
+        <v>-2.2297393878621718e-07</v>
       </c>
       <c r="S12">
-        <v>-5.8629824426148105e-06</v>
+        <v>-6.248287619315995e-06</v>
       </c>
       <c r="T12">
-        <v>-9.9853199002744104e-06</v>
+        <v>-1.0596812772207388e-05</v>
       </c>
       <c r="U12">
-        <v>1.3244037329865431e-05</v>
+        <v>1.436465799518815e-05</v>
       </c>
       <c r="V12">
-        <v>-1.3895136511261135e-06</v>
+        <v>-9.063151714073773e-07</v>
       </c>
       <c r="W12">
-        <v>1.2131480104485105e-06</v>
+        <v>1.7803446417798033e-06</v>
       </c>
       <c r="X12">
-        <v>4.8353945859318536e-06</v>
+        <v>4.4989500669006581e-06</v>
       </c>
       <c r="Y12">
-        <v>-1.6592569004102378e-06</v>
+        <v>-1.9094483336881404e-06</v>
       </c>
       <c r="Z12">
-        <v>-2.6543288045339635e-05</v>
+        <v>-2.7157703428098845e-05</v>
       </c>
       <c r="AA12">
-        <v>-5.1284221121947723e-06</v>
+        <v>-3.6761612594367478e-06</v>
       </c>
       <c r="AB12">
-        <v>-8.2864567449780173e-06</v>
+        <v>-7.0413633157318348e-06</v>
       </c>
       <c r="AC12">
-        <v>-6.7021501247420185e-06</v>
+        <v>-5.5340363770648717e-06</v>
       </c>
       <c r="AD12">
-        <v>-6.0174381488210799e-06</v>
+        <v>-4.717933822105455e-06</v>
       </c>
       <c r="AE12">
-        <v>-7.3972617268349515e-06</v>
+        <v>-6.538428092497768e-06</v>
       </c>
       <c r="AF12">
-        <v>-3.929834504762094e-06</v>
+        <v>-2.9057213094194881e-06</v>
       </c>
       <c r="AG12">
-        <v>1.4314811093280512e-06</v>
+        <v>1.4247585618967477e-06</v>
       </c>
       <c r="AH12">
-        <v>-2.6282177451205223e-05</v>
+        <v>-2.2626364425119899e-06</v>
+      </c>
+      <c r="AI12">
+        <v>-2.5026242273638586e-06</v>
+      </c>
+      <c r="AJ12">
+        <v>-2.8201969746309123e-05</v>
       </c>
     </row>
     <row r="13">
@@ -1721,103 +1799,109 @@
         <v>39</v>
       </c>
       <c r="B13">
-        <v>0.089268077716273264</v>
+        <v>0.089514165590736716</v>
       </c>
       <c r="C13">
-        <v>-0.00042433242154412705</v>
+        <v>-0.00042477101755662413</v>
       </c>
       <c r="D13">
-        <v>8.2333549944939496e-07</v>
+        <v>8.6552023993750523e-07</v>
       </c>
       <c r="E13">
-        <v>-3.9222811388244211e-08</v>
+        <v>-3.958036537029314e-08</v>
       </c>
       <c r="F13">
-        <v>7.9664515972540967e-05</v>
+        <v>8.3427250543406401e-05</v>
       </c>
       <c r="G13">
-        <v>4.7684286516681535e-05</v>
+        <v>5.25249177570374e-05</v>
       </c>
       <c r="H13">
-        <v>6.7351037229235766e-05</v>
+        <v>7.054752164711747e-05</v>
       </c>
       <c r="I13">
-        <v>8.2170133663235178e-05</v>
+        <v>8.6852708167312485e-05</v>
       </c>
       <c r="J13">
-        <v>-1.6125883602401086e-06</v>
+        <v>-1.5943984269933549e-06</v>
       </c>
       <c r="K13">
-        <v>5.7188767927676616e-05</v>
+        <v>5.794569055239447e-05</v>
       </c>
       <c r="L13">
-        <v>5.5681979030883015e-06</v>
+        <v>5.4187298588879362e-06</v>
       </c>
       <c r="M13">
-        <v>3.0348697276402229e-07</v>
+        <v>9.082504181894794e-08</v>
       </c>
       <c r="N13">
-        <v>0.0086194386277107776</v>
+        <v>0.0086560143558350976</v>
       </c>
       <c r="O13">
-        <v>1.6668655581624485e-06</v>
+        <v>1.5224934966399831e-06</v>
       </c>
       <c r="P13">
-        <v>-5.1067064288901992e-06</v>
+        <v>-1.2797378699486503e-05</v>
       </c>
       <c r="Q13">
-        <v>5.2569499553637474e-05</v>
+        <v>5.5769530201830141e-05</v>
       </c>
       <c r="R13">
-        <v>0.0050754832797341408</v>
+        <v>0.0050136053871246969</v>
       </c>
       <c r="S13">
-        <v>0.0050501878930057</v>
+        <v>0.0049888765242035709</v>
       </c>
       <c r="T13">
-        <v>0.0050232044529128564</v>
+        <v>0.0049611952792562239</v>
       </c>
       <c r="U13">
-        <v>0.00047562031389892546</v>
+        <v>0.00047718190255935291</v>
       </c>
       <c r="V13">
-        <v>0.00038695768746498235</v>
+        <v>0.0003922445210037314</v>
       </c>
       <c r="W13">
-        <v>0.00054069489522240097</v>
+        <v>0.00054544506682772985</v>
       </c>
       <c r="X13">
-        <v>-4.6782119701288202e-05</v>
+        <v>-4.7132921023004847e-05</v>
       </c>
       <c r="Y13">
-        <v>7.8108018194332453e-07</v>
+        <v>1.7089749209726239e-06</v>
       </c>
       <c r="Z13">
-        <v>-0.00019455881047950019</v>
+        <v>-0.00019790241739100958</v>
       </c>
       <c r="AA13">
-        <v>-8.2672830506223035e-05</v>
+        <v>-8.8766111784358784e-05</v>
       </c>
       <c r="AB13">
-        <v>-9.658300844157721e-05</v>
+        <v>-0.00010466159803707801</v>
       </c>
       <c r="AC13">
-        <v>-0.00010420801169911981</v>
+        <v>-0.00011200549554738826</v>
       </c>
       <c r="AD13">
-        <v>-8.2261303497731427e-05</v>
+        <v>-8.7585297829528234e-05</v>
       </c>
       <c r="AE13">
-        <v>-9.2899386823946158e-05</v>
+        <v>-0.0001014477349346528</v>
       </c>
       <c r="AF13">
-        <v>-0.0001177618979195913</v>
+        <v>-0.0001261852041956013</v>
       </c>
       <c r="AG13">
-        <v>9.1740824583342456e-09</v>
+        <v>-6.4342264269657049e-07</v>
       </c>
       <c r="AH13">
-        <v>-0.0052036650527938558</v>
+        <v>-2.2164138048162176e-05</v>
+      </c>
+      <c r="AI13">
+        <v>5.4763436536255702e-05</v>
+      </c>
+      <c r="AJ13">
+        <v>-0.0051345458324562228</v>
       </c>
     </row>
     <row r="14">
@@ -1825,103 +1909,109 @@
         <v>40</v>
       </c>
       <c r="B14">
-        <v>-0.0023059382147071722</v>
+        <v>-0.0022670456225304925</v>
       </c>
       <c r="C14">
-        <v>9.1092695125573891e-08</v>
+        <v>9.0939883462974436e-08</v>
       </c>
       <c r="D14">
-        <v>-2.8773079103080056e-07</v>
+        <v>-2.8893583893147131e-07</v>
       </c>
       <c r="E14">
-        <v>2.6493330990526786e-09</v>
+        <v>2.6591359089132346e-09</v>
       </c>
       <c r="F14">
-        <v>-1.7589163526709101e-07</v>
+        <v>-1.9504447077157633e-07</v>
       </c>
       <c r="G14">
-        <v>1.0792745720968088e-07</v>
+        <v>1.002143807837706e-07</v>
       </c>
       <c r="H14">
-        <v>1.6384444896190105e-07</v>
+        <v>1.4424970242157938e-07</v>
       </c>
       <c r="I14">
-        <v>-3.469218407606828e-08</v>
+        <v>-3.5753092428886456e-08</v>
       </c>
       <c r="J14">
-        <v>1.5347041682199427e-08</v>
+        <v>1.3473076405657386e-08</v>
       </c>
       <c r="K14">
-        <v>-3.57267789138076e-08</v>
+        <v>-4.2195512494135536e-08</v>
       </c>
       <c r="L14">
-        <v>2.566161407327924e-08</v>
+        <v>2.5109967207929017e-08</v>
       </c>
       <c r="M14">
-        <v>6.4978665811687819e-09</v>
+        <v>5.6320424013921407e-09</v>
       </c>
       <c r="N14">
-        <v>1.6668655581624485e-06</v>
+        <v>1.5224934966399831e-06</v>
       </c>
       <c r="O14">
-        <v>2.4546192782446342e-07</v>
+        <v>2.4443940829377713e-07</v>
       </c>
       <c r="P14">
-        <v>-5.7890526752315372e-07</v>
+        <v>-6.029852900389148e-07</v>
       </c>
       <c r="Q14">
-        <v>-6.3853998947432813e-06</v>
+        <v>-6.4103127571306589e-06</v>
       </c>
       <c r="R14">
-        <v>0.00010490065336710432</v>
+        <v>0.00010444461320091992</v>
       </c>
       <c r="S14">
-        <v>0.00010503408991854612</v>
+        <v>0.00010458397880891684</v>
       </c>
       <c r="T14">
-        <v>0.00010508634650764373</v>
+        <v>0.00010462847082416017</v>
       </c>
       <c r="U14">
-        <v>-1.6742524788768197e-06</v>
+        <v>-1.745433348129832e-06</v>
       </c>
       <c r="V14">
-        <v>-7.4810372965237711e-08</v>
+        <v>-1.2286863435495218e-07</v>
       </c>
       <c r="W14">
-        <v>-5.5811439303195666e-07</v>
+        <v>-6.0376742978289683e-07</v>
       </c>
       <c r="X14">
-        <v>5.0252007600607009e-07</v>
+        <v>5.0711547101110088e-07</v>
       </c>
       <c r="Y14">
-        <v>-1.2118360618791086e-06</v>
+        <v>-1.2194903045869823e-06</v>
       </c>
       <c r="Z14">
-        <v>2.0638426417259916e-06</v>
+        <v>2.1349448885148807e-06</v>
       </c>
       <c r="AA14">
-        <v>-1.6257769286366858e-07</v>
+        <v>-1.5685781831742667e-07</v>
       </c>
       <c r="AB14">
-        <v>-1.2290727439932272e-07</v>
+        <v>-1.1896263647887223e-07</v>
       </c>
       <c r="AC14">
-        <v>6.3858596175337177e-08</v>
+        <v>6.7224863809878748e-08</v>
       </c>
       <c r="AD14">
-        <v>-2.7688962830133273e-07</v>
+        <v>-2.8464340596502083e-07</v>
       </c>
       <c r="AE14">
-        <v>-2.33255875422019e-07</v>
+        <v>-2.2703670235616047e-07</v>
       </c>
       <c r="AF14">
-        <v>-3.9428947924147748e-08</v>
+        <v>-3.4574382276464022e-08</v>
       </c>
       <c r="AG14">
-        <v>-1.8458298843144048e-08</v>
+        <v>-1.2076834283234572e-08</v>
       </c>
       <c r="AH14">
-        <v>-9.7153524140074275e-05</v>
+        <v>-5.7196816117010857e-07</v>
+      </c>
+      <c r="AI14">
+        <v>8.8186565686442837e-08</v>
+      </c>
+      <c r="AJ14">
+        <v>-9.666866067589903e-05</v>
       </c>
     </row>
     <row r="15">
@@ -1929,103 +2019,109 @@
         <v>41</v>
       </c>
       <c r="B15">
-        <v>-0.020713206399528034</v>
+        <v>-0.019658465172190144</v>
       </c>
       <c r="C15">
-        <v>-6.9630187884068893e-07</v>
+        <v>-5.5365494455151705e-07</v>
       </c>
       <c r="D15">
-        <v>2.8529170781301794e-07</v>
+        <v>3.1809939197751243e-07</v>
       </c>
       <c r="E15">
-        <v>-6.538111937488371e-10</v>
+        <v>-9.4327821682507526e-10</v>
       </c>
       <c r="F15">
-        <v>-6.0548709677588065e-06</v>
+        <v>-7.6681099742058539e-06</v>
       </c>
       <c r="G15">
-        <v>-8.5154949488814529e-06</v>
+        <v>-8.8487608585180564e-06</v>
       </c>
       <c r="H15">
-        <v>-6.5998867637764146e-06</v>
+        <v>-6.6178325936134106e-06</v>
       </c>
       <c r="I15">
-        <v>-4.6355220483620501e-06</v>
+        <v>-5.4800625058765496e-06</v>
       </c>
       <c r="J15">
-        <v>-5.5559429458063994e-05</v>
+        <v>-5.5738154889283928e-05</v>
       </c>
       <c r="K15">
-        <v>4.9742589554302227e-06</v>
+        <v>5.259438075629881e-06</v>
       </c>
       <c r="L15">
-        <v>-1.0836245148114824e-06</v>
+        <v>-1.0909205124439425e-06</v>
       </c>
       <c r="M15">
-        <v>2.4102036469438977e-05</v>
+        <v>2.4114701378240636e-05</v>
       </c>
       <c r="N15">
-        <v>-5.1067064288901992e-06</v>
+        <v>-1.2797378699486503e-05</v>
       </c>
       <c r="O15">
-        <v>-5.7890526752315372e-07</v>
+        <v>-6.029852900389148e-07</v>
       </c>
       <c r="P15">
-        <v>0.0013576246192694482</v>
+        <v>0.0013651451892964612</v>
       </c>
       <c r="Q15">
-        <v>-0.00062591091523798547</v>
+        <v>-0.00063419603228546614</v>
       </c>
       <c r="R15">
-        <v>0.00044355264053986529</v>
+        <v>0.00041740945321769004</v>
       </c>
       <c r="S15">
-        <v>0.00044998494852252355</v>
+        <v>0.00042421826620405351</v>
       </c>
       <c r="T15">
-        <v>0.00045294408924998749</v>
+        <v>0.00042676338634160485</v>
       </c>
       <c r="U15">
-        <v>8.0740708856456541e-05</v>
+        <v>8.2891654328890742e-05</v>
       </c>
       <c r="V15">
-        <v>3.9429321252727875e-05</v>
+        <v>4.1725278152355042e-05</v>
       </c>
       <c r="W15">
-        <v>4.6554062546254012e-05</v>
+        <v>4.8772942484471204e-05</v>
       </c>
       <c r="X15">
-        <v>1.341921103619929e-05</v>
+        <v>1.2907688390869378e-05</v>
       </c>
       <c r="Y15">
-        <v>-1.2680170136373374e-05</v>
+        <v>-1.2909084500184344e-05</v>
       </c>
       <c r="Z15">
-        <v>-1.838557902013717e-05</v>
+        <v>-2.0661299500110961e-05</v>
       </c>
       <c r="AA15">
-        <v>2.1887496361575705e-05</v>
+        <v>2.4480863746305988e-05</v>
       </c>
       <c r="AB15">
-        <v>1.3711097321521899e-05</v>
+        <v>1.6708748131363219e-05</v>
       </c>
       <c r="AC15">
-        <v>4.623236220552477e-06</v>
+        <v>6.6184178924230008e-06</v>
       </c>
       <c r="AD15">
-        <v>2.2916275614285242e-05</v>
+        <v>2.4974489775260748e-05</v>
       </c>
       <c r="AE15">
-        <v>2.9564094892454399e-06</v>
+        <v>5.4294317632951387e-06</v>
       </c>
       <c r="AF15">
-        <v>2.5283624473737147e-05</v>
+        <v>2.8341475067845799e-05</v>
       </c>
       <c r="AG15">
-        <v>-8.6018516675320246e-08</v>
+        <v>-4.0507905806822829e-07</v>
       </c>
       <c r="AH15">
-        <v>-0.0004777439030639913</v>
+        <v>1.1604885549131006e-05</v>
+      </c>
+      <c r="AI15">
+        <v>1.0604849255206464e-05</v>
+      </c>
+      <c r="AJ15">
+        <v>-0.00045274442340696415</v>
       </c>
     </row>
     <row r="16">
@@ -2033,103 +2129,109 @@
         <v>42</v>
       </c>
       <c r="B16">
-        <v>-0.045136340172975312</v>
+        <v>-0.044450175980520895</v>
       </c>
       <c r="C16">
-        <v>-4.4291088169017185e-06</v>
+        <v>-4.4643412823985004e-06</v>
       </c>
       <c r="D16">
-        <v>-2.88184855673491e-08</v>
+        <v>-9.2049423138635105e-08</v>
       </c>
       <c r="E16">
-        <v>2.275567861549283e-09</v>
+        <v>2.9432057953050599e-09</v>
       </c>
       <c r="F16">
-        <v>8.2143268312577867e-06</v>
+        <v>9.5385467637937026e-06</v>
       </c>
       <c r="G16">
-        <v>1.1073215599314283e-05</v>
+        <v>1.159891588002625e-05</v>
       </c>
       <c r="H16">
-        <v>5.9116496688289687e-06</v>
+        <v>6.7493930827819065e-06</v>
       </c>
       <c r="I16">
-        <v>6.1050641238750348e-06</v>
+        <v>6.5896982252864441e-06</v>
       </c>
       <c r="J16">
-        <v>2.1856245634203768e-05</v>
+        <v>2.2172052801245286e-05</v>
       </c>
       <c r="K16">
-        <v>1.6116678415521154e-06</v>
+        <v>1.5325239321903013e-06</v>
       </c>
       <c r="L16">
-        <v>-2.3286269359875828e-07</v>
+        <v>-1.6022301973270842e-07</v>
       </c>
       <c r="M16">
-        <v>-4.2024789614385775e-05</v>
+        <v>-4.2136373622518569e-05</v>
       </c>
       <c r="N16">
-        <v>5.2569499553637474e-05</v>
+        <v>5.5769530201830141e-05</v>
       </c>
       <c r="O16">
-        <v>-6.3853998947432813e-06</v>
+        <v>-6.4103127571306589e-06</v>
       </c>
       <c r="P16">
-        <v>-0.00062591091523798547</v>
+        <v>-0.00063419603228546614</v>
       </c>
       <c r="Q16">
-        <v>0.0013212484691502418</v>
+        <v>0.0013462025470260754</v>
       </c>
       <c r="R16">
-        <v>-0.0023489461903688112</v>
+        <v>-0.0023462957784217017</v>
       </c>
       <c r="S16">
-        <v>-0.0023441016477040604</v>
+        <v>-0.0023413908993463526</v>
       </c>
       <c r="T16">
-        <v>-0.0023444653779455156</v>
+        <v>-0.0023412320237869298</v>
       </c>
       <c r="U16">
-        <v>-3.5055375999286376e-05</v>
+        <v>-3.5028199515943579e-05</v>
       </c>
       <c r="V16">
-        <v>1.2149533639442458e-05</v>
+        <v>1.1943944616648727e-05</v>
       </c>
       <c r="W16">
-        <v>1.0669507886652699e-05</v>
+        <v>1.0307649675155668e-05</v>
       </c>
       <c r="X16">
-        <v>-1.116506599004884e-05</v>
+        <v>-1.0743271145026477e-05</v>
       </c>
       <c r="Y16">
-        <v>4.9068335579272553e-06</v>
+        <v>4.7458392919060303e-06</v>
       </c>
       <c r="Z16">
-        <v>3.5383472222992205e-05</v>
+        <v>3.4096513352007232e-05</v>
       </c>
       <c r="AA16">
-        <v>-4.6053523644693905e-06</v>
+        <v>-4.8760279663096189e-06</v>
       </c>
       <c r="AB16">
-        <v>-5.5999208484619478e-06</v>
+        <v>-6.1243900260174889e-06</v>
       </c>
       <c r="AC16">
-        <v>1.0134508858396089e-05</v>
+        <v>1.1151586887880134e-05</v>
       </c>
       <c r="AD16">
-        <v>1.2856077569123976e-05</v>
+        <v>1.3065401879147837e-05</v>
       </c>
       <c r="AE16">
-        <v>2.6691720750643758e-05</v>
+        <v>2.6647312627876472e-05</v>
       </c>
       <c r="AF16">
-        <v>2.7645467661454508e-06</v>
+        <v>3.0591265652514424e-06</v>
       </c>
       <c r="AG16">
-        <v>-5.5269597205395856e-07</v>
+        <v>-5.597041323916139e-07</v>
       </c>
       <c r="AH16">
-        <v>0.0023588968083124527</v>
+        <v>1.9939508548757427e-05</v>
+      </c>
+      <c r="AI16">
+        <v>-2.0131342377696995e-05</v>
+      </c>
+      <c r="AJ16">
+        <v>0.0023562528910354447</v>
       </c>
     </row>
     <row r="17">
@@ -2137,103 +2239,109 @@
         <v>43</v>
       </c>
       <c r="B17">
-        <v>-1.2460470403433786</v>
+        <v>-1.2319510901957458</v>
       </c>
       <c r="C17">
-        <v>-0.00020488441457322765</v>
+        <v>-0.00020276970545396434</v>
       </c>
       <c r="D17">
-        <v>-0.00013289368719563159</v>
+        <v>-0.00013339923347572137</v>
       </c>
       <c r="E17">
-        <v>1.1737753706095371e-06</v>
+        <v>1.178256127163396e-06</v>
       </c>
       <c r="F17">
-        <v>-8.4748861329416817e-05</v>
+        <v>-8.6934742314077697e-05</v>
       </c>
       <c r="G17">
-        <v>-1.2104100224375977e-05</v>
+        <v>-9.9597856857855599e-06</v>
       </c>
       <c r="H17">
-        <v>5.4293659110573666e-05</v>
+        <v>5.1677075663596421e-05</v>
       </c>
       <c r="I17">
-        <v>-1.370963977263276e-05</v>
+        <v>-9.9348736545875816e-06</v>
       </c>
       <c r="J17">
-        <v>-1.4587525947807571e-05</v>
+        <v>-1.4521490597421205e-05</v>
       </c>
       <c r="K17">
-        <v>7.5268081404743865e-05</v>
+        <v>7.2942141221193967e-05</v>
       </c>
       <c r="L17">
-        <v>9.1571775018034444e-06</v>
+        <v>8.7873443139225703e-06</v>
       </c>
       <c r="M17">
-        <v>2.5659523892040982e-07</v>
+        <v>-2.2297393878621718e-07</v>
       </c>
       <c r="N17">
-        <v>0.0050754832797341408</v>
+        <v>0.0050136053871246969</v>
       </c>
       <c r="O17">
-        <v>0.00010490065336710432</v>
+        <v>0.00010444461320091992</v>
       </c>
       <c r="P17">
-        <v>0.00044355264053986529</v>
+        <v>0.00041740945321769004</v>
       </c>
       <c r="Q17">
-        <v>-0.0023489461903688112</v>
+        <v>-0.0023462957784217017</v>
       </c>
       <c r="R17">
-        <v>0.052272855574013025</v>
+        <v>0.052056543072756048</v>
       </c>
       <c r="S17">
-        <v>0.051978416640240541</v>
+        <v>0.051764222192104956</v>
       </c>
       <c r="T17">
-        <v>0.052023386175482661</v>
+        <v>0.051806231087411628</v>
       </c>
       <c r="U17">
-        <v>0.001985589458940229</v>
+        <v>0.0019554998409978403</v>
       </c>
       <c r="V17">
-        <v>0.00054863123020110205</v>
+        <v>0.00053031381109416853</v>
       </c>
       <c r="W17">
-        <v>0.00045183360194928079</v>
+        <v>0.00043258298256027006</v>
       </c>
       <c r="X17">
-        <v>0.00015405077340892217</v>
+        <v>0.00015721725389215889</v>
       </c>
       <c r="Y17">
-        <v>-0.0005141009245745046</v>
+        <v>-0.00051755826393656227</v>
       </c>
       <c r="Z17">
-        <v>0.00086808413924651176</v>
+        <v>0.00089127060186100504</v>
       </c>
       <c r="AA17">
-        <v>-0.00015970902141392712</v>
+        <v>-0.00014345429489732997</v>
       </c>
       <c r="AB17">
-        <v>-9.796613118667058e-05</v>
+        <v>-8.3691032520712139e-05</v>
       </c>
       <c r="AC17">
-        <v>6.68068666565165e-06</v>
+        <v>1.9830693334169786e-05</v>
       </c>
       <c r="AD17">
-        <v>-0.00022133172117906608</v>
+        <v>-0.00021070400319908589</v>
       </c>
       <c r="AE17">
-        <v>-0.00018486922394329863</v>
+        <v>-0.0001713867178525768</v>
       </c>
       <c r="AF17">
-        <v>-0.00011959226924120221</v>
+        <v>-0.00010334947615037171</v>
       </c>
       <c r="AG17">
-        <v>-6.1724273337825444e-06</v>
+        <v>-4.650223596836282e-06</v>
       </c>
       <c r="AH17">
-        <v>-0.048849629572997613</v>
+        <v>-0.0001895486371505592</v>
+      </c>
+      <c r="AI17">
+        <v>6.374556169201108e-05</v>
+      </c>
+      <c r="AJ17">
+        <v>-0.048628395941666985</v>
       </c>
     </row>
     <row r="18">
@@ -2241,103 +2349,109 @@
         <v>44</v>
       </c>
       <c r="B18">
-        <v>-1.1117121403700687</v>
+        <v>-1.0964251342103926</v>
       </c>
       <c r="C18">
-        <v>-0.00018583290833420433</v>
+        <v>-0.00018457906641151828</v>
       </c>
       <c r="D18">
-        <v>-0.00013909063257459549</v>
+        <v>-0.00013984982154221666</v>
       </c>
       <c r="E18">
-        <v>1.2684298192710072e-06</v>
+        <v>1.2750902600667099e-06</v>
       </c>
       <c r="F18">
-        <v>-8.4694143457047713e-05</v>
+        <v>-9.0659463184927195e-05</v>
       </c>
       <c r="G18">
-        <v>5.7740975907146489e-05</v>
+        <v>5.8883803869194855e-05</v>
       </c>
       <c r="H18">
-        <v>7.7710050512130055e-05</v>
+        <v>7.3886624544214119e-05</v>
       </c>
       <c r="I18">
-        <v>-1.2827912515240126e-05</v>
+        <v>-1.0058234629685758e-05</v>
       </c>
       <c r="J18">
-        <v>-1.5959082681540526e-05</v>
+        <v>-1.6105590771735326e-05</v>
       </c>
       <c r="K18">
-        <v>4.1560520250256858e-05</v>
+        <v>3.8903304867473406e-05</v>
       </c>
       <c r="L18">
-        <v>6.2764350888560335e-06</v>
+        <v>6.0585243863096099e-06</v>
       </c>
       <c r="M18">
-        <v>-5.8629824426148105e-06</v>
+        <v>-6.248287619315995e-06</v>
       </c>
       <c r="N18">
-        <v>0.0050501878930057</v>
+        <v>0.0049888765242035709</v>
       </c>
       <c r="O18">
-        <v>0.00010503408991854612</v>
+        <v>0.00010458397880891684</v>
       </c>
       <c r="P18">
-        <v>0.00044998494852252355</v>
+        <v>0.00042421826620405351</v>
       </c>
       <c r="Q18">
-        <v>-0.0023441016477040604</v>
+        <v>-0.0023413908993463526</v>
       </c>
       <c r="R18">
-        <v>0.051978416640240541</v>
+        <v>0.051764222192104956</v>
       </c>
       <c r="S18">
-        <v>0.052476921716346416</v>
+        <v>0.052266544011733578</v>
       </c>
       <c r="T18">
-        <v>0.052057240909184933</v>
+        <v>0.051843442062760696</v>
       </c>
       <c r="U18">
-        <v>0.0017096827572988318</v>
+        <v>0.0016759839972338569</v>
       </c>
       <c r="V18">
-        <v>0.00036524188115484579</v>
+        <v>0.00034556698589546103</v>
       </c>
       <c r="W18">
-        <v>0.00020940101278717205</v>
+        <v>0.00018994649714085265</v>
       </c>
       <c r="X18">
-        <v>0.00015085358617323392</v>
+        <v>0.00015391109031342217</v>
       </c>
       <c r="Y18">
-        <v>-0.00054109157998855984</v>
+        <v>-0.00054598826562006096</v>
       </c>
       <c r="Z18">
-        <v>0.001011832552426175</v>
+        <v>0.0010319563433645457</v>
       </c>
       <c r="AA18">
-        <v>-7.2127173569351555e-05</v>
+        <v>-5.4917603809427618e-05</v>
       </c>
       <c r="AB18">
-        <v>-4.3666801738166672e-05</v>
+        <v>-2.8529795788011236e-05</v>
       </c>
       <c r="AC18">
-        <v>7.0300032987269737e-05</v>
+        <v>8.3710665276034643e-05</v>
       </c>
       <c r="AD18">
-        <v>-0.0001012817213137257</v>
+        <v>-8.9978529541907826e-05</v>
       </c>
       <c r="AE18">
-        <v>-9.1629844759622686e-05</v>
+        <v>-7.7348360760081183e-05</v>
       </c>
       <c r="AF18">
-        <v>3.3619327642619989e-07</v>
+        <v>1.6882261361857685e-05</v>
       </c>
       <c r="AG18">
-        <v>-1.2741045310613259e-05</v>
+        <v>-1.1098044695567527e-05</v>
       </c>
       <c r="AH18">
-        <v>-0.048495498961884945</v>
+        <v>-0.00018796882303842577</v>
+      </c>
+      <c r="AI18">
+        <v>5.0209324960333659e-05</v>
+      </c>
+      <c r="AJ18">
+        <v>-0.048269432432185289</v>
       </c>
     </row>
     <row r="19">
@@ -2345,103 +2459,109 @@
         <v>45</v>
       </c>
       <c r="B19">
-        <v>-0.90411724415591754</v>
+        <v>-0.88586791670074161</v>
       </c>
       <c r="C19">
-        <v>-0.0001437379964723695</v>
+        <v>-0.00014230107507940196</v>
       </c>
       <c r="D19">
-        <v>-0.00013915259142187336</v>
+        <v>-0.00013983667603342863</v>
       </c>
       <c r="E19">
-        <v>1.2844227315813218e-06</v>
+        <v>1.2905328601471298e-06</v>
       </c>
       <c r="F19">
-        <v>-3.2755991009762988e-05</v>
+        <v>-3.7183345565693071e-05</v>
       </c>
       <c r="G19">
-        <v>8.5622407482293853e-05</v>
+        <v>8.8132520044139427e-05</v>
       </c>
       <c r="H19">
-        <v>0.00012302769918354166</v>
+        <v>0.00012020170536684142</v>
       </c>
       <c r="I19">
-        <v>1.6990177490073276e-05</v>
+        <v>2.1311724134353537e-05</v>
       </c>
       <c r="J19">
-        <v>-1.8387298203976624e-05</v>
+        <v>-1.8653698068622268e-05</v>
       </c>
       <c r="K19">
-        <v>-4.0093540460861771e-05</v>
+        <v>-4.2076096725377865e-05</v>
       </c>
       <c r="L19">
-        <v>2.1260633326848366e-06</v>
+        <v>1.8206085427353066e-06</v>
       </c>
       <c r="M19">
-        <v>-9.9853199002744104e-06</v>
+        <v>-1.0596812772207388e-05</v>
       </c>
       <c r="N19">
-        <v>0.0050232044529128564</v>
+        <v>0.0049611952792562239</v>
       </c>
       <c r="O19">
-        <v>0.00010508634650764373</v>
+        <v>0.00010462847082416017</v>
       </c>
       <c r="P19">
-        <v>0.00045294408924998749</v>
+        <v>0.00042676338634160485</v>
       </c>
       <c r="Q19">
-        <v>-0.0023444653779455156</v>
+        <v>-0.0023412320237869298</v>
       </c>
       <c r="R19">
-        <v>0.052023386175482661</v>
+        <v>0.051806231087411628</v>
       </c>
       <c r="S19">
-        <v>0.052057240909184933</v>
+        <v>0.051843442062760696</v>
       </c>
       <c r="T19">
-        <v>0.052508664302923336</v>
+        <v>0.052291670640890867</v>
       </c>
       <c r="U19">
-        <v>0.0011742653725614338</v>
+        <v>0.0011469699117394455</v>
       </c>
       <c r="V19">
-        <v>-0.0002292551065141632</v>
+        <v>-0.0002442016231819083</v>
       </c>
       <c r="W19">
-        <v>-0.00046594911132715605</v>
+        <v>-0.00048080279203675108</v>
       </c>
       <c r="X19">
-        <v>0.00013384724745219749</v>
+        <v>0.00013641980171128767</v>
       </c>
       <c r="Y19">
-        <v>-0.00055225352246418558</v>
+        <v>-0.0005569960839069397</v>
       </c>
       <c r="Z19">
-        <v>0.0010131884884441063</v>
+        <v>0.0010400001708056883</v>
       </c>
       <c r="AA19">
-        <v>-0.00012171966859791244</v>
+        <v>-0.00010644408694181207</v>
       </c>
       <c r="AB19">
-        <v>-8.6236695376440409e-05</v>
+        <v>-7.2881788181329565e-05</v>
       </c>
       <c r="AC19">
-        <v>1.6656544121773989e-05</v>
+        <v>2.9071147594358915e-05</v>
       </c>
       <c r="AD19">
-        <v>-0.00014398854076355661</v>
+        <v>-0.00013469766881531176</v>
       </c>
       <c r="AE19">
-        <v>-0.00013276447865572493</v>
+        <v>-0.00011938335773575316</v>
       </c>
       <c r="AF19">
-        <v>-5.0895615875704188e-05</v>
+        <v>-3.5312369631867666e-05</v>
       </c>
       <c r="AG19">
-        <v>-1.6854466762370466e-05</v>
+        <v>-1.5124170488833594e-05</v>
       </c>
       <c r="AH19">
-        <v>-0.047875562641307878</v>
+        <v>-0.0002140049657082671</v>
+      </c>
+      <c r="AI19">
+        <v>6.5692277114502359e-05</v>
+      </c>
+      <c r="AJ19">
+        <v>-0.047652712381011209</v>
       </c>
     </row>
     <row r="20">
@@ -2449,103 +2569,109 @@
         <v>46</v>
       </c>
       <c r="B20">
-        <v>1.5066066189594254</v>
+        <v>1.4880521478051685</v>
       </c>
       <c r="C20">
-        <v>-0.00043025157219142519</v>
+        <v>-0.00042824173032764926</v>
       </c>
       <c r="D20">
-        <v>9.2835608810035983e-05</v>
+        <v>9.4556681224327444e-05</v>
       </c>
       <c r="E20">
-        <v>-9.0644583065478604e-07</v>
+        <v>-9.2138299886223013e-07</v>
       </c>
       <c r="F20">
-        <v>5.4172295235524297e-05</v>
+        <v>7.3814813121306189e-05</v>
       </c>
       <c r="G20">
-        <v>8.3036332029209447e-05</v>
+        <v>8.5320300293013223e-05</v>
       </c>
       <c r="H20">
-        <v>0.00014629105508320726</v>
+        <v>0.00014718677037586051</v>
       </c>
       <c r="I20">
-        <v>1.0929610966390181e-05</v>
+        <v>1.1399888685241705e-05</v>
       </c>
       <c r="J20">
-        <v>-5.0935754477921896e-05</v>
+        <v>-5.3257989886495712e-05</v>
       </c>
       <c r="K20">
-        <v>0.0029916827384938714</v>
+        <v>0.002999366440053402</v>
       </c>
       <c r="L20">
-        <v>-7.5643521075182982e-05</v>
+        <v>-7.7503693165586649e-05</v>
       </c>
       <c r="M20">
-        <v>1.3244037329865431e-05</v>
+        <v>1.436465799518815e-05</v>
       </c>
       <c r="N20">
-        <v>0.00047562031389892546</v>
+        <v>0.00047718190255935291</v>
       </c>
       <c r="O20">
-        <v>-1.6742524788768197e-06</v>
+        <v>-1.745433348129832e-06</v>
       </c>
       <c r="P20">
-        <v>8.0740708856456541e-05</v>
+        <v>8.2891654328890742e-05</v>
       </c>
       <c r="Q20">
-        <v>-3.5055375999286376e-05</v>
+        <v>-3.5028199515943579e-05</v>
       </c>
       <c r="R20">
-        <v>0.001985589458940229</v>
+        <v>0.0019554998409978403</v>
       </c>
       <c r="S20">
-        <v>0.0017096827572988318</v>
+        <v>0.0016759839972338569</v>
       </c>
       <c r="T20">
-        <v>0.0011742653725614338</v>
+        <v>0.0011469699117394455</v>
       </c>
       <c r="U20">
-        <v>0.026360777242583861</v>
+        <v>0.026428338584982339</v>
       </c>
       <c r="V20">
-        <v>0.023467389480207147</v>
+        <v>0.023523019326517337</v>
       </c>
       <c r="W20">
-        <v>0.023790114967233808</v>
+        <v>0.023838768049555287</v>
       </c>
       <c r="X20">
-        <v>1.5854803337415945e-05</v>
+        <v>1.3214857350892211e-05</v>
       </c>
       <c r="Y20">
-        <v>0.00018059676259831532</v>
+        <v>0.00018415005674882927</v>
       </c>
       <c r="Z20">
-        <v>-0.00011025696117060967</v>
+        <v>-0.00010553482450312464</v>
       </c>
       <c r="AA20">
-        <v>-5.1728826957697649e-05</v>
+        <v>-3.3787078824263489e-05</v>
       </c>
       <c r="AB20">
-        <v>-0.00030443045987598588</v>
+        <v>-0.00028615808145876498</v>
       </c>
       <c r="AC20">
-        <v>-0.00044775772178987441</v>
+        <v>-0.00042684280750269425</v>
       </c>
       <c r="AD20">
-        <v>1.2339985309965662e-05</v>
+        <v>3.0242113666888171e-05</v>
       </c>
       <c r="AE20">
-        <v>-0.00020949657855305528</v>
+        <v>-0.00018854380716434079</v>
       </c>
       <c r="AF20">
-        <v>-0.00021687740502025462</v>
+        <v>-0.00020352959101305667</v>
       </c>
       <c r="AG20">
-        <v>-1.4329823761891102e-05</v>
+        <v>-1.2037901713926298e-05</v>
       </c>
       <c r="AH20">
-        <v>-0.026834991417646989</v>
+        <v>-0.0001512338373518933</v>
+      </c>
+      <c r="AI20">
+        <v>-3.2714931552187479e-05</v>
+      </c>
+      <c r="AJ20">
+        <v>-0.026942780966095696</v>
       </c>
     </row>
     <row r="21">
@@ -2553,103 +2679,109 @@
         <v>47</v>
       </c>
       <c r="B21">
-        <v>0.84366115382410967</v>
+        <v>0.82493796010081688</v>
       </c>
       <c r="C21">
-        <v>-0.00038948152581626505</v>
+        <v>-0.00038901432655613779</v>
       </c>
       <c r="D21">
-        <v>-1.8199907419089623e-05</v>
+        <v>-1.7461056325237417e-05</v>
       </c>
       <c r="E21">
-        <v>-2.5301988561612497e-08</v>
+        <v>-3.196357144212363e-08</v>
       </c>
       <c r="F21">
-        <v>-8.1881973549052258e-05</v>
+        <v>-6.1034824572332952e-05</v>
       </c>
       <c r="G21">
-        <v>1.6375039565686615e-05</v>
+        <v>1.7200407890189924e-05</v>
       </c>
       <c r="H21">
-        <v>0.00011471605355682865</v>
+        <v>0.00011459949982876333</v>
       </c>
       <c r="I21">
-        <v>1.3374220194669543e-05</v>
+        <v>1.307100996085454e-05</v>
       </c>
       <c r="J21">
-        <v>-4.9516874433796827e-05</v>
+        <v>-5.1986896564435784e-05</v>
       </c>
       <c r="K21">
-        <v>0.003045095528134539</v>
+        <v>0.003052238522011635</v>
       </c>
       <c r="L21">
-        <v>-7.7127714590427421e-05</v>
+        <v>-7.8663409873098978e-05</v>
       </c>
       <c r="M21">
-        <v>-1.3895136511261135e-06</v>
+        <v>-9.063151714073773e-07</v>
       </c>
       <c r="N21">
-        <v>0.00038695768746498235</v>
+        <v>0.0003922445210037314</v>
       </c>
       <c r="O21">
-        <v>-7.4810372965237711e-08</v>
+        <v>-1.2286863435495218e-07</v>
       </c>
       <c r="P21">
-        <v>3.9429321252727875e-05</v>
+        <v>4.1725278152355042e-05</v>
       </c>
       <c r="Q21">
-        <v>1.2149533639442458e-05</v>
+        <v>1.1943944616648727e-05</v>
       </c>
       <c r="R21">
-        <v>0.00054863123020110205</v>
+        <v>0.00053031381109416853</v>
       </c>
       <c r="S21">
-        <v>0.00036524188115484579</v>
+        <v>0.00034556698589546103</v>
       </c>
       <c r="T21">
-        <v>-0.0002292551065141632</v>
+        <v>-0.0002442016231819083</v>
       </c>
       <c r="U21">
-        <v>0.023467389480207147</v>
+        <v>0.023523019326517337</v>
       </c>
       <c r="V21">
-        <v>0.024321556860214814</v>
+        <v>0.024375367836511022</v>
       </c>
       <c r="W21">
-        <v>0.024393488754375074</v>
+        <v>0.024440359640698399</v>
       </c>
       <c r="X21">
-        <v>-5.555277000671632e-05</v>
+        <v>-5.9221490715636346e-05</v>
       </c>
       <c r="Y21">
-        <v>0.00011173847754391533</v>
+        <v>0.00011512955434016779</v>
       </c>
       <c r="Z21">
-        <v>-0.0002512294983747854</v>
+        <v>-0.00023861001404968957</v>
       </c>
       <c r="AA21">
-        <v>-3.404242622366202e-05</v>
+        <v>-2.7087647779604554e-05</v>
       </c>
       <c r="AB21">
-        <v>-0.00031135122940891512</v>
+        <v>-0.00030288158819016808</v>
       </c>
       <c r="AC21">
-        <v>-0.00044875602882456667</v>
+        <v>-0.0004365576943273974</v>
       </c>
       <c r="AD21">
-        <v>2.7765915279077264e-06</v>
+        <v>1.0262788959360114e-05</v>
       </c>
       <c r="AE21">
-        <v>-0.00019752927270313796</v>
+        <v>-0.00018557136633158295</v>
       </c>
       <c r="AF21">
-        <v>-0.0002152364161605992</v>
+        <v>-0.00021021413701004374</v>
       </c>
       <c r="AG21">
-        <v>-1.3631811037048344e-06</v>
+        <v>3.298568482878279e-07</v>
       </c>
       <c r="AH21">
-        <v>-0.022908844474863507</v>
+        <v>-0.0001359753622682848</v>
+      </c>
+      <c r="AI21">
+        <v>1.7109776470275624e-05</v>
+      </c>
+      <c r="AJ21">
+        <v>-0.022981610082609877</v>
       </c>
     </row>
     <row r="22">
@@ -2657,103 +2789,109 @@
         <v>48</v>
       </c>
       <c r="B22">
-        <v>0.91182492845814567</v>
+        <v>0.89043197007938524</v>
       </c>
       <c r="C22">
-        <v>-0.00054368934856143479</v>
+        <v>-0.00054219627613523783</v>
       </c>
       <c r="D22">
-        <v>3.4184986662915199e-05</v>
+        <v>3.4993562997956667e-05</v>
       </c>
       <c r="E22">
-        <v>-7.94541009372632e-07</v>
+        <v>-8.0194097487419187e-07</v>
       </c>
       <c r="F22">
-        <v>-8.626780096255036e-05</v>
+        <v>-7.2887149255579191e-05</v>
       </c>
       <c r="G22">
-        <v>7.0723872223454209e-05</v>
+        <v>7.3103565255648747e-05</v>
       </c>
       <c r="H22">
-        <v>0.00014042705096554026</v>
+        <v>0.00014111864591351823</v>
       </c>
       <c r="I22">
-        <v>2.1542359730252847e-05</v>
+        <v>2.0899714964468818e-05</v>
       </c>
       <c r="J22">
-        <v>-5.6314680192282662e-05</v>
+        <v>-5.8470650969077207e-05</v>
       </c>
       <c r="K22">
-        <v>0.0030868104116333612</v>
+        <v>0.0030930118556961434</v>
       </c>
       <c r="L22">
-        <v>-6.4099077036030045e-05</v>
+        <v>-6.546711117600631e-05</v>
       </c>
       <c r="M22">
-        <v>1.2131480104485105e-06</v>
+        <v>1.7803446417798033e-06</v>
       </c>
       <c r="N22">
-        <v>0.00054069489522240097</v>
+        <v>0.00054544506682772985</v>
       </c>
       <c r="O22">
-        <v>-5.5811439303195666e-07</v>
+        <v>-6.0376742978289683e-07</v>
       </c>
       <c r="P22">
-        <v>4.6554062546254012e-05</v>
+        <v>4.8772942484471204e-05</v>
       </c>
       <c r="Q22">
-        <v>1.0669507886652699e-05</v>
+        <v>1.0307649675155668e-05</v>
       </c>
       <c r="R22">
-        <v>0.00045183360194928079</v>
+        <v>0.00043258298256027006</v>
       </c>
       <c r="S22">
-        <v>0.00020940101278717205</v>
+        <v>0.00018994649714085265</v>
       </c>
       <c r="T22">
-        <v>-0.00046594911132715605</v>
+        <v>-0.00048080279203675108</v>
       </c>
       <c r="U22">
-        <v>0.023790114967233808</v>
+        <v>0.023838768049555287</v>
       </c>
       <c r="V22">
-        <v>0.024393488754375074</v>
+        <v>0.024440359640698399</v>
       </c>
       <c r="W22">
-        <v>0.026307490526385265</v>
+        <v>0.026347387477073592</v>
       </c>
       <c r="X22">
-        <v>-9.3825783574827491e-05</v>
+        <v>-9.6692698841411608e-05</v>
       </c>
       <c r="Y22">
-        <v>9.6961116737285429e-05</v>
+        <v>0.00010094760406168727</v>
       </c>
       <c r="Z22">
-        <v>-0.00029189933431725788</v>
+        <v>-0.00027720321106184959</v>
       </c>
       <c r="AA22">
-        <v>-4.5536644832460532e-05</v>
+        <v>-3.492590841396373e-05</v>
       </c>
       <c r="AB22">
-        <v>-0.00033727564414217162</v>
+        <v>-0.00032499519214412506</v>
       </c>
       <c r="AC22">
-        <v>-0.00043109935112108739</v>
+        <v>-0.00041555000174634937</v>
       </c>
       <c r="AD22">
-        <v>2.9091084384758048e-05</v>
+        <v>4.0257242717714123e-05</v>
       </c>
       <c r="AE22">
-        <v>-0.0002142572191855454</v>
+        <v>-0.00019909139433911278</v>
       </c>
       <c r="AF22">
-        <v>-0.00016989106295890819</v>
+        <v>-0.00015975550368417177</v>
       </c>
       <c r="AG22">
-        <v>-1.2259196194089328e-06</v>
+        <v>3.6350820467926336e-07</v>
       </c>
       <c r="AH22">
-        <v>-0.02377072641085777</v>
+        <v>-0.00011810315069277558</v>
+      </c>
+      <c r="AI22">
+        <v>4.4973636718738733e-06</v>
+      </c>
+      <c r="AJ22">
+        <v>-0.023842405045704632</v>
       </c>
     </row>
     <row r="23">
@@ -2761,103 +2899,109 @@
         <v>49</v>
       </c>
       <c r="B23">
-        <v>-0.16443818382971401</v>
+        <v>-0.16562418677036875</v>
       </c>
       <c r="C23">
-        <v>3.2875115851226283e-05</v>
+        <v>3.2606815590782098e-05</v>
       </c>
       <c r="D23">
-        <v>7.0596743197700326e-06</v>
+        <v>7.0259324899972927e-06</v>
       </c>
       <c r="E23">
-        <v>1.9096019429329625e-09</v>
+        <v>2.4718955330417382e-09</v>
       </c>
       <c r="F23">
-        <v>4.0877533799368282e-05</v>
+        <v>4.4439057352386403e-05</v>
       </c>
       <c r="G23">
-        <v>3.497730833551634e-05</v>
+        <v>3.3090857626206661e-05</v>
       </c>
       <c r="H23">
-        <v>2.7588099927021692e-05</v>
+        <v>2.723835413366407e-05</v>
       </c>
       <c r="I23">
-        <v>1.2382438929014677e-05</v>
+        <v>1.1635607613298661e-05</v>
       </c>
       <c r="J23">
-        <v>1.598184924259426e-06</v>
+        <v>1.9745750342813263e-06</v>
       </c>
       <c r="K23">
-        <v>-1.3878111332322801e-05</v>
+        <v>-1.42044052615582e-05</v>
       </c>
       <c r="L23">
-        <v>-3.8179162124950021e-06</v>
+        <v>-3.9028183123111055e-06</v>
       </c>
       <c r="M23">
-        <v>4.8353945859318536e-06</v>
+        <v>4.4989500669006581e-06</v>
       </c>
       <c r="N23">
-        <v>-4.6782119701288202e-05</v>
+        <v>-4.7132921023004847e-05</v>
       </c>
       <c r="O23">
-        <v>5.0252007600607009e-07</v>
+        <v>5.0711547101110088e-07</v>
       </c>
       <c r="P23">
-        <v>1.341921103619929e-05</v>
+        <v>1.2907688390869378e-05</v>
       </c>
       <c r="Q23">
-        <v>-1.116506599004884e-05</v>
+        <v>-1.0743271145026477e-05</v>
       </c>
       <c r="R23">
-        <v>0.00015405077340892217</v>
+        <v>0.00015721725389215889</v>
       </c>
       <c r="S23">
-        <v>0.00015085358617323392</v>
+        <v>0.00015391109031342217</v>
       </c>
       <c r="T23">
-        <v>0.00013384724745219749</v>
+        <v>0.00013641980171128767</v>
       </c>
       <c r="U23">
-        <v>1.5854803337415945e-05</v>
+        <v>1.3214857350892211e-05</v>
       </c>
       <c r="V23">
-        <v>-5.555277000671632e-05</v>
+        <v>-5.9221490715636346e-05</v>
       </c>
       <c r="W23">
-        <v>-9.3825783574827491e-05</v>
+        <v>-9.6692698841411608e-05</v>
       </c>
       <c r="X23">
-        <v>0.00073698992053537304</v>
+        <v>0.00073781342126298644</v>
       </c>
       <c r="Y23">
-        <v>0.00031819015943353488</v>
+        <v>0.00031916678969476977</v>
       </c>
       <c r="Z23">
-        <v>0.00039641171952480795</v>
+        <v>0.00039799076756211443</v>
       </c>
       <c r="AA23">
-        <v>-6.8691764685141227e-05</v>
+        <v>-6.6280645229651496e-05</v>
       </c>
       <c r="AB23">
-        <v>-9.1119440751068204e-05</v>
+        <v>-8.8778427547365536e-05</v>
       </c>
       <c r="AC23">
-        <v>-0.00010638648922825083</v>
+        <v>-0.0001025623456676171</v>
       </c>
       <c r="AD23">
-        <v>-8.4685032830998479e-05</v>
+        <v>-8.1845277992750713e-05</v>
       </c>
       <c r="AE23">
-        <v>-8.1631800335603351e-05</v>
+        <v>-7.9303566415632899e-05</v>
       </c>
       <c r="AF23">
-        <v>-9.5426843787421178e-05</v>
+        <v>-9.2811942185132366e-05</v>
       </c>
       <c r="AG23">
-        <v>3.0921685381445773e-06</v>
+        <v>2.8892275891271729e-06</v>
       </c>
       <c r="AH23">
-        <v>-0.00074744863532919524</v>
+        <v>2.3279697372624348e-05</v>
+      </c>
+      <c r="AI23">
+        <v>-4.8265097263521076e-06</v>
+      </c>
+      <c r="AJ23">
+        <v>-0.00074773814662214711</v>
       </c>
     </row>
     <row r="24">
@@ -2865,103 +3009,109 @@
         <v>50</v>
       </c>
       <c r="B24">
-        <v>-0.32946729787556228</v>
+        <v>-0.33038245343777334</v>
       </c>
       <c r="C24">
-        <v>1.2960937229377916e-05</v>
+        <v>1.2507353626023731e-05</v>
       </c>
       <c r="D24">
-        <v>3.3498853011830892e-05</v>
+        <v>3.3636494439989339e-05</v>
       </c>
       <c r="E24">
-        <v>-2.6422740261230321e-07</v>
+        <v>-2.6520618624859582e-07</v>
       </c>
       <c r="F24">
-        <v>5.0404522487951546e-05</v>
+        <v>5.7182990474016758e-05</v>
       </c>
       <c r="G24">
-        <v>-1.8459387842582608e-06</v>
+        <v>-3.0687237558719e-06</v>
       </c>
       <c r="H24">
-        <v>-9.6900770293089894e-06</v>
+        <v>-9.4038118989487331e-06</v>
       </c>
       <c r="I24">
-        <v>7.2643634315007145e-06</v>
+        <v>7.0885674723720956e-06</v>
       </c>
       <c r="J24">
-        <v>-5.5936669005860406e-07</v>
+        <v>-9.8666629231824524e-08</v>
       </c>
       <c r="K24">
-        <v>1.4850935956310212e-05</v>
+        <v>1.5362234224736333e-05</v>
       </c>
       <c r="L24">
-        <v>8.747500839220292e-08</v>
+        <v>1.4581552651866553e-07</v>
       </c>
       <c r="M24">
-        <v>-1.6592569004102378e-06</v>
+        <v>-1.9094483336881404e-06</v>
       </c>
       <c r="N24">
-        <v>7.8108018194332453e-07</v>
+        <v>1.7089749209726239e-06</v>
       </c>
       <c r="O24">
-        <v>-1.2118360618791086e-06</v>
+        <v>-1.2194903045869823e-06</v>
       </c>
       <c r="P24">
-        <v>-1.2680170136373374e-05</v>
+        <v>-1.2909084500184344e-05</v>
       </c>
       <c r="Q24">
-        <v>4.9068335579272553e-06</v>
+        <v>4.7458392919060303e-06</v>
       </c>
       <c r="R24">
-        <v>-0.0005141009245745046</v>
+        <v>-0.00051755826393656227</v>
       </c>
       <c r="S24">
-        <v>-0.00054109157998855984</v>
+        <v>-0.00054598826562006096</v>
       </c>
       <c r="T24">
-        <v>-0.00055225352246418558</v>
+        <v>-0.0005569960839069397</v>
       </c>
       <c r="U24">
-        <v>0.00018059676259831532</v>
+        <v>0.00018415005674882927</v>
       </c>
       <c r="V24">
-        <v>0.00011173847754391533</v>
+        <v>0.00011512955434016779</v>
       </c>
       <c r="W24">
-        <v>9.6961116737285429e-05</v>
+        <v>0.00010094760406168727</v>
       </c>
       <c r="X24">
-        <v>0.00031819015943353488</v>
+        <v>0.00031916678969476977</v>
       </c>
       <c r="Y24">
-        <v>0.00068367781747988375</v>
+        <v>0.00068688782566452694</v>
       </c>
       <c r="Z24">
-        <v>0.00034773189747253736</v>
+        <v>0.00034754770859169825</v>
       </c>
       <c r="AA24">
-        <v>-4.6965734606338699e-05</v>
+        <v>-4.7904968243904088e-05</v>
       </c>
       <c r="AB24">
-        <v>-2.923279558224919e-05</v>
+        <v>-2.9352671216799006e-05</v>
       </c>
       <c r="AC24">
-        <v>-6.6007459642419537e-05</v>
+        <v>-6.6569343664000434e-05</v>
       </c>
       <c r="AD24">
-        <v>-3.5135767100815426e-05</v>
+        <v>-3.4827249257180079e-05</v>
       </c>
       <c r="AE24">
-        <v>-2.9396846011165123e-05</v>
+        <v>-2.9747572854813415e-05</v>
       </c>
       <c r="AF24">
-        <v>-4.1457980832742397e-05</v>
+        <v>-4.2999107983410516e-05</v>
       </c>
       <c r="AG24">
-        <v>1.3405765647571658e-06</v>
+        <v>7.0353498413279949e-07</v>
       </c>
       <c r="AH24">
-        <v>-0.00082986178935164729</v>
+        <v>4.3654792742303509e-05</v>
+      </c>
+      <c r="AI24">
+        <v>8.7640245386980315e-06</v>
+      </c>
+      <c r="AJ24">
+        <v>-0.00082784343779009561</v>
       </c>
     </row>
     <row r="25">
@@ -2969,103 +3119,109 @@
         <v>51</v>
       </c>
       <c r="B25">
-        <v>-0.24660487780964813</v>
+        <v>-0.25057095185008144</v>
       </c>
       <c r="C25">
-        <v>0.00010968366927055643</v>
+        <v>0.00010919930756859229</v>
       </c>
       <c r="D25">
-        <v>1.2459658143304568e-05</v>
+        <v>1.2068406259105221e-05</v>
       </c>
       <c r="E25">
-        <v>-2.3703806077740918e-08</v>
+        <v>-2.019680137828838e-08</v>
       </c>
       <c r="F25">
-        <v>2.6840814959948789e-06</v>
+        <v>7.3325191904736575e-06</v>
       </c>
       <c r="G25">
-        <v>0.00010042887687203324</v>
+        <v>0.00010496985164197403</v>
       </c>
       <c r="H25">
-        <v>2.2871316319884326e-05</v>
+        <v>3.5154995881514023e-05</v>
       </c>
       <c r="I25">
-        <v>2.0656766935375653e-05</v>
+        <v>2.3598843092312557e-05</v>
       </c>
       <c r="J25">
-        <v>1.0739068533409171e-05</v>
+        <v>1.1311372692250869e-05</v>
       </c>
       <c r="K25">
-        <v>-2.7042754110714645e-05</v>
+        <v>-2.5286700238444392e-05</v>
       </c>
       <c r="L25">
-        <v>-1.3947854852402062e-05</v>
+        <v>-1.3796579052501655e-05</v>
       </c>
       <c r="M25">
-        <v>-2.6543288045339635e-05</v>
+        <v>-2.7157703428098845e-05</v>
       </c>
       <c r="N25">
-        <v>-0.00019455881047950019</v>
+        <v>-0.00019790241739100958</v>
       </c>
       <c r="O25">
-        <v>2.0638426417259916e-06</v>
+        <v>2.1349448885148807e-06</v>
       </c>
       <c r="P25">
-        <v>-1.838557902013717e-05</v>
+        <v>-2.0661299500110961e-05</v>
       </c>
       <c r="Q25">
-        <v>3.5383472222992205e-05</v>
+        <v>3.4096513352007232e-05</v>
       </c>
       <c r="R25">
-        <v>0.00086808413924651176</v>
+        <v>0.00089127060186100504</v>
       </c>
       <c r="S25">
-        <v>0.001011832552426175</v>
+        <v>0.0010319563433645457</v>
       </c>
       <c r="T25">
-        <v>0.0010131884884441063</v>
+        <v>0.0010400001708056883</v>
       </c>
       <c r="U25">
-        <v>-0.00011025696117060967</v>
+        <v>-0.00010553482450312464</v>
       </c>
       <c r="V25">
-        <v>-0.0002512294983747854</v>
+        <v>-0.00023861001404968957</v>
       </c>
       <c r="W25">
-        <v>-0.00029189933431725788</v>
+        <v>-0.00027720321106184959</v>
       </c>
       <c r="X25">
-        <v>0.00039641171952480795</v>
+        <v>0.00039799076756211443</v>
       </c>
       <c r="Y25">
-        <v>0.00034773189747253736</v>
+        <v>0.00034754770859169825</v>
       </c>
       <c r="Z25">
-        <v>0.0070342460774750837</v>
+        <v>0.007084741218361292</v>
       </c>
       <c r="AA25">
-        <v>-0.0001154367134606442</v>
+        <v>-0.00012305285941720484</v>
       </c>
       <c r="AB25">
-        <v>-7.3780374970814234e-05</v>
+        <v>-8.1863036665034993e-05</v>
       </c>
       <c r="AC25">
-        <v>-8.4013493835154434e-05</v>
+        <v>-9.7050776052944943e-05</v>
       </c>
       <c r="AD25">
-        <v>-6.8095470249913991e-05</v>
+        <v>-7.5280938311871721e-05</v>
       </c>
       <c r="AE25">
-        <v>-6.4623941889244884e-05</v>
+        <v>-7.5616856199937069e-05</v>
       </c>
       <c r="AF25">
-        <v>-0.00015215740231570534</v>
+        <v>-0.00016097100158499842</v>
       </c>
       <c r="AG25">
-        <v>-7.2766051630554189e-07</v>
+        <v>-4.461270944023758e-06</v>
       </c>
       <c r="AH25">
-        <v>-0.0015053921370662363</v>
+        <v>0.00018554183225410093</v>
+      </c>
+      <c r="AI25">
+        <v>8.7218874822208697e-05</v>
+      </c>
+      <c r="AJ25">
+        <v>-0.0014865553221428342</v>
       </c>
     </row>
     <row r="26">
@@ -3073,103 +3229,109 @@
         <v>52</v>
       </c>
       <c r="B26">
-        <v>0.24869216178533521</v>
+        <v>0.24989273312437241</v>
       </c>
       <c r="C26">
-        <v>2.2234755090753911e-05</v>
+        <v>2.008944525785602e-05</v>
       </c>
       <c r="D26">
-        <v>-2.8963431150097192e-07</v>
+        <v>-5.6742895563629365e-08</v>
       </c>
       <c r="E26">
-        <v>-4.3415141386539307e-09</v>
+        <v>-6.8232360607243115e-09</v>
       </c>
       <c r="F26">
-        <v>-0.00035665476068260933</v>
+        <v>-0.0003879657408031901</v>
       </c>
       <c r="G26">
-        <v>-3.9753025021668992e-07</v>
+        <v>-7.4596915694141459e-06</v>
       </c>
       <c r="H26">
-        <v>1.1202492387732697e-05</v>
+        <v>-3.0570556696946517e-07</v>
       </c>
       <c r="I26">
-        <v>-3.2349431402661517e-05</v>
+        <v>-3.490996641805142e-05</v>
       </c>
       <c r="J26">
-        <v>6.7777764299665312e-06</v>
+        <v>4.8588571204757222e-06</v>
       </c>
       <c r="K26">
-        <v>-1.3495049181258111e-05</v>
+        <v>-1.2605071197613945e-05</v>
       </c>
       <c r="L26">
-        <v>4.0115925639870137e-06</v>
+        <v>3.617953627115794e-06</v>
       </c>
       <c r="M26">
-        <v>-5.1284221121947723e-06</v>
+        <v>-3.6761612594367478e-06</v>
       </c>
       <c r="N26">
-        <v>-8.2672830506223035e-05</v>
+        <v>-8.8766111784358784e-05</v>
       </c>
       <c r="O26">
-        <v>-1.6257769286366858e-07</v>
+        <v>-1.5685781831742667e-07</v>
       </c>
       <c r="P26">
-        <v>2.1887496361575705e-05</v>
+        <v>2.4480863746305988e-05</v>
       </c>
       <c r="Q26">
-        <v>-4.6053523644693905e-06</v>
+        <v>-4.8760279663096189e-06</v>
       </c>
       <c r="R26">
-        <v>-0.00015970902141392712</v>
+        <v>-0.00014345429489732997</v>
       </c>
       <c r="S26">
-        <v>-7.2127173569351555e-05</v>
+        <v>-5.4917603809427618e-05</v>
       </c>
       <c r="T26">
-        <v>-0.00012171966859791244</v>
+        <v>-0.00010644408694181207</v>
       </c>
       <c r="U26">
-        <v>-5.1728826957697649e-05</v>
+        <v>-3.3787078824263489e-05</v>
       </c>
       <c r="V26">
-        <v>-3.404242622366202e-05</v>
+        <v>-2.7087647779604554e-05</v>
       </c>
       <c r="W26">
-        <v>-4.5536644832460532e-05</v>
+        <v>-3.492590841396373e-05</v>
       </c>
       <c r="X26">
-        <v>-6.8691764685141227e-05</v>
+        <v>-6.6280645229651496e-05</v>
       </c>
       <c r="Y26">
-        <v>-4.6965734606338699e-05</v>
+        <v>-4.7904968243904088e-05</v>
       </c>
       <c r="Z26">
-        <v>-0.0001154367134606442</v>
+        <v>-0.00012305285941720484</v>
       </c>
       <c r="AA26">
-        <v>0.0034634679795363253</v>
+        <v>0.0034619170763470239</v>
       </c>
       <c r="AB26">
-        <v>0.0029053006524198378</v>
+        <v>0.0029029759032347894</v>
       </c>
       <c r="AC26">
-        <v>0.0029095023967118509</v>
+        <v>0.0029085033857017997</v>
       </c>
       <c r="AD26">
-        <v>0.0029086551719373537</v>
+        <v>0.0029060405772065173</v>
       </c>
       <c r="AE26">
-        <v>0.0029087270204631562</v>
+        <v>0.0029087243273573822</v>
       </c>
       <c r="AF26">
-        <v>0.0029091359848835499</v>
+        <v>0.0029070270264578901</v>
       </c>
       <c r="AG26">
-        <v>-6.0430964146783003e-06</v>
+        <v>-1.4313372219291668e-06</v>
       </c>
       <c r="AH26">
-        <v>-0.0025364980888062374</v>
+        <v>-0.00023490624061426506</v>
+      </c>
+      <c r="AI26">
+        <v>-0.00010769817196022084</v>
+      </c>
+      <c r="AJ26">
+        <v>-0.0026099034608096233</v>
       </c>
     </row>
     <row r="27">
@@ -3177,103 +3339,109 @@
         <v>53</v>
       </c>
       <c r="B27">
-        <v>0.1186014202943803</v>
+        <v>0.12004958849408647</v>
       </c>
       <c r="C27">
-        <v>3.2851493319003622e-05</v>
+        <v>3.0620277680629821e-05</v>
       </c>
       <c r="D27">
-        <v>2.9920934160534854e-06</v>
+        <v>3.1955560987219204e-06</v>
       </c>
       <c r="E27">
-        <v>-3.2763529015902064e-08</v>
+        <v>-3.4670737634483481e-08</v>
       </c>
       <c r="F27">
-        <v>-0.00031278162733416247</v>
+        <v>-0.0003438759676396907</v>
       </c>
       <c r="G27">
-        <v>6.2341965845422702e-05</v>
+        <v>5.4673612840301764e-05</v>
       </c>
       <c r="H27">
-        <v>4.0732752038115892e-05</v>
+        <v>2.9363457396843162e-05</v>
       </c>
       <c r="I27">
-        <v>-1.7887042008131091e-05</v>
+        <v>-2.0527092432584375e-05</v>
       </c>
       <c r="J27">
-        <v>7.7405084287827147e-06</v>
+        <v>5.9795931515586247e-06</v>
       </c>
       <c r="K27">
-        <v>-4.968256124866983e-05</v>
+        <v>-4.8552193531725685e-05</v>
       </c>
       <c r="L27">
-        <v>3.056533745855855e-06</v>
+        <v>2.67415623426097e-06</v>
       </c>
       <c r="M27">
-        <v>-8.2864567449780173e-06</v>
+        <v>-7.0413633157318348e-06</v>
       </c>
       <c r="N27">
-        <v>-9.658300844157721e-05</v>
+        <v>-0.00010466159803707801</v>
       </c>
       <c r="O27">
-        <v>-1.2290727439932272e-07</v>
+        <v>-1.1896263647887223e-07</v>
       </c>
       <c r="P27">
-        <v>1.3711097321521899e-05</v>
+        <v>1.6708748131363219e-05</v>
       </c>
       <c r="Q27">
-        <v>-5.5999208484619478e-06</v>
+        <v>-6.1243900260174889e-06</v>
       </c>
       <c r="R27">
-        <v>-9.796613118667058e-05</v>
+        <v>-8.3691032520712139e-05</v>
       </c>
       <c r="S27">
-        <v>-4.3666801738166672e-05</v>
+        <v>-2.8529795788011236e-05</v>
       </c>
       <c r="T27">
-        <v>-8.6236695376440409e-05</v>
+        <v>-7.2881788181329565e-05</v>
       </c>
       <c r="U27">
-        <v>-0.00030443045987598588</v>
+        <v>-0.00028615808145876498</v>
       </c>
       <c r="V27">
-        <v>-0.00031135122940891512</v>
+        <v>-0.00030288158819016808</v>
       </c>
       <c r="W27">
-        <v>-0.00033727564414217162</v>
+        <v>-0.00032499519214412506</v>
       </c>
       <c r="X27">
-        <v>-9.1119440751068204e-05</v>
+        <v>-8.8778427547365536e-05</v>
       </c>
       <c r="Y27">
-        <v>-2.923279558224919e-05</v>
+        <v>-2.9352671216799006e-05</v>
       </c>
       <c r="Z27">
-        <v>-7.3780374970814234e-05</v>
+        <v>-8.1863036665034993e-05</v>
       </c>
       <c r="AA27">
-        <v>0.0029053006524198378</v>
+        <v>0.0029029759032347894</v>
       </c>
       <c r="AB27">
-        <v>0.0035366481164324105</v>
+        <v>0.0035373462453600541</v>
       </c>
       <c r="AC27">
-        <v>0.0029229124848833415</v>
+        <v>0.0029216686038496913</v>
       </c>
       <c r="AD27">
-        <v>0.0029076877790324696</v>
+        <v>0.0029052706475953551</v>
       </c>
       <c r="AE27">
-        <v>0.0029156119435319676</v>
+        <v>0.0029154973797012431</v>
       </c>
       <c r="AF27">
-        <v>0.0029094981720951718</v>
+        <v>0.0029077053027501297</v>
       </c>
       <c r="AG27">
-        <v>-5.0869656480458478e-06</v>
+        <v>-1.0244352968129001e-06</v>
       </c>
       <c r="AH27">
-        <v>-0.0024201521414660811</v>
+        <v>-0.00021127524913756943</v>
+      </c>
+      <c r="AI27">
+        <v>-8.7048774519841922e-05</v>
+      </c>
+      <c r="AJ27">
+        <v>-0.0024873590331442085</v>
       </c>
     </row>
     <row r="28">
@@ -3281,103 +3449,109 @@
         <v>54</v>
       </c>
       <c r="B28">
-        <v>0.37575415649523608</v>
+        <v>0.37943915130448625</v>
       </c>
       <c r="C28">
-        <v>1.9518044904853678e-05</v>
+        <v>1.737095255270012e-05</v>
       </c>
       <c r="D28">
-        <v>-7.7616755457745891e-07</v>
+        <v>-6.8472474563408703e-07</v>
       </c>
       <c r="E28">
-        <v>-9.6861377565618268e-09</v>
+        <v>-1.0666190224700449e-08</v>
       </c>
       <c r="F28">
-        <v>-0.00029149891908651052</v>
+        <v>-0.00032144368232211009</v>
       </c>
       <c r="G28">
-        <v>5.4421947256034584e-05</v>
+        <v>4.9310795184917987e-05</v>
       </c>
       <c r="H28">
-        <v>4.2613918864713538e-05</v>
+        <v>3.4039029180815849e-05</v>
       </c>
       <c r="I28">
-        <v>-5.894578668109681e-06</v>
+        <v>-7.3287296165411089e-06</v>
       </c>
       <c r="J28">
-        <v>5.1500515317105544e-06</v>
+        <v>3.8411332852990127e-06</v>
       </c>
       <c r="K28">
-        <v>-6.5003285620603179e-05</v>
+        <v>-6.3493944229510251e-05</v>
       </c>
       <c r="L28">
-        <v>4.1252634444072315e-06</v>
+        <v>3.9441884765833681e-06</v>
       </c>
       <c r="M28">
-        <v>-6.7021501247420185e-06</v>
+        <v>-5.5340363770648717e-06</v>
       </c>
       <c r="N28">
-        <v>-0.00010420801169911981</v>
+        <v>-0.00011200549554738826</v>
       </c>
       <c r="O28">
-        <v>6.3858596175337177e-08</v>
+        <v>6.7224863809878748e-08</v>
       </c>
       <c r="P28">
-        <v>4.623236220552477e-06</v>
+        <v>6.6184178924230008e-06</v>
       </c>
       <c r="Q28">
-        <v>1.0134508858396089e-05</v>
+        <v>1.1151586887880134e-05</v>
       </c>
       <c r="R28">
-        <v>6.68068666565165e-06</v>
+        <v>1.9830693334169786e-05</v>
       </c>
       <c r="S28">
-        <v>7.0300032987269737e-05</v>
+        <v>8.3710665276034643e-05</v>
       </c>
       <c r="T28">
-        <v>1.6656544121773989e-05</v>
+        <v>2.9071147594358915e-05</v>
       </c>
       <c r="U28">
-        <v>-0.00044775772178987441</v>
+        <v>-0.00042684280750269425</v>
       </c>
       <c r="V28">
-        <v>-0.00044875602882456667</v>
+        <v>-0.0004365576943273974</v>
       </c>
       <c r="W28">
-        <v>-0.00043109935112108739</v>
+        <v>-0.00041555000174634937</v>
       </c>
       <c r="X28">
-        <v>-0.00010638648922825083</v>
+        <v>-0.0001025623456676171</v>
       </c>
       <c r="Y28">
-        <v>-6.6007459642419537e-05</v>
+        <v>-6.6569343664000434e-05</v>
       </c>
       <c r="Z28">
-        <v>-8.4013493835154434e-05</v>
+        <v>-9.7050776052944943e-05</v>
       </c>
       <c r="AA28">
-        <v>0.0029095023967118509</v>
+        <v>0.0029085033857017997</v>
       </c>
       <c r="AB28">
-        <v>0.0029229124848833415</v>
+        <v>0.0029216686038496913</v>
       </c>
       <c r="AC28">
-        <v>0.00376612821519206</v>
+        <v>0.0037686949155632948</v>
       </c>
       <c r="AD28">
-        <v>0.0029111451942414671</v>
+        <v>0.0029101001154186691</v>
       </c>
       <c r="AE28">
-        <v>0.0029178433517936205</v>
+        <v>0.0029185591438347729</v>
       </c>
       <c r="AF28">
-        <v>0.0029120563030947755</v>
+        <v>0.0029115119018080456</v>
       </c>
       <c r="AG28">
-        <v>-1.0045971589327611e-05</v>
+        <v>-6.639213141441388e-06</v>
       </c>
       <c r="AH28">
-        <v>-0.0021825387384951708</v>
+        <v>-0.00015229613577247584</v>
+      </c>
+      <c r="AI28">
+        <v>-0.00010316146593031673</v>
+      </c>
+      <c r="AJ28">
+        <v>-0.0022453718805205509</v>
       </c>
     </row>
     <row r="29">
@@ -3385,103 +3559,109 @@
         <v>55</v>
       </c>
       <c r="B29">
-        <v>0.1967553746893452</v>
+        <v>0.19953268158107076</v>
       </c>
       <c r="C29">
-        <v>1.186426867075995e-05</v>
+        <v>9.9550358277092029e-06</v>
       </c>
       <c r="D29">
-        <v>2.9705298366321492e-06</v>
+        <v>3.2431857514446849e-06</v>
       </c>
       <c r="E29">
-        <v>-3.5228759364842849e-08</v>
+        <v>-3.7838868997234808e-08</v>
       </c>
       <c r="F29">
-        <v>-0.00030614056520443549</v>
+        <v>-0.00033621321242632862</v>
       </c>
       <c r="G29">
-        <v>5.3714956046137257e-05</v>
+        <v>4.5919926953411143e-05</v>
       </c>
       <c r="H29">
-        <v>4.362694109231747e-05</v>
+        <v>3.1579243025551076e-05</v>
       </c>
       <c r="I29">
-        <v>-1.3738714630288901e-05</v>
+        <v>-1.6400313896113033e-05</v>
       </c>
       <c r="J29">
-        <v>2.1048768021260701e-06</v>
+        <v>3.582330656313413e-07</v>
       </c>
       <c r="K29">
-        <v>-7.6640437867028875e-06</v>
+        <v>-6.7674234959375079e-06</v>
       </c>
       <c r="L29">
-        <v>3.8857613465943921e-06</v>
+        <v>3.5712211650880036e-06</v>
       </c>
       <c r="M29">
-        <v>-6.0174381488210799e-06</v>
+        <v>-4.717933822105455e-06</v>
       </c>
       <c r="N29">
-        <v>-8.2261303497731427e-05</v>
+        <v>-8.7585297829528234e-05</v>
       </c>
       <c r="O29">
-        <v>-2.7688962830133273e-07</v>
+        <v>-2.8464340596502083e-07</v>
       </c>
       <c r="P29">
-        <v>2.2916275614285242e-05</v>
+        <v>2.4974489775260748e-05</v>
       </c>
       <c r="Q29">
-        <v>1.2856077569123976e-05</v>
+        <v>1.3065401879147837e-05</v>
       </c>
       <c r="R29">
-        <v>-0.00022133172117906608</v>
+        <v>-0.00021070400319908589</v>
       </c>
       <c r="S29">
-        <v>-0.0001012817213137257</v>
+        <v>-8.9978529541907826e-05</v>
       </c>
       <c r="T29">
-        <v>-0.00014398854076355661</v>
+        <v>-0.00013469766881531176</v>
       </c>
       <c r="U29">
-        <v>1.2339985309965662e-05</v>
+        <v>3.0242113666888171e-05</v>
       </c>
       <c r="V29">
-        <v>2.7765915279077264e-06</v>
+        <v>1.0262788959360114e-05</v>
       </c>
       <c r="W29">
-        <v>2.9091084384758048e-05</v>
+        <v>4.0257242717714123e-05</v>
       </c>
       <c r="X29">
-        <v>-8.4685032830998479e-05</v>
+        <v>-8.1845277992750713e-05</v>
       </c>
       <c r="Y29">
-        <v>-3.5135767100815426e-05</v>
+        <v>-3.4827249257180079e-05</v>
       </c>
       <c r="Z29">
-        <v>-6.8095470249913991e-05</v>
+        <v>-7.5280938311871721e-05</v>
       </c>
       <c r="AA29">
-        <v>0.0029086551719373537</v>
+        <v>0.0029060405772065173</v>
       </c>
       <c r="AB29">
-        <v>0.0029076877790324696</v>
+        <v>0.0029052706475953551</v>
       </c>
       <c r="AC29">
-        <v>0.0029111451942414671</v>
+        <v>0.0029101001154186691</v>
       </c>
       <c r="AD29">
-        <v>0.0033894969917529208</v>
+        <v>0.0033873501817333592</v>
       </c>
       <c r="AE29">
-        <v>0.002914499956872132</v>
+        <v>0.0029144264479919156</v>
       </c>
       <c r="AF29">
-        <v>0.0029166080225927161</v>
+        <v>0.0029144657171838707</v>
       </c>
       <c r="AG29">
-        <v>-6.7784716042879382e-06</v>
+        <v>-2.4475277782291051e-06</v>
       </c>
       <c r="AH29">
-        <v>-0.0026229523256446809</v>
+        <v>-0.0002167506171987469</v>
+      </c>
+      <c r="AI29">
+        <v>-0.00010420829566168258</v>
+      </c>
+      <c r="AJ29">
+        <v>-0.0026899104053870653</v>
       </c>
     </row>
     <row r="30">
@@ -3489,103 +3669,109 @@
         <v>56</v>
       </c>
       <c r="B30">
-        <v>0.28713881263283192</v>
+        <v>0.28878556231026104</v>
       </c>
       <c r="C30">
-        <v>2.0848925512747659e-05</v>
+        <v>1.8740201872788885e-05</v>
       </c>
       <c r="D30">
-        <v>-7.6108715431803884e-07</v>
+        <v>-8.2469178198846168e-07</v>
       </c>
       <c r="E30">
-        <v>4.83441720118436e-09</v>
+        <v>5.3965842930057215e-09</v>
       </c>
       <c r="F30">
-        <v>-0.00030570504301377589</v>
+        <v>-0.00033238896329270599</v>
       </c>
       <c r="G30">
-        <v>6.5974288557758365e-05</v>
+        <v>6.1274752174575741e-05</v>
       </c>
       <c r="H30">
-        <v>6.1628326391954697e-05</v>
+        <v>5.5209910383559709e-05</v>
       </c>
       <c r="I30">
-        <v>1.6392407808113615e-06</v>
+        <v>7.8808003916201817e-07</v>
       </c>
       <c r="J30">
-        <v>7.0349394531768444e-06</v>
+        <v>5.711689207059639e-06</v>
       </c>
       <c r="K30">
-        <v>-3.3770335514039535e-05</v>
+        <v>-3.2184299087756286e-05</v>
       </c>
       <c r="L30">
-        <v>3.2539170285022785e-06</v>
+        <v>2.9579091092853315e-06</v>
       </c>
       <c r="M30">
-        <v>-7.3972617268349515e-06</v>
+        <v>-6.538428092497768e-06</v>
       </c>
       <c r="N30">
-        <v>-9.2899386823946158e-05</v>
+        <v>-0.0001014477349346528</v>
       </c>
       <c r="O30">
-        <v>-2.33255875422019e-07</v>
+        <v>-2.2703670235616047e-07</v>
       </c>
       <c r="P30">
-        <v>2.9564094892454399e-06</v>
+        <v>5.4294317632951387e-06</v>
       </c>
       <c r="Q30">
-        <v>2.6691720750643758e-05</v>
+        <v>2.6647312627876472e-05</v>
       </c>
       <c r="R30">
-        <v>-0.00018486922394329863</v>
+        <v>-0.0001713867178525768</v>
       </c>
       <c r="S30">
-        <v>-9.1629844759622686e-05</v>
+        <v>-7.7348360760081183e-05</v>
       </c>
       <c r="T30">
-        <v>-0.00013276447865572493</v>
+        <v>-0.00011938335773575316</v>
       </c>
       <c r="U30">
-        <v>-0.00020949657855305528</v>
+        <v>-0.00018854380716434079</v>
       </c>
       <c r="V30">
-        <v>-0.00019752927270313796</v>
+        <v>-0.00018557136633158295</v>
       </c>
       <c r="W30">
-        <v>-0.0002142572191855454</v>
+        <v>-0.00019909139433911278</v>
       </c>
       <c r="X30">
-        <v>-8.1631800335603351e-05</v>
+        <v>-7.9303566415632899e-05</v>
       </c>
       <c r="Y30">
-        <v>-2.9396846011165123e-05</v>
+        <v>-2.9747572854813415e-05</v>
       </c>
       <c r="Z30">
-        <v>-6.4623941889244884e-05</v>
+        <v>-7.5616856199937069e-05</v>
       </c>
       <c r="AA30">
-        <v>0.0029087270204631562</v>
+        <v>0.0029087243273573822</v>
       </c>
       <c r="AB30">
-        <v>0.0029156119435319676</v>
+        <v>0.0029154973797012431</v>
       </c>
       <c r="AC30">
-        <v>0.0029178433517936205</v>
+        <v>0.0029185591438347729</v>
       </c>
       <c r="AD30">
-        <v>0.002914499956872132</v>
+        <v>0.0029144264479919156</v>
       </c>
       <c r="AE30">
-        <v>0.0033107890975492861</v>
+        <v>0.003313065612739129</v>
       </c>
       <c r="AF30">
-        <v>0.0029149635045843175</v>
+        <v>0.0029152380562523788</v>
       </c>
       <c r="AG30">
-        <v>-6.8396461337696168e-06</v>
+        <v>-4.2143116683275095e-06</v>
       </c>
       <c r="AH30">
-        <v>-0.0023799265555945462</v>
+        <v>-0.00013314379931529544</v>
+      </c>
+      <c r="AI30">
+        <v>-6.5950887269362532e-05</v>
+      </c>
+      <c r="AJ30">
+        <v>-0.0024311174448058094</v>
       </c>
     </row>
     <row r="31">
@@ -3593,103 +3779,109 @@
         <v>57</v>
       </c>
       <c r="B31">
-        <v>0.16186216833390327</v>
+        <v>0.16224224554125677</v>
       </c>
       <c r="C31">
-        <v>1.8016048059746909e-05</v>
+        <v>1.6236824556625044e-05</v>
       </c>
       <c r="D31">
-        <v>-9.9309227653372669e-07</v>
+        <v>-1.0605696990893357e-06</v>
       </c>
       <c r="E31">
-        <v>-8.1460225145584858e-10</v>
+        <v>-7.9962469026845007e-10</v>
       </c>
       <c r="F31">
-        <v>-0.00030864186912341182</v>
+        <v>-0.00033821930018997277</v>
       </c>
       <c r="G31">
-        <v>6.9240617735101252e-05</v>
+        <v>6.3162003885449379e-05</v>
       </c>
       <c r="H31">
-        <v>4.9979475708497805e-05</v>
+        <v>4.0949210002263745e-05</v>
       </c>
       <c r="I31">
-        <v>-7.9407637682717063e-06</v>
+        <v>-1.0023184592857515e-05</v>
       </c>
       <c r="J31">
-        <v>1.4171980792534952e-05</v>
+        <v>1.2897999056349304e-05</v>
       </c>
       <c r="K31">
-        <v>-2.860533445252938e-05</v>
+        <v>-2.8043883466234308e-05</v>
       </c>
       <c r="L31">
-        <v>3.3464814574087493e-06</v>
+        <v>3.1652168661934511e-06</v>
       </c>
       <c r="M31">
-        <v>-3.929834504762094e-06</v>
+        <v>-2.9057213094194881e-06</v>
       </c>
       <c r="N31">
-        <v>-0.0001177618979195913</v>
+        <v>-0.0001261852041956013</v>
       </c>
       <c r="O31">
-        <v>-3.9428947924147748e-08</v>
+        <v>-3.4574382276464022e-08</v>
       </c>
       <c r="P31">
-        <v>2.5283624473737147e-05</v>
+        <v>2.8341475067845799e-05</v>
       </c>
       <c r="Q31">
-        <v>2.7645467661454508e-06</v>
+        <v>3.0591265652514424e-06</v>
       </c>
       <c r="R31">
-        <v>-0.00011959226924120221</v>
+        <v>-0.00010334947615037171</v>
       </c>
       <c r="S31">
-        <v>3.3619327642619989e-07</v>
+        <v>1.6882261361857685e-05</v>
       </c>
       <c r="T31">
-        <v>-5.0895615875704188e-05</v>
+        <v>-3.5312369631867666e-05</v>
       </c>
       <c r="U31">
-        <v>-0.00021687740502025462</v>
+        <v>-0.00020352959101305667</v>
       </c>
       <c r="V31">
-        <v>-0.0002152364161605992</v>
+        <v>-0.00021021413701004374</v>
       </c>
       <c r="W31">
-        <v>-0.00016989106295890819</v>
+        <v>-0.00015975550368417177</v>
       </c>
       <c r="X31">
-        <v>-9.5426843787421178e-05</v>
+        <v>-9.2811942185132366e-05</v>
       </c>
       <c r="Y31">
-        <v>-4.1457980832742397e-05</v>
+        <v>-4.2999107983410516e-05</v>
       </c>
       <c r="Z31">
-        <v>-0.00015215740231570534</v>
+        <v>-0.00016097100158499842</v>
       </c>
       <c r="AA31">
-        <v>0.0029091359848835499</v>
+        <v>0.0029070270264578901</v>
       </c>
       <c r="AB31">
-        <v>0.0029094981720951718</v>
+        <v>0.0029077053027501297</v>
       </c>
       <c r="AC31">
-        <v>0.0029120563030947755</v>
+        <v>0.0029115119018080456</v>
       </c>
       <c r="AD31">
-        <v>0.0029166080225927161</v>
+        <v>0.0029144657171838707</v>
       </c>
       <c r="AE31">
-        <v>0.0029149635045843175</v>
+        <v>0.0029152380562523788</v>
       </c>
       <c r="AF31">
-        <v>0.0034404797885385281</v>
+        <v>0.0034389348138001174</v>
       </c>
       <c r="AG31">
-        <v>-6.5205985603400242e-06</v>
+        <v>-2.9793961509160124e-06</v>
       </c>
       <c r="AH31">
-        <v>-0.0024522664016238174</v>
+        <v>-0.00016166259147393789</v>
+      </c>
+      <c r="AI31">
+        <v>-9.908780070286982e-05</v>
+      </c>
+      <c r="AJ31">
+        <v>-0.0025057044599426648</v>
       </c>
     </row>
     <row r="32">
@@ -3697,103 +3889,109 @@
         <v>58</v>
       </c>
       <c r="B32">
-        <v>-0.054980541675969698</v>
+        <v>-0.048669337576933626</v>
       </c>
       <c r="C32">
-        <v>3.2427673415165035e-07</v>
+        <v>4.5706930769845149e-07</v>
       </c>
       <c r="D32">
-        <v>-7.3688707800804895e-08</v>
+        <v>-1.2611444277851479e-08</v>
       </c>
       <c r="E32">
-        <v>-1.7697718347875624e-09</v>
+        <v>-2.1088776176912062e-09</v>
       </c>
       <c r="F32">
-        <v>1.312790935562137e-06</v>
+        <v>-1.0847629299590987e-06</v>
       </c>
       <c r="G32">
-        <v>-9.143016305353215e-07</v>
+        <v>-7.7394332615398398e-07</v>
       </c>
       <c r="H32">
-        <v>-4.1721118033656768e-06</v>
+        <v>-3.6728508684652067e-06</v>
       </c>
       <c r="I32">
-        <v>-2.6956156767708938e-06</v>
+        <v>-2.2712442873387257e-06</v>
       </c>
       <c r="J32">
-        <v>7.1113663786945166e-07</v>
+        <v>9.7116927496613578e-07</v>
       </c>
       <c r="K32">
-        <v>-6.5742139252626447e-07</v>
+        <v>-5.0741236670478877e-07</v>
       </c>
       <c r="L32">
-        <v>-2.7301158488969425e-07</v>
+        <v>-2.2299980491866647e-07</v>
       </c>
       <c r="M32">
-        <v>1.4314811093280512e-06</v>
+        <v>1.4247585618967477e-06</v>
       </c>
       <c r="N32">
-        <v>9.1740824583342456e-09</v>
+        <v>-6.4342264269657049e-07</v>
       </c>
       <c r="O32">
-        <v>-1.8458298843144048e-08</v>
+        <v>-1.2076834283234572e-08</v>
       </c>
       <c r="P32">
-        <v>-8.6018516675320246e-08</v>
+        <v>-4.0507905806822829e-07</v>
       </c>
       <c r="Q32">
-        <v>-5.5269597205395856e-07</v>
+        <v>-5.597041323916139e-07</v>
       </c>
       <c r="R32">
-        <v>-6.1724273337825444e-06</v>
+        <v>-4.650223596836282e-06</v>
       </c>
       <c r="S32">
-        <v>-1.2741045310613259e-05</v>
+        <v>-1.1098044695567527e-05</v>
       </c>
       <c r="T32">
-        <v>-1.6854466762370466e-05</v>
+        <v>-1.5124170488833594e-05</v>
       </c>
       <c r="U32">
-        <v>-1.4329823761891102e-05</v>
+        <v>-1.2037901713926298e-05</v>
       </c>
       <c r="V32">
-        <v>-1.3631811037048344e-06</v>
+        <v>3.298568482878279e-07</v>
       </c>
       <c r="W32">
-        <v>-1.2259196194089328e-06</v>
+        <v>3.6350820467926336e-07</v>
       </c>
       <c r="X32">
-        <v>3.0921685381445773e-06</v>
+        <v>2.8892275891271729e-06</v>
       </c>
       <c r="Y32">
-        <v>1.3405765647571658e-06</v>
+        <v>7.0353498413279949e-07</v>
       </c>
       <c r="Z32">
-        <v>-7.2766051630554189e-07</v>
+        <v>-4.461270944023758e-06</v>
       </c>
       <c r="AA32">
-        <v>-6.0430964146783003e-06</v>
+        <v>-1.4313372219291668e-06</v>
       </c>
       <c r="AB32">
-        <v>-5.0869656480458478e-06</v>
+        <v>-1.0244352968129001e-06</v>
       </c>
       <c r="AC32">
-        <v>-1.0045971589327611e-05</v>
+        <v>-6.639213141441388e-06</v>
       </c>
       <c r="AD32">
-        <v>-6.7784716042879382e-06</v>
+        <v>-2.4475277782291051e-06</v>
       </c>
       <c r="AE32">
-        <v>-6.8396461337696168e-06</v>
+        <v>-4.2143116683275095e-06</v>
       </c>
       <c r="AF32">
-        <v>-6.5205985603400242e-06</v>
+        <v>-2.9793961509160124e-06</v>
       </c>
       <c r="AG32">
-        <v>5.8071372461245838e-06</v>
+        <v>5.6533435071966701e-06</v>
       </c>
       <c r="AH32">
-        <v>-7.7171881835745929e-05</v>
+        <v>-5.997998105176366e-06</v>
+      </c>
+      <c r="AI32">
+        <v>-1.2444182098481972e-05</v>
+      </c>
+      <c r="AJ32">
+        <v>-8.371642391915619e-05</v>
       </c>
     </row>
     <row r="33">
@@ -3801,103 +3999,329 @@
         <v>59</v>
       </c>
       <c r="B33">
-        <v>0.39018980515380575</v>
+        <v>0.0015405392933348944</v>
       </c>
       <c r="C33">
-        <v>0.00034613295039739823</v>
+        <v>-1.1395694809765368e-05</v>
       </c>
       <c r="D33">
-        <v>-0.00028780368450828913</v>
+        <v>-1.7413413081221549e-06</v>
       </c>
       <c r="E33">
-        <v>2.7132771203039535e-06</v>
+        <v>2.52249146753247e-10</v>
       </c>
       <c r="F33">
-        <v>-0.00015056543033221308</v>
+        <v>0.0001415248638067281</v>
       </c>
       <c r="G33">
-        <v>-0.00034746826021087105</v>
+        <v>-2.2030612711127417e-05</v>
       </c>
       <c r="H33">
-        <v>-0.0002912081307662889</v>
+        <v>-2.6350577141604002e-06</v>
       </c>
       <c r="I33">
-        <v>-0.00013817329010755008</v>
+        <v>-2.4612296879961913e-05</v>
       </c>
       <c r="J33">
-        <v>3.8241408493853369e-05</v>
+        <v>-1.5609354672070172e-06</v>
       </c>
       <c r="K33">
-        <v>-0.0029148802844716684</v>
+        <v>-1.4728989282367707e-05</v>
       </c>
       <c r="L33">
-        <v>0.00011060536569436742</v>
+        <v>-1.2428005193927032e-06</v>
       </c>
       <c r="M33">
-        <v>-2.6282177451205223e-05</v>
+        <v>-2.2626364425119899e-06</v>
       </c>
       <c r="N33">
-        <v>-0.0052036650527938558</v>
+        <v>-2.2164138048162176e-05</v>
       </c>
       <c r="O33">
-        <v>-9.7153524140074275e-05</v>
+        <v>-5.7196816117010857e-07</v>
       </c>
       <c r="P33">
-        <v>-0.0004777439030639913</v>
+        <v>1.1604885549131006e-05</v>
       </c>
       <c r="Q33">
-        <v>0.0023588968083124527</v>
+        <v>1.9939508548757427e-05</v>
       </c>
       <c r="R33">
-        <v>-0.048849629572997613</v>
+        <v>-0.0001895486371505592</v>
       </c>
       <c r="S33">
-        <v>-0.048495498961884945</v>
+        <v>-0.00018796882303842577</v>
       </c>
       <c r="T33">
-        <v>-0.047875562641307878</v>
+        <v>-0.0002140049657082671</v>
       </c>
       <c r="U33">
-        <v>-0.026834991417646989</v>
+        <v>-0.0001512338373518933</v>
       </c>
       <c r="V33">
-        <v>-0.022908844474863507</v>
+        <v>-0.0001359753622682848</v>
       </c>
       <c r="W33">
-        <v>-0.02377072641085777</v>
+        <v>-0.00011810315069277558</v>
       </c>
       <c r="X33">
-        <v>-0.00074744863532919524</v>
+        <v>2.3279697372624348e-05</v>
       </c>
       <c r="Y33">
-        <v>-0.00082986178935164729</v>
+        <v>4.3654792742303509e-05</v>
       </c>
       <c r="Z33">
-        <v>-0.0015053921370662363</v>
+        <v>0.00018554183225410093</v>
       </c>
       <c r="AA33">
-        <v>-0.0025364980888062374</v>
+        <v>-0.00023490624061426506</v>
       </c>
       <c r="AB33">
-        <v>-0.0024201521414660811</v>
+        <v>-0.00021127524913756943</v>
       </c>
       <c r="AC33">
-        <v>-0.0021825387384951708</v>
+        <v>-0.00015229613577247584</v>
       </c>
       <c r="AD33">
-        <v>-0.0026229523256446809</v>
+        <v>-0.0002167506171987469</v>
       </c>
       <c r="AE33">
-        <v>-0.0023799265555945462</v>
+        <v>-0.00013314379931529544</v>
       </c>
       <c r="AF33">
-        <v>-0.0024522664016238174</v>
+        <v>-0.00016166259147393789</v>
       </c>
       <c r="AG33">
-        <v>-7.7171881835745929e-05</v>
+        <v>-5.997998105176366e-06</v>
       </c>
       <c r="AH33">
-        <v>0.082637151128951647</v>
+        <v>0.001799609755040728</v>
+      </c>
+      <c r="AI33">
+        <v>0.00019303518533604131</v>
+      </c>
+      <c r="AJ33">
+        <v>0.00060398840478209724</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s">
+        <v>60</v>
+      </c>
+      <c r="B34">
+        <v>-0.46934929547261428</v>
+      </c>
+      <c r="C34">
+        <v>7.7841352484640314e-07</v>
+      </c>
+      <c r="D34">
+        <v>-5.8608815061820762e-06</v>
+      </c>
+      <c r="E34">
+        <v>5.1451634562556878e-08</v>
+      </c>
+      <c r="F34">
+        <v>9.6796122039921882e-05</v>
+      </c>
+      <c r="G34">
+        <v>3.1578757810894997e-05</v>
+      </c>
+      <c r="H34">
+        <v>1.7121646091136532e-05</v>
+      </c>
+      <c r="I34">
+        <v>3.2512755883705105e-06</v>
+      </c>
+      <c r="J34">
+        <v>-1.3730403899072507e-05</v>
+      </c>
+      <c r="K34">
+        <v>6.3375947813017154e-06</v>
+      </c>
+      <c r="L34">
+        <v>-2.4194662693187976e-06</v>
+      </c>
+      <c r="M34">
+        <v>-2.5026242273638586e-06</v>
+      </c>
+      <c r="N34">
+        <v>5.4763436536255702e-05</v>
+      </c>
+      <c r="O34">
+        <v>8.8186565686442837e-08</v>
+      </c>
+      <c r="P34">
+        <v>1.0604849255206464e-05</v>
+      </c>
+      <c r="Q34">
+        <v>-2.0131342377696995e-05</v>
+      </c>
+      <c r="R34">
+        <v>6.374556169201108e-05</v>
+      </c>
+      <c r="S34">
+        <v>5.0209324960333659e-05</v>
+      </c>
+      <c r="T34">
+        <v>6.5692277114502359e-05</v>
+      </c>
+      <c r="U34">
+        <v>-3.2714931552187479e-05</v>
+      </c>
+      <c r="V34">
+        <v>1.7109776470275624e-05</v>
+      </c>
+      <c r="W34">
+        <v>4.4973636718738733e-06</v>
+      </c>
+      <c r="X34">
+        <v>-4.8265097263521076e-06</v>
+      </c>
+      <c r="Y34">
+        <v>8.7640245386980315e-06</v>
+      </c>
+      <c r="Z34">
+        <v>8.7218874822208697e-05</v>
+      </c>
+      <c r="AA34">
+        <v>-0.00010769817196022084</v>
+      </c>
+      <c r="AB34">
+        <v>-8.7048774519841922e-05</v>
+      </c>
+      <c r="AC34">
+        <v>-0.00010316146593031673</v>
+      </c>
+      <c r="AD34">
+        <v>-0.00010420829566168258</v>
+      </c>
+      <c r="AE34">
+        <v>-6.5950887269362532e-05</v>
+      </c>
+      <c r="AF34">
+        <v>-9.908780070286982e-05</v>
+      </c>
+      <c r="AG34">
+        <v>-1.2444182098481972e-05</v>
+      </c>
+      <c r="AH34">
+        <v>0.00019303518533604131</v>
+      </c>
+      <c r="AI34">
+        <v>0.0013755066770988658</v>
+      </c>
+      <c r="AJ34">
+        <v>0.00029855710082384284</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s">
+        <v>61</v>
+      </c>
+      <c r="B35">
+        <v>0.30558455146641017</v>
+      </c>
+      <c r="C35">
+        <v>0.00034627450460851311</v>
+      </c>
+      <c r="D35">
+        <v>-0.00029159833162855969</v>
+      </c>
+      <c r="E35">
+        <v>2.7453203057273422e-06</v>
+      </c>
+      <c r="F35">
+        <v>-0.00011587260424335971</v>
+      </c>
+      <c r="G35">
+        <v>-0.00034392369399797193</v>
+      </c>
+      <c r="H35">
+        <v>-0.00028215220952928924</v>
+      </c>
+      <c r="I35">
+        <v>-0.00014186833008786152</v>
+      </c>
+      <c r="J35">
+        <v>3.89467405004832e-05</v>
+      </c>
+      <c r="K35">
+        <v>-0.0029244195253660971</v>
+      </c>
+      <c r="L35">
+        <v>0.00011265633956514313</v>
+      </c>
+      <c r="M35">
+        <v>-2.8201969746309123e-05</v>
+      </c>
+      <c r="N35">
+        <v>-0.0051345458324562228</v>
+      </c>
+      <c r="O35">
+        <v>-9.666866067589903e-05</v>
+      </c>
+      <c r="P35">
+        <v>-0.00045274442340696415</v>
+      </c>
+      <c r="Q35">
+        <v>0.0023562528910354447</v>
+      </c>
+      <c r="R35">
+        <v>-0.048628395941666985</v>
+      </c>
+      <c r="S35">
+        <v>-0.048269432432185289</v>
+      </c>
+      <c r="T35">
+        <v>-0.047652712381011209</v>
+      </c>
+      <c r="U35">
+        <v>-0.026942780966095696</v>
+      </c>
+      <c r="V35">
+        <v>-0.022981610082609877</v>
+      </c>
+      <c r="W35">
+        <v>-0.023842405045704632</v>
+      </c>
+      <c r="X35">
+        <v>-0.00074773814662214711</v>
+      </c>
+      <c r="Y35">
+        <v>-0.00082784343779009561</v>
+      </c>
+      <c r="Z35">
+        <v>-0.0014865553221428342</v>
+      </c>
+      <c r="AA35">
+        <v>-0.0026099034608096233</v>
+      </c>
+      <c r="AB35">
+        <v>-0.0024873590331442085</v>
+      </c>
+      <c r="AC35">
+        <v>-0.0022453718805205509</v>
+      </c>
+      <c r="AD35">
+        <v>-0.0026899104053870653</v>
+      </c>
+      <c r="AE35">
+        <v>-0.0024311174448058094</v>
+      </c>
+      <c r="AF35">
+        <v>-0.0025057044599426648</v>
+      </c>
+      <c r="AG35">
+        <v>-8.371642391915619e-05</v>
+      </c>
+      <c r="AH35">
+        <v>0.00060398840478209724</v>
+      </c>
+      <c r="AI35">
+        <v>0.00029855710082384284</v>
+      </c>
+      <c r="AJ35">
+        <v>0.082699131413959515</v>
       </c>
     </row>
   </sheetData>
@@ -3906,7 +4330,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AG32"/>
+  <dimension ref="A1:AI34"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3914,7 +4338,7 @@
         <v>27</v>
       </c>
       <c r="B1" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C1" t="s">
         <v>28</v>
@@ -3935,10 +4359,10 @@
         <v>34</v>
       </c>
       <c r="I1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="J1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="K1" t="s">
         <v>36</v>
@@ -3947,16 +4371,16 @@
         <v>37</v>
       </c>
       <c r="M1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="N1" t="s">
         <v>39</v>
       </c>
       <c r="O1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="P1" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="Q1" t="s">
         <v>43</v>
@@ -4008,6 +4432,12 @@
       </c>
       <c r="AG1" t="s">
         <v>59</v>
+      </c>
+      <c r="AH1" t="s">
+        <v>60</v>
+      </c>
+      <c r="AI1" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="2">
@@ -4015,100 +4445,106 @@
         <v>28</v>
       </c>
       <c r="B2">
-        <v>-0.010260375686786991</v>
+        <v>-0.017140229570873192</v>
       </c>
       <c r="C2">
-        <v>0.00024387016420996554</v>
+        <v>0.00033806938097501703</v>
       </c>
       <c r="D2">
-        <v>-1.2346889182066968e-06</v>
+        <v>-1.1778298065185433e-06</v>
       </c>
       <c r="E2">
-        <v>2.5907712733071444e-08</v>
+        <v>3.3006838742514826e-08</v>
       </c>
       <c r="F2">
-        <v>1.6182934861110855e-05</v>
+        <v>2.3502177242822334e-05</v>
       </c>
       <c r="G2">
-        <v>-1.5298460107365573e-05</v>
+        <v>-2.1957961697634844e-05</v>
       </c>
       <c r="H2">
-        <v>-4.2808229553902553e-06</v>
+        <v>-1.4483117365472833e-05</v>
       </c>
       <c r="I2">
-        <v>-4.625680081441417e-05</v>
+        <v>-6.721971269187937e-05</v>
       </c>
       <c r="J2">
-        <v>7.673705623548462e-06</v>
+        <v>4.1213408368018641e-05</v>
       </c>
       <c r="K2">
-        <v>-1.5474481394921801e-05</v>
+        <v>-2.226764468905269e-05</v>
       </c>
       <c r="L2">
-        <v>-6.1491109097676031e-07</v>
+        <v>-5.8287437428686758e-07</v>
       </c>
       <c r="M2">
-        <v>-4.3113017440064528e-06</v>
+        <v>-3.1723494920810533e-05</v>
       </c>
       <c r="N2">
-        <v>-0.00024019820742180766</v>
+        <v>-0.00032721101553160996</v>
       </c>
       <c r="O2">
-        <v>-1.0288408450762515e-05</v>
+        <v>-5.2190345536982111e-05</v>
       </c>
       <c r="P2">
-        <v>4.6918486669518108e-06</v>
+        <v>3.3053013638421755e-05</v>
       </c>
       <c r="Q2">
-        <v>-0.00018588921021277688</v>
+        <v>-0.0002335383041085244</v>
       </c>
       <c r="R2">
-        <v>-0.00018033001386842074</v>
+        <v>-0.0002303058251058735</v>
       </c>
       <c r="S2">
-        <v>-0.00015615417739911936</v>
+        <v>-0.00019378965804275452</v>
       </c>
       <c r="T2">
-        <v>-0.00010149179620665957</v>
+        <v>-0.00011173905231292986</v>
       </c>
       <c r="U2">
-        <v>-3.5238291414956995e-05</v>
+        <v>-6.1625668049730789e-05</v>
       </c>
       <c r="V2">
-        <v>-0.00014666270436385764</v>
+        <v>-0.00021239483960761732</v>
       </c>
       <c r="W2">
-        <v>2.8452502558465828e-05</v>
+        <v>3.9564821483017843e-05</v>
       </c>
       <c r="X2">
-        <v>6.5652393812434846e-06</v>
+        <v>-8.9443228905280233e-07</v>
       </c>
       <c r="Y2">
-        <v>0.000102507548319959</v>
+        <v>0.00013778405085550639</v>
       </c>
       <c r="Z2">
-        <v>-8.877803668276503e-06</v>
+        <v>5.7221913230602833e-06</v>
       </c>
       <c r="AA2">
-        <v>-5.8973248747452438e-06</v>
+        <v>1.0577578694776009e-05</v>
       </c>
       <c r="AB2">
-        <v>-9.8714966054679304e-06</v>
+        <v>7.2822143498292637e-06</v>
       </c>
       <c r="AC2">
-        <v>-9.2243777165275349e-06</v>
+        <v>4.2572345110106642e-06</v>
       </c>
       <c r="AD2">
-        <v>-2.4221781435151366e-05</v>
+        <v>-1.8895805004206254e-05</v>
       </c>
       <c r="AE2">
-        <v>-3.0923984250093275e-06</v>
+        <v>9.3130314107987875e-06</v>
       </c>
       <c r="AF2">
-        <v>-1.0539886173293146e-06</v>
+        <v>-1.1801453572122004e-07</v>
       </c>
       <c r="AG2">
-        <v>0.00017151388028960356</v>
+        <v>-7.8303737241919042e-05</v>
+      </c>
+      <c r="AH2">
+        <v>-2.8586673719581114e-05</v>
+      </c>
+      <c r="AI2">
+        <v>0.00018030146354133222</v>
       </c>
     </row>
     <row r="3">
@@ -4116,100 +4552,106 @@
         <v>29</v>
       </c>
       <c r="B3">
-        <v>0.0079645408854857203</v>
+        <v>0.016935458362687471</v>
       </c>
       <c r="C3">
-        <v>-1.2346889182066968e-06</v>
+        <v>-1.1778298065185433e-06</v>
       </c>
       <c r="D3">
-        <v>1.187891504660902e-05</v>
+        <v>1.6416486361387738e-05</v>
       </c>
       <c r="E3">
-        <v>-1.0212374728358824e-07</v>
+        <v>-1.4363105323651625e-07</v>
       </c>
       <c r="F3">
-        <v>-4.6992045521010335e-06</v>
+        <v>-1.112691849875408e-05</v>
       </c>
       <c r="G3">
-        <v>-4.7609444038821897e-06</v>
+        <v>-1.049610769144287e-05</v>
       </c>
       <c r="H3">
-        <v>-7.9329939238223531e-06</v>
+        <v>-1.2277270060586291e-05</v>
       </c>
       <c r="I3">
-        <v>8.1183592218770902e-06</v>
+        <v>5.0313548365215613e-06</v>
       </c>
       <c r="J3">
-        <v>-6.1481107264909062e-07</v>
+        <v>-4.5307554241174784e-06</v>
       </c>
       <c r="K3">
-        <v>-2.3805408801780891e-06</v>
+        <v>-3.0609639437874859e-06</v>
       </c>
       <c r="L3">
-        <v>-8.6606786674804546e-07</v>
+        <v>-6.4280215891314599e-07</v>
       </c>
       <c r="M3">
-        <v>-2.7555205775670662e-07</v>
+        <v>1.6638624846267825e-06</v>
       </c>
       <c r="N3">
-        <v>8.1266654860760729e-08</v>
+        <v>1.6105749166989508e-06</v>
       </c>
       <c r="O3">
-        <v>1.3278797462765355e-07</v>
+        <v>4.7435608756717042e-06</v>
       </c>
       <c r="P3">
-        <v>1.1797481650982711e-07</v>
+        <v>-2.2758995772888545e-06</v>
       </c>
       <c r="Q3">
-        <v>-2.1407780739264993e-05</v>
+        <v>-2.4673197894813532e-05</v>
       </c>
       <c r="R3">
-        <v>-2.9710612782519373e-05</v>
+        <v>-3.6716647217242154e-05</v>
       </c>
       <c r="S3">
-        <v>-2.1951774781963339e-05</v>
+        <v>-2.7617825972556318e-05</v>
       </c>
       <c r="T3">
-        <v>3.8033274340980888e-05</v>
+        <v>5.5278619335626046e-05</v>
       </c>
       <c r="U3">
-        <v>-2.6751340245998614e-05</v>
+        <v>-2.9886890183150925e-05</v>
       </c>
       <c r="V3">
-        <v>-1.0460529573620136e-05</v>
+        <v>-4.4623759993101366e-06</v>
       </c>
       <c r="W3">
-        <v>1.0216310574711063e-05</v>
+        <v>8.9429306130692885e-06</v>
       </c>
       <c r="X3">
-        <v>2.6522687314115122e-05</v>
+        <v>3.4881524734780984e-05</v>
       </c>
       <c r="Y3">
-        <v>1.0112087376620995e-05</v>
+        <v>1.0546391990252503e-05</v>
       </c>
       <c r="Z3">
-        <v>1.156960100076414e-06</v>
+        <v>-3.5955745998582085e-07</v>
       </c>
       <c r="AA3">
-        <v>3.7377401114815629e-06</v>
+        <v>2.7308923763493925e-06</v>
       </c>
       <c r="AB3">
-        <v>4.6265665702065824e-06</v>
+        <v>2.697070694620193e-06</v>
       </c>
       <c r="AC3">
-        <v>3.9144467829741868e-06</v>
+        <v>3.3111745535957895e-06</v>
       </c>
       <c r="AD3">
-        <v>3.8214061891865504e-06</v>
+        <v>2.7098451452058439e-06</v>
       </c>
       <c r="AE3">
-        <v>-3.9748307806056623e-06</v>
+        <v>-3.7182472273433852e-06</v>
       </c>
       <c r="AF3">
-        <v>-1.0164325202820428e-07</v>
+        <v>-1.0517234437267577e-07</v>
       </c>
       <c r="AG3">
-        <v>-0.00027447695095998183</v>
+        <v>6.7792657439162902e-07</v>
+      </c>
+      <c r="AH3">
+        <v>-2.1025786509196349e-06</v>
+      </c>
+      <c r="AI3">
+        <v>-0.00037727989086930693</v>
       </c>
     </row>
     <row r="4">
@@ -4217,100 +4659,106 @@
         <v>30</v>
       </c>
       <c r="B4">
-        <v>-7.1609550370957872e-05</v>
+        <v>-0.00013172557719345085</v>
       </c>
       <c r="C4">
-        <v>2.5907712733071444e-08</v>
+        <v>3.3006838742514826e-08</v>
       </c>
       <c r="D4">
-        <v>-1.0212374728358824e-07</v>
+        <v>-1.4363105323651625e-07</v>
       </c>
       <c r="E4">
-        <v>9.3019968586059136e-10</v>
+        <v>1.329093588220942e-09</v>
       </c>
       <c r="F4">
-        <v>5.2774573006136682e-08</v>
+        <v>1.3257966234866214e-07</v>
       </c>
       <c r="G4">
-        <v>4.9637533590616021e-08</v>
+        <v>1.1876124015754986e-07</v>
       </c>
       <c r="H4">
-        <v>1.0129699688830441e-07</v>
+        <v>1.6483488710737124e-07</v>
       </c>
       <c r="I4">
-        <v>-2.2084939021040794e-08</v>
+        <v>3.1801700551144731e-08</v>
       </c>
       <c r="J4">
-        <v>4.1122901093325748e-09</v>
+        <v>3.9366403143661224e-08</v>
       </c>
       <c r="K4">
-        <v>5.3157982944807594e-09</v>
+        <v>6.937684904624332e-09</v>
       </c>
       <c r="L4">
-        <v>9.5353104650458061e-09</v>
+        <v>8.3378763345040892e-09</v>
       </c>
       <c r="M4">
-        <v>1.8071073194478636e-09</v>
+        <v>-2.1655739911599938e-08</v>
       </c>
       <c r="N4">
-        <v>-1.5654567780587191e-08</v>
+        <v>-3.5207519034754194e-08</v>
       </c>
       <c r="O4">
-        <v>8.3366516590246226e-10</v>
+        <v>-3.8195828957995975e-08</v>
       </c>
       <c r="P4">
-        <v>-8.7617767856733949e-10</v>
+        <v>2.457048710279807e-08</v>
       </c>
       <c r="Q4">
-        <v>1.4119886020460961e-07</v>
+        <v>1.5643170299260902e-07</v>
       </c>
       <c r="R4">
-        <v>2.3314111540483845e-07</v>
+        <v>2.9063490963525747e-07</v>
       </c>
       <c r="S4">
-        <v>1.8096306399121193e-07</v>
+        <v>2.294840276284424e-07</v>
       </c>
       <c r="T4">
-        <v>-3.6361981013645856e-07</v>
+        <v>-5.2139548909216559e-07</v>
       </c>
       <c r="U4">
-        <v>1.0661295843582858e-07</v>
+        <v>1.0555085868033711e-07</v>
       </c>
       <c r="V4">
-        <v>-1.6168915785791999e-07</v>
+        <v>-2.9672922183350712e-07</v>
       </c>
       <c r="W4">
-        <v>-4.7657272907616299e-08</v>
+        <v>-2.5885828971758204e-08</v>
       </c>
       <c r="X4">
-        <v>-2.0691183931877857e-07</v>
+        <v>-2.8117749342473678e-07</v>
       </c>
       <c r="Y4">
-        <v>-3.8040347883048606e-08</v>
+        <v>-1.9302764471890355e-08</v>
       </c>
       <c r="Z4">
-        <v>-3.7501710989713656e-08</v>
+        <v>-5.5699364489547746e-09</v>
       </c>
       <c r="AA4">
-        <v>-6.8936656713701994e-08</v>
+        <v>-4.0956090897983854e-08</v>
       </c>
       <c r="AB4">
-        <v>-7.5057046272668922e-08</v>
+        <v>-4.0279910068181208e-08</v>
       </c>
       <c r="AC4">
-        <v>-6.8818484765936329e-08</v>
+        <v>-4.6066599677972516e-08</v>
       </c>
       <c r="AD4">
-        <v>-6.2548400488715465e-08</v>
+        <v>-3.3901780022848824e-08</v>
       </c>
       <c r="AE4">
-        <v>-1.9607169780295065e-10</v>
+        <v>1.8326230847159117e-08</v>
       </c>
       <c r="AF4">
-        <v>-6.9834347979371075e-10</v>
+        <v>-7.9769449682427677e-10</v>
       </c>
       <c r="AG4">
-        <v>2.3688879857051789e-06</v>
+        <v>-2.0616752399827562e-08</v>
+      </c>
+      <c r="AH4">
+        <v>9.7628222075587755e-09</v>
+      </c>
+      <c r="AI4">
+        <v>3.2579248682791623e-06</v>
       </c>
     </row>
     <row r="5">
@@ -4318,100 +4766,106 @@
         <v>32</v>
       </c>
       <c r="B5">
-        <v>0.014957040159856867</v>
+        <v>0.035394831601462694</v>
       </c>
       <c r="C5">
-        <v>1.6182934861110855e-05</v>
+        <v>2.3502177242822334e-05</v>
       </c>
       <c r="D5">
-        <v>-4.6992045521010335e-06</v>
+        <v>-1.112691849875408e-05</v>
       </c>
       <c r="E5">
-        <v>5.2774573006136682e-08</v>
+        <v>1.3257966234866214e-07</v>
       </c>
       <c r="F5">
-        <v>0.0032503569473464325</v>
+        <v>0.0043205698248378628</v>
       </c>
       <c r="G5">
-        <v>0.0024858624394528467</v>
+        <v>0.003331974742639575</v>
       </c>
       <c r="H5">
-        <v>0.0024981933059437566</v>
+        <v>0.0033508516809490014</v>
       </c>
       <c r="I5">
-        <v>0.0024902366818681408</v>
+        <v>0.0033348456927829056</v>
       </c>
       <c r="J5">
-        <v>9.5626898841416359e-06</v>
+        <v>5.4545645044529537e-06</v>
       </c>
       <c r="K5">
-        <v>1.3152490895937884e-05</v>
+        <v>1.9796338654559292e-05</v>
       </c>
       <c r="L5">
-        <v>-4.1695182500271283e-06</v>
+        <v>-5.7405188505130732e-06</v>
       </c>
       <c r="M5">
-        <v>-1.6138216965445515e-05</v>
+        <v>-6.8646367053233843e-05</v>
       </c>
       <c r="N5">
-        <v>-1.6269787054758731e-05</v>
+        <v>-2.2211741921381923e-05</v>
       </c>
       <c r="O5">
-        <v>-9.8142529099163418e-06</v>
+        <v>-2.542835841340494e-06</v>
       </c>
       <c r="P5">
-        <v>1.5416105629659563e-05</v>
+        <v>6.2499291838728137e-05</v>
       </c>
       <c r="Q5">
-        <v>-1.1249784006980932e-05</v>
+        <v>3.4178594085720882e-05</v>
       </c>
       <c r="R5">
-        <v>3.0418839046161047e-05</v>
+        <v>9.2978855768374204e-05</v>
       </c>
       <c r="S5">
-        <v>1.7181464922683912e-05</v>
+        <v>7.2527720131985041e-05</v>
       </c>
       <c r="T5">
-        <v>7.4266916942861833e-05</v>
+        <v>0.0001052124654547246</v>
       </c>
       <c r="U5">
-        <v>8.8792500542317961e-05</v>
+        <v>0.00013217582648960798</v>
       </c>
       <c r="V5">
-        <v>4.6188856845626094e-05</v>
+        <v>3.4050800023753395e-05</v>
       </c>
       <c r="W5">
-        <v>-2.2435390006407253e-05</v>
+        <v>2.3762492316839416e-06</v>
       </c>
       <c r="X5">
-        <v>-3.2441540281280242e-05</v>
+        <v>-1.119198441620786e-05</v>
       </c>
       <c r="Y5">
-        <v>3.1618796387728734e-05</v>
+        <v>5.7622309281317365e-05</v>
       </c>
       <c r="Z5">
-        <v>-5.0134462642295857e-05</v>
+        <v>-5.5970222525287064e-05</v>
       </c>
       <c r="AA5">
-        <v>-3.5659616485143918e-05</v>
+        <v>-3.256235592747638e-05</v>
       </c>
       <c r="AB5">
-        <v>-3.9655761580559994e-05</v>
+        <v>-4.3692492921836609e-05</v>
       </c>
       <c r="AC5">
-        <v>-7.446299160707116e-05</v>
+        <v>-9.425875026856283e-05</v>
       </c>
       <c r="AD5">
-        <v>1.3809560856642422e-06</v>
+        <v>1.0258616395554358e-05</v>
       </c>
       <c r="AE5">
-        <v>-1.5600412780258758e-05</v>
+        <v>-5.2922973063558609e-06</v>
       </c>
       <c r="AF5">
-        <v>-1.4390174210012711e-07</v>
+        <v>-2.1242813873393685e-06</v>
       </c>
       <c r="AG5">
-        <v>-0.0024249514036422341</v>
+        <v>1.3254611324652228e-05</v>
+      </c>
+      <c r="AH5">
+        <v>-8.3220067583281154e-07</v>
+      </c>
+      <c r="AI5">
+        <v>-0.0031909959915158394</v>
       </c>
     </row>
     <row r="6">
@@ -4419,100 +4873,106 @@
         <v>33</v>
       </c>
       <c r="B6">
-        <v>0.022640611421299608</v>
+        <v>0.075078818242933027</v>
       </c>
       <c r="C6">
-        <v>-1.5298460107365573e-05</v>
+        <v>-2.1957961697634844e-05</v>
       </c>
       <c r="D6">
-        <v>-4.7609444038821897e-06</v>
+        <v>-1.049610769144287e-05</v>
       </c>
       <c r="E6">
-        <v>4.9637533590616021e-08</v>
+        <v>1.1876124015754986e-07</v>
       </c>
       <c r="F6">
-        <v>0.0024858624394528467</v>
+        <v>0.003331974742639575</v>
       </c>
       <c r="G6">
-        <v>0.0027552631783213091</v>
+        <v>0.0036920244587947296</v>
       </c>
       <c r="H6">
-        <v>0.0025610166528776232</v>
+        <v>0.0034464926035572812</v>
       </c>
       <c r="I6">
-        <v>0.0025647591301565321</v>
+        <v>0.0034460096641565387</v>
       </c>
       <c r="J6">
-        <v>-7.9474593351957579e-06</v>
+        <v>-3.8075677654614542e-05</v>
       </c>
       <c r="K6">
-        <v>1.2494003102702088e-05</v>
+        <v>1.6986230532526804e-05</v>
       </c>
       <c r="L6">
-        <v>-4.2522590666086596e-06</v>
+        <v>-6.3799710366713535e-06</v>
       </c>
       <c r="M6">
-        <v>4.7714268274553096e-08</v>
+        <v>-2.4006494258163938e-05</v>
       </c>
       <c r="N6">
-        <v>9.601122841489129e-06</v>
+        <v>1.2710445295975419e-05</v>
       </c>
       <c r="O6">
-        <v>4.8722524336313475e-06</v>
+        <v>2.7578659373188319e-05</v>
       </c>
       <c r="P6">
-        <v>1.6045205627177083e-06</v>
+        <v>3.0300963965835246e-05</v>
       </c>
       <c r="Q6">
-        <v>4.9168630931017109e-05</v>
+        <v>0.00011240303205274291</v>
       </c>
       <c r="R6">
-        <v>3.9121108881171041e-05</v>
+        <v>0.00010714980149372465</v>
       </c>
       <c r="S6">
-        <v>4.5106865196108386e-05</v>
+        <v>0.00010556458696630135</v>
       </c>
       <c r="T6">
-        <v>6.2197105422482322e-05</v>
+        <v>7.074332874305346e-05</v>
       </c>
       <c r="U6">
-        <v>0.000101760397985971</v>
+        <v>0.0001212270011351161</v>
       </c>
       <c r="V6">
-        <v>8.7680816693028012e-05</v>
+        <v>7.4130549102363239e-05</v>
       </c>
       <c r="W6">
-        <v>7.5493809545012125e-06</v>
+        <v>2.933742301836893e-05</v>
       </c>
       <c r="X6">
-        <v>1.0432826523100718e-05</v>
+        <v>3.5010963706506772e-05</v>
       </c>
       <c r="Y6">
-        <v>8.1664137176609653e-05</v>
+        <v>0.00011082359073710498</v>
       </c>
       <c r="Z6">
-        <v>-2.5102434169491962e-05</v>
+        <v>-3.2237887984472476e-05</v>
       </c>
       <c r="AA6">
-        <v>-2.7779003373911088e-05</v>
+        <v>-3.3365374743733918e-05</v>
       </c>
       <c r="AB6">
-        <v>-2.4704014749193145e-05</v>
+        <v>-3.4721204415569468e-05</v>
       </c>
       <c r="AC6">
-        <v>-7.2821221714079645e-05</v>
+        <v>-9.5267496664021333e-05</v>
       </c>
       <c r="AD6">
-        <v>-1.4506514775377449e-05</v>
+        <v>-3.6770110894328648e-07</v>
       </c>
       <c r="AE6">
-        <v>-4.9130978743581392e-06</v>
+        <v>1.7840588211187744e-06</v>
       </c>
       <c r="AF6">
-        <v>-1.9204040409130673e-06</v>
+        <v>-4.9769320234327978e-06</v>
       </c>
       <c r="AG6">
-        <v>-0.0024963187450407738</v>
+        <v>2.3653988487843877e-05</v>
+      </c>
+      <c r="AH6">
+        <v>5.0810295743719102e-05</v>
+      </c>
+      <c r="AI6">
+        <v>-0.003270466191866302</v>
       </c>
     </row>
     <row r="7">
@@ -4520,302 +4980,320 @@
         <v>34</v>
       </c>
       <c r="B7">
-        <v>0.039952871423114392</v>
+        <v>0.09944830669733494</v>
       </c>
       <c r="C7">
-        <v>-4.2808229553902553e-06</v>
+        <v>-1.4483117365472833e-05</v>
       </c>
       <c r="D7">
-        <v>-7.9329939238223531e-06</v>
+        <v>-1.2277270060586291e-05</v>
       </c>
       <c r="E7">
-        <v>1.0129699688830441e-07</v>
+        <v>1.6483488710737124e-07</v>
       </c>
       <c r="F7">
-        <v>0.0024981933059437566</v>
+        <v>0.0033508516809490014</v>
       </c>
       <c r="G7">
-        <v>0.0025610166528776232</v>
+        <v>0.0034464926035572812</v>
       </c>
       <c r="H7">
-        <v>0.0027185615057805481</v>
+        <v>0.0036653828547718171</v>
       </c>
       <c r="I7">
-        <v>0.0026524611622677679</v>
+        <v>0.0035791111171026052</v>
       </c>
       <c r="J7">
-        <v>-1.6101206548960472e-05</v>
+        <v>-4.4592238851128528e-05</v>
       </c>
       <c r="K7">
-        <v>6.8715091231081563e-06</v>
+        <v>1.3464568744444205e-05</v>
       </c>
       <c r="L7">
-        <v>-2.4508328212608259e-06</v>
+        <v>-4.661062151143344e-06</v>
       </c>
       <c r="M7">
-        <v>7.4801339880340226e-06</v>
+        <v>-5.4427010099697242e-06</v>
       </c>
       <c r="N7">
-        <v>5.3468363539406244e-06</v>
+        <v>1.7016537144485373e-05</v>
       </c>
       <c r="O7">
-        <v>2.1096058993988801e-05</v>
+        <v>5.8140799589011683e-05</v>
       </c>
       <c r="P7">
-        <v>-1.0385885076641036e-05</v>
+        <v>-6.9123038476550216e-06</v>
       </c>
       <c r="Q7">
-        <v>7.3815426198823707e-05</v>
+        <v>0.00012205513947016397</v>
       </c>
       <c r="R7">
-        <v>4.8715742661558075e-05</v>
+        <v>9.5082755675074404e-05</v>
       </c>
       <c r="S7">
-        <v>4.0443525073821044e-05</v>
+        <v>7.4378963457746687e-05</v>
       </c>
       <c r="T7">
-        <v>1.8095212749575859e-05</v>
+        <v>6.3200722583111636e-05</v>
       </c>
       <c r="U7">
-        <v>0.00010180836593608428</v>
+        <v>0.0001504576395539274</v>
       </c>
       <c r="V7">
-        <v>4.3515158044219685e-05</v>
+        <v>6.15511025975745e-05</v>
       </c>
       <c r="W7">
-        <v>-9.1081904446003515e-06</v>
+        <v>1.1349132512395238e-05</v>
       </c>
       <c r="X7">
-        <v>7.7039305647939134e-06</v>
+        <v>2.826723158468286e-05</v>
       </c>
       <c r="Y7">
-        <v>0.00010051261800222392</v>
+        <v>0.00014103812543211003</v>
       </c>
       <c r="Z7">
-        <v>-7.3997089550669956e-05</v>
+        <v>-7.1696895795612167e-05</v>
       </c>
       <c r="AA7">
-        <v>-8.9198778641227635e-05</v>
+        <v>-8.9513114637770463e-05</v>
       </c>
       <c r="AB7">
-        <v>-8.7012589759390331e-05</v>
+        <v>-9.6464399529598956e-05</v>
       </c>
       <c r="AC7">
-        <v>-0.0001299171678492226</v>
+        <v>-0.00014677624567278631</v>
       </c>
       <c r="AD7">
-        <v>-6.1442403194493837e-05</v>
+        <v>-5.7995603966465303e-05</v>
       </c>
       <c r="AE7">
-        <v>-4.4432150647458278e-05</v>
+        <v>-4.1755144483655708e-05</v>
       </c>
       <c r="AF7">
-        <v>-1.8707608751687319e-06</v>
+        <v>-3.812822218944009e-06</v>
       </c>
       <c r="AG7">
-        <v>-0.0024842963424730052</v>
+        <v>-9.4182418717767002e-07</v>
+      </c>
+      <c r="AH7">
+        <v>1.1790754280966483e-05</v>
+      </c>
+      <c r="AI7">
+        <v>-0.003381134787782597</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B8">
-        <v>0.041356645977558108</v>
+        <v>0.10173563395839548</v>
       </c>
       <c r="C8">
-        <v>-4.625680081441417e-05</v>
+        <v>-6.721971269187937e-05</v>
       </c>
       <c r="D8">
-        <v>8.1183592218770902e-06</v>
+        <v>5.0313548365215613e-06</v>
       </c>
       <c r="E8">
-        <v>-2.2084939021040794e-08</v>
+        <v>3.1801700551144731e-08</v>
       </c>
       <c r="F8">
-        <v>0.0024902366818681408</v>
+        <v>0.0033348456927829056</v>
       </c>
       <c r="G8">
-        <v>0.0025647591301565321</v>
+        <v>0.0034460096641565387</v>
       </c>
       <c r="H8">
-        <v>0.0026524611622677679</v>
+        <v>0.0035791111171026052</v>
       </c>
       <c r="I8">
-        <v>0.0031002817989955996</v>
+        <v>0.0041393192982061922</v>
       </c>
       <c r="J8">
-        <v>-4.1798859174149152e-05</v>
+        <v>-0.00015800051402928067</v>
       </c>
       <c r="K8">
-        <v>1.7038615665442437e-06</v>
+        <v>6.5553985238626469e-06</v>
       </c>
       <c r="L8">
-        <v>-1.0334265039564832e-05</v>
+        <v>-1.7084432362418025e-05</v>
       </c>
       <c r="M8">
-        <v>2.3447892628289651e-05</v>
+        <v>8.2796029395649866e-05</v>
       </c>
       <c r="N8">
-        <v>4.1048973395538615e-05</v>
+        <v>6.0961084983034175e-05</v>
       </c>
       <c r="O8">
-        <v>3.9245238564457829e-05</v>
+        <v>0.00019340393619652913</v>
       </c>
       <c r="P8">
-        <v>-2.3651249507488585e-05</v>
+        <v>-0.00010385536595319497</v>
       </c>
       <c r="Q8">
-        <v>0.0001408563208576412</v>
+        <v>0.00022570642505646658</v>
       </c>
       <c r="R8">
-        <v>0.00013397533207149329</v>
+        <v>0.00022836685530649645</v>
       </c>
       <c r="S8">
-        <v>7.3717243789573218e-05</v>
+        <v>0.0001324128404685404</v>
       </c>
       <c r="T8">
-        <v>-7.7953591892699747e-05</v>
+        <v>-0.00012814723418749568</v>
       </c>
       <c r="U8">
-        <v>-4.5988627532732654e-05</v>
+        <v>-5.159543964531753e-05</v>
       </c>
       <c r="V8">
-        <v>-8.2820324649471311e-05</v>
+        <v>-0.00011983592278242523</v>
       </c>
       <c r="W8">
-        <v>-1.0276551325011395e-05</v>
+        <v>-1.2675792881725387e-07</v>
       </c>
       <c r="X8">
-        <v>4.7409652537944678e-05</v>
+        <v>7.4293942289223444e-05</v>
       </c>
       <c r="Y8">
-        <v>0.00010989618229234458</v>
+        <v>0.00013772907671989266</v>
       </c>
       <c r="Z8">
-        <v>1.4588222487678729e-05</v>
+        <v>-5.7447948003091359e-06</v>
       </c>
       <c r="AA8">
-        <v>-2.7344143241462854e-05</v>
+        <v>-5.5462795353136696e-05</v>
       </c>
       <c r="AB8">
-        <v>-3.5443741443949334e-05</v>
+        <v>-7.5872728060489116e-05</v>
       </c>
       <c r="AC8">
-        <v>-5.0452409494885792e-05</v>
+        <v>-9.1320964737238216e-05</v>
       </c>
       <c r="AD8">
-        <v>5.679111209082083e-05</v>
+        <v>4.7570217411091985e-05</v>
       </c>
       <c r="AE8">
-        <v>1.0067916064749119e-05</v>
+        <v>-1.0998181087716835e-05</v>
       </c>
       <c r="AF8">
-        <v>2.3481140046250883e-06</v>
+        <v>-1.5225029826202927e-06</v>
       </c>
       <c r="AG8">
-        <v>-0.0030329053243088669</v>
+        <v>0.00017677745986703283</v>
+      </c>
+      <c r="AH8">
+        <v>6.4729527955960983e-05</v>
+      </c>
+      <c r="AI8">
+        <v>-0.0039087046616684516</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B9">
-        <v>0.62539999132686031</v>
+        <v>1.5183111231000272</v>
       </c>
       <c r="C9">
-        <v>7.673705623548462e-06</v>
+        <v>4.1213408368018641e-05</v>
       </c>
       <c r="D9">
-        <v>-6.1481107264909062e-07</v>
+        <v>-4.5307554241174784e-06</v>
       </c>
       <c r="E9">
-        <v>4.1122901093325748e-09</v>
+        <v>3.9366403143661224e-08</v>
       </c>
       <c r="F9">
-        <v>9.5626898841416359e-06</v>
+        <v>5.4545645044529537e-06</v>
       </c>
       <c r="G9">
-        <v>-7.9474593351957579e-06</v>
+        <v>-3.8075677654614542e-05</v>
       </c>
       <c r="H9">
-        <v>-1.6101206548960472e-05</v>
+        <v>-4.4592238851128528e-05</v>
       </c>
       <c r="I9">
-        <v>-4.1798859174149152e-05</v>
+        <v>-0.00015800051402928067</v>
       </c>
       <c r="J9">
-        <v>7.6929278623924193e-05</v>
+        <v>0.00064210866217899898</v>
       </c>
       <c r="K9">
-        <v>-2.932310522463555e-06</v>
+        <v>-2.2350172380330125e-05</v>
       </c>
       <c r="L9">
-        <v>-1.008236735213733e-06</v>
+        <v>7.4984738807742944e-06</v>
       </c>
       <c r="M9">
-        <v>-6.4742447803613077e-05</v>
+        <v>-0.00045996963522548811</v>
       </c>
       <c r="N9">
-        <v>-3.225826560839141e-06</v>
+        <v>-2.2946718541055334e-05</v>
       </c>
       <c r="O9">
-        <v>-7.5867268212224915e-05</v>
+        <v>-0.00063948629735780839</v>
       </c>
       <c r="P9">
-        <v>6.3154889599536246e-05</v>
+        <v>0.00044001378139978126</v>
       </c>
       <c r="Q9">
-        <v>-4.6086554464684485e-05</v>
+        <v>-0.00028142695421273859</v>
       </c>
       <c r="R9">
-        <v>-4.5781852662590803e-05</v>
+        <v>-0.00028114959275801315</v>
       </c>
       <c r="S9">
-        <v>-4.4132819116729377e-05</v>
+        <v>-0.00024195772820361438</v>
       </c>
       <c r="T9">
-        <v>-1.6236028211765117e-05</v>
+        <v>-5.427711514046656e-05</v>
       </c>
       <c r="U9">
-        <v>-2.9049290787453615e-05</v>
+        <v>-8.684763448134892e-05</v>
       </c>
       <c r="V9">
-        <v>-2.9113971377562904e-05</v>
+        <v>-0.00011456626608425207</v>
       </c>
       <c r="W9">
-        <v>3.9206455833612448e-07</v>
+        <v>1.8842634774256128e-05</v>
       </c>
       <c r="X9">
-        <v>-1.8946519835451321e-05</v>
+        <v>-6.1086821669755975e-05</v>
       </c>
       <c r="Y9">
-        <v>-2.4925453487590297e-05</v>
+        <v>-6.0210898848725486e-05</v>
       </c>
       <c r="Z9">
-        <v>7.113626159366366e-06</v>
+        <v>8.5311790844845093e-06</v>
       </c>
       <c r="AA9">
-        <v>6.5266818568562961e-06</v>
+        <v>7.6920219427976225e-06</v>
       </c>
       <c r="AB9">
-        <v>1.6847673087838663e-06</v>
+        <v>-1.024119070579583e-05</v>
       </c>
       <c r="AC9">
-        <v>7.3527247910234905e-06</v>
+        <v>9.4274848582951993e-06</v>
       </c>
       <c r="AD9">
-        <v>-1.043391205122893e-05</v>
+        <v>-7.4113146721242862e-05</v>
       </c>
       <c r="AE9">
-        <v>7.9098447125638991e-06</v>
+        <v>-3.34843595512793e-06</v>
       </c>
       <c r="AF9">
-        <v>-1.5370353053766594e-06</v>
+        <v>-1.2766501460807108e-06</v>
       </c>
       <c r="AG9">
-        <v>0.00010027052921489057</v>
+        <v>-0.00016867270152082627</v>
+      </c>
+      <c r="AH9">
+        <v>-8.3141777482098215e-05</v>
+      </c>
+      <c r="AI9">
+        <v>0.00037117144109132753</v>
       </c>
     </row>
     <row r="10">
@@ -4823,100 +5301,106 @@
         <v>36</v>
       </c>
       <c r="B10">
-        <v>0.022697258873002099</v>
+        <v>0.019507095327876152</v>
       </c>
       <c r="C10">
-        <v>-1.5474481394921801e-05</v>
+        <v>-2.226764468905269e-05</v>
       </c>
       <c r="D10">
-        <v>-2.3805408801780891e-06</v>
+        <v>-3.0609639437874859e-06</v>
       </c>
       <c r="E10">
-        <v>5.3157982944807594e-09</v>
+        <v>6.937684904624332e-09</v>
       </c>
       <c r="F10">
-        <v>1.3152490895937884e-05</v>
+        <v>1.9796338654559292e-05</v>
       </c>
       <c r="G10">
-        <v>1.2494003102702088e-05</v>
+        <v>1.6986230532526804e-05</v>
       </c>
       <c r="H10">
-        <v>6.8715091231081563e-06</v>
+        <v>1.3464568744444205e-05</v>
       </c>
       <c r="I10">
-        <v>1.7038615665442437e-06</v>
+        <v>6.5553985238626469e-06</v>
       </c>
       <c r="J10">
-        <v>-2.932310522463555e-06</v>
+        <v>-2.2350172380330125e-05</v>
       </c>
       <c r="K10">
-        <v>0.00025070925440420961</v>
+        <v>0.00032887685903156271</v>
       </c>
       <c r="L10">
-        <v>-2.0030502121559094e-05</v>
+        <v>-2.4770403754243677e-05</v>
       </c>
       <c r="M10">
-        <v>-7.5187747691578787e-07</v>
+        <v>9.7229906533740165e-06</v>
       </c>
       <c r="N10">
-        <v>1.3760451635539978e-05</v>
+        <v>1.9103405061938144e-05</v>
       </c>
       <c r="O10">
-        <v>3.1596256065994852e-06</v>
+        <v>2.2991581508446522e-05</v>
       </c>
       <c r="P10">
-        <v>6.7808597837643253e-07</v>
+        <v>-8.8130101792035479e-06</v>
       </c>
       <c r="Q10">
-        <v>8.9025031551175473e-05</v>
+        <v>0.00011345800635159751</v>
       </c>
       <c r="R10">
-        <v>6.4639160226439662e-05</v>
+        <v>8.5593527860833296e-05</v>
       </c>
       <c r="S10">
-        <v>1.0556010034055508e-05</v>
+        <v>1.4060996713626765e-05</v>
       </c>
       <c r="T10">
-        <v>0.0018605517103708583</v>
+        <v>0.0024487103081431687</v>
       </c>
       <c r="U10">
-        <v>0.0018954827188694323</v>
+        <v>0.0024932705477126752</v>
       </c>
       <c r="V10">
-        <v>0.0019154924101912867</v>
+        <v>0.0025184652257739613</v>
       </c>
       <c r="W10">
-        <v>-2.0060586050050185e-05</v>
+        <v>-2.956393193700654e-05</v>
       </c>
       <c r="X10">
-        <v>6.3031171327357317e-06</v>
+        <v>1.522582992835868e-06</v>
       </c>
       <c r="Y10">
-        <v>5.3595193619314949e-05</v>
+        <v>4.4895728899750978e-05</v>
       </c>
       <c r="Z10">
-        <v>2.0529081635585478e-05</v>
+        <v>9.5288826796151305e-06</v>
       </c>
       <c r="AA10">
-        <v>2.8023596746982191e-06</v>
+        <v>-1.9570131783865075e-05</v>
       </c>
       <c r="AB10">
-        <v>-2.9381163177773142e-06</v>
+        <v>-2.6616656722436446e-05</v>
       </c>
       <c r="AC10">
-        <v>2.1275909058952858e-05</v>
+        <v>8.045076416849338e-06</v>
       </c>
       <c r="AD10">
-        <v>3.6484657821675859e-06</v>
+        <v>-1.6211091124791006e-05</v>
       </c>
       <c r="AE10">
-        <v>1.2841854113162447e-05</v>
+        <v>1.2277340705570843e-05</v>
       </c>
       <c r="AF10">
-        <v>1.114564633412457e-06</v>
+        <v>7.6871471711810675e-07</v>
       </c>
       <c r="AG10">
-        <v>-0.0018496775650005404</v>
+        <v>1.6656694351073042e-05</v>
+      </c>
+      <c r="AH10">
+        <v>3.2264897530520989e-05</v>
+      </c>
+      <c r="AI10">
+        <v>-0.002408534962640044</v>
       </c>
     </row>
     <row r="11">
@@ -4924,201 +5408,213 @@
         <v>37</v>
       </c>
       <c r="B11">
-        <v>0.0072378692847669835</v>
+        <v>0.0067365302942258513</v>
       </c>
       <c r="C11">
-        <v>-6.1491109097676031e-07</v>
+        <v>-5.8287437428686758e-07</v>
       </c>
       <c r="D11">
-        <v>-8.6606786674804546e-07</v>
+        <v>-6.4280215891314599e-07</v>
       </c>
       <c r="E11">
-        <v>9.5353104650458061e-09</v>
+        <v>8.3378763345040892e-09</v>
       </c>
       <c r="F11">
-        <v>-4.1695182500271283e-06</v>
+        <v>-5.7405188505130732e-06</v>
       </c>
       <c r="G11">
-        <v>-4.2522590666086596e-06</v>
+        <v>-6.3799710366713535e-06</v>
       </c>
       <c r="H11">
-        <v>-2.4508328212608259e-06</v>
+        <v>-4.661062151143344e-06</v>
       </c>
       <c r="I11">
-        <v>-1.0334265039564832e-05</v>
+        <v>-1.7084432362418025e-05</v>
       </c>
       <c r="J11">
-        <v>-1.008236735213733e-06</v>
+        <v>7.4984738807742944e-06</v>
       </c>
       <c r="K11">
-        <v>-2.0030502121559094e-05</v>
+        <v>-2.4770403754243677e-05</v>
       </c>
       <c r="L11">
-        <v>1.7300285242636376e-05</v>
+        <v>2.175116941829289e-05</v>
       </c>
       <c r="M11">
-        <v>1.9321673857553294e-06</v>
+        <v>-4.2656021039700153e-06</v>
       </c>
       <c r="N11">
-        <v>7.7830917832707825e-07</v>
+        <v>7.0522282635133661e-07</v>
       </c>
       <c r="O11">
-        <v>8.7532994417048158e-07</v>
+        <v>-8.5357450856608926e-06</v>
       </c>
       <c r="P11">
-        <v>-1.8309190480761078e-06</v>
+        <v>4.8322519843575747e-06</v>
       </c>
       <c r="Q11">
-        <v>-5.8565788806541657e-06</v>
+        <v>-9.1853752335519542e-06</v>
       </c>
       <c r="R11">
-        <v>-1.834383022346386e-05</v>
+        <v>-2.5537299756361466e-05</v>
       </c>
       <c r="S11">
-        <v>-6.7301486291642315e-06</v>
+        <v>-1.2851763871653474e-05</v>
       </c>
       <c r="T11">
-        <v>-4.1037722728565702e-05</v>
+        <v>-4.5785419642202534e-05</v>
       </c>
       <c r="U11">
-        <v>-4.866778028618133e-05</v>
+        <v>-6.2587876562417014e-05</v>
       </c>
       <c r="V11">
-        <v>-4.5567818225643035e-05</v>
+        <v>-5.4942421264625129e-05</v>
       </c>
       <c r="W11">
-        <v>1.4519148175705456e-07</v>
+        <v>3.9323988728646681e-07</v>
       </c>
       <c r="X11">
-        <v>3.3062321293020559e-06</v>
+        <v>2.8840996153256368e-06</v>
       </c>
       <c r="Y11">
-        <v>4.8908047596068295e-06</v>
+        <v>9.6987525820311322e-06</v>
       </c>
       <c r="Z11">
-        <v>-9.0823849218972318e-06</v>
+        <v>-6.0049578820980547e-06</v>
       </c>
       <c r="AA11">
-        <v>-1.1126898249002362e-05</v>
+        <v>-8.3258245848905986e-06</v>
       </c>
       <c r="AB11">
-        <v>-8.3157441435049803e-06</v>
+        <v>-4.5104831088476339e-06</v>
       </c>
       <c r="AC11">
-        <v>-9.9556821724918097e-06</v>
+        <v>-7.3148628605913319e-06</v>
       </c>
       <c r="AD11">
-        <v>-1.2031140510936847e-05</v>
+        <v>-1.1032005505418663e-05</v>
       </c>
       <c r="AE11">
-        <v>-8.7974991603492583e-06</v>
+        <v>-5.3927727825969897e-06</v>
       </c>
       <c r="AF11">
-        <v>-2.1870100858353579e-07</v>
+        <v>-2.8400275670942545e-07</v>
       </c>
       <c r="AG11">
-        <v>7.2099035883625066e-05</v>
+        <v>-4.7572744028242836e-06</v>
+      </c>
+      <c r="AH11">
+        <v>-7.4010554880799231e-06</v>
+      </c>
+      <c r="AI11">
+        <v>7.7037032292740965e-05</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B12">
-        <v>0.23628660407834953</v>
+        <v>0.65327016067453847</v>
       </c>
       <c r="C12">
-        <v>-4.3113017440064528e-06</v>
+        <v>-3.1723494920810533e-05</v>
       </c>
       <c r="D12">
-        <v>-2.7555205775670662e-07</v>
+        <v>1.6638624846267825e-06</v>
       </c>
       <c r="E12">
-        <v>1.8071073194478636e-09</v>
+        <v>-2.1655739911599938e-08</v>
       </c>
       <c r="F12">
-        <v>-1.6138216965445515e-05</v>
+        <v>-6.8646367053233843e-05</v>
       </c>
       <c r="G12">
-        <v>4.7714268274553096e-08</v>
+        <v>-2.4006494258163938e-05</v>
       </c>
       <c r="H12">
-        <v>7.4801339880340226e-06</v>
+        <v>-5.4427010099697242e-06</v>
       </c>
       <c r="I12">
-        <v>2.3447892628289651e-05</v>
+        <v>8.2796029395649866e-05</v>
       </c>
       <c r="J12">
-        <v>-6.4742447803613077e-05</v>
+        <v>-0.00045996963522548811</v>
       </c>
       <c r="K12">
-        <v>-7.5187747691578787e-07</v>
+        <v>9.7229906533740165e-06</v>
       </c>
       <c r="L12">
-        <v>1.9321673857553294e-06</v>
+        <v>-4.2656021039700153e-06</v>
       </c>
       <c r="M12">
-        <v>7.4984025355989849e-05</v>
+        <v>0.00063890354726480261</v>
       </c>
       <c r="N12">
-        <v>-2.6015459680644409e-07</v>
+        <v>8.9759368205663441e-06</v>
       </c>
       <c r="O12">
-        <v>6.3510283491509341e-05</v>
+        <v>0.00045450976423457522</v>
       </c>
       <c r="P12">
-        <v>-7.2918983784428604e-05</v>
+        <v>-0.00061150762929524315</v>
       </c>
       <c r="Q12">
-        <v>-3.0778834246309142e-05</v>
+        <v>-0.00019879542569420361</v>
       </c>
       <c r="R12">
-        <v>-3.2382250607231259e-05</v>
+        <v>-0.00018439082620359744</v>
       </c>
       <c r="S12">
-        <v>-3.2442179673281772e-05</v>
+        <v>-0.0002258836783469497</v>
       </c>
       <c r="T12">
-        <v>-2.595979210691195e-06</v>
+        <v>-4.0859574182594242e-05</v>
       </c>
       <c r="U12">
-        <v>7.4391143985481646e-06</v>
+        <v>1.5597952882382601e-05</v>
       </c>
       <c r="V12">
-        <v>4.5135328584244114e-06</v>
+        <v>3.051233833794083e-05</v>
       </c>
       <c r="W12">
-        <v>-1.8141988435718015e-06</v>
+        <v>-1.8682077194645524e-05</v>
       </c>
       <c r="X12">
-        <v>1.0476244968268607e-05</v>
+        <v>3.8780828261938898e-05</v>
       </c>
       <c r="Y12">
-        <v>-3.1247008213823618e-05</v>
+        <v>-0.00018981797359741528</v>
       </c>
       <c r="Z12">
-        <v>-9.9475852460585566e-06</v>
+        <v>-5.2738991774779885e-05</v>
       </c>
       <c r="AA12">
-        <v>-1.4895073867319593e-05</v>
+        <v>-8.1565824726875994e-05</v>
       </c>
       <c r="AB12">
-        <v>-1.7391891510250446e-05</v>
+        <v>-7.4531000168357822e-05</v>
       </c>
       <c r="AC12">
-        <v>-1.2703353865582253e-05</v>
+        <v>-6.6399652958953561e-05</v>
       </c>
       <c r="AD12">
-        <v>-1.0578123565384703e-05</v>
+        <v>-5.2142528327796093e-05</v>
       </c>
       <c r="AE12">
-        <v>-1.2087935056753014e-05</v>
+        <v>-5.4684359378744815e-05</v>
       </c>
       <c r="AF12">
-        <v>1.4554320829353008e-06</v>
+        <v>4.5341083384152171e-06</v>
       </c>
       <c r="AG12">
-        <v>-3.1354179638707811e-05</v>
+        <v>7.9370531799451678e-05</v>
+      </c>
+      <c r="AH12">
+        <v>5.013149121636935e-05</v>
+      </c>
+      <c r="AI12">
+        <v>-0.00010796927102515791</v>
       </c>
     </row>
     <row r="13">
@@ -5126,302 +5622,320 @@
         <v>39</v>
       </c>
       <c r="B13">
-        <v>0.046344716958013572</v>
+        <v>0.076266537637629681</v>
       </c>
       <c r="C13">
-        <v>-0.00024019820742180766</v>
+        <v>-0.00032721101553160996</v>
       </c>
       <c r="D13">
-        <v>8.1266654860760729e-08</v>
+        <v>1.6105749166989508e-06</v>
       </c>
       <c r="E13">
-        <v>-1.5654567780587191e-08</v>
+        <v>-3.5207519034754194e-08</v>
       </c>
       <c r="F13">
-        <v>-1.6269787054758731e-05</v>
+        <v>-2.2211741921381923e-05</v>
       </c>
       <c r="G13">
-        <v>9.601122841489129e-06</v>
+        <v>1.2710445295975419e-05</v>
       </c>
       <c r="H13">
-        <v>5.3468363539406244e-06</v>
+        <v>1.7016537144485373e-05</v>
       </c>
       <c r="I13">
-        <v>4.1048973395538615e-05</v>
+        <v>6.0961084983034175e-05</v>
       </c>
       <c r="J13">
-        <v>-3.225826560839141e-06</v>
+        <v>-2.2946718541055334e-05</v>
       </c>
       <c r="K13">
-        <v>1.3760451635539978e-05</v>
+        <v>1.9103405061938144e-05</v>
       </c>
       <c r="L13">
-        <v>7.7830917832707825e-07</v>
+        <v>7.0522282635133661e-07</v>
       </c>
       <c r="M13">
-        <v>-2.6015459680644409e-07</v>
+        <v>8.9759368205663441e-06</v>
       </c>
       <c r="N13">
-        <v>0.0053985998612576863</v>
+        <v>0.0074391994945310841</v>
       </c>
       <c r="O13">
-        <v>-0.00012742007941077315</v>
+        <v>0.00012093042132118714</v>
       </c>
       <c r="P13">
-        <v>0.00023518842262033521</v>
+        <v>0.00057843243999440694</v>
       </c>
       <c r="Q13">
-        <v>0.0029959590540514056</v>
+        <v>0.0044503371439920062</v>
       </c>
       <c r="R13">
-        <v>0.0029882236154351108</v>
+        <v>0.0044446210162897761</v>
       </c>
       <c r="S13">
-        <v>0.0029673587473815844</v>
+        <v>0.0044155113288065658</v>
       </c>
       <c r="T13">
-        <v>0.00014003549456308986</v>
+        <v>0.0001269330852393532</v>
       </c>
       <c r="U13">
-        <v>2.6630746857018647e-05</v>
+        <v>4.2134927435865614e-05</v>
       </c>
       <c r="V13">
-        <v>0.00013667950602798754</v>
+        <v>0.00019110709000858057</v>
       </c>
       <c r="W13">
-        <v>-3.2582206665644444e-05</v>
+        <v>-4.1771402812106916e-05</v>
       </c>
       <c r="X13">
-        <v>-9.9831334759697271e-06</v>
+        <v>1.1926379245470742e-07</v>
       </c>
       <c r="Y13">
-        <v>-9.894796143190593e-05</v>
+        <v>-0.00012504007718881338</v>
       </c>
       <c r="Z13">
-        <v>0.00012443407783389133</v>
+        <v>6.3903171694334451e-05</v>
       </c>
       <c r="AA13">
-        <v>0.00016002541178001314</v>
+        <v>0.00011456175015991151</v>
       </c>
       <c r="AB13">
-        <v>0.00019690878900844965</v>
+        <v>0.00013430757200705204</v>
       </c>
       <c r="AC13">
-        <v>0.00014719297904257009</v>
+        <v>9.8039917483482919e-05</v>
       </c>
       <c r="AD13">
-        <v>0.00012940082653870814</v>
+        <v>7.1475371197587522e-05</v>
       </c>
       <c r="AE13">
-        <v>0.00018590963167223012</v>
+        <v>0.00012324085976339047</v>
       </c>
       <c r="AF13">
-        <v>6.7391443724539919e-07</v>
+        <v>-1.6854814070528881e-06</v>
       </c>
       <c r="AG13">
-        <v>-0.0030707085921171592</v>
+        <v>6.7198161181713026e-05</v>
+      </c>
+      <c r="AH13">
+        <v>3.4162190225686239e-05</v>
+      </c>
+      <c r="AI13">
+        <v>-0.004452135442681469</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B14">
-        <v>-0.022004001322487473</v>
+        <v>-0.13691387330468932</v>
       </c>
       <c r="C14">
-        <v>-1.0288408450762515e-05</v>
+        <v>-5.2190345536982111e-05</v>
       </c>
       <c r="D14">
-        <v>1.3278797462765355e-07</v>
+        <v>4.7435608756717042e-06</v>
       </c>
       <c r="E14">
-        <v>8.3366516590246226e-10</v>
+        <v>-3.8195828957995975e-08</v>
       </c>
       <c r="F14">
-        <v>-9.8142529099163418e-06</v>
+        <v>-2.542835841340494e-06</v>
       </c>
       <c r="G14">
-        <v>4.8722524336313475e-06</v>
+        <v>2.7578659373188319e-05</v>
       </c>
       <c r="H14">
-        <v>2.1096058993988801e-05</v>
+        <v>5.8140799589011683e-05</v>
       </c>
       <c r="I14">
-        <v>3.9245238564457829e-05</v>
+        <v>0.00019340393619652913</v>
       </c>
       <c r="J14">
-        <v>-7.5867268212224915e-05</v>
+        <v>-0.00063948629735780839</v>
       </c>
       <c r="K14">
-        <v>3.1596256065994852e-06</v>
+        <v>2.2991581508446522e-05</v>
       </c>
       <c r="L14">
-        <v>8.7532994417048158e-07</v>
+        <v>-8.5357450856608926e-06</v>
       </c>
       <c r="M14">
-        <v>6.3510283491509341e-05</v>
+        <v>0.00045450976423457522</v>
       </c>
       <c r="N14">
-        <v>-0.00012742007941077315</v>
+        <v>0.00012093042132118714</v>
       </c>
       <c r="O14">
-        <v>0.0012557026596516439</v>
+        <v>0.010574454106923811</v>
       </c>
       <c r="P14">
-        <v>-0.0010175137244134932</v>
+        <v>-0.0074843242081282972</v>
       </c>
       <c r="Q14">
-        <v>0.00071743148755479161</v>
+        <v>0.003772712901295393</v>
       </c>
       <c r="R14">
-        <v>0.00071803700257074021</v>
+        <v>0.0037718232656827151</v>
       </c>
       <c r="S14">
-        <v>0.00071796054298879414</v>
+        <v>0.0037332183932664458</v>
       </c>
       <c r="T14">
-        <v>2.3166075228149151e-05</v>
+        <v>6.3569120295488822e-05</v>
       </c>
       <c r="U14">
-        <v>2.7198761180284147e-05</v>
+        <v>7.7539521417399929e-05</v>
       </c>
       <c r="V14">
-        <v>2.8145886120179494e-05</v>
+        <v>0.00010938102572210823</v>
       </c>
       <c r="W14">
-        <v>-1.6648805997233284e-06</v>
+        <v>-2.182191783004425e-05</v>
       </c>
       <c r="X14">
-        <v>1.7857557763969738e-05</v>
+        <v>6.1591036288373402e-05</v>
       </c>
       <c r="Y14">
-        <v>2.592070187650388e-05</v>
+        <v>6.0157633434816129e-05</v>
       </c>
       <c r="Z14">
-        <v>-4.111867761025581e-05</v>
+        <v>-0.00011543975939217192</v>
       </c>
       <c r="AA14">
-        <v>-3.6374920994950376e-05</v>
+        <v>-9.5444848122407241e-05</v>
       </c>
       <c r="AB14">
-        <v>-3.755046210642095e-05</v>
+        <v>-9.9987714929009334e-05</v>
       </c>
       <c r="AC14">
-        <v>-4.480835318752699e-05</v>
+        <v>-0.00012832431907419813</v>
       </c>
       <c r="AD14">
-        <v>-3.7254365094515377e-05</v>
+        <v>-4.7235486771416541e-05</v>
       </c>
       <c r="AE14">
-        <v>-4.3357434046430605e-05</v>
+        <v>-9.5000747710684023e-05</v>
       </c>
       <c r="AF14">
-        <v>2.2138589919915682e-07</v>
+        <v>-2.9715070134869425e-06</v>
       </c>
       <c r="AG14">
-        <v>-0.00070074022067162707</v>
+        <v>0.0001750698952145773</v>
+      </c>
+      <c r="AH14">
+        <v>0.00022189868718456023</v>
+      </c>
+      <c r="AI14">
+        <v>-0.0037005242288102864</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="B15">
-        <v>0.040890787183952212</v>
+        <v>0.042525396567240963</v>
       </c>
       <c r="C15">
-        <v>4.6918486669518108e-06</v>
+        <v>3.3053013638421755e-05</v>
       </c>
       <c r="D15">
-        <v>1.1797481650982711e-07</v>
+        <v>-2.2758995772888545e-06</v>
       </c>
       <c r="E15">
-        <v>-8.7617767856733949e-10</v>
+        <v>2.457048710279807e-08</v>
       </c>
       <c r="F15">
-        <v>1.5416105629659563e-05</v>
+        <v>6.2499291838728137e-05</v>
       </c>
       <c r="G15">
-        <v>1.6045205627177083e-06</v>
+        <v>3.0300963965835246e-05</v>
       </c>
       <c r="H15">
-        <v>-1.0385885076641036e-05</v>
+        <v>-6.9123038476550216e-06</v>
       </c>
       <c r="I15">
-        <v>-2.3651249507488585e-05</v>
+        <v>-0.00010385536595319497</v>
       </c>
       <c r="J15">
-        <v>6.3154889599536246e-05</v>
+        <v>0.00044001378139978126</v>
       </c>
       <c r="K15">
-        <v>6.7808597837643253e-07</v>
+        <v>-8.8130101792035479e-06</v>
       </c>
       <c r="L15">
-        <v>-1.8309190480761078e-06</v>
+        <v>4.8322519843575747e-06</v>
       </c>
       <c r="M15">
-        <v>-7.2918983784428604e-05</v>
+        <v>-0.00061150762929524315</v>
       </c>
       <c r="N15">
-        <v>0.00023518842262033521</v>
+        <v>0.00057843243999440694</v>
       </c>
       <c r="O15">
-        <v>-0.0010175137244134932</v>
+        <v>-0.0074843242081282972</v>
       </c>
       <c r="P15">
-        <v>0.0012270350749420797</v>
+        <v>0.0096880455925068675</v>
       </c>
       <c r="Q15">
-        <v>0.0010058804348796507</v>
+        <v>0.0034901810177060716</v>
       </c>
       <c r="R15">
-        <v>0.0010083390794696219</v>
+        <v>0.0034801524514338385</v>
       </c>
       <c r="S15">
-        <v>0.0010071662686694616</v>
+        <v>0.0035208298416822166</v>
       </c>
       <c r="T15">
-        <v>-2.2676424316012134e-05</v>
+        <v>-2.4394633965528793e-05</v>
       </c>
       <c r="U15">
-        <v>-7.1175939865589471e-06</v>
+        <v>-4.4100356099130694e-06</v>
       </c>
       <c r="V15">
-        <v>-4.649296344547279e-06</v>
+        <v>-1.8891590283882259e-05</v>
       </c>
       <c r="W15">
-        <v>1.6260607281493305e-06</v>
+        <v>1.8707009413747772e-05</v>
       </c>
       <c r="X15">
-        <v>-1.0304127086822201e-05</v>
+        <v>-3.9132342708521708e-05</v>
       </c>
       <c r="Y15">
-        <v>1.9935133595597968e-05</v>
+        <v>0.00015936702076296003</v>
       </c>
       <c r="Z15">
-        <v>3.0076837371328068e-05</v>
+        <v>8.6421126252416661e-05</v>
       </c>
       <c r="AA15">
-        <v>3.2413127683596731e-05</v>
+        <v>0.00010814157455045134</v>
       </c>
       <c r="AB15">
-        <v>3.6912521479181914e-05</v>
+        <v>8.854105528242098e-05</v>
       </c>
       <c r="AC15">
-        <v>3.3099817879172567e-05</v>
+        <v>0.00010920062210723416</v>
       </c>
       <c r="AD15">
-        <v>3.1536699458196743e-05</v>
+        <v>6.8460209244772773e-05</v>
       </c>
       <c r="AE15">
-        <v>2.8392876978894691e-05</v>
+        <v>5.8168987783405678e-05</v>
       </c>
       <c r="AF15">
-        <v>-1.6227347779727098e-06</v>
+        <v>-4.8550016487323321e-06</v>
       </c>
       <c r="AG15">
-        <v>-0.00095467605227211806</v>
+        <v>-4.5373912749079905e-05</v>
+      </c>
+      <c r="AH15">
+        <v>-0.00015097457733100018</v>
+      </c>
+      <c r="AI15">
+        <v>-0.0031854452860888309</v>
       </c>
     </row>
     <row r="16">
@@ -5429,100 +5943,106 @@
         <v>43</v>
       </c>
       <c r="B16">
-        <v>-0.03415828864287343</v>
+        <v>-0.27907468457175877</v>
       </c>
       <c r="C16">
-        <v>-0.00018588921021277688</v>
+        <v>-0.0002335383041085244</v>
       </c>
       <c r="D16">
-        <v>-2.1407780739264993e-05</v>
+        <v>-2.4673197894813532e-05</v>
       </c>
       <c r="E16">
-        <v>1.4119886020460961e-07</v>
+        <v>1.5643170299260902e-07</v>
       </c>
       <c r="F16">
-        <v>-1.1249784006980932e-05</v>
+        <v>3.4178594085720882e-05</v>
       </c>
       <c r="G16">
-        <v>4.9168630931017109e-05</v>
+        <v>0.00011240303205274291</v>
       </c>
       <c r="H16">
-        <v>7.3815426198823707e-05</v>
+        <v>0.00012205513947016397</v>
       </c>
       <c r="I16">
-        <v>0.0001408563208576412</v>
+        <v>0.00022570642505646658</v>
       </c>
       <c r="J16">
-        <v>-4.6086554464684485e-05</v>
+        <v>-0.00028142695421273859</v>
       </c>
       <c r="K16">
-        <v>8.9025031551175473e-05</v>
+        <v>0.00011345800635159751</v>
       </c>
       <c r="L16">
-        <v>-5.8565788806541657e-06</v>
+        <v>-9.1853752335519542e-06</v>
       </c>
       <c r="M16">
-        <v>-3.0778834246309142e-05</v>
+        <v>-0.00019879542569420361</v>
       </c>
       <c r="N16">
-        <v>0.0029959590540514056</v>
+        <v>0.0044503371439920062</v>
       </c>
       <c r="O16">
-        <v>0.00071743148755479161</v>
+        <v>0.003772712901295393</v>
       </c>
       <c r="P16">
-        <v>0.0010058804348796507</v>
+        <v>0.0034901810177060716</v>
       </c>
       <c r="Q16">
-        <v>0.011950211898996045</v>
+        <v>0.016758042712536586</v>
       </c>
       <c r="R16">
-        <v>0.011639968079113043</v>
+        <v>0.016323141568697592</v>
       </c>
       <c r="S16">
-        <v>0.011616885271847935</v>
+        <v>0.016302657286524705</v>
       </c>
       <c r="T16">
-        <v>0.0029829488542857442</v>
+        <v>0.0036031776442228642</v>
       </c>
       <c r="U16">
-        <v>0.00054507977568107706</v>
+        <v>0.00067996828917176746</v>
       </c>
       <c r="V16">
-        <v>0.00066306631186454279</v>
+        <v>0.0008445104196873538</v>
       </c>
       <c r="W16">
-        <v>-3.785896107794893e-05</v>
+        <v>-4.6238094873402381e-05</v>
       </c>
       <c r="X16">
-        <v>1.645607298874697e-05</v>
+        <v>2.9497718223016941e-05</v>
       </c>
       <c r="Y16">
-        <v>0.00011849889305156399</v>
+        <v>0.00021911050133918177</v>
       </c>
       <c r="Z16">
-        <v>7.8370239379261554e-05</v>
+        <v>-1.4042573154109811e-05</v>
       </c>
       <c r="AA16">
-        <v>0.00010370438898322371</v>
+        <v>4.6668522205139517e-05</v>
       </c>
       <c r="AB16">
-        <v>0.00016643072961185397</v>
+        <v>9.9448226390481693e-05</v>
       </c>
       <c r="AC16">
-        <v>4.4590480214139888e-05</v>
+        <v>-3.4255856849454633e-05</v>
       </c>
       <c r="AD16">
-        <v>0.00012793408227820694</v>
+        <v>6.6467335825516442e-05</v>
       </c>
       <c r="AE16">
-        <v>8.6163876814509015e-05</v>
+        <v>-5.7145689075200311e-07</v>
       </c>
       <c r="AF16">
-        <v>3.4382323716401623e-06</v>
+        <v>-4.2520489844773894e-06</v>
       </c>
       <c r="AG16">
-        <v>-0.011541645251482602</v>
+        <v>0.00031607126843852251</v>
+      </c>
+      <c r="AH16">
+        <v>0.00019648143661476526</v>
+      </c>
+      <c r="AI16">
+        <v>-0.015830166702359098</v>
       </c>
     </row>
     <row r="17">
@@ -5530,100 +6050,106 @@
         <v>44</v>
       </c>
       <c r="B17">
-        <v>-0.0024440366939254615</v>
+        <v>-0.21399226506175684</v>
       </c>
       <c r="C17">
-        <v>-0.00018033001386842074</v>
+        <v>-0.0002303058251058735</v>
       </c>
       <c r="D17">
-        <v>-2.9710612782519373e-05</v>
+        <v>-3.6716647217242154e-05</v>
       </c>
       <c r="E17">
-        <v>2.3314111540483845e-07</v>
+        <v>2.9063490963525747e-07</v>
       </c>
       <c r="F17">
-        <v>3.0418839046161047e-05</v>
+        <v>9.2978855768374204e-05</v>
       </c>
       <c r="G17">
-        <v>3.9121108881171041e-05</v>
+        <v>0.00010714980149372465</v>
       </c>
       <c r="H17">
-        <v>4.8715742661558075e-05</v>
+        <v>9.5082755675074404e-05</v>
       </c>
       <c r="I17">
-        <v>0.00013397533207149329</v>
+        <v>0.00022836685530649645</v>
       </c>
       <c r="J17">
-        <v>-4.5781852662590803e-05</v>
+        <v>-0.00028114959275801315</v>
       </c>
       <c r="K17">
-        <v>6.4639160226439662e-05</v>
+        <v>8.5593527860833296e-05</v>
       </c>
       <c r="L17">
-        <v>-1.834383022346386e-05</v>
+        <v>-2.5537299756361466e-05</v>
       </c>
       <c r="M17">
-        <v>-3.2382250607231259e-05</v>
+        <v>-0.00018439082620359744</v>
       </c>
       <c r="N17">
-        <v>0.0029882236154351108</v>
+        <v>0.0044446210162897761</v>
       </c>
       <c r="O17">
-        <v>0.00071803700257074021</v>
+        <v>0.0037718232656827151</v>
       </c>
       <c r="P17">
-        <v>0.0010083390794696219</v>
+        <v>0.0034801524514338385</v>
       </c>
       <c r="Q17">
-        <v>0.011639968079113043</v>
+        <v>0.016323141568697592</v>
       </c>
       <c r="R17">
-        <v>0.011837510872904335</v>
+        <v>0.016585533691270422</v>
       </c>
       <c r="S17">
-        <v>0.011526239557870951</v>
+        <v>0.016168166483734661</v>
       </c>
       <c r="T17">
-        <v>0.0025724603290250628</v>
+        <v>0.0031028692919028824</v>
       </c>
       <c r="U17">
-        <v>0.0003025909530322197</v>
+        <v>0.00040633665604698299</v>
       </c>
       <c r="V17">
-        <v>0.00040218269014782393</v>
+        <v>0.00052868522768988624</v>
       </c>
       <c r="W17">
-        <v>-5.0787013047568993e-05</v>
+        <v>-6.2072318204642253e-05</v>
       </c>
       <c r="X17">
-        <v>-1.5647959112147485e-05</v>
+        <v>-5.0913165239407747e-06</v>
       </c>
       <c r="Y17">
-        <v>5.1045829180399252e-06</v>
+        <v>8.2035876236467332e-05</v>
       </c>
       <c r="Z17">
-        <v>8.005698389369504e-05</v>
+        <v>9.9292650511473638e-06</v>
       </c>
       <c r="AA17">
-        <v>0.00011048888750356776</v>
+        <v>6.579859296115256e-05</v>
       </c>
       <c r="AB17">
-        <v>0.00014151696742741027</v>
+        <v>7.9745894430414922e-05</v>
       </c>
       <c r="AC17">
-        <v>6.8886509464106092e-05</v>
+        <v>1.0732254452152333e-05</v>
       </c>
       <c r="AD17">
-        <v>0.00013270359470377957</v>
+        <v>8.7401855542785893e-05</v>
       </c>
       <c r="AE17">
-        <v>0.00010845629984538121</v>
+        <v>3.5825910529381022e-05</v>
       </c>
       <c r="AF17">
-        <v>-2.5388167044774926e-07</v>
+        <v>-8.6593109527509067e-06</v>
       </c>
       <c r="AG17">
-        <v>-0.010890448498852215</v>
+        <v>0.00028715676090059969</v>
+      </c>
+      <c r="AH17">
+        <v>0.00018711060073023714</v>
+      </c>
+      <c r="AI17">
+        <v>-0.015025821244958616</v>
       </c>
     </row>
     <row r="18">
@@ -5631,100 +6157,106 @@
         <v>45</v>
       </c>
       <c r="B18">
-        <v>0.053612609893776461</v>
+        <v>-0.12513703312581384</v>
       </c>
       <c r="C18">
-        <v>-0.00015615417739911936</v>
+        <v>-0.00019378965804275452</v>
       </c>
       <c r="D18">
-        <v>-2.1951774781963339e-05</v>
+        <v>-2.7617825972556318e-05</v>
       </c>
       <c r="E18">
-        <v>1.8096306399121193e-07</v>
+        <v>2.294840276284424e-07</v>
       </c>
       <c r="F18">
-        <v>1.7181464922683912e-05</v>
+        <v>7.2527720131985041e-05</v>
       </c>
       <c r="G18">
-        <v>4.5106865196108386e-05</v>
+        <v>0.00010556458696630135</v>
       </c>
       <c r="H18">
-        <v>4.0443525073821044e-05</v>
+        <v>7.4378963457746687e-05</v>
       </c>
       <c r="I18">
-        <v>7.3717243789573218e-05</v>
+        <v>0.0001324128404685404</v>
       </c>
       <c r="J18">
-        <v>-4.4132819116729377e-05</v>
+        <v>-0.00024195772820361438</v>
       </c>
       <c r="K18">
-        <v>1.0556010034055508e-05</v>
+        <v>1.4060996713626765e-05</v>
       </c>
       <c r="L18">
-        <v>-6.7301486291642315e-06</v>
+        <v>-1.2851763871653474e-05</v>
       </c>
       <c r="M18">
-        <v>-3.2442179673281772e-05</v>
+        <v>-0.0002258836783469497</v>
       </c>
       <c r="N18">
-        <v>0.0029673587473815844</v>
+        <v>0.0044155113288065658</v>
       </c>
       <c r="O18">
-        <v>0.00071796054298879414</v>
+        <v>0.0037332183932664458</v>
       </c>
       <c r="P18">
-        <v>0.0010071662686694616</v>
+        <v>0.0035208298416822166</v>
       </c>
       <c r="Q18">
-        <v>0.011616885271847935</v>
+        <v>0.016302657286524705</v>
       </c>
       <c r="R18">
-        <v>0.011526239557870951</v>
+        <v>0.016168166483734661</v>
       </c>
       <c r="S18">
-        <v>0.011698243305008439</v>
+        <v>0.016411463768413431</v>
       </c>
       <c r="T18">
-        <v>0.0023784408503682002</v>
+        <v>0.002830381218431534</v>
       </c>
       <c r="U18">
-        <v>-3.0646796768570017e-06</v>
+        <v>-1.3807853405045645e-05</v>
       </c>
       <c r="V18">
-        <v>4.3199190173644469e-05</v>
+        <v>4.3320037314492762e-05</v>
       </c>
       <c r="W18">
-        <v>-5.7223854230534525e-05</v>
+        <v>-6.9648624537904256e-05</v>
       </c>
       <c r="X18">
-        <v>-1.5720243553254487e-05</v>
+        <v>-2.2127136224194943e-05</v>
       </c>
       <c r="Y18">
-        <v>0.00010042533029580841</v>
+        <v>0.0002056334237344401</v>
       </c>
       <c r="Z18">
-        <v>2.6445192924559081e-05</v>
+        <v>-1.6775914302801127e-05</v>
       </c>
       <c r="AA18">
-        <v>5.8156844814681932e-05</v>
+        <v>4.3098241443089141e-05</v>
       </c>
       <c r="AB18">
-        <v>9.47806128909481e-05</v>
+        <v>7.1132001372349076e-05</v>
       </c>
       <c r="AC18">
-        <v>1.7733500546512036e-05</v>
+        <v>-6.5461614596439011e-06</v>
       </c>
       <c r="AD18">
-        <v>7.3752860993755521e-05</v>
+        <v>5.932915766124116e-05</v>
       </c>
       <c r="AE18">
-        <v>5.5914348687922727e-05</v>
+        <v>1.7578409182146797e-05</v>
       </c>
       <c r="AF18">
-        <v>-3.7297443935173445e-06</v>
+        <v>-1.1463604557539225e-05</v>
       </c>
       <c r="AG18">
-        <v>-0.010699410321673423</v>
+        <v>0.00020059819423439221</v>
+      </c>
+      <c r="AH18">
+        <v>0.00014551465158310021</v>
+      </c>
+      <c r="AI18">
+        <v>-0.014774351112696028</v>
       </c>
     </row>
     <row r="19">
@@ -5732,100 +6264,106 @@
         <v>46</v>
       </c>
       <c r="B19">
-        <v>0.24152667921630172</v>
+        <v>0.30175223928742079</v>
       </c>
       <c r="C19">
-        <v>-0.00010149179620665957</v>
+        <v>-0.00011173905231292986</v>
       </c>
       <c r="D19">
-        <v>3.8033274340980888e-05</v>
+        <v>5.5278619335626046e-05</v>
       </c>
       <c r="E19">
-        <v>-3.6361981013645856e-07</v>
+        <v>-5.2139548909216559e-07</v>
       </c>
       <c r="F19">
-        <v>7.4266916942861833e-05</v>
+        <v>0.0001052124654547246</v>
       </c>
       <c r="G19">
-        <v>6.2197105422482322e-05</v>
+        <v>7.074332874305346e-05</v>
       </c>
       <c r="H19">
-        <v>1.8095212749575859e-05</v>
+        <v>6.3200722583111636e-05</v>
       </c>
       <c r="I19">
-        <v>-7.7953591892699747e-05</v>
+        <v>-0.00012814723418749568</v>
       </c>
       <c r="J19">
-        <v>-1.6236028211765117e-05</v>
+        <v>-5.427711514046656e-05</v>
       </c>
       <c r="K19">
-        <v>0.0018605517103708583</v>
+        <v>0.0024487103081431687</v>
       </c>
       <c r="L19">
-        <v>-4.1037722728565702e-05</v>
+        <v>-4.5785419642202534e-05</v>
       </c>
       <c r="M19">
-        <v>-2.595979210691195e-06</v>
+        <v>-4.0859574182594242e-05</v>
       </c>
       <c r="N19">
-        <v>0.00014003549456308986</v>
+        <v>0.0001269330852393532</v>
       </c>
       <c r="O19">
-        <v>2.3166075228149151e-05</v>
+        <v>6.3569120295488822e-05</v>
       </c>
       <c r="P19">
-        <v>-2.2676424316012134e-05</v>
+        <v>-2.4394633965528793e-05</v>
       </c>
       <c r="Q19">
-        <v>0.0029829488542857442</v>
+        <v>0.0036031776442228642</v>
       </c>
       <c r="R19">
-        <v>0.0025724603290250628</v>
+        <v>0.0031028692919028824</v>
       </c>
       <c r="S19">
-        <v>0.0023784408503682002</v>
+        <v>0.002830381218431534</v>
       </c>
       <c r="T19">
-        <v>0.017834473325615663</v>
+        <v>0.023335704424347504</v>
       </c>
       <c r="U19">
-        <v>0.014887615487547013</v>
+        <v>0.019628108190124963</v>
       </c>
       <c r="V19">
-        <v>0.014991669923725416</v>
+        <v>0.019757722921737629</v>
       </c>
       <c r="W19">
-        <v>6.0207210732806803e-05</v>
+        <v>2.1100730272364903e-05</v>
       </c>
       <c r="X19">
-        <v>8.2725801491395027e-05</v>
+        <v>1.2912768528288224e-05</v>
       </c>
       <c r="Y19">
-        <v>0.00068664896546850613</v>
+        <v>0.00072054389331477169</v>
       </c>
       <c r="Z19">
-        <v>8.5609147356592585e-05</v>
+        <v>-1.7703820299388301e-06</v>
       </c>
       <c r="AA19">
-        <v>-6.7232512064425987e-05</v>
+        <v>-0.0002391107342234371</v>
       </c>
       <c r="AB19">
-        <v>-7.5683183965416685e-05</v>
+        <v>-0.00023331829453876549</v>
       </c>
       <c r="AC19">
-        <v>5.8530405087612106e-05</v>
+        <v>-4.9629513844086891e-05</v>
       </c>
       <c r="AD19">
-        <v>-8.7427247758829676e-05</v>
+        <v>-0.00028632919040400863</v>
       </c>
       <c r="AE19">
-        <v>-7.8777702720571764e-05</v>
+        <v>-6.6982911648969141e-05</v>
       </c>
       <c r="AF19">
-        <v>2.8996886032412687e-06</v>
+        <v>-2.9561829437222678e-07</v>
       </c>
       <c r="AG19">
-        <v>-0.018521867812695998</v>
+        <v>-4.8286190883990721e-05</v>
+      </c>
+      <c r="AH19">
+        <v>0.00016431300235473373</v>
+      </c>
+      <c r="AI19">
+        <v>-0.024007797661731684</v>
       </c>
     </row>
     <row r="20">
@@ -5833,100 +6371,106 @@
         <v>47</v>
       </c>
       <c r="B20">
-        <v>0.25457763409553291</v>
+        <v>0.25746884824837424</v>
       </c>
       <c r="C20">
-        <v>-3.5238291414956995e-05</v>
+        <v>-6.1625668049730789e-05</v>
       </c>
       <c r="D20">
-        <v>-2.6751340245998614e-05</v>
+        <v>-2.9886890183150925e-05</v>
       </c>
       <c r="E20">
-        <v>1.0661295843582858e-07</v>
+        <v>1.0555085868033711e-07</v>
       </c>
       <c r="F20">
-        <v>8.8792500542317961e-05</v>
+        <v>0.00013217582648960798</v>
       </c>
       <c r="G20">
-        <v>0.000101760397985971</v>
+        <v>0.0001212270011351161</v>
       </c>
       <c r="H20">
-        <v>0.00010180836593608428</v>
+        <v>0.0001504576395539274</v>
       </c>
       <c r="I20">
-        <v>-4.5988627532732654e-05</v>
+        <v>-5.159543964531753e-05</v>
       </c>
       <c r="J20">
-        <v>-2.9049290787453615e-05</v>
+        <v>-8.684763448134892e-05</v>
       </c>
       <c r="K20">
-        <v>0.0018954827188694323</v>
+        <v>0.0024932705477126752</v>
       </c>
       <c r="L20">
-        <v>-4.866778028618133e-05</v>
+        <v>-6.2587876562417014e-05</v>
       </c>
       <c r="M20">
-        <v>7.4391143985481646e-06</v>
+        <v>1.5597952882382601e-05</v>
       </c>
       <c r="N20">
-        <v>2.6630746857018647e-05</v>
+        <v>4.2134927435865614e-05</v>
       </c>
       <c r="O20">
-        <v>2.7198761180284147e-05</v>
+        <v>7.7539521417399929e-05</v>
       </c>
       <c r="P20">
-        <v>-7.1175939865589471e-06</v>
+        <v>-4.4100356099130694e-06</v>
       </c>
       <c r="Q20">
-        <v>0.00054507977568107706</v>
+        <v>0.00067996828917176746</v>
       </c>
       <c r="R20">
-        <v>0.0003025909530322197</v>
+        <v>0.00040633665604698299</v>
       </c>
       <c r="S20">
-        <v>-3.0646796768570017e-06</v>
+        <v>-1.3807853405045645e-05</v>
       </c>
       <c r="T20">
-        <v>0.014887615487547013</v>
+        <v>0.019628108190124963</v>
       </c>
       <c r="U20">
-        <v>0.015498240896026132</v>
+        <v>0.020330161876498044</v>
       </c>
       <c r="V20">
-        <v>0.01544547620080625</v>
+        <v>0.020263020209561857</v>
       </c>
       <c r="W20">
-        <v>-7.6738343130027344e-05</v>
+        <v>-0.00013911405428177116</v>
       </c>
       <c r="X20">
-        <v>7.9709506529911621e-05</v>
+        <v>2.0679287143843435e-05</v>
       </c>
       <c r="Y20">
-        <v>0.00056641884096285833</v>
+        <v>0.00051600613871761233</v>
       </c>
       <c r="Z20">
-        <v>0.00017904404506962658</v>
+        <v>6.6596775726588363e-05</v>
       </c>
       <c r="AA20">
-        <v>4.0388758760768334e-05</v>
+        <v>-0.0001612216177934913</v>
       </c>
       <c r="AB20">
-        <v>-4.5198774517446472e-06</v>
+        <v>-0.000213103502907863</v>
       </c>
       <c r="AC20">
-        <v>0.00018975146506003231</v>
+        <v>5.6877917379005542e-05</v>
       </c>
       <c r="AD20">
-        <v>1.1739242101864358e-05</v>
+        <v>-0.00019822358007756495</v>
       </c>
       <c r="AE20">
-        <v>9.4348963746079643e-05</v>
+        <v>6.8994809937670707e-05</v>
       </c>
       <c r="AF20">
-        <v>8.7478830651788718e-06</v>
+        <v>6.434105305371939e-06</v>
       </c>
       <c r="AG20">
-        <v>-0.014676313792467369</v>
+        <v>3.5529327898728424e-05</v>
+      </c>
+      <c r="AH20">
+        <v>0.00016931722591211236</v>
+      </c>
+      <c r="AI20">
+        <v>-0.019144972698791899</v>
       </c>
     </row>
     <row r="21">
@@ -5934,100 +6478,106 @@
         <v>48</v>
       </c>
       <c r="B21">
-        <v>0.29290071033697601</v>
+        <v>0.31264245698831505</v>
       </c>
       <c r="C21">
-        <v>-0.00014666270436385764</v>
+        <v>-0.00021239483960761732</v>
       </c>
       <c r="D21">
-        <v>-1.0460529573620136e-05</v>
+        <v>-4.4623759993101366e-06</v>
       </c>
       <c r="E21">
-        <v>-1.6168915785791999e-07</v>
+        <v>-2.9672922183350712e-07</v>
       </c>
       <c r="F21">
-        <v>4.6188856845626094e-05</v>
+        <v>3.4050800023753395e-05</v>
       </c>
       <c r="G21">
-        <v>8.7680816693028012e-05</v>
+        <v>7.4130549102363239e-05</v>
       </c>
       <c r="H21">
-        <v>4.3515158044219685e-05</v>
+        <v>6.15511025975745e-05</v>
       </c>
       <c r="I21">
-        <v>-8.2820324649471311e-05</v>
+        <v>-0.00011983592278242523</v>
       </c>
       <c r="J21">
-        <v>-2.9113971377562904e-05</v>
+        <v>-0.00011456626608425207</v>
       </c>
       <c r="K21">
-        <v>0.0019154924101912867</v>
+        <v>0.0025184652257739613</v>
       </c>
       <c r="L21">
-        <v>-4.5567818225643035e-05</v>
+        <v>-5.4942421264625129e-05</v>
       </c>
       <c r="M21">
-        <v>4.5135328584244114e-06</v>
+        <v>3.051233833794083e-05</v>
       </c>
       <c r="N21">
-        <v>0.00013667950602798754</v>
+        <v>0.00019110709000858057</v>
       </c>
       <c r="O21">
-        <v>2.8145886120179494e-05</v>
+        <v>0.00010938102572210823</v>
       </c>
       <c r="P21">
-        <v>-4.649296344547279e-06</v>
+        <v>-1.8891590283882259e-05</v>
       </c>
       <c r="Q21">
-        <v>0.00066306631186454279</v>
+        <v>0.0008445104196873538</v>
       </c>
       <c r="R21">
-        <v>0.00040218269014782393</v>
+        <v>0.00052868522768988624</v>
       </c>
       <c r="S21">
-        <v>4.3199190173644469e-05</v>
+        <v>4.3320037314492762e-05</v>
       </c>
       <c r="T21">
-        <v>0.014991669923725416</v>
+        <v>0.019757722921737629</v>
       </c>
       <c r="U21">
-        <v>0.01544547620080625</v>
+        <v>0.020263020209561857</v>
       </c>
       <c r="V21">
-        <v>0.016182635129747183</v>
+        <v>0.021314650250681227</v>
       </c>
       <c r="W21">
-        <v>-0.00011340972255222169</v>
+        <v>-0.00017066564095262157</v>
       </c>
       <c r="X21">
-        <v>4.7857481138262152e-05</v>
+        <v>1.6094479887793483e-05</v>
       </c>
       <c r="Y21">
-        <v>0.00052358466533746276</v>
+        <v>0.00048255718139797454</v>
       </c>
       <c r="Z21">
-        <v>0.00019498703200088521</v>
+        <v>3.234588801504304e-05</v>
       </c>
       <c r="AA21">
-        <v>6.9679719341041169e-05</v>
+        <v>-0.00019776480947328486</v>
       </c>
       <c r="AB21">
-        <v>3.561173431261425e-05</v>
+        <v>-0.000228015592020864</v>
       </c>
       <c r="AC21">
-        <v>0.0002295639778916083</v>
+        <v>5.064178824815916e-05</v>
       </c>
       <c r="AD21">
-        <v>3.2942630155763288e-05</v>
+        <v>-0.00022346204295744382</v>
       </c>
       <c r="AE21">
-        <v>0.00013364260780112107</v>
+        <v>6.0863052053493219e-05</v>
       </c>
       <c r="AF21">
-        <v>9.7024294156043895e-06</v>
+        <v>6.5462480586167397e-06</v>
       </c>
       <c r="AG21">
-        <v>-0.014979031873911988</v>
+        <v>0.00010284722603032259</v>
+      </c>
+      <c r="AH21">
+        <v>0.00021353528251407371</v>
+      </c>
+      <c r="AI21">
+        <v>-0.019555278136735209</v>
       </c>
     </row>
     <row r="22">
@@ -6035,100 +6585,106 @@
         <v>49</v>
       </c>
       <c r="B22">
-        <v>-0.0050669037175389755</v>
+        <v>0.0054815085061861984</v>
       </c>
       <c r="C22">
-        <v>2.8452502558465828e-05</v>
+        <v>3.9564821483017843e-05</v>
       </c>
       <c r="D22">
-        <v>1.0216310574711063e-05</v>
+        <v>8.9429306130692885e-06</v>
       </c>
       <c r="E22">
-        <v>-4.7657272907616299e-08</v>
+        <v>-2.5885828971758204e-08</v>
       </c>
       <c r="F22">
-        <v>-2.2435390006407253e-05</v>
+        <v>2.3762492316839416e-06</v>
       </c>
       <c r="G22">
-        <v>7.5493809545012125e-06</v>
+        <v>2.933742301836893e-05</v>
       </c>
       <c r="H22">
-        <v>-9.1081904446003515e-06</v>
+        <v>1.1349132512395238e-05</v>
       </c>
       <c r="I22">
-        <v>-1.0276551325011395e-05</v>
+        <v>-1.2675792881725387e-07</v>
       </c>
       <c r="J22">
-        <v>3.9206455833612448e-07</v>
+        <v>1.8842634774256128e-05</v>
       </c>
       <c r="K22">
-        <v>-2.0060586050050185e-05</v>
+        <v>-2.956393193700654e-05</v>
       </c>
       <c r="L22">
-        <v>1.4519148175705456e-07</v>
+        <v>3.9323988728646681e-07</v>
       </c>
       <c r="M22">
-        <v>-1.8141988435718015e-06</v>
+        <v>-1.8682077194645524e-05</v>
       </c>
       <c r="N22">
-        <v>-3.2582206665644444e-05</v>
+        <v>-4.1771402812106916e-05</v>
       </c>
       <c r="O22">
-        <v>-1.6648805997233284e-06</v>
+        <v>-2.182191783004425e-05</v>
       </c>
       <c r="P22">
-        <v>1.6260607281493305e-06</v>
+        <v>1.8707009413747772e-05</v>
       </c>
       <c r="Q22">
-        <v>-3.785896107794893e-05</v>
+        <v>-4.6238094873402381e-05</v>
       </c>
       <c r="R22">
-        <v>-5.0787013047568993e-05</v>
+        <v>-6.2072318204642253e-05</v>
       </c>
       <c r="S22">
-        <v>-5.7223854230534525e-05</v>
+        <v>-6.9648624537904256e-05</v>
       </c>
       <c r="T22">
-        <v>6.0207210732806803e-05</v>
+        <v>2.1100730272364903e-05</v>
       </c>
       <c r="U22">
-        <v>-7.6738343130027344e-05</v>
+        <v>-0.00013911405428177116</v>
       </c>
       <c r="V22">
-        <v>-0.00011340972255222169</v>
+        <v>-0.00017066564095262157</v>
       </c>
       <c r="W22">
-        <v>0.00047622575856370912</v>
+        <v>0.00063084839585771145</v>
       </c>
       <c r="X22">
-        <v>0.0001645760360801522</v>
+        <v>0.00020733605832726429</v>
       </c>
       <c r="Y22">
-        <v>0.00024735304098880042</v>
+        <v>0.00031608076664480216</v>
       </c>
       <c r="Z22">
-        <v>1.1046440640983434e-05</v>
+        <v>-3.0080707959581621e-07</v>
       </c>
       <c r="AA22">
-        <v>2.5488095709870473e-06</v>
+        <v>-1.2805140901900563e-05</v>
       </c>
       <c r="AB22">
-        <v>1.5095500511921934e-05</v>
+        <v>1.2864131794275286e-06</v>
       </c>
       <c r="AC22">
-        <v>8.4272525953695536e-06</v>
+        <v>-6.3322716246603925e-06</v>
       </c>
       <c r="AD22">
-        <v>1.9232827080719784e-05</v>
+        <v>7.5633144020334964e-06</v>
       </c>
       <c r="AE22">
-        <v>-4.6446445691187226e-05</v>
+        <v>-4.9954516738316636e-05</v>
       </c>
       <c r="AF22">
-        <v>5.912035099158284e-08</v>
+        <v>2.6429877657229862e-07</v>
       </c>
       <c r="AG22">
-        <v>-0.00041274289625724552</v>
+        <v>3.383842085780478e-05</v>
+      </c>
+      <c r="AH22">
+        <v>-1.1683104600936545e-05</v>
+      </c>
+      <c r="AI22">
+        <v>-0.00041100116851545585</v>
       </c>
     </row>
     <row r="23">
@@ -6136,100 +6692,106 @@
         <v>50</v>
       </c>
       <c r="B23">
-        <v>0.041333434976749295</v>
+        <v>0.075606241716321951</v>
       </c>
       <c r="C23">
-        <v>6.5652393812434846e-06</v>
+        <v>-8.9443228905280233e-07</v>
       </c>
       <c r="D23">
-        <v>2.6522687314115122e-05</v>
+        <v>3.4881524734780984e-05</v>
       </c>
       <c r="E23">
-        <v>-2.0691183931877857e-07</v>
+        <v>-2.8117749342473678e-07</v>
       </c>
       <c r="F23">
-        <v>-3.2441540281280242e-05</v>
+        <v>-1.119198441620786e-05</v>
       </c>
       <c r="G23">
-        <v>1.0432826523100718e-05</v>
+        <v>3.5010963706506772e-05</v>
       </c>
       <c r="H23">
-        <v>7.7039305647939134e-06</v>
+        <v>2.826723158468286e-05</v>
       </c>
       <c r="I23">
-        <v>4.7409652537944678e-05</v>
+        <v>7.4293942289223444e-05</v>
       </c>
       <c r="J23">
-        <v>-1.8946519835451321e-05</v>
+        <v>-6.1086821669755975e-05</v>
       </c>
       <c r="K23">
-        <v>6.3031171327357317e-06</v>
+        <v>1.522582992835868e-06</v>
       </c>
       <c r="L23">
-        <v>3.3062321293020559e-06</v>
+        <v>2.8840996153256368e-06</v>
       </c>
       <c r="M23">
-        <v>1.0476244968268607e-05</v>
+        <v>3.8780828261938898e-05</v>
       </c>
       <c r="N23">
-        <v>-9.9831334759697271e-06</v>
+        <v>1.1926379245470742e-07</v>
       </c>
       <c r="O23">
-        <v>1.7857557763969738e-05</v>
+        <v>6.1591036288373402e-05</v>
       </c>
       <c r="P23">
-        <v>-1.0304127086822201e-05</v>
+        <v>-3.9132342708521708e-05</v>
       </c>
       <c r="Q23">
-        <v>1.645607298874697e-05</v>
+        <v>2.9497718223016941e-05</v>
       </c>
       <c r="R23">
-        <v>-1.5647959112147485e-05</v>
+        <v>-5.0913165239407747e-06</v>
       </c>
       <c r="S23">
-        <v>-1.5720243553254487e-05</v>
+        <v>-2.2127136224194943e-05</v>
       </c>
       <c r="T23">
-        <v>8.2725801491395027e-05</v>
+        <v>1.2912768528288224e-05</v>
       </c>
       <c r="U23">
-        <v>7.9709506529911621e-05</v>
+        <v>2.0679287143843435e-05</v>
       </c>
       <c r="V23">
-        <v>4.7857481138262152e-05</v>
+        <v>1.6094479887793483e-05</v>
       </c>
       <c r="W23">
-        <v>0.0001645760360801522</v>
+        <v>0.00020733605832726429</v>
       </c>
       <c r="X23">
-        <v>0.0003990050599759113</v>
+        <v>0.00053786741536874085</v>
       </c>
       <c r="Y23">
-        <v>0.00018317449458446115</v>
+        <v>0.00022308529666843194</v>
       </c>
       <c r="Z23">
-        <v>-1.2757695637534731e-05</v>
+        <v>9.9461068469423614e-06</v>
       </c>
       <c r="AA23">
-        <v>-1.3153728805381944e-05</v>
+        <v>1.5265079848251746e-05</v>
       </c>
       <c r="AB23">
-        <v>-2.3117710078388574e-07</v>
+        <v>2.4269044024923377e-05</v>
       </c>
       <c r="AC23">
-        <v>-3.0538695615703586e-06</v>
+        <v>1.8885996400031121e-05</v>
       </c>
       <c r="AD23">
-        <v>2.2398552687026541e-05</v>
+        <v>5.9731947545477453e-05</v>
       </c>
       <c r="AE23">
-        <v>-2.6679733562360656e-05</v>
+        <v>1.2268955093169197e-05</v>
       </c>
       <c r="AF23">
-        <v>9.721238783416431e-07</v>
+        <v>-1.2264595303643813e-07</v>
       </c>
       <c r="AG23">
-        <v>-0.0010035270209452747</v>
+        <v>0.00011583449999951964</v>
+      </c>
+      <c r="AH23">
+        <v>1.5224501182161082e-05</v>
+      </c>
+      <c r="AI23">
+        <v>-0.0012675766661341425</v>
       </c>
     </row>
     <row r="24">
@@ -6237,100 +6799,106 @@
         <v>51</v>
       </c>
       <c r="B24">
-        <v>0.19741793888614137</v>
+        <v>0.58030121769813392</v>
       </c>
       <c r="C24">
-        <v>0.000102507548319959</v>
+        <v>0.00013778405085550639</v>
       </c>
       <c r="D24">
-        <v>1.0112087376620995e-05</v>
+        <v>1.0546391990252503e-05</v>
       </c>
       <c r="E24">
-        <v>-3.8040347883048606e-08</v>
+        <v>-1.9302764471890355e-08</v>
       </c>
       <c r="F24">
-        <v>3.1618796387728734e-05</v>
+        <v>5.7622309281317365e-05</v>
       </c>
       <c r="G24">
-        <v>8.1664137176609653e-05</v>
+        <v>0.00011082359073710498</v>
       </c>
       <c r="H24">
-        <v>0.00010051261800222392</v>
+        <v>0.00014103812543211003</v>
       </c>
       <c r="I24">
-        <v>0.00010989618229234458</v>
+        <v>0.00013772907671989266</v>
       </c>
       <c r="J24">
-        <v>-2.4925453487590297e-05</v>
+        <v>-6.0210898848725486e-05</v>
       </c>
       <c r="K24">
-        <v>5.3595193619314949e-05</v>
+        <v>4.4895728899750978e-05</v>
       </c>
       <c r="L24">
-        <v>4.8908047596068295e-06</v>
+        <v>9.6987525820311322e-06</v>
       </c>
       <c r="M24">
-        <v>-3.1247008213823618e-05</v>
+        <v>-0.00018981797359741528</v>
       </c>
       <c r="N24">
-        <v>-9.894796143190593e-05</v>
+        <v>-0.00012504007718881338</v>
       </c>
       <c r="O24">
-        <v>2.592070187650388e-05</v>
+        <v>6.0157633434816129e-05</v>
       </c>
       <c r="P24">
-        <v>1.9935133595597968e-05</v>
+        <v>0.00015936702076296003</v>
       </c>
       <c r="Q24">
-        <v>0.00011849889305156399</v>
+        <v>0.00021911050133918177</v>
       </c>
       <c r="R24">
-        <v>5.1045829180399252e-06</v>
+        <v>8.2035876236467332e-05</v>
       </c>
       <c r="S24">
-        <v>0.00010042533029580841</v>
+        <v>0.0002056334237344401</v>
       </c>
       <c r="T24">
-        <v>0.00068664896546850613</v>
+        <v>0.00072054389331477169</v>
       </c>
       <c r="U24">
-        <v>0.00056641884096285833</v>
+        <v>0.00051600613871761233</v>
       </c>
       <c r="V24">
-        <v>0.00052358466533746276</v>
+        <v>0.00048255718139797454</v>
       </c>
       <c r="W24">
-        <v>0.00024735304098880042</v>
+        <v>0.00031608076664480216</v>
       </c>
       <c r="X24">
-        <v>0.00018317449458446115</v>
+        <v>0.00022308529666843194</v>
       </c>
       <c r="Y24">
-        <v>0.0034212038441354129</v>
+        <v>0.0049127713774817644</v>
       </c>
       <c r="Z24">
-        <v>1.0044551303252304e-05</v>
+        <v>4.544531451682553e-05</v>
       </c>
       <c r="AA24">
-        <v>3.0398733317869105e-05</v>
+        <v>6.0082731177777028e-05</v>
       </c>
       <c r="AB24">
-        <v>5.7202697432759371e-05</v>
+        <v>9.2823550993128756e-05</v>
       </c>
       <c r="AC24">
-        <v>8.0919534755876017e-06</v>
+        <v>3.3394181581054242e-05</v>
       </c>
       <c r="AD24">
-        <v>5.0059007667118896e-05</v>
+        <v>9.2201178753770717e-05</v>
       </c>
       <c r="AE24">
-        <v>-5.4425320463299819e-05</v>
+        <v>-2.3088192576370845e-05</v>
       </c>
       <c r="AF24">
-        <v>-3.5096290110600916e-06</v>
+        <v>-9.1016462402966812e-06</v>
       </c>
       <c r="AG24">
-        <v>-0.0011215853421955352</v>
+        <v>7.3739496584565752e-05</v>
+      </c>
+      <c r="AH24">
+        <v>1.185222418444978e-05</v>
+      </c>
+      <c r="AI24">
+        <v>-0.0011978237530955954</v>
       </c>
     </row>
     <row r="25">
@@ -6338,100 +6906,106 @@
         <v>52</v>
       </c>
       <c r="B25">
-        <v>-0.10137318234779459</v>
+        <v>-0.17691015112612518</v>
       </c>
       <c r="C25">
-        <v>-8.877803668276503e-06</v>
+        <v>5.7221913230602833e-06</v>
       </c>
       <c r="D25">
-        <v>1.156960100076414e-06</v>
+        <v>-3.5955745998582085e-07</v>
       </c>
       <c r="E25">
-        <v>-3.7501710989713656e-08</v>
+        <v>-5.5699364489547746e-09</v>
       </c>
       <c r="F25">
-        <v>-5.0134462642295857e-05</v>
+        <v>-5.5970222525287064e-05</v>
       </c>
       <c r="G25">
-        <v>-2.5102434169491962e-05</v>
+        <v>-3.2237887984472476e-05</v>
       </c>
       <c r="H25">
-        <v>-7.3997089550669956e-05</v>
+        <v>-7.1696895795612167e-05</v>
       </c>
       <c r="I25">
-        <v>1.4588222487678729e-05</v>
+        <v>-5.7447948003091359e-06</v>
       </c>
       <c r="J25">
-        <v>7.113626159366366e-06</v>
+        <v>8.5311790844845093e-06</v>
       </c>
       <c r="K25">
-        <v>2.0529081635585478e-05</v>
+        <v>9.5288826796151305e-06</v>
       </c>
       <c r="L25">
-        <v>-9.0823849218972318e-06</v>
+        <v>-6.0049578820980547e-06</v>
       </c>
       <c r="M25">
-        <v>-9.9475852460585566e-06</v>
+        <v>-5.2738991774779885e-05</v>
       </c>
       <c r="N25">
-        <v>0.00012443407783389133</v>
+        <v>6.3903171694334451e-05</v>
       </c>
       <c r="O25">
-        <v>-4.111867761025581e-05</v>
+        <v>-0.00011543975939217192</v>
       </c>
       <c r="P25">
-        <v>3.0076837371328068e-05</v>
+        <v>8.6421126252416661e-05</v>
       </c>
       <c r="Q25">
-        <v>7.8370239379261554e-05</v>
+        <v>-1.4042573154109811e-05</v>
       </c>
       <c r="R25">
-        <v>8.005698389369504e-05</v>
+        <v>9.9292650511473638e-06</v>
       </c>
       <c r="S25">
-        <v>2.6445192924559081e-05</v>
+        <v>-1.6775914302801127e-05</v>
       </c>
       <c r="T25">
-        <v>8.5609147356592585e-05</v>
+        <v>-1.7703820299388301e-06</v>
       </c>
       <c r="U25">
-        <v>0.00017904404506962658</v>
+        <v>6.6596775726588363e-05</v>
       </c>
       <c r="V25">
-        <v>0.00019498703200088521</v>
+        <v>3.234588801504304e-05</v>
       </c>
       <c r="W25">
-        <v>1.1046440640983434e-05</v>
+        <v>-3.0080707959581621e-07</v>
       </c>
       <c r="X25">
-        <v>-1.2757695637534731e-05</v>
+        <v>9.9461068469423614e-06</v>
       </c>
       <c r="Y25">
-        <v>1.0044551303252304e-05</v>
+        <v>4.544531451682553e-05</v>
       </c>
       <c r="Z25">
-        <v>0.0023662454592939192</v>
+        <v>0.0027353329559316282</v>
       </c>
       <c r="AA25">
-        <v>0.0021244110545033217</v>
+        <v>0.0024019470371932561</v>
       </c>
       <c r="AB25">
-        <v>0.0021278383844272396</v>
+        <v>0.0024003706698320004</v>
       </c>
       <c r="AC25">
-        <v>0.0021272513774244651</v>
+        <v>0.0024053124015353117</v>
       </c>
       <c r="AD25">
-        <v>0.0021306519155457303</v>
+        <v>0.0024130635737536028</v>
       </c>
       <c r="AE25">
-        <v>0.0021131702073767331</v>
+        <v>0.0023943327021205148</v>
       </c>
       <c r="AF25">
-        <v>8.4272321518982698e-06</v>
+        <v>6.8855059488431573e-06</v>
       </c>
       <c r="AG25">
-        <v>-0.0023404140812224375</v>
+        <v>3.9008417406748153e-05</v>
+      </c>
+      <c r="AH25">
+        <v>6.6071984716610348e-06</v>
+      </c>
+      <c r="AI25">
+        <v>-0.0024091914813475467</v>
       </c>
     </row>
     <row r="26">
@@ -6439,100 +7013,106 @@
         <v>53</v>
       </c>
       <c r="B26">
-        <v>-0.035314062558909065</v>
+        <v>-0.041780170364350111</v>
       </c>
       <c r="C26">
-        <v>-5.8973248747452438e-06</v>
+        <v>1.0577578694776009e-05</v>
       </c>
       <c r="D26">
-        <v>3.7377401114815629e-06</v>
+        <v>2.7308923763493925e-06</v>
       </c>
       <c r="E26">
-        <v>-6.8936656713701994e-08</v>
+        <v>-4.0956090897983854e-08</v>
       </c>
       <c r="F26">
-        <v>-3.5659616485143918e-05</v>
+        <v>-3.256235592747638e-05</v>
       </c>
       <c r="G26">
-        <v>-2.7779003373911088e-05</v>
+        <v>-3.3365374743733918e-05</v>
       </c>
       <c r="H26">
-        <v>-8.9198778641227635e-05</v>
+        <v>-8.9513114637770463e-05</v>
       </c>
       <c r="I26">
-        <v>-2.7344143241462854e-05</v>
+        <v>-5.5462795353136696e-05</v>
       </c>
       <c r="J26">
-        <v>6.5266818568562961e-06</v>
+        <v>7.6920219427976225e-06</v>
       </c>
       <c r="K26">
-        <v>2.8023596746982191e-06</v>
+        <v>-1.9570131783865075e-05</v>
       </c>
       <c r="L26">
-        <v>-1.1126898249002362e-05</v>
+        <v>-8.3258245848905986e-06</v>
       </c>
       <c r="M26">
-        <v>-1.4895073867319593e-05</v>
+        <v>-8.1565824726875994e-05</v>
       </c>
       <c r="N26">
-        <v>0.00016002541178001314</v>
+        <v>0.00011456175015991151</v>
       </c>
       <c r="O26">
-        <v>-3.6374920994950376e-05</v>
+        <v>-9.5444848122407241e-05</v>
       </c>
       <c r="P26">
-        <v>3.2413127683596731e-05</v>
+        <v>0.00010814157455045134</v>
       </c>
       <c r="Q26">
-        <v>0.00010370438898322371</v>
+        <v>4.6668522205139517e-05</v>
       </c>
       <c r="R26">
-        <v>0.00011048888750356776</v>
+        <v>6.579859296115256e-05</v>
       </c>
       <c r="S26">
-        <v>5.8156844814681932e-05</v>
+        <v>4.3098241443089141e-05</v>
       </c>
       <c r="T26">
-        <v>-6.7232512064425987e-05</v>
+        <v>-0.0002391107342234371</v>
       </c>
       <c r="U26">
-        <v>4.0388758760768334e-05</v>
+        <v>-0.0001612216177934913</v>
       </c>
       <c r="V26">
-        <v>6.9679719341041169e-05</v>
+        <v>-0.00019776480947328486</v>
       </c>
       <c r="W26">
-        <v>2.5488095709870473e-06</v>
+        <v>-1.2805140901900563e-05</v>
       </c>
       <c r="X26">
-        <v>-1.3153728805381944e-05</v>
+        <v>1.5265079848251746e-05</v>
       </c>
       <c r="Y26">
-        <v>3.0398733317869105e-05</v>
+        <v>6.0082731177777028e-05</v>
       </c>
       <c r="Z26">
-        <v>0.0021244110545033217</v>
+        <v>0.0024019470371932561</v>
       </c>
       <c r="AA26">
-        <v>0.0024756239690290342</v>
+        <v>0.0029132641563827297</v>
       </c>
       <c r="AB26">
-        <v>0.0021366268989155444</v>
+        <v>0.0024145795193169753</v>
       </c>
       <c r="AC26">
-        <v>0.0021276330899440677</v>
+        <v>0.002407777320436252</v>
       </c>
       <c r="AD26">
-        <v>0.002131898567389844</v>
+        <v>0.0024183629461501988</v>
       </c>
       <c r="AE26">
-        <v>0.0021142020575477699</v>
+        <v>0.0023961305224088668</v>
       </c>
       <c r="AF26">
-        <v>7.0217618232480057e-06</v>
+        <v>5.0341015421428035e-06</v>
       </c>
       <c r="AG26">
-        <v>-0.0022033836382427344</v>
+        <v>3.5143103445039927e-05</v>
+      </c>
+      <c r="AH26">
+        <v>-2.8320511428704806e-05</v>
+      </c>
+      <c r="AI26">
+        <v>-0.0021972512193771704</v>
       </c>
     </row>
     <row r="27">
@@ -6540,100 +7120,106 @@
         <v>54</v>
       </c>
       <c r="B27">
-        <v>-0.050783832529671558</v>
+        <v>-0.041959917611259147</v>
       </c>
       <c r="C27">
-        <v>-9.8714966054679304e-06</v>
+        <v>7.2822143498292637e-06</v>
       </c>
       <c r="D27">
-        <v>4.6265665702065824e-06</v>
+        <v>2.697070694620193e-06</v>
       </c>
       <c r="E27">
-        <v>-7.5057046272668922e-08</v>
+        <v>-4.0279910068181208e-08</v>
       </c>
       <c r="F27">
-        <v>-3.9655761580559994e-05</v>
+        <v>-4.3692492921836609e-05</v>
       </c>
       <c r="G27">
-        <v>-2.4704014749193145e-05</v>
+        <v>-3.4721204415569468e-05</v>
       </c>
       <c r="H27">
-        <v>-8.7012589759390331e-05</v>
+        <v>-9.6464399529598956e-05</v>
       </c>
       <c r="I27">
-        <v>-3.5443741443949334e-05</v>
+        <v>-7.5872728060489116e-05</v>
       </c>
       <c r="J27">
-        <v>1.6847673087838663e-06</v>
+        <v>-1.024119070579583e-05</v>
       </c>
       <c r="K27">
-        <v>-2.9381163177773142e-06</v>
+        <v>-2.6616656722436446e-05</v>
       </c>
       <c r="L27">
-        <v>-8.3157441435049803e-06</v>
+        <v>-4.5104831088476339e-06</v>
       </c>
       <c r="M27">
-        <v>-1.7391891510250446e-05</v>
+        <v>-7.4531000168357822e-05</v>
       </c>
       <c r="N27">
-        <v>0.00019690878900844965</v>
+        <v>0.00013430757200705204</v>
       </c>
       <c r="O27">
-        <v>-3.755046210642095e-05</v>
+        <v>-9.9987714929009334e-05</v>
       </c>
       <c r="P27">
-        <v>3.6912521479181914e-05</v>
+        <v>8.854105528242098e-05</v>
       </c>
       <c r="Q27">
-        <v>0.00016643072961185397</v>
+        <v>9.9448226390481693e-05</v>
       </c>
       <c r="R27">
-        <v>0.00014151696742741027</v>
+        <v>7.9745894430414922e-05</v>
       </c>
       <c r="S27">
-        <v>9.47806128909481e-05</v>
+        <v>7.1132001372349076e-05</v>
       </c>
       <c r="T27">
-        <v>-7.5683183965416685e-05</v>
+        <v>-0.00023331829453876549</v>
       </c>
       <c r="U27">
-        <v>-4.5198774517446472e-06</v>
+        <v>-0.000213103502907863</v>
       </c>
       <c r="V27">
-        <v>3.561173431261425e-05</v>
+        <v>-0.000228015592020864</v>
       </c>
       <c r="W27">
-        <v>1.5095500511921934e-05</v>
+        <v>1.2864131794275286e-06</v>
       </c>
       <c r="X27">
-        <v>-2.3117710078388574e-07</v>
+        <v>2.4269044024923377e-05</v>
       </c>
       <c r="Y27">
-        <v>5.7202697432759371e-05</v>
+        <v>9.2823550993128756e-05</v>
       </c>
       <c r="Z27">
-        <v>0.0021278383844272396</v>
+        <v>0.0024003706698320004</v>
       </c>
       <c r="AA27">
-        <v>0.0021366268989155444</v>
+        <v>0.0024145795193169753</v>
       </c>
       <c r="AB27">
-        <v>0.0024598407612613617</v>
+        <v>0.0028900449380497972</v>
       </c>
       <c r="AC27">
-        <v>0.0021298492476775014</v>
+        <v>0.0024043897227105974</v>
       </c>
       <c r="AD27">
-        <v>0.0021365454202894253</v>
+        <v>0.0024166781997009002</v>
       </c>
       <c r="AE27">
-        <v>0.0021146631244888846</v>
+        <v>0.0023922319415731258</v>
       </c>
       <c r="AF27">
-        <v>6.9310533764034815e-06</v>
+        <v>3.9761924869891407e-06</v>
       </c>
       <c r="AG27">
-        <v>-0.0022337355730764554</v>
+        <v>8.4925635283048407e-05</v>
+      </c>
+      <c r="AH27">
+        <v>1.8899554389884433e-05</v>
+      </c>
+      <c r="AI27">
+        <v>-0.0021741961383255994</v>
       </c>
     </row>
     <row r="28">
@@ -6641,100 +7227,106 @@
         <v>55</v>
       </c>
       <c r="B28">
-        <v>-0.1048815473685934</v>
+        <v>-0.17308448932077908</v>
       </c>
       <c r="C28">
-        <v>-9.2243777165275349e-06</v>
+        <v>4.2572345110106642e-06</v>
       </c>
       <c r="D28">
-        <v>3.9144467829741868e-06</v>
+        <v>3.3111745535957895e-06</v>
       </c>
       <c r="E28">
-        <v>-6.8818484765936329e-08</v>
+        <v>-4.6066599677972516e-08</v>
       </c>
       <c r="F28">
-        <v>-7.446299160707116e-05</v>
+        <v>-9.425875026856283e-05</v>
       </c>
       <c r="G28">
-        <v>-7.2821221714079645e-05</v>
+        <v>-9.5267496664021333e-05</v>
       </c>
       <c r="H28">
-        <v>-0.0001299171678492226</v>
+        <v>-0.00014677624567278631</v>
       </c>
       <c r="I28">
-        <v>-5.0452409494885792e-05</v>
+        <v>-9.1320964737238216e-05</v>
       </c>
       <c r="J28">
-        <v>7.3527247910234905e-06</v>
+        <v>9.4274848582951993e-06</v>
       </c>
       <c r="K28">
-        <v>2.1275909058952858e-05</v>
+        <v>8.045076416849338e-06</v>
       </c>
       <c r="L28">
-        <v>-9.9556821724918097e-06</v>
+        <v>-7.3148628605913319e-06</v>
       </c>
       <c r="M28">
-        <v>-1.2703353865582253e-05</v>
+        <v>-6.6399652958953561e-05</v>
       </c>
       <c r="N28">
-        <v>0.00014719297904257009</v>
+        <v>9.8039917483482919e-05</v>
       </c>
       <c r="O28">
-        <v>-4.480835318752699e-05</v>
+        <v>-0.00012832431907419813</v>
       </c>
       <c r="P28">
-        <v>3.3099817879172567e-05</v>
+        <v>0.00010920062210723416</v>
       </c>
       <c r="Q28">
-        <v>4.4590480214139888e-05</v>
+        <v>-3.4255856849454633e-05</v>
       </c>
       <c r="R28">
-        <v>6.8886509464106092e-05</v>
+        <v>1.0732254452152333e-05</v>
       </c>
       <c r="S28">
-        <v>1.7733500546512036e-05</v>
+        <v>-6.5461614596439011e-06</v>
       </c>
       <c r="T28">
-        <v>5.8530405087612106e-05</v>
+        <v>-4.9629513844086891e-05</v>
       </c>
       <c r="U28">
-        <v>0.00018975146506003231</v>
+        <v>5.6877917379005542e-05</v>
       </c>
       <c r="V28">
-        <v>0.0002295639778916083</v>
+        <v>5.064178824815916e-05</v>
       </c>
       <c r="W28">
-        <v>8.4272525953695536e-06</v>
+        <v>-6.3322716246603925e-06</v>
       </c>
       <c r="X28">
-        <v>-3.0538695615703586e-06</v>
+        <v>1.8885996400031121e-05</v>
       </c>
       <c r="Y28">
-        <v>8.0919534755876017e-06</v>
+        <v>3.3394181581054242e-05</v>
       </c>
       <c r="Z28">
-        <v>0.0021272513774244651</v>
+        <v>0.0024053124015353117</v>
       </c>
       <c r="AA28">
-        <v>0.0021276330899440677</v>
+        <v>0.002407777320436252</v>
       </c>
       <c r="AB28">
-        <v>0.0021298492476775014</v>
+        <v>0.0024043897227105974</v>
       </c>
       <c r="AC28">
-        <v>0.0023693636478806751</v>
+        <v>0.002736857499425413</v>
       </c>
       <c r="AD28">
-        <v>0.0021327709559643025</v>
+        <v>0.0024153830837603122</v>
       </c>
       <c r="AE28">
-        <v>0.0021153181181380598</v>
+        <v>0.0023988742628119177</v>
       </c>
       <c r="AF28">
-        <v>9.1784161796599204e-06</v>
+        <v>7.3288350495538185e-06</v>
       </c>
       <c r="AG28">
-        <v>-0.0023351606799294905</v>
+        <v>3.0846391880545981e-05</v>
+      </c>
+      <c r="AH28">
+        <v>-1.8176728307583035e-05</v>
+      </c>
+      <c r="AI28">
+        <v>-0.0023874069787615457</v>
       </c>
     </row>
     <row r="29">
@@ -6742,100 +7334,106 @@
         <v>56</v>
       </c>
       <c r="B29">
-        <v>-0.049380617756219353</v>
+        <v>-0.059777586583149328</v>
       </c>
       <c r="C29">
-        <v>-2.4221781435151366e-05</v>
+        <v>-1.8895805004206254e-05</v>
       </c>
       <c r="D29">
-        <v>3.8214061891865504e-06</v>
+        <v>2.7098451452058439e-06</v>
       </c>
       <c r="E29">
-        <v>-6.2548400488715465e-08</v>
+        <v>-3.3901780022848824e-08</v>
       </c>
       <c r="F29">
-        <v>1.3809560856642422e-06</v>
+        <v>1.0258616395554358e-05</v>
       </c>
       <c r="G29">
-        <v>-1.4506514775377449e-05</v>
+        <v>-3.6770110894328648e-07</v>
       </c>
       <c r="H29">
-        <v>-6.1442403194493837e-05</v>
+        <v>-5.7995603966465303e-05</v>
       </c>
       <c r="I29">
-        <v>5.679111209082083e-05</v>
+        <v>4.7570217411091985e-05</v>
       </c>
       <c r="J29">
-        <v>-1.043391205122893e-05</v>
+        <v>-7.4113146721242862e-05</v>
       </c>
       <c r="K29">
-        <v>3.6484657821675859e-06</v>
+        <v>-1.6211091124791006e-05</v>
       </c>
       <c r="L29">
-        <v>-1.2031140510936847e-05</v>
+        <v>-1.1032005505418663e-05</v>
       </c>
       <c r="M29">
-        <v>-1.0578123565384703e-05</v>
+        <v>-5.2142528327796093e-05</v>
       </c>
       <c r="N29">
-        <v>0.00012940082653870814</v>
+        <v>7.1475371197587522e-05</v>
       </c>
       <c r="O29">
-        <v>-3.7254365094515377e-05</v>
+        <v>-4.7235486771416541e-05</v>
       </c>
       <c r="P29">
-        <v>3.1536699458196743e-05</v>
+        <v>6.8460209244772773e-05</v>
       </c>
       <c r="Q29">
-        <v>0.00012793408227820694</v>
+        <v>6.6467335825516442e-05</v>
       </c>
       <c r="R29">
-        <v>0.00013270359470377957</v>
+        <v>8.7401855542785893e-05</v>
       </c>
       <c r="S29">
-        <v>7.3752860993755521e-05</v>
+        <v>5.932915766124116e-05</v>
       </c>
       <c r="T29">
-        <v>-8.7427247758829676e-05</v>
+        <v>-0.00028632919040400863</v>
       </c>
       <c r="U29">
-        <v>1.1739242101864358e-05</v>
+        <v>-0.00019822358007756495</v>
       </c>
       <c r="V29">
-        <v>3.2942630155763288e-05</v>
+        <v>-0.00022346204295744382</v>
       </c>
       <c r="W29">
-        <v>1.9232827080719784e-05</v>
+        <v>7.5633144020334964e-06</v>
       </c>
       <c r="X29">
-        <v>2.2398552687026541e-05</v>
+        <v>5.9731947545477453e-05</v>
       </c>
       <c r="Y29">
-        <v>5.0059007667118896e-05</v>
+        <v>9.2201178753770717e-05</v>
       </c>
       <c r="Z29">
-        <v>0.0021306519155457303</v>
+        <v>0.0024130635737536028</v>
       </c>
       <c r="AA29">
-        <v>0.002131898567389844</v>
+        <v>0.0024183629461501988</v>
       </c>
       <c r="AB29">
-        <v>0.0021365454202894253</v>
+        <v>0.0024166781997009002</v>
       </c>
       <c r="AC29">
-        <v>0.0021327709559643025</v>
+        <v>0.0024153830837603122</v>
       </c>
       <c r="AD29">
-        <v>0.0023624732826171167</v>
+        <v>0.002741044324812615</v>
       </c>
       <c r="AE29">
-        <v>0.0021132352193214991</v>
+        <v>0.002399823517029775</v>
       </c>
       <c r="AF29">
-        <v>1.1857945925722413e-05</v>
+        <v>6.7432536734442293e-06</v>
       </c>
       <c r="AG29">
-        <v>-0.002320178887264668</v>
+        <v>0.0002488530751332714</v>
+      </c>
+      <c r="AH29">
+        <v>-2.8456481678028681e-07</v>
+      </c>
+      <c r="AI29">
+        <v>-0.0022674087277131556</v>
       </c>
     </row>
     <row r="30">
@@ -6843,100 +7441,106 @@
         <v>57</v>
       </c>
       <c r="B30">
-        <v>-0.10830747053401948</v>
+        <v>-0.15103280478580675</v>
       </c>
       <c r="C30">
-        <v>-3.0923984250093275e-06</v>
+        <v>9.3130314107987875e-06</v>
       </c>
       <c r="D30">
-        <v>-3.9748307806056623e-06</v>
+        <v>-3.7182472273433852e-06</v>
       </c>
       <c r="E30">
-        <v>-1.9607169780295065e-10</v>
+        <v>1.8326230847159117e-08</v>
       </c>
       <c r="F30">
-        <v>-1.5600412780258758e-05</v>
+        <v>-5.2922973063558609e-06</v>
       </c>
       <c r="G30">
-        <v>-4.9130978743581392e-06</v>
+        <v>1.7840588211187744e-06</v>
       </c>
       <c r="H30">
-        <v>-4.4432150647458278e-05</v>
+        <v>-4.1755144483655708e-05</v>
       </c>
       <c r="I30">
-        <v>1.0067916064749119e-05</v>
+        <v>-1.0998181087716835e-05</v>
       </c>
       <c r="J30">
-        <v>7.9098447125638991e-06</v>
+        <v>-3.34843595512793e-06</v>
       </c>
       <c r="K30">
-        <v>1.2841854113162447e-05</v>
+        <v>1.2277340705570843e-05</v>
       </c>
       <c r="L30">
-        <v>-8.7974991603492583e-06</v>
+        <v>-5.3927727825969897e-06</v>
       </c>
       <c r="M30">
-        <v>-1.2087935056753014e-05</v>
+        <v>-5.4684359378744815e-05</v>
       </c>
       <c r="N30">
-        <v>0.00018590963167223012</v>
+        <v>0.00012324085976339047</v>
       </c>
       <c r="O30">
-        <v>-4.3357434046430605e-05</v>
+        <v>-9.5000747710684023e-05</v>
       </c>
       <c r="P30">
-        <v>2.8392876978894691e-05</v>
+        <v>5.8168987783405678e-05</v>
       </c>
       <c r="Q30">
-        <v>8.6163876814509015e-05</v>
+        <v>-5.7145689075200311e-07</v>
       </c>
       <c r="R30">
-        <v>0.00010845629984538121</v>
+        <v>3.5825910529381022e-05</v>
       </c>
       <c r="S30">
-        <v>5.5914348687922727e-05</v>
+        <v>1.7578409182146797e-05</v>
       </c>
       <c r="T30">
-        <v>-7.8777702720571764e-05</v>
+        <v>-6.6982911648969141e-05</v>
       </c>
       <c r="U30">
-        <v>9.4348963746079643e-05</v>
+        <v>6.8994809937670707e-05</v>
       </c>
       <c r="V30">
-        <v>0.00013364260780112107</v>
+        <v>6.0863052053493219e-05</v>
       </c>
       <c r="W30">
-        <v>-4.6446445691187226e-05</v>
+        <v>-4.9954516738316636e-05</v>
       </c>
       <c r="X30">
-        <v>-2.6679733562360656e-05</v>
+        <v>1.2268955093169197e-05</v>
       </c>
       <c r="Y30">
-        <v>-5.4425320463299819e-05</v>
+        <v>-2.3088192576370845e-05</v>
       </c>
       <c r="Z30">
-        <v>0.0021131702073767331</v>
+        <v>0.0023943327021205148</v>
       </c>
       <c r="AA30">
-        <v>0.0021142020575477699</v>
+        <v>0.0023961305224088668</v>
       </c>
       <c r="AB30">
-        <v>0.0021146631244888846</v>
+        <v>0.0023922319415731258</v>
       </c>
       <c r="AC30">
-        <v>0.0021153181181380598</v>
+        <v>0.0023988742628119177</v>
       </c>
       <c r="AD30">
-        <v>0.0021132352193214991</v>
+        <v>0.002399823517029775</v>
       </c>
       <c r="AE30">
-        <v>0.0024600845166822954</v>
+        <v>0.0028590045554329315</v>
       </c>
       <c r="AF30">
-        <v>5.2442169749257372e-06</v>
+        <v>4.640559718731578e-06</v>
       </c>
       <c r="AG30">
-        <v>-0.0020692446765736309</v>
+        <v>2.7589194120178871e-05</v>
+      </c>
+      <c r="AH30">
+        <v>-3.89107080160404e-05</v>
+      </c>
+      <c r="AI30">
+        <v>-0.0022996381816512762</v>
       </c>
     </row>
     <row r="31">
@@ -6944,100 +7548,106 @@
         <v>58</v>
       </c>
       <c r="B31">
-        <v>0.0073297059529603467</v>
+        <v>0.022623976220380211</v>
       </c>
       <c r="C31">
-        <v>-1.0539886173293146e-06</v>
+        <v>-1.1801453572122004e-07</v>
       </c>
       <c r="D31">
-        <v>-1.0164325202820428e-07</v>
+        <v>-1.0517234437267577e-07</v>
       </c>
       <c r="E31">
-        <v>-6.9834347979371075e-10</v>
+        <v>-7.9769449682427677e-10</v>
       </c>
       <c r="F31">
-        <v>-1.4390174210012711e-07</v>
+        <v>-2.1242813873393685e-06</v>
       </c>
       <c r="G31">
-        <v>-1.9204040409130673e-06</v>
+        <v>-4.9769320234327978e-06</v>
       </c>
       <c r="H31">
-        <v>-1.8707608751687319e-06</v>
+        <v>-3.812822218944009e-06</v>
       </c>
       <c r="I31">
-        <v>2.3481140046250883e-06</v>
+        <v>-1.5225029826202927e-06</v>
       </c>
       <c r="J31">
-        <v>-1.5370353053766594e-06</v>
+        <v>-1.2766501460807108e-06</v>
       </c>
       <c r="K31">
-        <v>1.114564633412457e-06</v>
+        <v>7.6871471711810675e-07</v>
       </c>
       <c r="L31">
-        <v>-2.1870100858353579e-07</v>
+        <v>-2.8400275670942545e-07</v>
       </c>
       <c r="M31">
-        <v>1.4554320829353008e-06</v>
+        <v>4.5341083384152171e-06</v>
       </c>
       <c r="N31">
-        <v>6.7391443724539919e-07</v>
+        <v>-1.6854814070528881e-06</v>
       </c>
       <c r="O31">
-        <v>2.2138589919915682e-07</v>
+        <v>-2.9715070134869425e-06</v>
       </c>
       <c r="P31">
-        <v>-1.6227347779727098e-06</v>
+        <v>-4.8550016487323321e-06</v>
       </c>
       <c r="Q31">
-        <v>3.4382323716401623e-06</v>
+        <v>-4.2520489844773894e-06</v>
       </c>
       <c r="R31">
-        <v>-2.5388167044774926e-07</v>
+        <v>-8.6593109527509067e-06</v>
       </c>
       <c r="S31">
-        <v>-3.7297443935173445e-06</v>
+        <v>-1.1463604557539225e-05</v>
       </c>
       <c r="T31">
-        <v>2.8996886032412687e-06</v>
+        <v>-2.9561829437222678e-07</v>
       </c>
       <c r="U31">
-        <v>8.7478830651788718e-06</v>
+        <v>6.434105305371939e-06</v>
       </c>
       <c r="V31">
-        <v>9.7024294156043895e-06</v>
+        <v>6.5462480586167397e-06</v>
       </c>
       <c r="W31">
-        <v>5.912035099158284e-08</v>
+        <v>2.6429877657229862e-07</v>
       </c>
       <c r="X31">
-        <v>9.721238783416431e-07</v>
+        <v>-1.2264595303643813e-07</v>
       </c>
       <c r="Y31">
-        <v>-3.5096290110600916e-06</v>
+        <v>-9.1016462402966812e-06</v>
       </c>
       <c r="Z31">
-        <v>8.4272321518982698e-06</v>
+        <v>6.8855059488431573e-06</v>
       </c>
       <c r="AA31">
-        <v>7.0217618232480057e-06</v>
+        <v>5.0341015421428035e-06</v>
       </c>
       <c r="AB31">
-        <v>6.9310533764034815e-06</v>
+        <v>3.9761924869891407e-06</v>
       </c>
       <c r="AC31">
-        <v>9.1784161796599204e-06</v>
+        <v>7.3288350495538185e-06</v>
       </c>
       <c r="AD31">
-        <v>1.1857945925722413e-05</v>
+        <v>6.7432536734442293e-06</v>
       </c>
       <c r="AE31">
-        <v>5.2442169749257372e-06</v>
+        <v>4.640559718731578e-06</v>
       </c>
       <c r="AF31">
-        <v>3.0938552504869883e-06</v>
+        <v>3.8262559738154043e-06</v>
       </c>
       <c r="AG31">
-        <v>-5.9901912604673263e-05</v>
+        <v>-6.0272775925399258e-06</v>
+      </c>
+      <c r="AH31">
+        <v>-1.1944329663813337e-05</v>
+      </c>
+      <c r="AI31">
+        <v>-6.1229541170580211e-05</v>
       </c>
     </row>
     <row r="32">
@@ -7045,100 +7655,320 @@
         <v>59</v>
       </c>
       <c r="B32">
-        <v>-0.26603228404670176</v>
+        <v>-0.20141914495740831</v>
       </c>
       <c r="C32">
-        <v>0.00017151388028960356</v>
+        <v>-7.8303737241919042e-05</v>
       </c>
       <c r="D32">
-        <v>-0.00027447695095998183</v>
+        <v>6.7792657439162902e-07</v>
       </c>
       <c r="E32">
-        <v>2.3688879857051789e-06</v>
+        <v>-2.0616752399827562e-08</v>
       </c>
       <c r="F32">
-        <v>-0.0024249514036422341</v>
+        <v>1.3254611324652228e-05</v>
       </c>
       <c r="G32">
-        <v>-0.0024963187450407738</v>
+        <v>2.3653988487843877e-05</v>
       </c>
       <c r="H32">
-        <v>-0.0024842963424730052</v>
+        <v>-9.4182418717767002e-07</v>
       </c>
       <c r="I32">
-        <v>-0.0030329053243088669</v>
+        <v>0.00017677745986703283</v>
       </c>
       <c r="J32">
-        <v>0.00010027052921489057</v>
+        <v>-0.00016867270152082627</v>
       </c>
       <c r="K32">
-        <v>-0.0018496775650005404</v>
+        <v>1.6656694351073042e-05</v>
       </c>
       <c r="L32">
-        <v>7.2099035883625066e-05</v>
+        <v>-4.7572744028242836e-06</v>
       </c>
       <c r="M32">
-        <v>-3.1354179638707811e-05</v>
+        <v>7.9370531799451678e-05</v>
       </c>
       <c r="N32">
-        <v>-0.0030707085921171592</v>
+        <v>6.7198161181713026e-05</v>
       </c>
       <c r="O32">
-        <v>-0.00070074022067162707</v>
+        <v>0.0001750698952145773</v>
       </c>
       <c r="P32">
-        <v>-0.00095467605227211806</v>
+        <v>-4.5373912749079905e-05</v>
       </c>
       <c r="Q32">
-        <v>-0.011541645251482602</v>
+        <v>0.00031607126843852251</v>
       </c>
       <c r="R32">
-        <v>-0.010890448498852215</v>
+        <v>0.00028715676090059969</v>
       </c>
       <c r="S32">
-        <v>-0.010699410321673423</v>
+        <v>0.00020059819423439221</v>
       </c>
       <c r="T32">
-        <v>-0.018521867812695998</v>
+        <v>-4.8286190883990721e-05</v>
       </c>
       <c r="U32">
-        <v>-0.014676313792467369</v>
+        <v>3.5529327898728424e-05</v>
       </c>
       <c r="V32">
-        <v>-0.014979031873911988</v>
+        <v>0.00010284722603032259</v>
       </c>
       <c r="W32">
-        <v>-0.00041274289625724552</v>
+        <v>3.383842085780478e-05</v>
       </c>
       <c r="X32">
-        <v>-0.0010035270209452747</v>
+        <v>0.00011583449999951964</v>
       </c>
       <c r="Y32">
-        <v>-0.0011215853421955352</v>
+        <v>7.3739496584565752e-05</v>
       </c>
       <c r="Z32">
-        <v>-0.0023404140812224375</v>
+        <v>3.9008417406748153e-05</v>
       </c>
       <c r="AA32">
-        <v>-0.0022033836382427344</v>
+        <v>3.5143103445039927e-05</v>
       </c>
       <c r="AB32">
-        <v>-0.0022337355730764554</v>
+        <v>8.4925635283048407e-05</v>
       </c>
       <c r="AC32">
-        <v>-0.0023351606799294905</v>
+        <v>3.0846391880545981e-05</v>
       </c>
       <c r="AD32">
-        <v>-0.002320178887264668</v>
+        <v>0.0002488530751332714</v>
       </c>
       <c r="AE32">
-        <v>-0.0020692446765736309</v>
+        <v>2.7589194120178871e-05</v>
       </c>
       <c r="AF32">
-        <v>-5.9901912604673263e-05</v>
+        <v>-6.0272775925399258e-06</v>
       </c>
       <c r="AG32">
-        <v>0.038988563307745978</v>
+        <v>0.0017435790274805698</v>
+      </c>
+      <c r="AH32">
+        <v>0.0002839342265336464</v>
+      </c>
+      <c r="AI32">
+        <v>-0.00031764632932575275</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s">
+        <v>60</v>
+      </c>
+      <c r="B33">
+        <v>-0.12567371101174948</v>
+      </c>
+      <c r="C33">
+        <v>-2.8586673719581114e-05</v>
+      </c>
+      <c r="D33">
+        <v>-2.1025786509196349e-06</v>
+      </c>
+      <c r="E33">
+        <v>9.7628222075587755e-09</v>
+      </c>
+      <c r="F33">
+        <v>-8.3220067583281154e-07</v>
+      </c>
+      <c r="G33">
+        <v>5.0810295743719102e-05</v>
+      </c>
+      <c r="H33">
+        <v>1.1790754280966483e-05</v>
+      </c>
+      <c r="I33">
+        <v>6.4729527955960983e-05</v>
+      </c>
+      <c r="J33">
+        <v>-8.3141777482098215e-05</v>
+      </c>
+      <c r="K33">
+        <v>3.2264897530520989e-05</v>
+      </c>
+      <c r="L33">
+        <v>-7.4010554880799231e-06</v>
+      </c>
+      <c r="M33">
+        <v>5.013149121636935e-05</v>
+      </c>
+      <c r="N33">
+        <v>3.4162190225686239e-05</v>
+      </c>
+      <c r="O33">
+        <v>0.00022189868718456023</v>
+      </c>
+      <c r="P33">
+        <v>-0.00015097457733100018</v>
+      </c>
+      <c r="Q33">
+        <v>0.00019648143661476526</v>
+      </c>
+      <c r="R33">
+        <v>0.00018711060073023714</v>
+      </c>
+      <c r="S33">
+        <v>0.00014551465158310021</v>
+      </c>
+      <c r="T33">
+        <v>0.00016431300235473373</v>
+      </c>
+      <c r="U33">
+        <v>0.00016931722591211236</v>
+      </c>
+      <c r="V33">
+        <v>0.00021353528251407371</v>
+      </c>
+      <c r="W33">
+        <v>-1.1683104600936545e-05</v>
+      </c>
+      <c r="X33">
+        <v>1.5224501182161082e-05</v>
+      </c>
+      <c r="Y33">
+        <v>1.185222418444978e-05</v>
+      </c>
+      <c r="Z33">
+        <v>6.6071984716610348e-06</v>
+      </c>
+      <c r="AA33">
+        <v>-2.8320511428704806e-05</v>
+      </c>
+      <c r="AB33">
+        <v>1.8899554389884433e-05</v>
+      </c>
+      <c r="AC33">
+        <v>-1.8176728307583035e-05</v>
+      </c>
+      <c r="AD33">
+        <v>-2.8456481678028681e-07</v>
+      </c>
+      <c r="AE33">
+        <v>-3.89107080160404e-05</v>
+      </c>
+      <c r="AF33">
+        <v>-1.1944329663813337e-05</v>
+      </c>
+      <c r="AG33">
+        <v>0.0002839342265336464</v>
+      </c>
+      <c r="AH33">
+        <v>0.0014619434463006196</v>
+      </c>
+      <c r="AI33">
+        <v>-0.00011722674572657436</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s">
+        <v>61</v>
+      </c>
+      <c r="B34">
+        <v>-0.4431631749946896</v>
+      </c>
+      <c r="C34">
+        <v>0.00018030146354133222</v>
+      </c>
+      <c r="D34">
+        <v>-0.00037727989086930693</v>
+      </c>
+      <c r="E34">
+        <v>3.2579248682791623e-06</v>
+      </c>
+      <c r="F34">
+        <v>-0.0031909959915158394</v>
+      </c>
+      <c r="G34">
+        <v>-0.003270466191866302</v>
+      </c>
+      <c r="H34">
+        <v>-0.003381134787782597</v>
+      </c>
+      <c r="I34">
+        <v>-0.0039087046616684516</v>
+      </c>
+      <c r="J34">
+        <v>0.00037117144109132753</v>
+      </c>
+      <c r="K34">
+        <v>-0.002408534962640044</v>
+      </c>
+      <c r="L34">
+        <v>7.7037032292740965e-05</v>
+      </c>
+      <c r="M34">
+        <v>-0.00010796927102515791</v>
+      </c>
+      <c r="N34">
+        <v>-0.004452135442681469</v>
+      </c>
+      <c r="O34">
+        <v>-0.0037005242288102864</v>
+      </c>
+      <c r="P34">
+        <v>-0.0031854452860888309</v>
+      </c>
+      <c r="Q34">
+        <v>-0.015830166702359098</v>
+      </c>
+      <c r="R34">
+        <v>-0.015025821244958616</v>
+      </c>
+      <c r="S34">
+        <v>-0.014774351112696028</v>
+      </c>
+      <c r="T34">
+        <v>-0.024007797661731684</v>
+      </c>
+      <c r="U34">
+        <v>-0.019144972698791899</v>
+      </c>
+      <c r="V34">
+        <v>-0.019555278136735209</v>
+      </c>
+      <c r="W34">
+        <v>-0.00041100116851545585</v>
+      </c>
+      <c r="X34">
+        <v>-0.0012675766661341425</v>
+      </c>
+      <c r="Y34">
+        <v>-0.0011978237530955954</v>
+      </c>
+      <c r="Z34">
+        <v>-0.0024091914813475467</v>
+      </c>
+      <c r="AA34">
+        <v>-0.0021972512193771704</v>
+      </c>
+      <c r="AB34">
+        <v>-0.0021741961383255994</v>
+      </c>
+      <c r="AC34">
+        <v>-0.0023874069787615457</v>
+      </c>
+      <c r="AD34">
+        <v>-0.0022674087277131556</v>
+      </c>
+      <c r="AE34">
+        <v>-0.0022996381816512762</v>
+      </c>
+      <c r="AF34">
+        <v>-6.1229541170580211e-05</v>
+      </c>
+      <c r="AG34">
+        <v>-0.00031764632932575275</v>
+      </c>
+      <c r="AH34">
+        <v>-0.00011722674572657436</v>
+      </c>
+      <c r="AI34">
+        <v>0.051332128838372015</v>
       </c>
     </row>
   </sheetData>

--- a/input/ES/reg_income.xlsx
+++ b/input/ES/reg_income.xlsx
@@ -389,7 +389,7 @@
         <v>16</v>
       </c>
       <c r="B7">
-        <v>0.32020493334424105</v>
+        <v>0.32022555969286282</v>
       </c>
       <c r="C7"/>
       <c r="D7"/>
@@ -397,7 +397,7 @@
         <v>24</v>
       </c>
       <c r="F7">
-        <v>15106.424510469089</v>
+        <v>15120.96397464909</v>
       </c>
     </row>
     <row r="8">
@@ -413,7 +413,7 @@
         <v>25</v>
       </c>
       <c r="F8">
-        <v>-97416839.566960737</v>
+        <v>-97413945.038870797</v>
       </c>
     </row>
     <row r="9">
@@ -448,7 +448,7 @@
         <v>19</v>
       </c>
       <c r="B13">
-        <v>0.54353966627829697</v>
+        <v>0.54362013493723471</v>
       </c>
       <c r="C13"/>
       <c r="D13"/>
@@ -589,109 +589,109 @@
         <v>28</v>
       </c>
       <c r="B2">
-        <v>-0.049047819627476584</v>
+        <v>-0.049300765356468324</v>
       </c>
       <c r="C2">
-        <v>0.00043189762075675279</v>
+        <v>0.0004320678229514082</v>
       </c>
       <c r="D2">
-        <v>-7.1937156704148443e-07</v>
+        <v>-6.9062008955716232e-07</v>
       </c>
       <c r="E2">
-        <v>3.3578253004639401e-08</v>
+        <v>3.3311247282225842e-08</v>
       </c>
       <c r="F2">
-        <v>-8.241966738302059e-06</v>
+        <v>-8.8045323919624035e-06</v>
       </c>
       <c r="G2">
-        <v>1.855934931981686e-05</v>
+        <v>1.8086939996334903e-05</v>
       </c>
       <c r="H2">
-        <v>-1.6690760842623853e-08</v>
+        <v>-2.294909408279684e-07</v>
       </c>
       <c r="I2">
-        <v>-7.3914409938055097e-07</v>
+        <v>-1.0622280811435487e-06</v>
       </c>
       <c r="J2">
-        <v>1.6071703646335672e-06</v>
+        <v>1.565604587709865e-06</v>
       </c>
       <c r="K2">
-        <v>-5.7547310330336932e-05</v>
+        <v>-5.6389401741769238e-05</v>
       </c>
       <c r="L2">
-        <v>-5.6414867353351785e-06</v>
+        <v>-5.7524396055269288e-06</v>
       </c>
       <c r="M2">
-        <v>-8.3731349492827086e-07</v>
+        <v>-8.8146591988703629e-07</v>
       </c>
       <c r="N2">
-        <v>-0.00042477101755662413</v>
+        <v>-0.00042494060407132281</v>
       </c>
       <c r="O2">
-        <v>9.0939883462974436e-08</v>
+        <v>9.2940732608185477e-08</v>
       </c>
       <c r="P2">
-        <v>-5.5365494455151705e-07</v>
+        <v>-4.8286539081760669e-07</v>
       </c>
       <c r="Q2">
-        <v>-4.4643412823985004e-06</v>
+        <v>-4.4273242537313297e-06</v>
       </c>
       <c r="R2">
-        <v>-0.00020276970545396434</v>
+        <v>-0.00020231358560382365</v>
       </c>
       <c r="S2">
-        <v>-0.00018457906641151828</v>
+        <v>-0.00018398417332608218</v>
       </c>
       <c r="T2">
-        <v>-0.00014230107507940196</v>
+        <v>-0.00014179299679633472</v>
       </c>
       <c r="U2">
-        <v>-0.00042824173032764926</v>
+        <v>-0.00041969083244662255</v>
       </c>
       <c r="V2">
-        <v>-0.00038901432655613779</v>
+        <v>-0.00037891908621315155</v>
       </c>
       <c r="W2">
-        <v>-0.00054219627613523783</v>
+        <v>-0.00053279197319087946</v>
       </c>
       <c r="X2">
-        <v>3.2606815590782098e-05</v>
+        <v>3.3192940103519456e-05</v>
       </c>
       <c r="Y2">
-        <v>1.2507353626023731e-05</v>
+        <v>1.2824885642311791e-05</v>
       </c>
       <c r="Z2">
-        <v>0.00010919930756859229</v>
+        <v>0.00011215434604868531</v>
       </c>
       <c r="AA2">
-        <v>2.008944525785602e-05</v>
+        <v>2.0237935776571509e-05</v>
       </c>
       <c r="AB2">
-        <v>3.0620277680629821e-05</v>
+        <v>3.063302764934984e-05</v>
       </c>
       <c r="AC2">
-        <v>1.737095255270012e-05</v>
+        <v>1.7472107568759453e-05</v>
       </c>
       <c r="AD2">
-        <v>9.9550358277092029e-06</v>
+        <v>1.0119824896696742e-05</v>
       </c>
       <c r="AE2">
-        <v>1.8740201872788885e-05</v>
+        <v>1.8933072447856352e-05</v>
       </c>
       <c r="AF2">
-        <v>1.6236824556625044e-05</v>
+        <v>1.6187612961458784e-05</v>
       </c>
       <c r="AG2">
-        <v>4.5706930769845149e-07</v>
+        <v>4.685086402398406e-07</v>
       </c>
       <c r="AH2">
-        <v>-1.1395694809765368e-05</v>
+        <v>-1.1473847005678611e-05</v>
       </c>
       <c r="AI2">
-        <v>7.7841352484640314e-07</v>
+        <v>6.2958735926880365e-07</v>
       </c>
       <c r="AJ2">
-        <v>0.00034627450460851311</v>
+        <v>0.0003356742477047146</v>
       </c>
     </row>
     <row r="3">
@@ -699,109 +699,109 @@
         <v>29</v>
       </c>
       <c r="B3">
-        <v>-0.022291752349886996</v>
+        <v>-0.022267171855309881</v>
       </c>
       <c r="C3">
-        <v>-7.1937156704148443e-07</v>
+        <v>-6.9062008955716232e-07</v>
       </c>
       <c r="D3">
-        <v>1.8125442436254629e-05</v>
+        <v>1.8129961899296135e-05</v>
       </c>
       <c r="E3">
-        <v>-1.6888010944626742e-07</v>
+        <v>-1.6886692693779025e-07</v>
       </c>
       <c r="F3">
-        <v>3.7800642651957662e-06</v>
+        <v>3.7553293738077628e-06</v>
       </c>
       <c r="G3">
-        <v>-9.4488630177101824e-06</v>
+        <v>-9.4589397696312716e-06</v>
       </c>
       <c r="H3">
-        <v>-1.4270496977472148e-05</v>
+        <v>-1.4325993612345714e-05</v>
       </c>
       <c r="I3">
-        <v>-1.2432825514939752e-05</v>
+        <v>-1.2437410010059336e-05</v>
       </c>
       <c r="J3">
-        <v>-9.6927094243349794e-07</v>
+        <v>-9.8708412104348555e-07</v>
       </c>
       <c r="K3">
-        <v>-9.6672651619156798e-07</v>
+        <v>-1.0741711980089554e-06</v>
       </c>
       <c r="L3">
-        <v>-2.6211966690228471e-06</v>
+        <v>-2.6350739653878427e-06</v>
       </c>
       <c r="M3">
-        <v>-2.8019044137940674e-07</v>
+        <v>-2.8032076893867846e-07</v>
       </c>
       <c r="N3">
-        <v>8.6552023993750523e-07</v>
+        <v>8.4233338508026468e-07</v>
       </c>
       <c r="O3">
-        <v>-2.8893583893147131e-07</v>
+        <v>-2.8857191346755779e-07</v>
       </c>
       <c r="P3">
-        <v>3.1809939197751243e-07</v>
+        <v>3.4489570855576878e-07</v>
       </c>
       <c r="Q3">
-        <v>-9.2049423138635105e-08</v>
+        <v>-9.43274956047074e-08</v>
       </c>
       <c r="R3">
-        <v>-0.00013339923347572137</v>
+        <v>-0.00013329788888462221</v>
       </c>
       <c r="S3">
-        <v>-0.00013984982154221666</v>
+        <v>-0.00013972298769855186</v>
       </c>
       <c r="T3">
-        <v>-0.00013983667603342863</v>
+        <v>-0.00013968963599298267</v>
       </c>
       <c r="U3">
-        <v>9.4556681224327444e-05</v>
+        <v>9.3662377662510855e-05</v>
       </c>
       <c r="V3">
-        <v>-1.7461056325237417e-05</v>
+        <v>-1.8499401183820431e-05</v>
       </c>
       <c r="W3">
-        <v>3.4993562997956667e-05</v>
+        <v>3.3991798199576375e-05</v>
       </c>
       <c r="X3">
-        <v>7.0259324899972927e-06</v>
+        <v>7.3126564292932959e-06</v>
       </c>
       <c r="Y3">
-        <v>3.3636494439989339e-05</v>
+        <v>3.3780340277062494e-05</v>
       </c>
       <c r="Z3">
-        <v>1.2068406259105221e-05</v>
+        <v>1.2297618082755761e-05</v>
       </c>
       <c r="AA3">
-        <v>-5.6742895563629365e-08</v>
+        <v>-1.669834780127985e-08</v>
       </c>
       <c r="AB3">
-        <v>3.1955560987219204e-06</v>
+        <v>3.2788772190521498e-06</v>
       </c>
       <c r="AC3">
-        <v>-6.8472474563408703e-07</v>
+        <v>-6.1852160726400007e-07</v>
       </c>
       <c r="AD3">
-        <v>3.2431857514446849e-06</v>
+        <v>3.2796974968972556e-06</v>
       </c>
       <c r="AE3">
-        <v>-8.2469178198846168e-07</v>
+        <v>-7.8189918378808134e-07</v>
       </c>
       <c r="AF3">
-        <v>-1.0605696990893357e-06</v>
+        <v>-1.042311372228119e-06</v>
       </c>
       <c r="AG3">
-        <v>-1.2611444277851479e-08</v>
+        <v>-1.7128619020336376e-08</v>
       </c>
       <c r="AH3">
-        <v>-1.7413413081221549e-06</v>
+        <v>-1.6847001325930749e-06</v>
       </c>
       <c r="AI3">
-        <v>-5.8608815061820762e-06</v>
+        <v>-5.8392477553168619e-06</v>
       </c>
       <c r="AJ3">
-        <v>-0.00029159833162855969</v>
+        <v>-0.00029112257386346889</v>
       </c>
     </row>
     <row r="4">
@@ -809,109 +809,109 @@
         <v>30</v>
       </c>
       <c r="B4">
-        <v>0.0002226663494288233</v>
+        <v>0.00022191120813197171</v>
       </c>
       <c r="C4">
-        <v>3.3578253004639401e-08</v>
+        <v>3.3311247282225842e-08</v>
       </c>
       <c r="D4">
-        <v>-1.6888010944626742e-07</v>
+        <v>-1.6886692693779025e-07</v>
       </c>
       <c r="E4">
-        <v>1.6727282583411538e-09</v>
+        <v>1.6723198359842075e-09</v>
       </c>
       <c r="F4">
-        <v>-1.070237855945143e-07</v>
+        <v>-1.0731508387139053e-07</v>
       </c>
       <c r="G4">
-        <v>1.0273546572809171e-08</v>
+        <v>9.9546817291893955e-09</v>
       </c>
       <c r="H4">
-        <v>6.671136080329205e-08</v>
+        <v>6.6960643529535606e-08</v>
       </c>
       <c r="I4">
-        <v>9.081154328071772e-08</v>
+        <v>9.0616651425715809e-08</v>
       </c>
       <c r="J4">
-        <v>7.7275767180458687e-09</v>
+        <v>7.8308741485893969e-09</v>
       </c>
       <c r="K4">
-        <v>-1.4816671349479194e-08</v>
+        <v>-1.4021310502046913e-08</v>
       </c>
       <c r="L4">
-        <v>2.4445942903902144e-08</v>
+        <v>2.441550343093122e-08</v>
       </c>
       <c r="M4">
-        <v>-7.2624813416632366e-10</v>
+        <v>-6.992392574004635e-10</v>
       </c>
       <c r="N4">
-        <v>-3.958036537029314e-08</v>
+        <v>-3.9303184920979113e-08</v>
       </c>
       <c r="O4">
-        <v>2.6591359089132346e-09</v>
+        <v>2.6575757467650639e-09</v>
       </c>
       <c r="P4">
-        <v>-9.4327821682507526e-10</v>
+        <v>-1.0770642637111888e-09</v>
       </c>
       <c r="Q4">
-        <v>2.9432057953050599e-09</v>
+        <v>2.920987653168926e-09</v>
       </c>
       <c r="R4">
-        <v>1.178256127163396e-06</v>
+        <v>1.17800335508749e-06</v>
       </c>
       <c r="S4">
-        <v>1.2750902600667099e-06</v>
+        <v>1.2746922838202954e-06</v>
       </c>
       <c r="T4">
-        <v>1.2905328601471298e-06</v>
+        <v>1.289991934333784e-06</v>
       </c>
       <c r="U4">
-        <v>-9.2138299886223013e-07</v>
+        <v>-9.1556608696194586e-07</v>
       </c>
       <c r="V4">
-        <v>-3.196357144212363e-08</v>
+        <v>-2.4830345160458135e-08</v>
       </c>
       <c r="W4">
-        <v>-8.0194097487419187e-07</v>
+        <v>-7.9542950311009419e-07</v>
       </c>
       <c r="X4">
-        <v>2.4718955330417382e-09</v>
+        <v>9.5806522806021828e-10</v>
       </c>
       <c r="Y4">
-        <v>-2.6520618624859582e-07</v>
+        <v>-2.656627698468034e-07</v>
       </c>
       <c r="Z4">
-        <v>-2.019680137828838e-08</v>
+        <v>-2.0608999658077889e-08</v>
       </c>
       <c r="AA4">
-        <v>-6.8232360607243115e-09</v>
+        <v>-7.3285979386071544e-09</v>
       </c>
       <c r="AB4">
-        <v>-3.4670737634483481e-08</v>
+        <v>-3.5393546576996303e-08</v>
       </c>
       <c r="AC4">
-        <v>-1.0666190224700449e-08</v>
+        <v>-1.1252977230179877e-08</v>
       </c>
       <c r="AD4">
-        <v>-3.7838868997234808e-08</v>
+        <v>-3.8147409859343333e-08</v>
       </c>
       <c r="AE4">
-        <v>5.3965842930057215e-09</v>
+        <v>5.1737164344847225e-09</v>
       </c>
       <c r="AF4">
-        <v>-7.9962469026845007e-10</v>
+        <v>-1.064809383806628e-09</v>
       </c>
       <c r="AG4">
-        <v>-2.1088776176912062e-09</v>
+        <v>-2.0780692991291288e-09</v>
       </c>
       <c r="AH4">
-        <v>2.52249146753247e-10</v>
+        <v>-8.1730982407672239e-11</v>
       </c>
       <c r="AI4">
-        <v>5.1451634562556878e-08</v>
+        <v>5.1166537494513596e-08</v>
       </c>
       <c r="AJ4">
-        <v>2.7453203057273422e-06</v>
+        <v>2.740662570786367e-06</v>
       </c>
     </row>
     <row r="5">
@@ -919,109 +919,109 @@
         <v>31</v>
       </c>
       <c r="B5">
-        <v>-0.1272697368254139</v>
+        <v>-0.12679276700838688</v>
       </c>
       <c r="C5">
-        <v>-8.241966738302059e-06</v>
+        <v>-8.8045323919624035e-06</v>
       </c>
       <c r="D5">
-        <v>3.7800642651957662e-06</v>
+        <v>3.7553293738077628e-06</v>
       </c>
       <c r="E5">
-        <v>-1.070237855945143e-07</v>
+        <v>-1.0731508387139053e-07</v>
       </c>
       <c r="F5">
-        <v>0.0070011271870271284</v>
+        <v>0.00700400095850054</v>
       </c>
       <c r="G5">
-        <v>0.00089594544329824652</v>
+        <v>0.0008957418220371864</v>
       </c>
       <c r="H5">
-        <v>0.00075579857920740439</v>
+        <v>0.00075554865064359508</v>
       </c>
       <c r="I5">
-        <v>0.00059028655789596291</v>
+        <v>0.00059038987569394604</v>
       </c>
       <c r="J5">
-        <v>6.0484794832162373e-06</v>
+        <v>5.960579394658296e-06</v>
       </c>
       <c r="K5">
-        <v>4.7606042383823601e-06</v>
+        <v>4.9044793795440146e-06</v>
       </c>
       <c r="L5">
-        <v>3.9998818759418743e-07</v>
+        <v>5.1415094624973477e-07</v>
       </c>
       <c r="M5">
-        <v>-1.1265379461933814e-05</v>
+        <v>-1.1148563881110986e-05</v>
       </c>
       <c r="N5">
-        <v>8.3427250543406401e-05</v>
+        <v>8.4164617804920113e-05</v>
       </c>
       <c r="O5">
-        <v>-1.9504447077157633e-07</v>
+        <v>-2.003788892056409e-07</v>
       </c>
       <c r="P5">
-        <v>-7.6681099742058539e-06</v>
+        <v>-7.7041018302724682e-06</v>
       </c>
       <c r="Q5">
-        <v>9.5385467637937026e-06</v>
+        <v>9.4458180992310053e-06</v>
       </c>
       <c r="R5">
-        <v>-8.6934742314077697e-05</v>
+        <v>-8.8519845622121843e-05</v>
       </c>
       <c r="S5">
-        <v>-9.0659463184927195e-05</v>
+        <v>-9.2294009691585785e-05</v>
       </c>
       <c r="T5">
-        <v>-3.7183345565693071e-05</v>
+        <v>-3.8756048365634637e-05</v>
       </c>
       <c r="U5">
-        <v>7.3814813121306189e-05</v>
+        <v>7.5062176232829688e-05</v>
       </c>
       <c r="V5">
-        <v>-6.1034824572332952e-05</v>
+        <v>-5.8716815479269234e-05</v>
       </c>
       <c r="W5">
-        <v>-7.2887149255579191e-05</v>
+        <v>-7.0888410993000771e-05</v>
       </c>
       <c r="X5">
-        <v>4.4439057352386403e-05</v>
+        <v>3.9680682377887424e-05</v>
       </c>
       <c r="Y5">
-        <v>5.7182990474016758e-05</v>
+        <v>5.5510194103842742e-05</v>
       </c>
       <c r="Z5">
-        <v>7.3325191904736575e-06</v>
+        <v>-1.8526597375711552e-06</v>
       </c>
       <c r="AA5">
-        <v>-0.0003879657408031901</v>
+        <v>-0.00038803656878563016</v>
       </c>
       <c r="AB5">
-        <v>-0.0003438759676396907</v>
+        <v>-0.00034371360137544455</v>
       </c>
       <c r="AC5">
-        <v>-0.00032144368232211009</v>
+        <v>-0.00032112532557556934</v>
       </c>
       <c r="AD5">
-        <v>-0.00033621321242632862</v>
+        <v>-0.00033621873709881764</v>
       </c>
       <c r="AE5">
-        <v>-0.00033238896329270599</v>
+        <v>-0.00033220243341828973</v>
       </c>
       <c r="AF5">
-        <v>-0.00033821930018997277</v>
+        <v>-0.00033806807430963762</v>
       </c>
       <c r="AG5">
-        <v>-1.0847629299590987e-06</v>
+        <v>-1.0993353286844086e-06</v>
       </c>
       <c r="AH5">
-        <v>0.0001415248638067281</v>
+        <v>0.00014236051972801872</v>
       </c>
       <c r="AI5">
-        <v>9.6796122039921882e-05</v>
+        <v>9.7074715787209397e-05</v>
       </c>
       <c r="AJ5">
-        <v>-0.00011587260424335971</v>
+        <v>-0.00011186756021824623</v>
       </c>
     </row>
     <row r="6">
@@ -1029,109 +1029,109 @@
         <v>32</v>
       </c>
       <c r="B6">
-        <v>-0.1688379343589245</v>
+        <v>-0.1683958087921309</v>
       </c>
       <c r="C6">
-        <v>1.855934931981686e-05</v>
+        <v>1.8086939996334903e-05</v>
       </c>
       <c r="D6">
-        <v>-9.4488630177101824e-06</v>
+        <v>-9.4589397696312716e-06</v>
       </c>
       <c r="E6">
-        <v>1.0273546572809171e-08</v>
+        <v>9.9546817291893955e-09</v>
       </c>
       <c r="F6">
-        <v>0.00089594544329824652</v>
+        <v>0.0008957418220371864</v>
       </c>
       <c r="G6">
-        <v>0.0023041814130098995</v>
+        <v>0.002303895419386809</v>
       </c>
       <c r="H6">
-        <v>0.00077996021318262672</v>
+        <v>0.00077960752983280944</v>
       </c>
       <c r="I6">
-        <v>0.0005952103883234025</v>
+        <v>0.00059523250974639853</v>
       </c>
       <c r="J6">
-        <v>7.7739891524872083e-06</v>
+        <v>7.7135886135036011e-06</v>
       </c>
       <c r="K6">
-        <v>1.2262476722449255e-05</v>
+        <v>1.2118949465135333e-05</v>
       </c>
       <c r="L6">
-        <v>2.8329295447831688e-06</v>
+        <v>2.9508639095980631e-06</v>
       </c>
       <c r="M6">
-        <v>-9.8463402691600676e-06</v>
+        <v>-9.7677370469626822e-06</v>
       </c>
       <c r="N6">
-        <v>5.25249177570374e-05</v>
+        <v>5.3109162629937508e-05</v>
       </c>
       <c r="O6">
-        <v>1.002143807837706e-07</v>
+        <v>9.6162094389352572e-08</v>
       </c>
       <c r="P6">
-        <v>-8.8487608585180564e-06</v>
+        <v>-8.8817029502552372e-06</v>
       </c>
       <c r="Q6">
-        <v>1.159891588002625e-05</v>
+        <v>1.1544650936498027e-05</v>
       </c>
       <c r="R6">
-        <v>-9.9597856857855599e-06</v>
+        <v>-1.1201843588113769e-05</v>
       </c>
       <c r="S6">
-        <v>5.8883803869194855e-05</v>
+        <v>5.7695089277118083e-05</v>
       </c>
       <c r="T6">
-        <v>8.8132520044139427e-05</v>
+        <v>8.6916696627620653e-05</v>
       </c>
       <c r="U6">
-        <v>8.5320300293013223e-05</v>
+        <v>8.4264841621156683e-05</v>
       </c>
       <c r="V6">
-        <v>1.7200407890189924e-05</v>
+        <v>1.7161572828430218e-05</v>
       </c>
       <c r="W6">
-        <v>7.3103565255648747e-05</v>
+        <v>7.291928654417856e-05</v>
       </c>
       <c r="X6">
-        <v>3.3090857626206661e-05</v>
+        <v>2.9197358813644926e-05</v>
       </c>
       <c r="Y6">
-        <v>-3.0687237558719e-06</v>
+        <v>-4.2873511370718469e-06</v>
       </c>
       <c r="Z6">
-        <v>0.00010496985164197403</v>
+        <v>0.00010021275369884908</v>
       </c>
       <c r="AA6">
-        <v>-7.4596915694141459e-06</v>
+        <v>-6.9627304752195433e-06</v>
       </c>
       <c r="AB6">
-        <v>5.4673612840301764e-05</v>
+        <v>5.539265703185438e-05</v>
       </c>
       <c r="AC6">
-        <v>4.9310795184917987e-05</v>
+        <v>5.0136807107502518e-05</v>
       </c>
       <c r="AD6">
-        <v>4.5919926953411143e-05</v>
+        <v>4.646954156561396e-05</v>
       </c>
       <c r="AE6">
-        <v>6.1274752174575741e-05</v>
+        <v>6.2051039214802662e-05</v>
       </c>
       <c r="AF6">
-        <v>6.3162003885449379e-05</v>
+        <v>6.3854481917491782e-05</v>
       </c>
       <c r="AG6">
-        <v>-7.7394332615398398e-07</v>
+        <v>-7.7939584630807104e-07</v>
       </c>
       <c r="AH6">
-        <v>-2.2030612711127417e-05</v>
+        <v>-2.1333762626362404e-05</v>
       </c>
       <c r="AI6">
-        <v>3.1578757810894997e-05</v>
+        <v>3.1445221417489129e-05</v>
       </c>
       <c r="AJ6">
-        <v>-0.00034392369399797193</v>
+        <v>-0.00033968865995608174</v>
       </c>
     </row>
     <row r="7">
@@ -1139,109 +1139,109 @@
         <v>33</v>
       </c>
       <c r="B7">
-        <v>-0.098748510927967229</v>
+        <v>-0.09870262639364992</v>
       </c>
       <c r="C7">
-        <v>-1.6690760842623853e-08</v>
+        <v>-2.294909408279684e-07</v>
       </c>
       <c r="D7">
-        <v>-1.4270496977472148e-05</v>
+        <v>-1.4325993612345714e-05</v>
       </c>
       <c r="E7">
-        <v>6.671136080329205e-08</v>
+        <v>6.6960643529535606e-08</v>
       </c>
       <c r="F7">
-        <v>0.00075579857920740439</v>
+        <v>0.00075554865064359508</v>
       </c>
       <c r="G7">
-        <v>0.00077996021318262672</v>
+        <v>0.00077960752983280944</v>
       </c>
       <c r="H7">
-        <v>0.0011315132796168752</v>
+        <v>0.0011311127660984905</v>
       </c>
       <c r="I7">
-        <v>0.00058888876881138085</v>
+        <v>0.00058879215333672037</v>
       </c>
       <c r="J7">
-        <v>3.2360955125311024e-06</v>
+        <v>3.2407752346205585e-06</v>
       </c>
       <c r="K7">
-        <v>2.0982357384107968e-05</v>
+        <v>1.9505887923350064e-05</v>
       </c>
       <c r="L7">
-        <v>1.9737877711997582e-06</v>
+        <v>2.5581594988571763e-06</v>
       </c>
       <c r="M7">
-        <v>-2.542223090869507e-06</v>
+        <v>-2.4990374583737832e-06</v>
       </c>
       <c r="N7">
-        <v>7.054752164711747e-05</v>
+        <v>7.0851389711187098e-05</v>
       </c>
       <c r="O7">
-        <v>1.4424970242157938e-07</v>
+        <v>1.4132492164322296e-07</v>
       </c>
       <c r="P7">
-        <v>-6.6178325936134106e-06</v>
+        <v>-6.7121306119295923e-06</v>
       </c>
       <c r="Q7">
-        <v>6.7493930827819065e-06</v>
+        <v>6.7243614272814922e-06</v>
       </c>
       <c r="R7">
-        <v>5.1677075663596421e-05</v>
+        <v>5.0574442507335157e-05</v>
       </c>
       <c r="S7">
-        <v>7.3886624544214119e-05</v>
+        <v>7.2850241262352282e-05</v>
       </c>
       <c r="T7">
-        <v>0.00012020170536684142</v>
+        <v>0.00011927957709169772</v>
       </c>
       <c r="U7">
-        <v>0.00014718677037586051</v>
+        <v>0.00013884443051822155</v>
       </c>
       <c r="V7">
-        <v>0.00011459949982876333</v>
+        <v>0.0001068796270325013</v>
       </c>
       <c r="W7">
-        <v>0.00014111864591351823</v>
+        <v>0.00013324158118378172</v>
       </c>
       <c r="X7">
-        <v>2.723835413366407e-05</v>
+        <v>2.3677383821942535e-05</v>
       </c>
       <c r="Y7">
-        <v>-9.4038118989487331e-06</v>
+        <v>-1.0649829981368006e-05</v>
       </c>
       <c r="Z7">
-        <v>3.5154995881514023e-05</v>
+        <v>3.0256074356232451e-05</v>
       </c>
       <c r="AA7">
-        <v>-3.0570556696946517e-07</v>
+        <v>-7.0027007500529127e-09</v>
       </c>
       <c r="AB7">
-        <v>2.9363457396843162e-05</v>
+        <v>2.9894755415335817e-05</v>
       </c>
       <c r="AC7">
-        <v>3.4039029180815849e-05</v>
+        <v>3.4667182851725134e-05</v>
       </c>
       <c r="AD7">
-        <v>3.1579243025551076e-05</v>
+        <v>3.1970297516162294e-05</v>
       </c>
       <c r="AE7">
-        <v>5.5209910383559709e-05</v>
+        <v>5.5802811006823383e-05</v>
       </c>
       <c r="AF7">
-        <v>4.0949210002263745e-05</v>
+        <v>4.1433461054875513e-05</v>
       </c>
       <c r="AG7">
-        <v>-3.6728508684652067e-06</v>
+        <v>-3.674586900181292e-06</v>
       </c>
       <c r="AH7">
-        <v>-2.6350577141604002e-06</v>
+        <v>-2.2220081230308599e-06</v>
       </c>
       <c r="AI7">
-        <v>1.7121646091136532e-05</v>
+        <v>1.696137444533167e-05</v>
       </c>
       <c r="AJ7">
-        <v>-0.00028215220952928924</v>
+        <v>-0.00027024954788798375</v>
       </c>
     </row>
     <row r="8">
@@ -1249,109 +1249,109 @@
         <v>34</v>
       </c>
       <c r="B8">
-        <v>-0.040879888998375774</v>
+        <v>-0.040813992003821152</v>
       </c>
       <c r="C8">
-        <v>-7.3914409938055097e-07</v>
+        <v>-1.0622280811435487e-06</v>
       </c>
       <c r="D8">
-        <v>-1.2432825514939752e-05</v>
+        <v>-1.2437410010059336e-05</v>
       </c>
       <c r="E8">
-        <v>9.081154328071772e-08</v>
+        <v>9.0616651425715809e-08</v>
       </c>
       <c r="F8">
-        <v>0.00059028655789596291</v>
+        <v>0.00059038987569394604</v>
       </c>
       <c r="G8">
-        <v>0.0005952103883234025</v>
+        <v>0.00059523250974639853</v>
       </c>
       <c r="H8">
-        <v>0.00058888876881138085</v>
+        <v>0.00058879215333672037</v>
       </c>
       <c r="I8">
-        <v>0.00069174820066388628</v>
+        <v>0.00069174596310155902</v>
       </c>
       <c r="J8">
-        <v>2.0368523341756255e-06</v>
+        <v>2.0586825835604219e-06</v>
       </c>
       <c r="K8">
-        <v>2.5789119911564537e-06</v>
+        <v>1.8306032430465029e-06</v>
       </c>
       <c r="L8">
-        <v>5.5289611406675109e-08</v>
+        <v>2.2732877948179659e-08</v>
       </c>
       <c r="M8">
-        <v>-4.3570862052101599e-06</v>
+        <v>-4.3066240526775848e-06</v>
       </c>
       <c r="N8">
-        <v>8.6852708167312485e-05</v>
+        <v>8.7255528410043047e-05</v>
       </c>
       <c r="O8">
-        <v>-3.5753092428886456e-08</v>
+        <v>-4.059398181710641e-08</v>
       </c>
       <c r="P8">
-        <v>-5.4800625058765496e-06</v>
+        <v>-5.6162502440788658e-06</v>
       </c>
       <c r="Q8">
-        <v>6.5896982252864441e-06</v>
+        <v>6.5631159500669998e-06</v>
       </c>
       <c r="R8">
-        <v>-9.9348736545875816e-06</v>
+        <v>-1.1464132507908167e-05</v>
       </c>
       <c r="S8">
-        <v>-1.0058234629685758e-05</v>
+        <v>-1.175040090011482e-05</v>
       </c>
       <c r="T8">
-        <v>2.1311724134353537e-05</v>
+        <v>1.9711166127756782e-05</v>
       </c>
       <c r="U8">
-        <v>1.1399888685241705e-05</v>
+        <v>4.6850382681404333e-06</v>
       </c>
       <c r="V8">
-        <v>1.307100996085454e-05</v>
+        <v>5.6209481419087256e-06</v>
       </c>
       <c r="W8">
-        <v>2.0899714964468818e-05</v>
+        <v>1.3952038894635876e-05</v>
       </c>
       <c r="X8">
-        <v>1.1635607613298661e-05</v>
+        <v>8.7386925523103588e-06</v>
       </c>
       <c r="Y8">
-        <v>7.0885674723720956e-06</v>
+        <v>6.2293114007861089e-06</v>
       </c>
       <c r="Z8">
-        <v>2.3598843092312557e-05</v>
+        <v>1.5647627642145255e-05</v>
       </c>
       <c r="AA8">
-        <v>-3.490996641805142e-05</v>
+        <v>-3.4380106914374197e-05</v>
       </c>
       <c r="AB8">
-        <v>-2.0527092432584375e-05</v>
+        <v>-1.9935297925802279e-05</v>
       </c>
       <c r="AC8">
-        <v>-7.3287296165411089e-06</v>
+        <v>-6.5916114264355285e-06</v>
       </c>
       <c r="AD8">
-        <v>-1.6400313896113033e-05</v>
+        <v>-1.5896844646890568e-05</v>
       </c>
       <c r="AE8">
-        <v>7.8808003916201817e-07</v>
+        <v>1.4989926946922406e-06</v>
       </c>
       <c r="AF8">
-        <v>-1.0023184592857515e-05</v>
+        <v>-9.3011282859750245e-06</v>
       </c>
       <c r="AG8">
-        <v>-2.2712442873387257e-06</v>
+        <v>-2.2756531562364967e-06</v>
       </c>
       <c r="AH8">
-        <v>-2.4612296879961913e-05</v>
+        <v>-2.4201914548092619e-05</v>
       </c>
       <c r="AI8">
-        <v>3.2512755883705105e-06</v>
+        <v>3.1194738703972828e-06</v>
       </c>
       <c r="AJ8">
-        <v>-0.00014186833008786152</v>
+        <v>-0.00013200696768560455</v>
       </c>
     </row>
     <row r="9">
@@ -1359,109 +1359,109 @@
         <v>35</v>
       </c>
       <c r="B9">
-        <v>0.52230224930162195</v>
+        <v>0.52230013548726506</v>
       </c>
       <c r="C9">
-        <v>1.6071703646335672e-06</v>
+        <v>1.565604587709865e-06</v>
       </c>
       <c r="D9">
-        <v>-9.6927094243349794e-07</v>
+        <v>-9.8708412104348555e-07</v>
       </c>
       <c r="E9">
-        <v>7.7275767180458687e-09</v>
+        <v>7.8308741485893969e-09</v>
       </c>
       <c r="F9">
-        <v>6.0484794832162373e-06</v>
+        <v>5.960579394658296e-06</v>
       </c>
       <c r="G9">
-        <v>7.7739891524872083e-06</v>
+        <v>7.7135886135036011e-06</v>
       </c>
       <c r="H9">
-        <v>3.2360955125311024e-06</v>
+        <v>3.2407752346205585e-06</v>
       </c>
       <c r="I9">
-        <v>2.0368523341756255e-06</v>
+        <v>2.0586825835604219e-06</v>
       </c>
       <c r="J9">
-        <v>5.4637988424876221e-05</v>
+        <v>5.4615361033128088e-05</v>
       </c>
       <c r="K9">
-        <v>-6.589703952821758e-06</v>
+        <v>-6.7124776851584324e-06</v>
       </c>
       <c r="L9">
-        <v>6.727853820748999e-07</v>
+        <v>8.9569633382951323e-07</v>
       </c>
       <c r="M9">
-        <v>-2.1129394291012563e-05</v>
+        <v>-2.1115831598526515e-05</v>
       </c>
       <c r="N9">
-        <v>-1.5943984269933549e-06</v>
+        <v>-1.5487956687778484e-06</v>
       </c>
       <c r="O9">
-        <v>1.3473076405657386e-08</v>
+        <v>1.3356654009354097e-08</v>
       </c>
       <c r="P9">
-        <v>-5.5738154889283928e-05</v>
+        <v>-5.5733732647365725e-05</v>
       </c>
       <c r="Q9">
-        <v>2.2172052801245286e-05</v>
+        <v>2.2159030191799726e-05</v>
       </c>
       <c r="R9">
-        <v>-1.4521490597421205e-05</v>
+        <v>-1.458293378569843e-05</v>
       </c>
       <c r="S9">
-        <v>-1.6105590771735326e-05</v>
+        <v>-1.6096076573179211e-05</v>
       </c>
       <c r="T9">
-        <v>-1.8653698068622268e-05</v>
+        <v>-1.8697484877354045e-05</v>
       </c>
       <c r="U9">
-        <v>-5.3257989886495712e-05</v>
+        <v>-5.2694409922412577e-05</v>
       </c>
       <c r="V9">
-        <v>-5.1986896564435784e-05</v>
+        <v>-5.095736396605553e-05</v>
       </c>
       <c r="W9">
-        <v>-5.8470650969077207e-05</v>
+        <v>-5.7636971513690732e-05</v>
       </c>
       <c r="X9">
-        <v>1.9745750342813263e-06</v>
+        <v>1.5187159163144827e-06</v>
       </c>
       <c r="Y9">
-        <v>-9.8666629231824524e-08</v>
+        <v>-2.7228154228016899e-07</v>
       </c>
       <c r="Z9">
-        <v>1.1311372692250869e-05</v>
+        <v>1.0944686118085697e-05</v>
       </c>
       <c r="AA9">
-        <v>4.8588571204757222e-06</v>
+        <v>4.563412095390282e-06</v>
       </c>
       <c r="AB9">
-        <v>5.9795931515586247e-06</v>
+        <v>5.7019445878961817e-06</v>
       </c>
       <c r="AC9">
-        <v>3.8411332852990127e-06</v>
+        <v>3.5746262626243575e-06</v>
       </c>
       <c r="AD9">
-        <v>3.582330656313413e-07</v>
+        <v>6.8099845108449441e-08</v>
       </c>
       <c r="AE9">
-        <v>5.711689207059639e-06</v>
+        <v>5.4088922260687786e-06</v>
       </c>
       <c r="AF9">
-        <v>1.2897999056349304e-05</v>
+        <v>1.2543127161724476e-05</v>
       </c>
       <c r="AG9">
-        <v>9.7116927496613578e-07</v>
+        <v>9.7408680415872816e-07</v>
       </c>
       <c r="AH9">
-        <v>-1.5609354672070172e-06</v>
+        <v>-1.6489243343083217e-06</v>
       </c>
       <c r="AI9">
-        <v>-1.3730403899072507e-05</v>
+        <v>-1.3764479233565625e-05</v>
       </c>
       <c r="AJ9">
-        <v>3.89467405004832e-05</v>
+        <v>3.9220754620448019e-05</v>
       </c>
     </row>
     <row r="10">
@@ -1469,109 +1469,109 @@
         <v>36</v>
       </c>
       <c r="B10">
-        <v>0.11838812140458939</v>
+        <v>0.11922627834683182</v>
       </c>
       <c r="C10">
-        <v>-5.7547310330336932e-05</v>
+        <v>-5.6389401741769238e-05</v>
       </c>
       <c r="D10">
-        <v>-9.6672651619156798e-07</v>
+        <v>-1.0741711980089554e-06</v>
       </c>
       <c r="E10">
-        <v>-1.4816671349479194e-08</v>
+        <v>-1.4021310502046913e-08</v>
       </c>
       <c r="F10">
-        <v>4.7606042383823601e-06</v>
+        <v>4.9044793795440146e-06</v>
       </c>
       <c r="G10">
-        <v>1.2262476722449255e-05</v>
+        <v>1.2118949465135333e-05</v>
       </c>
       <c r="H10">
-        <v>2.0982357384107968e-05</v>
+        <v>1.9505887923350064e-05</v>
       </c>
       <c r="I10">
-        <v>2.5789119911564537e-06</v>
+        <v>1.8306032430465029e-06</v>
       </c>
       <c r="J10">
-        <v>-6.589703952821758e-06</v>
+        <v>-6.7124776851584324e-06</v>
       </c>
       <c r="K10">
-        <v>0.00040416536467221626</v>
+        <v>0.00041378812144239282</v>
       </c>
       <c r="L10">
-        <v>-2.46725333418743e-05</v>
+        <v>-2.5143554407136451e-05</v>
       </c>
       <c r="M10">
-        <v>-1.4549384709005733e-07</v>
+        <v>-3.184080884462033e-07</v>
       </c>
       <c r="N10">
-        <v>5.794569055239447e-05</v>
+        <v>5.6727634811130116e-05</v>
       </c>
       <c r="O10">
-        <v>-4.2195512494135536e-08</v>
+        <v>-3.9484048506591718e-08</v>
       </c>
       <c r="P10">
-        <v>5.259438075629881e-06</v>
+        <v>5.4196531910764025e-06</v>
       </c>
       <c r="Q10">
-        <v>1.5325239321903013e-06</v>
+        <v>1.7210574420158174e-06</v>
       </c>
       <c r="R10">
-        <v>7.2942141221193967e-05</v>
+        <v>7.3841560566632013e-05</v>
       </c>
       <c r="S10">
-        <v>3.8903304867473406e-05</v>
+        <v>3.9047724367708022e-05</v>
       </c>
       <c r="T10">
-        <v>-4.2076096725377865e-05</v>
+        <v>-4.2614332092917953e-05</v>
       </c>
       <c r="U10">
-        <v>0.002999366440053402</v>
+        <v>0.0030734036057055206</v>
       </c>
       <c r="V10">
-        <v>0.003052238522011635</v>
+        <v>0.0031272941639419976</v>
       </c>
       <c r="W10">
-        <v>0.0030930118556961434</v>
+        <v>0.0031694215943281136</v>
       </c>
       <c r="X10">
-        <v>-1.42044052615582e-05</v>
+        <v>-1.3646221008052379e-05</v>
       </c>
       <c r="Y10">
-        <v>1.5362234224736333e-05</v>
+        <v>1.4936732166567914e-05</v>
       </c>
       <c r="Z10">
-        <v>-2.5286700238444392e-05</v>
+        <v>-2.3331419959735523e-05</v>
       </c>
       <c r="AA10">
-        <v>-1.2605071197613945e-05</v>
+        <v>-1.3311846407239661e-05</v>
       </c>
       <c r="AB10">
-        <v>-4.8552193531725685e-05</v>
+        <v>-5.0562670370734924e-05</v>
       </c>
       <c r="AC10">
-        <v>-6.3493944229510251e-05</v>
+        <v>-6.5379825519015626e-05</v>
       </c>
       <c r="AD10">
-        <v>-6.7674234959375079e-06</v>
+        <v>-7.5124868898083022e-06</v>
       </c>
       <c r="AE10">
-        <v>-3.2184299087756286e-05</v>
+        <v>-3.3859203520010322e-05</v>
       </c>
       <c r="AF10">
-        <v>-2.8043883466234308e-05</v>
+        <v>-3.0170302346778518e-05</v>
       </c>
       <c r="AG10">
-        <v>-5.0741236670478877e-07</v>
+        <v>-4.2931440931529312e-07</v>
       </c>
       <c r="AH10">
-        <v>-1.4728989282367707e-05</v>
+        <v>-1.4824104831611794e-05</v>
       </c>
       <c r="AI10">
-        <v>6.3375947813017154e-06</v>
+        <v>6.6164744494148471e-06</v>
       </c>
       <c r="AJ10">
-        <v>-0.0029244195253660971</v>
+        <v>-0.0029969009466277357</v>
       </c>
     </row>
     <row r="11">
@@ -1579,109 +1579,109 @@
         <v>37</v>
       </c>
       <c r="B11">
-        <v>0.014659101291421114</v>
+        <v>0.013920849456736415</v>
       </c>
       <c r="C11">
-        <v>-5.6414867353351785e-06</v>
+        <v>-5.7524396055269288e-06</v>
       </c>
       <c r="D11">
-        <v>-2.6211966690228471e-06</v>
+        <v>-2.6350739653878427e-06</v>
       </c>
       <c r="E11">
-        <v>2.4445942903902144e-08</v>
+        <v>2.441550343093122e-08</v>
       </c>
       <c r="F11">
-        <v>3.9998818759418743e-07</v>
+        <v>5.1415094624973477e-07</v>
       </c>
       <c r="G11">
-        <v>2.8329295447831688e-06</v>
+        <v>2.9508639095980631e-06</v>
       </c>
       <c r="H11">
-        <v>1.9737877711997582e-06</v>
+        <v>2.5581594988571763e-06</v>
       </c>
       <c r="I11">
-        <v>5.5289611406675109e-08</v>
+        <v>2.2732877948179659e-08</v>
       </c>
       <c r="J11">
-        <v>6.727853820748999e-07</v>
+        <v>8.9569633382951323e-07</v>
       </c>
       <c r="K11">
-        <v>-2.46725333418743e-05</v>
+        <v>-2.5143554407136451e-05</v>
       </c>
       <c r="L11">
-        <v>2.0645238593851432e-05</v>
+        <v>2.0933769564816489e-05</v>
       </c>
       <c r="M11">
-        <v>5.1357797594993791e-07</v>
+        <v>4.9075322493113249e-07</v>
       </c>
       <c r="N11">
-        <v>5.4187298588879362e-06</v>
+        <v>5.515883724139557e-06</v>
       </c>
       <c r="O11">
-        <v>2.5109967207929017e-08</v>
+        <v>2.5454904168992517e-08</v>
       </c>
       <c r="P11">
-        <v>-1.0909205124439425e-06</v>
+        <v>-1.3151635669412123e-06</v>
       </c>
       <c r="Q11">
-        <v>-1.6022301973270842e-07</v>
+        <v>-1.2528513505008618e-07</v>
       </c>
       <c r="R11">
-        <v>8.7873443139225703e-06</v>
+        <v>9.1036503715173502e-06</v>
       </c>
       <c r="S11">
-        <v>6.0585243863096099e-06</v>
+        <v>6.1964832623185661e-06</v>
       </c>
       <c r="T11">
-        <v>1.8206085427353066e-06</v>
+        <v>2.0631416918886031e-06</v>
       </c>
       <c r="U11">
-        <v>-7.7503693165586649e-05</v>
+        <v>-7.9252671789549044e-05</v>
       </c>
       <c r="V11">
-        <v>-7.8663409873098978e-05</v>
+        <v>-7.9886872264672588e-05</v>
       </c>
       <c r="W11">
-        <v>-6.546711117600631e-05</v>
+        <v>-6.6873346616419982e-05</v>
       </c>
       <c r="X11">
-        <v>-3.9028183123111055e-06</v>
+        <v>-3.9952673498581093e-06</v>
       </c>
       <c r="Y11">
-        <v>1.4581552651866553e-07</v>
+        <v>1.9520252475299079e-07</v>
       </c>
       <c r="Z11">
-        <v>-1.3796579052501655e-05</v>
+        <v>-1.2159413859166159e-05</v>
       </c>
       <c r="AA11">
-        <v>3.617953627115794e-06</v>
+        <v>3.5730168075219011e-06</v>
       </c>
       <c r="AB11">
-        <v>2.67415623426097e-06</v>
+        <v>2.6211495365810082e-06</v>
       </c>
       <c r="AC11">
-        <v>3.9441884765833681e-06</v>
+        <v>3.866317762942793e-06</v>
       </c>
       <c r="AD11">
-        <v>3.5712211650880036e-06</v>
+        <v>3.6237078676050022e-06</v>
       </c>
       <c r="AE11">
-        <v>2.9579091092853315e-06</v>
+        <v>3.0357571961333704e-06</v>
       </c>
       <c r="AF11">
-        <v>3.1652168661934511e-06</v>
+        <v>3.2406817488013394e-06</v>
       </c>
       <c r="AG11">
-        <v>-2.2299980491866647e-07</v>
+        <v>-2.0092746265654915e-07</v>
       </c>
       <c r="AH11">
-        <v>-1.2428005193927032e-06</v>
+        <v>-1.9726154642598932e-06</v>
       </c>
       <c r="AI11">
-        <v>-2.4194662693187976e-06</v>
+        <v>-2.6014107358379848e-06</v>
       </c>
       <c r="AJ11">
-        <v>0.00011265633956514313</v>
+        <v>0.00011415001739169365</v>
       </c>
     </row>
     <row r="12">
@@ -1689,109 +1689,109 @@
         <v>38</v>
       </c>
       <c r="B12">
-        <v>0.29268427736767672</v>
+        <v>0.29283488485079845</v>
       </c>
       <c r="C12">
-        <v>-8.3731349492827086e-07</v>
+        <v>-8.8146591988703629e-07</v>
       </c>
       <c r="D12">
-        <v>-2.8019044137940674e-07</v>
+        <v>-2.8032076893867846e-07</v>
       </c>
       <c r="E12">
-        <v>-7.2624813416632366e-10</v>
+        <v>-6.992392574004635e-10</v>
       </c>
       <c r="F12">
-        <v>-1.1265379461933814e-05</v>
+        <v>-1.1148563881110986e-05</v>
       </c>
       <c r="G12">
-        <v>-9.8463402691600676e-06</v>
+        <v>-9.7677370469626822e-06</v>
       </c>
       <c r="H12">
-        <v>-2.542223090869507e-06</v>
+        <v>-2.4990374583737832e-06</v>
       </c>
       <c r="I12">
-        <v>-4.3570862052101599e-06</v>
+        <v>-4.3066240526775848e-06</v>
       </c>
       <c r="J12">
-        <v>-2.1129394291012563e-05</v>
+        <v>-2.1115831598526515e-05</v>
       </c>
       <c r="K12">
-        <v>-1.4549384709005733e-07</v>
+        <v>-3.184080884462033e-07</v>
       </c>
       <c r="L12">
-        <v>5.1357797594993791e-07</v>
+        <v>4.9075322493113249e-07</v>
       </c>
       <c r="M12">
-        <v>4.1741776084694758e-05</v>
+        <v>4.1733042371213853e-05</v>
       </c>
       <c r="N12">
-        <v>9.082504181894794e-08</v>
+        <v>1.6666764150998193e-07</v>
       </c>
       <c r="O12">
-        <v>5.6320424013921407e-09</v>
+        <v>5.0572901578541346e-09</v>
       </c>
       <c r="P12">
-        <v>2.4114701378240636e-05</v>
+        <v>2.4099562305945632e-05</v>
       </c>
       <c r="Q12">
-        <v>-4.2136373622518569e-05</v>
+        <v>-4.2120458483468737e-05</v>
       </c>
       <c r="R12">
-        <v>-2.2297393878621718e-07</v>
+        <v>-3.5767592206161348e-07</v>
       </c>
       <c r="S12">
-        <v>-6.248287619315995e-06</v>
+        <v>-6.4874106035148872e-06</v>
       </c>
       <c r="T12">
-        <v>-1.0596812772207388e-05</v>
+        <v>-1.0750340923965505e-05</v>
       </c>
       <c r="U12">
-        <v>1.436465799518815e-05</v>
+        <v>1.2779232817086045e-05</v>
       </c>
       <c r="V12">
-        <v>-9.063151714073773e-07</v>
+        <v>-2.7945135216985721e-06</v>
       </c>
       <c r="W12">
-        <v>1.7803446417798033e-06</v>
+        <v>4.6765662453192566e-08</v>
       </c>
       <c r="X12">
-        <v>4.4989500669006581e-06</v>
+        <v>4.7043120312743931e-06</v>
       </c>
       <c r="Y12">
-        <v>-1.9094483336881404e-06</v>
+        <v>-1.6823651593301702e-06</v>
       </c>
       <c r="Z12">
-        <v>-2.7157703428098845e-05</v>
+        <v>-2.8533560617156782e-05</v>
       </c>
       <c r="AA12">
-        <v>-3.6761612594367478e-06</v>
+        <v>-3.2530016249742996e-06</v>
       </c>
       <c r="AB12">
-        <v>-7.0413633157318348e-06</v>
+        <v>-6.5779641755963787e-06</v>
       </c>
       <c r="AC12">
-        <v>-5.5340363770648717e-06</v>
+        <v>-5.0858548197488004e-06</v>
       </c>
       <c r="AD12">
-        <v>-4.717933822105455e-06</v>
+        <v>-4.3034677956591379e-06</v>
       </c>
       <c r="AE12">
-        <v>-6.538428092497768e-06</v>
+        <v>-6.1215711150157103e-06</v>
       </c>
       <c r="AF12">
-        <v>-2.9057213094194881e-06</v>
+        <v>-2.3852948837333645e-06</v>
       </c>
       <c r="AG12">
-        <v>1.4247585618967477e-06</v>
+        <v>1.423080122863651e-06</v>
       </c>
       <c r="AH12">
-        <v>-2.2626364425119899e-06</v>
+        <v>-2.1417966548243286e-06</v>
       </c>
       <c r="AI12">
-        <v>-2.5026242273638586e-06</v>
+        <v>-2.4784653892905579e-06</v>
       </c>
       <c r="AJ12">
-        <v>-2.8201969746309123e-05</v>
+        <v>-2.6998152560893485e-05</v>
       </c>
     </row>
     <row r="13">
@@ -1799,109 +1799,109 @@
         <v>39</v>
       </c>
       <c r="B13">
-        <v>0.089514165590736716</v>
+        <v>0.089568989617882802</v>
       </c>
       <c r="C13">
-        <v>-0.00042477101755662413</v>
+        <v>-0.00042494060407132281</v>
       </c>
       <c r="D13">
-        <v>8.6552023993750523e-07</v>
+        <v>8.4233338508026468e-07</v>
       </c>
       <c r="E13">
-        <v>-3.958036537029314e-08</v>
+        <v>-3.9303184920979113e-08</v>
       </c>
       <c r="F13">
-        <v>8.3427250543406401e-05</v>
+        <v>8.4164617804920113e-05</v>
       </c>
       <c r="G13">
-        <v>5.25249177570374e-05</v>
+        <v>5.3109162629937508e-05</v>
       </c>
       <c r="H13">
-        <v>7.054752164711747e-05</v>
+        <v>7.0851389711187098e-05</v>
       </c>
       <c r="I13">
-        <v>8.6852708167312485e-05</v>
+        <v>8.7255528410043047e-05</v>
       </c>
       <c r="J13">
-        <v>-1.5943984269933549e-06</v>
+        <v>-1.5487956687778484e-06</v>
       </c>
       <c r="K13">
-        <v>5.794569055239447e-05</v>
+        <v>5.6727634811130116e-05</v>
       </c>
       <c r="L13">
-        <v>5.4187298588879362e-06</v>
+        <v>5.515883724139557e-06</v>
       </c>
       <c r="M13">
-        <v>9.082504181894794e-08</v>
+        <v>1.6666764150998193e-07</v>
       </c>
       <c r="N13">
-        <v>0.0086560143558350976</v>
+        <v>0.0086567481466529872</v>
       </c>
       <c r="O13">
-        <v>1.5224934966399831e-06</v>
+        <v>1.5202882870387675e-06</v>
       </c>
       <c r="P13">
-        <v>-1.2797378699486503e-05</v>
+        <v>-1.2975329004103397e-05</v>
       </c>
       <c r="Q13">
-        <v>5.5769530201830141e-05</v>
+        <v>5.5388937112973855e-05</v>
       </c>
       <c r="R13">
-        <v>0.0050136053871246969</v>
+        <v>0.0050128377310155068</v>
       </c>
       <c r="S13">
-        <v>0.0049888765242035709</v>
+        <v>0.0049879202616647132</v>
       </c>
       <c r="T13">
-        <v>0.0049611952792562239</v>
+        <v>0.0049603393092707698</v>
       </c>
       <c r="U13">
-        <v>0.00047718190255935291</v>
+        <v>0.00046846746817583596</v>
       </c>
       <c r="V13">
-        <v>0.0003922445210037314</v>
+        <v>0.00038171065689898438</v>
       </c>
       <c r="W13">
-        <v>0.00054544506682772985</v>
+        <v>0.00053554605412811174</v>
       </c>
       <c r="X13">
-        <v>-4.7132921023004847e-05</v>
+        <v>-4.6811606737229939e-05</v>
       </c>
       <c r="Y13">
-        <v>1.7089749209726239e-06</v>
+        <v>1.7097905717668714e-06</v>
       </c>
       <c r="Z13">
-        <v>-0.00019790241739100958</v>
+        <v>-0.00020313281106342559</v>
       </c>
       <c r="AA13">
-        <v>-8.8766111784358784e-05</v>
+        <v>-8.9020669276913822e-05</v>
       </c>
       <c r="AB13">
-        <v>-0.00010466159803707801</v>
+        <v>-0.000104670008912009</v>
       </c>
       <c r="AC13">
-        <v>-0.00011200549554738826</v>
+        <v>-0.00011217044980173924</v>
       </c>
       <c r="AD13">
-        <v>-8.7585297829528234e-05</v>
+        <v>-8.7723857067682938e-05</v>
       </c>
       <c r="AE13">
-        <v>-0.0001014477349346528</v>
+        <v>-0.00010165862295907183</v>
       </c>
       <c r="AF13">
-        <v>-0.0001261852041956013</v>
+        <v>-0.00012612118486749618</v>
       </c>
       <c r="AG13">
-        <v>-6.4342264269657049e-07</v>
+        <v>-6.4948030421008705e-07</v>
       </c>
       <c r="AH13">
-        <v>-2.2164138048162176e-05</v>
+        <v>-2.2028666156672684e-05</v>
       </c>
       <c r="AI13">
-        <v>5.4763436536255702e-05</v>
+        <v>5.4917609153452753e-05</v>
       </c>
       <c r="AJ13">
-        <v>-0.0051345458324562228</v>
+        <v>-0.0051239555920228677</v>
       </c>
     </row>
     <row r="14">
@@ -1909,109 +1909,109 @@
         <v>40</v>
       </c>
       <c r="B14">
-        <v>-0.0022670456225304925</v>
+        <v>-0.0022717155046265104</v>
       </c>
       <c r="C14">
-        <v>9.0939883462974436e-08</v>
+        <v>9.2940732608185477e-08</v>
       </c>
       <c r="D14">
-        <v>-2.8893583893147131e-07</v>
+        <v>-2.8857191346755779e-07</v>
       </c>
       <c r="E14">
-        <v>2.6591359089132346e-09</v>
+        <v>2.6575757467650639e-09</v>
       </c>
       <c r="F14">
-        <v>-1.9504447077157633e-07</v>
+        <v>-2.003788892056409e-07</v>
       </c>
       <c r="G14">
-        <v>1.002143807837706e-07</v>
+        <v>9.6162094389352572e-08</v>
       </c>
       <c r="H14">
-        <v>1.4424970242157938e-07</v>
+        <v>1.4132492164322296e-07</v>
       </c>
       <c r="I14">
-        <v>-3.5753092428886456e-08</v>
+        <v>-4.059398181710641e-08</v>
       </c>
       <c r="J14">
-        <v>1.3473076405657386e-08</v>
+        <v>1.3356654009354097e-08</v>
       </c>
       <c r="K14">
-        <v>-4.2195512494135536e-08</v>
+        <v>-3.9484048506591718e-08</v>
       </c>
       <c r="L14">
-        <v>2.5109967207929017e-08</v>
+        <v>2.5454904168992517e-08</v>
       </c>
       <c r="M14">
-        <v>5.6320424013921407e-09</v>
+        <v>5.0572901578541346e-09</v>
       </c>
       <c r="N14">
-        <v>1.5224934966399831e-06</v>
+        <v>1.5202882870387675e-06</v>
       </c>
       <c r="O14">
-        <v>2.4443940829377713e-07</v>
+        <v>2.4456272683392755e-07</v>
       </c>
       <c r="P14">
-        <v>-6.029852900389148e-07</v>
+        <v>-6.0464082912555599e-07</v>
       </c>
       <c r="Q14">
-        <v>-6.4103127571306589e-06</v>
+        <v>-6.4124891978603217e-06</v>
       </c>
       <c r="R14">
-        <v>0.00010444461320091992</v>
+        <v>0.00010449281622900439</v>
       </c>
       <c r="S14">
-        <v>0.00010458397880891684</v>
+        <v>0.00010463315483627241</v>
       </c>
       <c r="T14">
-        <v>0.00010462847082416017</v>
+        <v>0.00010467593786300072</v>
       </c>
       <c r="U14">
-        <v>-1.745433348129832e-06</v>
+        <v>-1.7245315808773381e-06</v>
       </c>
       <c r="V14">
-        <v>-1.2286863435495218e-07</v>
+        <v>-9.6290245728269941e-08</v>
       </c>
       <c r="W14">
-        <v>-6.0376742978289683e-07</v>
+        <v>-5.78371426275011e-07</v>
       </c>
       <c r="X14">
-        <v>5.0711547101110088e-07</v>
+        <v>5.2258944216950771e-07</v>
       </c>
       <c r="Y14">
-        <v>-1.2194903045869823e-06</v>
+        <v>-1.2084750160305139e-06</v>
       </c>
       <c r="Z14">
-        <v>2.1349448885148807e-06</v>
+        <v>2.2032967250036368e-06</v>
       </c>
       <c r="AA14">
-        <v>-1.5685781831742667e-07</v>
+        <v>-1.5678825988286646e-07</v>
       </c>
       <c r="AB14">
-        <v>-1.1896263647887223e-07</v>
+        <v>-1.2004808776803968e-07</v>
       </c>
       <c r="AC14">
-        <v>6.7224863809878748e-08</v>
+        <v>6.8078232379643612e-08</v>
       </c>
       <c r="AD14">
-        <v>-2.8464340596502083e-07</v>
+        <v>-2.8313884517011309e-07</v>
       </c>
       <c r="AE14">
-        <v>-2.2703670235616047e-07</v>
+        <v>-2.2422821792017136e-07</v>
       </c>
       <c r="AF14">
-        <v>-3.4574382276464022e-08</v>
+        <v>-3.5245553032679024e-08</v>
       </c>
       <c r="AG14">
-        <v>-1.2076834283234572e-08</v>
+        <v>-1.1950083090177597e-08</v>
       </c>
       <c r="AH14">
-        <v>-5.7196816117010857e-07</v>
+        <v>-5.6983902704059431e-07</v>
       </c>
       <c r="AI14">
-        <v>8.8186565686442837e-08</v>
+        <v>8.643054992173987e-08</v>
       </c>
       <c r="AJ14">
-        <v>-9.666866067589903e-05</v>
+        <v>-9.6764647735694614e-05</v>
       </c>
     </row>
     <row r="15">
@@ -2019,109 +2019,109 @@
         <v>41</v>
       </c>
       <c r="B15">
-        <v>-0.019658465172190144</v>
+        <v>-0.019750788209937347</v>
       </c>
       <c r="C15">
-        <v>-5.5365494455151705e-07</v>
+        <v>-4.8286539081760669e-07</v>
       </c>
       <c r="D15">
-        <v>3.1809939197751243e-07</v>
+        <v>3.4489570855576878e-07</v>
       </c>
       <c r="E15">
-        <v>-9.4327821682507526e-10</v>
+        <v>-1.0770642637111888e-09</v>
       </c>
       <c r="F15">
-        <v>-7.6681099742058539e-06</v>
+        <v>-7.7041018302724682e-06</v>
       </c>
       <c r="G15">
-        <v>-8.8487608585180564e-06</v>
+        <v>-8.8817029502552372e-06</v>
       </c>
       <c r="H15">
-        <v>-6.6178325936134106e-06</v>
+        <v>-6.7121306119295923e-06</v>
       </c>
       <c r="I15">
-        <v>-5.4800625058765496e-06</v>
+        <v>-5.6162502440788658e-06</v>
       </c>
       <c r="J15">
-        <v>-5.5738154889283928e-05</v>
+        <v>-5.5733732647365725e-05</v>
       </c>
       <c r="K15">
-        <v>5.259438075629881e-06</v>
+        <v>5.4196531910764025e-06</v>
       </c>
       <c r="L15">
-        <v>-1.0909205124439425e-06</v>
+        <v>-1.3151635669412123e-06</v>
       </c>
       <c r="M15">
-        <v>2.4114701378240636e-05</v>
+        <v>2.4099562305945632e-05</v>
       </c>
       <c r="N15">
-        <v>-1.2797378699486503e-05</v>
+        <v>-1.2975329004103397e-05</v>
       </c>
       <c r="O15">
-        <v>-6.029852900389148e-07</v>
+        <v>-6.0464082912555599e-07</v>
       </c>
       <c r="P15">
-        <v>0.0013651451892964612</v>
+        <v>0.0013652549419435774</v>
       </c>
       <c r="Q15">
-        <v>-0.00063419603228546614</v>
+        <v>-0.00063443879104279602</v>
       </c>
       <c r="R15">
-        <v>0.00041740945321769004</v>
+        <v>0.00041658240002564025</v>
       </c>
       <c r="S15">
-        <v>0.00042421826620405351</v>
+        <v>0.00042330895112368741</v>
       </c>
       <c r="T15">
-        <v>0.00042676338634160485</v>
+        <v>0.00042590788647179332</v>
       </c>
       <c r="U15">
-        <v>8.2891654328890742e-05</v>
+        <v>8.2690509820924256e-05</v>
       </c>
       <c r="V15">
-        <v>4.1725278152355042e-05</v>
+        <v>4.10067958537862e-05</v>
       </c>
       <c r="W15">
-        <v>4.8772942484471204e-05</v>
+        <v>4.8227435063112893e-05</v>
       </c>
       <c r="X15">
-        <v>1.2907688390869378e-05</v>
+        <v>1.369052260642481e-05</v>
       </c>
       <c r="Y15">
-        <v>-1.2909084500184344e-05</v>
+        <v>-1.2500156078522399e-05</v>
       </c>
       <c r="Z15">
-        <v>-2.0661299500110961e-05</v>
+        <v>-2.0180063355706328e-05</v>
       </c>
       <c r="AA15">
-        <v>2.4480863746305988e-05</v>
+        <v>2.4682265270006582e-05</v>
       </c>
       <c r="AB15">
-        <v>1.6708748131363219e-05</v>
+        <v>1.6865130448984807e-05</v>
       </c>
       <c r="AC15">
-        <v>6.6184178924230008e-06</v>
+        <v>6.7775508544231446e-06</v>
       </c>
       <c r="AD15">
-        <v>2.4974489775260748e-05</v>
+        <v>2.5225174432318663e-05</v>
       </c>
       <c r="AE15">
-        <v>5.4294317632951387e-06</v>
+        <v>5.7037174097784301e-06</v>
       </c>
       <c r="AF15">
-        <v>2.8341475067845799e-05</v>
+        <v>2.8610057892047004e-05</v>
       </c>
       <c r="AG15">
-        <v>-4.0507905806822829e-07</v>
+        <v>-4.0725713930974466e-07</v>
       </c>
       <c r="AH15">
-        <v>1.1604885549131006e-05</v>
+        <v>1.1781240804482353e-05</v>
       </c>
       <c r="AI15">
-        <v>1.0604849255206464e-05</v>
+        <v>1.0623709512893069e-05</v>
       </c>
       <c r="AJ15">
-        <v>-0.00045274442340696415</v>
+        <v>-0.00045285693650963738</v>
       </c>
     </row>
     <row r="16">
@@ -2129,109 +2129,109 @@
         <v>42</v>
       </c>
       <c r="B16">
-        <v>-0.044450175980520895</v>
+        <v>-0.044604298658397448</v>
       </c>
       <c r="C16">
-        <v>-4.4643412823985004e-06</v>
+        <v>-4.4273242537313297e-06</v>
       </c>
       <c r="D16">
-        <v>-9.2049423138635105e-08</v>
+        <v>-9.43274956047074e-08</v>
       </c>
       <c r="E16">
-        <v>2.9432057953050599e-09</v>
+        <v>2.920987653168926e-09</v>
       </c>
       <c r="F16">
-        <v>9.5385467637937026e-06</v>
+        <v>9.4458180992310053e-06</v>
       </c>
       <c r="G16">
-        <v>1.159891588002625e-05</v>
+        <v>1.1544650936498027e-05</v>
       </c>
       <c r="H16">
-        <v>6.7493930827819065e-06</v>
+        <v>6.7243614272814922e-06</v>
       </c>
       <c r="I16">
-        <v>6.5896982252864441e-06</v>
+        <v>6.5631159500669998e-06</v>
       </c>
       <c r="J16">
-        <v>2.2172052801245286e-05</v>
+        <v>2.2159030191799726e-05</v>
       </c>
       <c r="K16">
-        <v>1.5325239321903013e-06</v>
+        <v>1.7210574420158174e-06</v>
       </c>
       <c r="L16">
-        <v>-1.6022301973270842e-07</v>
+        <v>-1.2528513505008618e-07</v>
       </c>
       <c r="M16">
-        <v>-4.2136373622518569e-05</v>
+        <v>-4.2120458483468737e-05</v>
       </c>
       <c r="N16">
-        <v>5.5769530201830141e-05</v>
+        <v>5.5388937112973855e-05</v>
       </c>
       <c r="O16">
-        <v>-6.4103127571306589e-06</v>
+        <v>-6.4124891978603217e-06</v>
       </c>
       <c r="P16">
-        <v>-0.00063419603228546614</v>
+        <v>-0.00063443879104279602</v>
       </c>
       <c r="Q16">
-        <v>0.0013462025470260754</v>
+        <v>0.0013465352276774395</v>
       </c>
       <c r="R16">
-        <v>-0.0023462957784217017</v>
+        <v>-0.002347512271927667</v>
       </c>
       <c r="S16">
-        <v>-0.0023413908993463526</v>
+        <v>-0.0023424989928072081</v>
       </c>
       <c r="T16">
-        <v>-0.0023412320237869298</v>
+        <v>-0.00234244519955636</v>
       </c>
       <c r="U16">
-        <v>-3.5028199515943579e-05</v>
+        <v>-3.325422298235234e-05</v>
       </c>
       <c r="V16">
-        <v>1.1943944616648727e-05</v>
+        <v>1.4035117395257276e-05</v>
       </c>
       <c r="W16">
-        <v>1.0307649675155668e-05</v>
+        <v>1.2250506760192294e-05</v>
       </c>
       <c r="X16">
-        <v>-1.0743271145026477e-05</v>
+        <v>-1.1047667116436052e-05</v>
       </c>
       <c r="Y16">
-        <v>4.7458392919060303e-06</v>
+        <v>4.4446441463498666e-06</v>
       </c>
       <c r="Z16">
-        <v>3.4096513352007232e-05</v>
+        <v>3.5644371805208515e-05</v>
       </c>
       <c r="AA16">
-        <v>-4.8760279663096189e-06</v>
+        <v>-5.3586008497560293e-06</v>
       </c>
       <c r="AB16">
-        <v>-6.1243900260174889e-06</v>
+        <v>-6.6648461606380605e-06</v>
       </c>
       <c r="AC16">
-        <v>1.1151586887880134e-05</v>
+        <v>1.0633462070013238e-05</v>
       </c>
       <c r="AD16">
-        <v>1.3065401879147837e-05</v>
+        <v>1.2598573094939293e-05</v>
       </c>
       <c r="AE16">
-        <v>2.6647312627876472e-05</v>
+        <v>2.6173973083163467e-05</v>
       </c>
       <c r="AF16">
-        <v>3.0591265652514424e-06</v>
+        <v>2.4875571624396304e-06</v>
       </c>
       <c r="AG16">
-        <v>-5.597041323916139e-07</v>
+        <v>-5.5825187629298588e-07</v>
       </c>
       <c r="AH16">
-        <v>1.9939508548757427e-05</v>
+        <v>1.9853810276576752e-05</v>
       </c>
       <c r="AI16">
-        <v>-2.0131342377696995e-05</v>
+        <v>-2.0149280674294963e-05</v>
       </c>
       <c r="AJ16">
-        <v>0.0023562528910354447</v>
+        <v>0.0023564039702391984</v>
       </c>
     </row>
     <row r="17">
@@ -2239,109 +2239,109 @@
         <v>43</v>
       </c>
       <c r="B17">
-        <v>-1.2319510901957458</v>
+        <v>-1.2330920861383068</v>
       </c>
       <c r="C17">
-        <v>-0.00020276970545396434</v>
+        <v>-0.00020231358560382365</v>
       </c>
       <c r="D17">
-        <v>-0.00013339923347572137</v>
+        <v>-0.00013329788888462221</v>
       </c>
       <c r="E17">
-        <v>1.178256127163396e-06</v>
+        <v>1.17800335508749e-06</v>
       </c>
       <c r="F17">
-        <v>-8.6934742314077697e-05</v>
+        <v>-8.8519845622121843e-05</v>
       </c>
       <c r="G17">
-        <v>-9.9597856857855599e-06</v>
+        <v>-1.1201843588113769e-05</v>
       </c>
       <c r="H17">
-        <v>5.1677075663596421e-05</v>
+        <v>5.0574442507335157e-05</v>
       </c>
       <c r="I17">
-        <v>-9.9348736545875816e-06</v>
+        <v>-1.1464132507908167e-05</v>
       </c>
       <c r="J17">
-        <v>-1.4521490597421205e-05</v>
+        <v>-1.458293378569843e-05</v>
       </c>
       <c r="K17">
-        <v>7.2942141221193967e-05</v>
+        <v>7.3841560566632013e-05</v>
       </c>
       <c r="L17">
-        <v>8.7873443139225703e-06</v>
+        <v>9.1036503715173502e-06</v>
       </c>
       <c r="M17">
-        <v>-2.2297393878621718e-07</v>
+        <v>-3.5767592206161348e-07</v>
       </c>
       <c r="N17">
-        <v>0.0050136053871246969</v>
+        <v>0.0050128377310155068</v>
       </c>
       <c r="O17">
-        <v>0.00010444461320091992</v>
+        <v>0.00010449281622900439</v>
       </c>
       <c r="P17">
-        <v>0.00041740945321769004</v>
+        <v>0.00041658240002564025</v>
       </c>
       <c r="Q17">
-        <v>-0.0023462957784217017</v>
+        <v>-0.002347512271927667</v>
       </c>
       <c r="R17">
-        <v>0.052056543072756048</v>
+        <v>0.052075479142882311</v>
       </c>
       <c r="S17">
-        <v>0.051764222192104956</v>
+        <v>0.051783582117141909</v>
       </c>
       <c r="T17">
-        <v>0.051806231087411628</v>
+        <v>0.051824590711764054</v>
       </c>
       <c r="U17">
-        <v>0.0019554998409978403</v>
+        <v>0.0019633978807842567</v>
       </c>
       <c r="V17">
-        <v>0.00053031381109416853</v>
+        <v>0.00053958269569864825</v>
       </c>
       <c r="W17">
-        <v>0.00043258298256027006</v>
+        <v>0.00044210566048756561</v>
       </c>
       <c r="X17">
-        <v>0.00015721725389215889</v>
+        <v>0.0001639563913303204</v>
       </c>
       <c r="Y17">
-        <v>-0.00051755826393656227</v>
+        <v>-0.00051278134564965204</v>
       </c>
       <c r="Z17">
-        <v>0.00089127060186100504</v>
+        <v>0.00091370112522068739</v>
       </c>
       <c r="AA17">
-        <v>-0.00014345429489732997</v>
+        <v>-0.0001432648957492913</v>
       </c>
       <c r="AB17">
-        <v>-8.3691032520712139e-05</v>
+        <v>-8.3755075490569986e-05</v>
       </c>
       <c r="AC17">
-        <v>1.9830693334169786e-05</v>
+        <v>2.0211083847265082e-05</v>
       </c>
       <c r="AD17">
-        <v>-0.00021070400319908589</v>
+        <v>-0.00020992014986082747</v>
       </c>
       <c r="AE17">
-        <v>-0.0001713867178525768</v>
+        <v>-0.00017012548983189046</v>
       </c>
       <c r="AF17">
-        <v>-0.00010334947615037171</v>
+        <v>-0.00010322925820934435</v>
       </c>
       <c r="AG17">
-        <v>-4.650223596836282e-06</v>
+        <v>-4.613170688084426e-06</v>
       </c>
       <c r="AH17">
-        <v>-0.0001895486371505592</v>
+        <v>-0.00018856615181738617</v>
       </c>
       <c r="AI17">
-        <v>6.374556169201108e-05</v>
+        <v>6.3385690700804714e-05</v>
       </c>
       <c r="AJ17">
-        <v>-0.048628395941666985</v>
+        <v>-0.048664961998171108</v>
       </c>
     </row>
     <row r="18">
@@ -2349,109 +2349,109 @@
         <v>44</v>
       </c>
       <c r="B18">
-        <v>-1.0964251342103926</v>
+        <v>-1.0976025301574781</v>
       </c>
       <c r="C18">
-        <v>-0.00018457906641151828</v>
+        <v>-0.00018398417332608218</v>
       </c>
       <c r="D18">
-        <v>-0.00013984982154221666</v>
+        <v>-0.00013972298769855186</v>
       </c>
       <c r="E18">
-        <v>1.2750902600667099e-06</v>
+        <v>1.2746922838202954e-06</v>
       </c>
       <c r="F18">
-        <v>-9.0659463184927195e-05</v>
+        <v>-9.2294009691585785e-05</v>
       </c>
       <c r="G18">
-        <v>5.8883803869194855e-05</v>
+        <v>5.7695089277118083e-05</v>
       </c>
       <c r="H18">
-        <v>7.3886624544214119e-05</v>
+        <v>7.2850241262352282e-05</v>
       </c>
       <c r="I18">
-        <v>-1.0058234629685758e-05</v>
+        <v>-1.175040090011482e-05</v>
       </c>
       <c r="J18">
-        <v>-1.6105590771735326e-05</v>
+        <v>-1.6096076573179211e-05</v>
       </c>
       <c r="K18">
-        <v>3.8903304867473406e-05</v>
+        <v>3.9047724367708022e-05</v>
       </c>
       <c r="L18">
-        <v>6.0585243863096099e-06</v>
+        <v>6.1964832623185661e-06</v>
       </c>
       <c r="M18">
-        <v>-6.248287619315995e-06</v>
+        <v>-6.4874106035148872e-06</v>
       </c>
       <c r="N18">
-        <v>0.0049888765242035709</v>
+        <v>0.0049879202616647132</v>
       </c>
       <c r="O18">
-        <v>0.00010458397880891684</v>
+        <v>0.00010463315483627241</v>
       </c>
       <c r="P18">
-        <v>0.00042421826620405351</v>
+        <v>0.00042330895112368741</v>
       </c>
       <c r="Q18">
-        <v>-0.0023413908993463526</v>
+        <v>-0.0023424989928072081</v>
       </c>
       <c r="R18">
-        <v>0.051764222192104956</v>
+        <v>0.051783582117141909</v>
       </c>
       <c r="S18">
-        <v>0.052266544011733578</v>
+        <v>0.052286295351905265</v>
       </c>
       <c r="T18">
-        <v>0.051843442062760696</v>
+        <v>0.051862466352397725</v>
       </c>
       <c r="U18">
-        <v>0.0016759839972338569</v>
+        <v>0.0016765918476811942</v>
       </c>
       <c r="V18">
-        <v>0.00034556698589546103</v>
+        <v>0.00034654585663072141</v>
       </c>
       <c r="W18">
-        <v>0.00018994649714085265</v>
+        <v>0.0001915351786292846</v>
       </c>
       <c r="X18">
-        <v>0.00015391109031342217</v>
+        <v>0.00016027439420103311</v>
       </c>
       <c r="Y18">
-        <v>-0.00054598826562006096</v>
+        <v>-0.00054139523420764293</v>
       </c>
       <c r="Z18">
-        <v>0.0010319563433645457</v>
+        <v>0.0010587494873965479</v>
       </c>
       <c r="AA18">
-        <v>-5.4917603809427618e-05</v>
+        <v>-5.4904635408727087e-05</v>
       </c>
       <c r="AB18">
-        <v>-2.8529795788011236e-05</v>
+        <v>-2.8740775308358502e-05</v>
       </c>
       <c r="AC18">
-        <v>8.3710665276034643e-05</v>
+        <v>8.4232763960374185e-05</v>
       </c>
       <c r="AD18">
-        <v>-8.9978529541907826e-05</v>
+        <v>-8.9349235680963313e-05</v>
       </c>
       <c r="AE18">
-        <v>-7.7348360760081183e-05</v>
+        <v>-7.6229307958565473e-05</v>
       </c>
       <c r="AF18">
-        <v>1.6882261361857685e-05</v>
+        <v>1.6836283824382507e-05</v>
       </c>
       <c r="AG18">
-        <v>-1.1098044695567527e-05</v>
+        <v>-1.1071130271835504e-05</v>
       </c>
       <c r="AH18">
-        <v>-0.00018796882303842577</v>
+        <v>-0.00018733853906845871</v>
       </c>
       <c r="AI18">
-        <v>5.0209324960333659e-05</v>
+        <v>4.9853689155833839e-05</v>
       </c>
       <c r="AJ18">
-        <v>-0.048269432432185289</v>
+        <v>-0.048299124947391303</v>
       </c>
     </row>
     <row r="19">
@@ -2459,109 +2459,109 @@
         <v>45</v>
       </c>
       <c r="B19">
-        <v>-0.88586791670074161</v>
+        <v>-0.88745322241961644</v>
       </c>
       <c r="C19">
-        <v>-0.00014230107507940196</v>
+        <v>-0.00014179299679633472</v>
       </c>
       <c r="D19">
-        <v>-0.00013983667603342863</v>
+        <v>-0.00013968963599298267</v>
       </c>
       <c r="E19">
-        <v>1.2905328601471298e-06</v>
+        <v>1.289991934333784e-06</v>
       </c>
       <c r="F19">
-        <v>-3.7183345565693071e-05</v>
+        <v>-3.8756048365634637e-05</v>
       </c>
       <c r="G19">
-        <v>8.8132520044139427e-05</v>
+        <v>8.6916696627620653e-05</v>
       </c>
       <c r="H19">
-        <v>0.00012020170536684142</v>
+        <v>0.00011927957709169772</v>
       </c>
       <c r="I19">
-        <v>2.1311724134353537e-05</v>
+        <v>1.9711166127756782e-05</v>
       </c>
       <c r="J19">
-        <v>-1.8653698068622268e-05</v>
+        <v>-1.8697484877354045e-05</v>
       </c>
       <c r="K19">
-        <v>-4.2076096725377865e-05</v>
+        <v>-4.2614332092917953e-05</v>
       </c>
       <c r="L19">
-        <v>1.8206085427353066e-06</v>
+        <v>2.0631416918886031e-06</v>
       </c>
       <c r="M19">
-        <v>-1.0596812772207388e-05</v>
+        <v>-1.0750340923965505e-05</v>
       </c>
       <c r="N19">
-        <v>0.0049611952792562239</v>
+        <v>0.0049603393092707698</v>
       </c>
       <c r="O19">
-        <v>0.00010462847082416017</v>
+        <v>0.00010467593786300072</v>
       </c>
       <c r="P19">
-        <v>0.00042676338634160485</v>
+        <v>0.00042590788647179332</v>
       </c>
       <c r="Q19">
-        <v>-0.0023412320237869298</v>
+        <v>-0.00234244519955636</v>
       </c>
       <c r="R19">
-        <v>0.051806231087411628</v>
+        <v>0.051824590711764054</v>
       </c>
       <c r="S19">
-        <v>0.051843442062760696</v>
+        <v>0.051862466352397725</v>
       </c>
       <c r="T19">
-        <v>0.052291670640890867</v>
+        <v>0.05230958953984817</v>
       </c>
       <c r="U19">
-        <v>0.0011469699117394455</v>
+        <v>0.0011427075500639872</v>
       </c>
       <c r="V19">
-        <v>-0.0002442016231819083</v>
+        <v>-0.00024765203562917421</v>
       </c>
       <c r="W19">
-        <v>-0.00048080279203675108</v>
+        <v>-0.00048400055613233295</v>
       </c>
       <c r="X19">
-        <v>0.00013641980171128767</v>
+        <v>0.0001438393558657932</v>
       </c>
       <c r="Y19">
-        <v>-0.0005569960839069397</v>
+        <v>-0.00055177099781556676</v>
       </c>
       <c r="Z19">
-        <v>0.0010400001708056883</v>
+        <v>0.0010616380279193302</v>
       </c>
       <c r="AA19">
-        <v>-0.00010644408694181207</v>
+        <v>-0.00010684925799648443</v>
       </c>
       <c r="AB19">
-        <v>-7.2881788181329565e-05</v>
+        <v>-7.3557328757453688e-05</v>
       </c>
       <c r="AC19">
-        <v>2.9071147594358915e-05</v>
+        <v>2.9173819291400741e-05</v>
       </c>
       <c r="AD19">
-        <v>-0.00013469766881531176</v>
+        <v>-0.00013456539808588686</v>
       </c>
       <c r="AE19">
-        <v>-0.00011938335773575316</v>
+        <v>-0.00011863249829174166</v>
       </c>
       <c r="AF19">
-        <v>-3.5312369631867666e-05</v>
+        <v>-3.5722352160293298e-05</v>
       </c>
       <c r="AG19">
-        <v>-1.5124170488833594e-05</v>
+        <v>-1.5086855361954969e-05</v>
       </c>
       <c r="AH19">
-        <v>-0.0002140049657082671</v>
+        <v>-0.00021340453470937437</v>
       </c>
       <c r="AI19">
-        <v>6.5692277114502359e-05</v>
+        <v>6.5039223023342224e-05</v>
       </c>
       <c r="AJ19">
-        <v>-0.047652712381011209</v>
+        <v>-0.047677452669036363</v>
       </c>
     </row>
     <row r="20">
@@ -2569,109 +2569,109 @@
         <v>46</v>
       </c>
       <c r="B20">
-        <v>1.4880521478051685</v>
+        <v>1.4889411946286662</v>
       </c>
       <c r="C20">
-        <v>-0.00042824173032764926</v>
+        <v>-0.00041969083244662255</v>
       </c>
       <c r="D20">
-        <v>9.4556681224327444e-05</v>
+        <v>9.3662377662510855e-05</v>
       </c>
       <c r="E20">
-        <v>-9.2138299886223013e-07</v>
+        <v>-9.1556608696194586e-07</v>
       </c>
       <c r="F20">
-        <v>7.3814813121306189e-05</v>
+        <v>7.5062176232829688e-05</v>
       </c>
       <c r="G20">
-        <v>8.5320300293013223e-05</v>
+        <v>8.4264841621156683e-05</v>
       </c>
       <c r="H20">
-        <v>0.00014718677037586051</v>
+        <v>0.00013884443051822155</v>
       </c>
       <c r="I20">
-        <v>1.1399888685241705e-05</v>
+        <v>4.6850382681404333e-06</v>
       </c>
       <c r="J20">
-        <v>-5.3257989886495712e-05</v>
+        <v>-5.2694409922412577e-05</v>
       </c>
       <c r="K20">
-        <v>0.002999366440053402</v>
+        <v>0.0030734036057055206</v>
       </c>
       <c r="L20">
-        <v>-7.7503693165586649e-05</v>
+        <v>-7.9252671789549044e-05</v>
       </c>
       <c r="M20">
-        <v>1.436465799518815e-05</v>
+        <v>1.2779232817086045e-05</v>
       </c>
       <c r="N20">
-        <v>0.00047718190255935291</v>
+        <v>0.00046846746817583596</v>
       </c>
       <c r="O20">
-        <v>-1.745433348129832e-06</v>
+        <v>-1.7245315808773381e-06</v>
       </c>
       <c r="P20">
-        <v>8.2891654328890742e-05</v>
+        <v>8.2690509820924256e-05</v>
       </c>
       <c r="Q20">
-        <v>-3.5028199515943579e-05</v>
+        <v>-3.325422298235234e-05</v>
       </c>
       <c r="R20">
-        <v>0.0019554998409978403</v>
+        <v>0.0019633978807842567</v>
       </c>
       <c r="S20">
-        <v>0.0016759839972338569</v>
+        <v>0.0016765918476811942</v>
       </c>
       <c r="T20">
-        <v>0.0011469699117394455</v>
+        <v>0.0011427075500639872</v>
       </c>
       <c r="U20">
-        <v>0.026428338584982339</v>
+        <v>0.027011228686011284</v>
       </c>
       <c r="V20">
-        <v>0.023523019326517337</v>
+        <v>0.02411746558278495</v>
       </c>
       <c r="W20">
-        <v>0.023838768049555287</v>
+        <v>0.024443212441252339</v>
       </c>
       <c r="X20">
-        <v>1.3214857350892211e-05</v>
+        <v>1.8937156905408058e-05</v>
       </c>
       <c r="Y20">
-        <v>0.00018415005674882927</v>
+        <v>0.00018358407132773244</v>
       </c>
       <c r="Z20">
-        <v>-0.00010553482450312464</v>
+        <v>-9.1700850137538606e-05</v>
       </c>
       <c r="AA20">
-        <v>-3.3787078824263489e-05</v>
+        <v>-3.9417612084442083e-05</v>
       </c>
       <c r="AB20">
-        <v>-0.00028615808145876498</v>
+        <v>-0.0003019759362838069</v>
       </c>
       <c r="AC20">
-        <v>-0.00042684280750269425</v>
+        <v>-0.00044183785270163201</v>
       </c>
       <c r="AD20">
-        <v>3.0242113666888171e-05</v>
+        <v>2.5111280528497537e-05</v>
       </c>
       <c r="AE20">
-        <v>-0.00018854380716434079</v>
+        <v>-0.00020073732666149764</v>
       </c>
       <c r="AF20">
-        <v>-0.00020352959101305667</v>
+        <v>-0.00021985978950927326</v>
       </c>
       <c r="AG20">
-        <v>-1.2037901713926298e-05</v>
+        <v>-1.1265101323157758e-05</v>
       </c>
       <c r="AH20">
-        <v>-0.0001512338373518933</v>
+        <v>-0.00015787462477048764</v>
       </c>
       <c r="AI20">
-        <v>-3.2714931552187479e-05</v>
+        <v>-3.2008186709652116e-05</v>
       </c>
       <c r="AJ20">
-        <v>-0.026942780966095696</v>
+        <v>-0.027517145322816634</v>
       </c>
     </row>
     <row r="21">
@@ -2679,109 +2679,109 @@
         <v>47</v>
       </c>
       <c r="B21">
-        <v>0.82493796010081688</v>
+        <v>0.82418749774230837</v>
       </c>
       <c r="C21">
-        <v>-0.00038901432655613779</v>
+        <v>-0.00037891908621315155</v>
       </c>
       <c r="D21">
-        <v>-1.7461056325237417e-05</v>
+        <v>-1.8499401183820431e-05</v>
       </c>
       <c r="E21">
-        <v>-3.196357144212363e-08</v>
+        <v>-2.4830345160458135e-08</v>
       </c>
       <c r="F21">
-        <v>-6.1034824572332952e-05</v>
+        <v>-5.8716815479269234e-05</v>
       </c>
       <c r="G21">
-        <v>1.7200407890189924e-05</v>
+        <v>1.7161572828430218e-05</v>
       </c>
       <c r="H21">
-        <v>0.00011459949982876333</v>
+        <v>0.0001068796270325013</v>
       </c>
       <c r="I21">
-        <v>1.307100996085454e-05</v>
+        <v>5.6209481419087256e-06</v>
       </c>
       <c r="J21">
-        <v>-5.1986896564435784e-05</v>
+        <v>-5.095736396605553e-05</v>
       </c>
       <c r="K21">
-        <v>0.003052238522011635</v>
+        <v>0.0031272941639419976</v>
       </c>
       <c r="L21">
-        <v>-7.8663409873098978e-05</v>
+        <v>-7.9886872264672588e-05</v>
       </c>
       <c r="M21">
-        <v>-9.063151714073773e-07</v>
+        <v>-2.7945135216985721e-06</v>
       </c>
       <c r="N21">
-        <v>0.0003922445210037314</v>
+        <v>0.00038171065689898438</v>
       </c>
       <c r="O21">
-        <v>-1.2286863435495218e-07</v>
+        <v>-9.6290245728269941e-08</v>
       </c>
       <c r="P21">
-        <v>4.1725278152355042e-05</v>
+        <v>4.10067958537862e-05</v>
       </c>
       <c r="Q21">
-        <v>1.1943944616648727e-05</v>
+        <v>1.4035117395257276e-05</v>
       </c>
       <c r="R21">
-        <v>0.00053031381109416853</v>
+        <v>0.00053958269569864825</v>
       </c>
       <c r="S21">
-        <v>0.00034556698589546103</v>
+        <v>0.00034654585663072141</v>
       </c>
       <c r="T21">
-        <v>-0.0002442016231819083</v>
+        <v>-0.00024765203562917421</v>
       </c>
       <c r="U21">
-        <v>0.023523019326517337</v>
+        <v>0.02411746558278495</v>
       </c>
       <c r="V21">
-        <v>0.024375367836511022</v>
+        <v>0.024979624074321242</v>
       </c>
       <c r="W21">
-        <v>0.024440359640698399</v>
+        <v>0.025056481616757269</v>
       </c>
       <c r="X21">
-        <v>-5.9221490715636346e-05</v>
+        <v>-5.3708603207902107e-05</v>
       </c>
       <c r="Y21">
-        <v>0.00011512955434016779</v>
+        <v>0.00011321444235727466</v>
       </c>
       <c r="Z21">
-        <v>-0.00023861001404968957</v>
+        <v>-0.00021560798461217525</v>
       </c>
       <c r="AA21">
-        <v>-2.7087647779604554e-05</v>
+        <v>-3.4087703917488887e-05</v>
       </c>
       <c r="AB21">
-        <v>-0.00030288158819016808</v>
+        <v>-0.0003211117580010376</v>
       </c>
       <c r="AC21">
-        <v>-0.0004365576943273974</v>
+        <v>-0.00045312768769832732</v>
       </c>
       <c r="AD21">
-        <v>1.0262788959360114e-05</v>
+        <v>3.7972442476913448e-06</v>
       </c>
       <c r="AE21">
-        <v>-0.00018557136633158295</v>
+        <v>-0.00019975503862872807</v>
       </c>
       <c r="AF21">
-        <v>-0.00021021413701004374</v>
+        <v>-0.00022840052681100077</v>
       </c>
       <c r="AG21">
-        <v>3.298568482878279e-07</v>
+        <v>1.1891398285518049e-06</v>
       </c>
       <c r="AH21">
-        <v>-0.0001359753622682848</v>
+        <v>-0.00014501762955623776</v>
       </c>
       <c r="AI21">
-        <v>1.7109776470275624e-05</v>
+        <v>1.7419839376479201e-05</v>
       </c>
       <c r="AJ21">
-        <v>-0.022981610082609877</v>
+        <v>-0.023565759690329612</v>
       </c>
     </row>
     <row r="22">
@@ -2789,109 +2789,109 @@
         <v>48</v>
       </c>
       <c r="B22">
-        <v>0.89043197007938524</v>
+        <v>0.89061218502477291</v>
       </c>
       <c r="C22">
-        <v>-0.00054219627613523783</v>
+        <v>-0.00053279197319087946</v>
       </c>
       <c r="D22">
-        <v>3.4993562997956667e-05</v>
+        <v>3.3991798199576375e-05</v>
       </c>
       <c r="E22">
-        <v>-8.0194097487419187e-07</v>
+        <v>-7.9542950311009419e-07</v>
       </c>
       <c r="F22">
-        <v>-7.2887149255579191e-05</v>
+        <v>-7.0888410993000771e-05</v>
       </c>
       <c r="G22">
-        <v>7.3103565255648747e-05</v>
+        <v>7.291928654417856e-05</v>
       </c>
       <c r="H22">
-        <v>0.00014111864591351823</v>
+        <v>0.00013324158118378172</v>
       </c>
       <c r="I22">
-        <v>2.0899714964468818e-05</v>
+        <v>1.3952038894635876e-05</v>
       </c>
       <c r="J22">
-        <v>-5.8470650969077207e-05</v>
+        <v>-5.7636971513690732e-05</v>
       </c>
       <c r="K22">
-        <v>0.0030930118556961434</v>
+        <v>0.0031694215943281136</v>
       </c>
       <c r="L22">
-        <v>-6.546711117600631e-05</v>
+        <v>-6.6873346616419982e-05</v>
       </c>
       <c r="M22">
-        <v>1.7803446417798033e-06</v>
+        <v>4.6765662453192566e-08</v>
       </c>
       <c r="N22">
-        <v>0.00054544506682772985</v>
+        <v>0.00053554605412811174</v>
       </c>
       <c r="O22">
-        <v>-6.0376742978289683e-07</v>
+        <v>-5.78371426275011e-07</v>
       </c>
       <c r="P22">
-        <v>4.8772942484471204e-05</v>
+        <v>4.8227435063112893e-05</v>
       </c>
       <c r="Q22">
-        <v>1.0307649675155668e-05</v>
+        <v>1.2250506760192294e-05</v>
       </c>
       <c r="R22">
-        <v>0.00043258298256027006</v>
+        <v>0.00044210566048756561</v>
       </c>
       <c r="S22">
-        <v>0.00018994649714085265</v>
+        <v>0.0001915351786292846</v>
       </c>
       <c r="T22">
-        <v>-0.00048080279203675108</v>
+        <v>-0.00048400055613233295</v>
       </c>
       <c r="U22">
-        <v>0.023838768049555287</v>
+        <v>0.024443212441252339</v>
       </c>
       <c r="V22">
-        <v>0.024440359640698399</v>
+        <v>0.025056481616757269</v>
       </c>
       <c r="W22">
-        <v>0.026347387477073592</v>
+        <v>0.026974243859010899</v>
       </c>
       <c r="X22">
-        <v>-9.6692698841411608e-05</v>
+        <v>-9.1661300590390512e-05</v>
       </c>
       <c r="Y22">
-        <v>0.00010094760406168727</v>
+        <v>9.8769339682521331e-05</v>
       </c>
       <c r="Z22">
-        <v>-0.00027720321106184959</v>
+        <v>-0.00025305479865876234</v>
       </c>
       <c r="AA22">
-        <v>-3.492590841396373e-05</v>
+        <v>-4.1450545557274871e-05</v>
       </c>
       <c r="AB22">
-        <v>-0.00032499519214412506</v>
+        <v>-0.00034266042857816412</v>
       </c>
       <c r="AC22">
-        <v>-0.00041555000174634937</v>
+        <v>-0.00043202806515636435</v>
       </c>
       <c r="AD22">
-        <v>4.0257242717714123e-05</v>
+        <v>3.4204621375849564e-05</v>
       </c>
       <c r="AE22">
-        <v>-0.00019909139433911278</v>
+        <v>-0.00021289182875552579</v>
       </c>
       <c r="AF22">
-        <v>-0.00015975550368417177</v>
+        <v>-0.00017745958410599234</v>
       </c>
       <c r="AG22">
-        <v>3.6350820467926336e-07</v>
+        <v>1.2072349175609124e-06</v>
       </c>
       <c r="AH22">
-        <v>-0.00011810315069277558</v>
+        <v>-0.00012588171197223594</v>
       </c>
       <c r="AI22">
-        <v>4.4973636718738733e-06</v>
+        <v>5.1264841992903001e-06</v>
       </c>
       <c r="AJ22">
-        <v>-0.023842405045704632</v>
+        <v>-0.024436653697039588</v>
       </c>
     </row>
     <row r="23">
@@ -2899,109 +2899,109 @@
         <v>49</v>
       </c>
       <c r="B23">
-        <v>-0.16562418677036875</v>
+        <v>-0.17044716370653146</v>
       </c>
       <c r="C23">
-        <v>3.2606815590782098e-05</v>
+        <v>3.3192940103519456e-05</v>
       </c>
       <c r="D23">
-        <v>7.0259324899972927e-06</v>
+        <v>7.3126564292932959e-06</v>
       </c>
       <c r="E23">
-        <v>2.4718955330417382e-09</v>
+        <v>9.5806522806021828e-10</v>
       </c>
       <c r="F23">
-        <v>4.4439057352386403e-05</v>
+        <v>3.9680682377887424e-05</v>
       </c>
       <c r="G23">
-        <v>3.3090857626206661e-05</v>
+        <v>2.9197358813644926e-05</v>
       </c>
       <c r="H23">
-        <v>2.723835413366407e-05</v>
+        <v>2.3677383821942535e-05</v>
       </c>
       <c r="I23">
-        <v>1.1635607613298661e-05</v>
+        <v>8.7386925523103588e-06</v>
       </c>
       <c r="J23">
-        <v>1.9745750342813263e-06</v>
+        <v>1.5187159163144827e-06</v>
       </c>
       <c r="K23">
-        <v>-1.42044052615582e-05</v>
+        <v>-1.3646221008052379e-05</v>
       </c>
       <c r="L23">
-        <v>-3.9028183123111055e-06</v>
+        <v>-3.9952673498581093e-06</v>
       </c>
       <c r="M23">
-        <v>4.4989500669006581e-06</v>
+        <v>4.7043120312743931e-06</v>
       </c>
       <c r="N23">
-        <v>-4.7132921023004847e-05</v>
+        <v>-4.6811606737229939e-05</v>
       </c>
       <c r="O23">
-        <v>5.0711547101110088e-07</v>
+        <v>5.2258944216950771e-07</v>
       </c>
       <c r="P23">
-        <v>1.2907688390869378e-05</v>
+        <v>1.369052260642481e-05</v>
       </c>
       <c r="Q23">
-        <v>-1.0743271145026477e-05</v>
+        <v>-1.1047667116436052e-05</v>
       </c>
       <c r="R23">
-        <v>0.00015721725389215889</v>
+        <v>0.0001639563913303204</v>
       </c>
       <c r="S23">
-        <v>0.00015391109031342217</v>
+        <v>0.00016027439420103311</v>
       </c>
       <c r="T23">
-        <v>0.00013641980171128767</v>
+        <v>0.0001438393558657932</v>
       </c>
       <c r="U23">
-        <v>1.3214857350892211e-05</v>
+        <v>1.8937156905408058e-05</v>
       </c>
       <c r="V23">
-        <v>-5.9221490715636346e-05</v>
+        <v>-5.3708603207902107e-05</v>
       </c>
       <c r="W23">
-        <v>-9.6692698841411608e-05</v>
+        <v>-9.1661300590390512e-05</v>
       </c>
       <c r="X23">
-        <v>0.00073781342126298644</v>
+        <v>0.00074053364046482531</v>
       </c>
       <c r="Y23">
-        <v>0.00031916678969476977</v>
+        <v>0.00032371155686058452</v>
       </c>
       <c r="Z23">
-        <v>0.00039799076756211443</v>
+        <v>0.00040571764312913105</v>
       </c>
       <c r="AA23">
-        <v>-6.6280645229651496e-05</v>
+        <v>-6.7388589266341057e-05</v>
       </c>
       <c r="AB23">
-        <v>-8.8778427547365536e-05</v>
+        <v>-8.8098282990746392e-05</v>
       </c>
       <c r="AC23">
-        <v>-0.0001025623456676171</v>
+        <v>-0.0001020339454392385</v>
       </c>
       <c r="AD23">
-        <v>-8.1845277992750713e-05</v>
+        <v>-8.0919734234278183e-05</v>
       </c>
       <c r="AE23">
-        <v>-7.9303566415632899e-05</v>
+        <v>-7.7961844058088649e-05</v>
       </c>
       <c r="AF23">
-        <v>-9.2811942185132366e-05</v>
+        <v>-9.3829830660649205e-05</v>
       </c>
       <c r="AG23">
-        <v>2.8892275891271729e-06</v>
+        <v>2.8039958578033729e-06</v>
       </c>
       <c r="AH23">
-        <v>2.3279697372624348e-05</v>
+        <v>2.3317861304507446e-05</v>
       </c>
       <c r="AI23">
-        <v>-4.8265097263521076e-06</v>
+        <v>-5.5474953689810301e-06</v>
       </c>
       <c r="AJ23">
-        <v>-0.00074773814662214711</v>
+        <v>-0.00076972963302752388</v>
       </c>
     </row>
     <row r="24">
@@ -3009,109 +3009,109 @@
         <v>50</v>
       </c>
       <c r="B24">
-        <v>-0.33038245343777334</v>
+        <v>-0.33367050863168646</v>
       </c>
       <c r="C24">
-        <v>1.2507353626023731e-05</v>
+        <v>1.2824885642311791e-05</v>
       </c>
       <c r="D24">
-        <v>3.3636494439989339e-05</v>
+        <v>3.3780340277062494e-05</v>
       </c>
       <c r="E24">
-        <v>-2.6520618624859582e-07</v>
+        <v>-2.656627698468034e-07</v>
       </c>
       <c r="F24">
-        <v>5.7182990474016758e-05</v>
+        <v>5.5510194103842742e-05</v>
       </c>
       <c r="G24">
-        <v>-3.0687237558719e-06</v>
+        <v>-4.2873511370718469e-06</v>
       </c>
       <c r="H24">
-        <v>-9.4038118989487331e-06</v>
+        <v>-1.0649829981368006e-05</v>
       </c>
       <c r="I24">
-        <v>7.0885674723720956e-06</v>
+        <v>6.2293114007861089e-06</v>
       </c>
       <c r="J24">
-        <v>-9.8666629231824524e-08</v>
+        <v>-2.7228154228016899e-07</v>
       </c>
       <c r="K24">
-        <v>1.5362234224736333e-05</v>
+        <v>1.4936732166567914e-05</v>
       </c>
       <c r="L24">
-        <v>1.4581552651866553e-07</v>
+        <v>1.9520252475299079e-07</v>
       </c>
       <c r="M24">
-        <v>-1.9094483336881404e-06</v>
+        <v>-1.6823651593301702e-06</v>
       </c>
       <c r="N24">
-        <v>1.7089749209726239e-06</v>
+        <v>1.7097905717668714e-06</v>
       </c>
       <c r="O24">
-        <v>-1.2194903045869823e-06</v>
+        <v>-1.2084750160305139e-06</v>
       </c>
       <c r="P24">
-        <v>-1.2909084500184344e-05</v>
+        <v>-1.2500156078522399e-05</v>
       </c>
       <c r="Q24">
-        <v>4.7458392919060303e-06</v>
+        <v>4.4446441463498666e-06</v>
       </c>
       <c r="R24">
-        <v>-0.00051755826393656227</v>
+        <v>-0.00051278134564965204</v>
       </c>
       <c r="S24">
-        <v>-0.00054598826562006096</v>
+        <v>-0.00054139523420764293</v>
       </c>
       <c r="T24">
-        <v>-0.0005569960839069397</v>
+        <v>-0.00055177099781556676</v>
       </c>
       <c r="U24">
-        <v>0.00018415005674882927</v>
+        <v>0.00018358407132773244</v>
       </c>
       <c r="V24">
-        <v>0.00011512955434016779</v>
+        <v>0.00011321444235727466</v>
       </c>
       <c r="W24">
-        <v>0.00010094760406168727</v>
+        <v>9.8769339682521331e-05</v>
       </c>
       <c r="X24">
-        <v>0.00031916678969476977</v>
+        <v>0.00032371155686058452</v>
       </c>
       <c r="Y24">
-        <v>0.00068688782566452694</v>
+        <v>0.00068989091704433497</v>
       </c>
       <c r="Z24">
-        <v>0.00034754770859169825</v>
+        <v>0.00035433772858881301</v>
       </c>
       <c r="AA24">
-        <v>-4.7904968243904088e-05</v>
+        <v>-4.9404338160263317e-05</v>
       </c>
       <c r="AB24">
-        <v>-2.9352671216799006e-05</v>
+        <v>-2.9713001422008783e-05</v>
       </c>
       <c r="AC24">
-        <v>-6.6569343664000434e-05</v>
+        <v>-6.7370281808433333e-05</v>
       </c>
       <c r="AD24">
-        <v>-3.4827249257180079e-05</v>
+        <v>-3.5315141041959751e-05</v>
       </c>
       <c r="AE24">
-        <v>-2.9747572854813415e-05</v>
+        <v>-3.0264781551167134e-05</v>
       </c>
       <c r="AF24">
-        <v>-4.2999107983410516e-05</v>
+        <v>-4.4527193572601581e-05</v>
       </c>
       <c r="AG24">
-        <v>7.0353498413279949e-07</v>
+        <v>6.5366012054694141e-07</v>
       </c>
       <c r="AH24">
-        <v>4.3654792742303509e-05</v>
+        <v>4.3362025318772384e-05</v>
       </c>
       <c r="AI24">
-        <v>8.7640245386980315e-06</v>
+        <v>8.5938831198583462e-06</v>
       </c>
       <c r="AJ24">
-        <v>-0.00082784343779009561</v>
+        <v>-0.0008372696049304179</v>
       </c>
     </row>
     <row r="25">
@@ -3119,109 +3119,109 @@
         <v>51</v>
       </c>
       <c r="B25">
-        <v>-0.25057095185008144</v>
+        <v>-0.25092251366718016</v>
       </c>
       <c r="C25">
-        <v>0.00010919930756859229</v>
+        <v>0.00011215434604868531</v>
       </c>
       <c r="D25">
-        <v>1.2068406259105221e-05</v>
+        <v>1.2297618082755761e-05</v>
       </c>
       <c r="E25">
-        <v>-2.019680137828838e-08</v>
+        <v>-2.0608999658077889e-08</v>
       </c>
       <c r="F25">
-        <v>7.3325191904736575e-06</v>
+        <v>-1.8526597375711552e-06</v>
       </c>
       <c r="G25">
-        <v>0.00010496985164197403</v>
+        <v>0.00010021275369884908</v>
       </c>
       <c r="H25">
-        <v>3.5154995881514023e-05</v>
+        <v>3.0256074356232451e-05</v>
       </c>
       <c r="I25">
-        <v>2.3598843092312557e-05</v>
+        <v>1.5647627642145255e-05</v>
       </c>
       <c r="J25">
-        <v>1.1311372692250869e-05</v>
+        <v>1.0944686118085697e-05</v>
       </c>
       <c r="K25">
-        <v>-2.5286700238444392e-05</v>
+        <v>-2.3331419959735523e-05</v>
       </c>
       <c r="L25">
-        <v>-1.3796579052501655e-05</v>
+        <v>-1.2159413859166159e-05</v>
       </c>
       <c r="M25">
-        <v>-2.7157703428098845e-05</v>
+        <v>-2.8533560617156782e-05</v>
       </c>
       <c r="N25">
-        <v>-0.00019790241739100958</v>
+        <v>-0.00020313281106342559</v>
       </c>
       <c r="O25">
-        <v>2.1349448885148807e-06</v>
+        <v>2.2032967250036368e-06</v>
       </c>
       <c r="P25">
-        <v>-2.0661299500110961e-05</v>
+        <v>-2.0180063355706328e-05</v>
       </c>
       <c r="Q25">
-        <v>3.4096513352007232e-05</v>
+        <v>3.5644371805208515e-05</v>
       </c>
       <c r="R25">
-        <v>0.00089127060186100504</v>
+        <v>0.00091370112522068739</v>
       </c>
       <c r="S25">
-        <v>0.0010319563433645457</v>
+        <v>0.0010587494873965479</v>
       </c>
       <c r="T25">
-        <v>0.0010400001708056883</v>
+        <v>0.0010616380279193302</v>
       </c>
       <c r="U25">
-        <v>-0.00010553482450312464</v>
+        <v>-9.1700850137538606e-05</v>
       </c>
       <c r="V25">
-        <v>-0.00023861001404968957</v>
+        <v>-0.00021560798461217525</v>
       </c>
       <c r="W25">
-        <v>-0.00027720321106184959</v>
+        <v>-0.00025305479865876234</v>
       </c>
       <c r="X25">
-        <v>0.00039799076756211443</v>
+        <v>0.00040571764312913105</v>
       </c>
       <c r="Y25">
-        <v>0.00034754770859169825</v>
+        <v>0.00035433772858881301</v>
       </c>
       <c r="Z25">
-        <v>0.007084741218361292</v>
+        <v>0.0072464493667857791</v>
       </c>
       <c r="AA25">
-        <v>-0.00012305285941720484</v>
+        <v>-0.00012217780685600183</v>
       </c>
       <c r="AB25">
-        <v>-8.1863036665034993e-05</v>
+        <v>-8.6092845103106597e-05</v>
       </c>
       <c r="AC25">
-        <v>-9.7050776052944943e-05</v>
+        <v>-9.5881723961179416e-05</v>
       </c>
       <c r="AD25">
-        <v>-7.5280938311871721e-05</v>
+        <v>-7.3710678641835596e-05</v>
       </c>
       <c r="AE25">
-        <v>-7.5616856199937069e-05</v>
+        <v>-7.1108276546815623e-05</v>
       </c>
       <c r="AF25">
-        <v>-0.00016097100158499842</v>
+        <v>-0.00016207797794405823</v>
       </c>
       <c r="AG25">
-        <v>-4.461270944023758e-06</v>
+        <v>-4.3156808805736786e-06</v>
       </c>
       <c r="AH25">
-        <v>0.00018554183225410093</v>
+        <v>0.00019335347703999676</v>
       </c>
       <c r="AI25">
-        <v>8.7218874822208697e-05</v>
+        <v>8.3855991784810449e-05</v>
       </c>
       <c r="AJ25">
-        <v>-0.0014865553221428342</v>
+        <v>-0.0015484547893658395</v>
       </c>
     </row>
     <row r="26">
@@ -3229,109 +3229,109 @@
         <v>52</v>
       </c>
       <c r="B26">
-        <v>0.24989273312437241</v>
+        <v>0.24884572296528087</v>
       </c>
       <c r="C26">
-        <v>2.008944525785602e-05</v>
+        <v>2.0237935776571509e-05</v>
       </c>
       <c r="D26">
-        <v>-5.6742895563629365e-08</v>
+        <v>-1.669834780127985e-08</v>
       </c>
       <c r="E26">
-        <v>-6.8232360607243115e-09</v>
+        <v>-7.3285979386071544e-09</v>
       </c>
       <c r="F26">
-        <v>-0.0003879657408031901</v>
+        <v>-0.00038803656878563016</v>
       </c>
       <c r="G26">
-        <v>-7.4596915694141459e-06</v>
+        <v>-6.9627304752195433e-06</v>
       </c>
       <c r="H26">
-        <v>-3.0570556696946517e-07</v>
+        <v>-7.0027007500529127e-09</v>
       </c>
       <c r="I26">
-        <v>-3.490996641805142e-05</v>
+        <v>-3.4380106914374197e-05</v>
       </c>
       <c r="J26">
-        <v>4.8588571204757222e-06</v>
+        <v>4.563412095390282e-06</v>
       </c>
       <c r="K26">
-        <v>-1.2605071197613945e-05</v>
+        <v>-1.3311846407239661e-05</v>
       </c>
       <c r="L26">
-        <v>3.617953627115794e-06</v>
+        <v>3.5730168075219011e-06</v>
       </c>
       <c r="M26">
-        <v>-3.6761612594367478e-06</v>
+        <v>-3.2530016249742996e-06</v>
       </c>
       <c r="N26">
-        <v>-8.8766111784358784e-05</v>
+        <v>-8.9020669276913822e-05</v>
       </c>
       <c r="O26">
-        <v>-1.5685781831742667e-07</v>
+        <v>-1.5678825988286646e-07</v>
       </c>
       <c r="P26">
-        <v>2.4480863746305988e-05</v>
+        <v>2.4682265270006582e-05</v>
       </c>
       <c r="Q26">
-        <v>-4.8760279663096189e-06</v>
+        <v>-5.3586008497560293e-06</v>
       </c>
       <c r="R26">
-        <v>-0.00014345429489732997</v>
+        <v>-0.0001432648957492913</v>
       </c>
       <c r="S26">
-        <v>-5.4917603809427618e-05</v>
+        <v>-5.4904635408727087e-05</v>
       </c>
       <c r="T26">
-        <v>-0.00010644408694181207</v>
+        <v>-0.00010684925799648443</v>
       </c>
       <c r="U26">
-        <v>-3.3787078824263489e-05</v>
+        <v>-3.9417612084442083e-05</v>
       </c>
       <c r="V26">
-        <v>-2.7087647779604554e-05</v>
+        <v>-3.4087703917488887e-05</v>
       </c>
       <c r="W26">
-        <v>-3.492590841396373e-05</v>
+        <v>-4.1450545557274871e-05</v>
       </c>
       <c r="X26">
-        <v>-6.6280645229651496e-05</v>
+        <v>-6.7388589266341057e-05</v>
       </c>
       <c r="Y26">
-        <v>-4.7904968243904088e-05</v>
+        <v>-4.9404338160263317e-05</v>
       </c>
       <c r="Z26">
-        <v>-0.00012305285941720484</v>
+        <v>-0.00012217780685600183</v>
       </c>
       <c r="AA26">
-        <v>0.0034619170763470239</v>
+        <v>0.0034546438021019919</v>
       </c>
       <c r="AB26">
-        <v>0.0029029759032347894</v>
+        <v>0.002895408457057839</v>
       </c>
       <c r="AC26">
-        <v>0.0029085033857017997</v>
+        <v>0.002901000262001698</v>
       </c>
       <c r="AD26">
-        <v>0.0029060405772065173</v>
+        <v>0.0028987171562500471</v>
       </c>
       <c r="AE26">
-        <v>0.0029087243273573822</v>
+        <v>0.002901398655199513</v>
       </c>
       <c r="AF26">
-        <v>0.0029070270264578901</v>
+        <v>0.0028997381361196848</v>
       </c>
       <c r="AG26">
-        <v>-1.4313372219291668e-06</v>
+        <v>-1.4020876682834243e-06</v>
       </c>
       <c r="AH26">
-        <v>-0.00023490624061426506</v>
+        <v>-0.00023463508191903359</v>
       </c>
       <c r="AI26">
-        <v>-0.00010769817196022084</v>
+        <v>-0.00010827397067764713</v>
       </c>
       <c r="AJ26">
-        <v>-0.0026099034608096233</v>
+        <v>-0.0025970306508298147</v>
       </c>
     </row>
     <row r="27">
@@ -3339,109 +3339,109 @@
         <v>53</v>
       </c>
       <c r="B27">
-        <v>0.12004958849408647</v>
+        <v>0.11872590854763053</v>
       </c>
       <c r="C27">
-        <v>3.0620277680629821e-05</v>
+        <v>3.063302764934984e-05</v>
       </c>
       <c r="D27">
-        <v>3.1955560987219204e-06</v>
+        <v>3.2788772190521498e-06</v>
       </c>
       <c r="E27">
-        <v>-3.4670737634483481e-08</v>
+        <v>-3.5393546576996303e-08</v>
       </c>
       <c r="F27">
-        <v>-0.0003438759676396907</v>
+        <v>-0.00034371360137544455</v>
       </c>
       <c r="G27">
-        <v>5.4673612840301764e-05</v>
+        <v>5.539265703185438e-05</v>
       </c>
       <c r="H27">
-        <v>2.9363457396843162e-05</v>
+        <v>2.9894755415335817e-05</v>
       </c>
       <c r="I27">
-        <v>-2.0527092432584375e-05</v>
+        <v>-1.9935297925802279e-05</v>
       </c>
       <c r="J27">
-        <v>5.9795931515586247e-06</v>
+        <v>5.7019445878961817e-06</v>
       </c>
       <c r="K27">
-        <v>-4.8552193531725685e-05</v>
+        <v>-5.0562670370734924e-05</v>
       </c>
       <c r="L27">
-        <v>2.67415623426097e-06</v>
+        <v>2.6211495365810082e-06</v>
       </c>
       <c r="M27">
-        <v>-7.0413633157318348e-06</v>
+        <v>-6.5779641755963787e-06</v>
       </c>
       <c r="N27">
-        <v>-0.00010466159803707801</v>
+        <v>-0.000104670008912009</v>
       </c>
       <c r="O27">
-        <v>-1.1896263647887223e-07</v>
+        <v>-1.2004808776803968e-07</v>
       </c>
       <c r="P27">
-        <v>1.6708748131363219e-05</v>
+        <v>1.6865130448984807e-05</v>
       </c>
       <c r="Q27">
-        <v>-6.1243900260174889e-06</v>
+        <v>-6.6648461606380605e-06</v>
       </c>
       <c r="R27">
-        <v>-8.3691032520712139e-05</v>
+        <v>-8.3755075490569986e-05</v>
       </c>
       <c r="S27">
-        <v>-2.8529795788011236e-05</v>
+        <v>-2.8740775308358502e-05</v>
       </c>
       <c r="T27">
-        <v>-7.2881788181329565e-05</v>
+        <v>-7.3557328757453688e-05</v>
       </c>
       <c r="U27">
-        <v>-0.00028615808145876498</v>
+        <v>-0.0003019759362838069</v>
       </c>
       <c r="V27">
-        <v>-0.00030288158819016808</v>
+        <v>-0.0003211117580010376</v>
       </c>
       <c r="W27">
-        <v>-0.00032499519214412506</v>
+        <v>-0.00034266042857816412</v>
       </c>
       <c r="X27">
-        <v>-8.8778427547365536e-05</v>
+        <v>-8.8098282990746392e-05</v>
       </c>
       <c r="Y27">
-        <v>-2.9352671216799006e-05</v>
+        <v>-2.9713001422008783e-05</v>
       </c>
       <c r="Z27">
-        <v>-8.1863036665034993e-05</v>
+        <v>-8.6092845103106597e-05</v>
       </c>
       <c r="AA27">
-        <v>0.0029029759032347894</v>
+        <v>0.002895408457057839</v>
       </c>
       <c r="AB27">
-        <v>0.0035373462453600541</v>
+        <v>0.003529688256691713</v>
       </c>
       <c r="AC27">
-        <v>0.0029216686038496913</v>
+        <v>0.0029140377497693087</v>
       </c>
       <c r="AD27">
-        <v>0.0029052706475953551</v>
+        <v>0.0028976281791675191</v>
       </c>
       <c r="AE27">
-        <v>0.0029154973797012431</v>
+        <v>0.0029080038048700002</v>
       </c>
       <c r="AF27">
-        <v>0.0029077053027501297</v>
+        <v>0.0029003232849200127</v>
       </c>
       <c r="AG27">
-        <v>-1.0244352968129001e-06</v>
+        <v>-9.9832694210193781e-07</v>
       </c>
       <c r="AH27">
-        <v>-0.00021127524913756943</v>
+        <v>-0.00021092997712584584</v>
       </c>
       <c r="AI27">
-        <v>-8.7048774519841922e-05</v>
+        <v>-8.7623671190626947e-05</v>
       </c>
       <c r="AJ27">
-        <v>-0.0024873590331442085</v>
+        <v>-0.0024655060688184112</v>
       </c>
     </row>
     <row r="28">
@@ -3449,109 +3449,109 @@
         <v>54</v>
       </c>
       <c r="B28">
-        <v>0.37943915130448625</v>
+        <v>0.37806239454416102</v>
       </c>
       <c r="C28">
-        <v>1.737095255270012e-05</v>
+        <v>1.7472107568759453e-05</v>
       </c>
       <c r="D28">
-        <v>-6.8472474563408703e-07</v>
+        <v>-6.1852160726400007e-07</v>
       </c>
       <c r="E28">
-        <v>-1.0666190224700449e-08</v>
+        <v>-1.1252977230179877e-08</v>
       </c>
       <c r="F28">
-        <v>-0.00032144368232211009</v>
+        <v>-0.00032112532557556934</v>
       </c>
       <c r="G28">
-        <v>4.9310795184917987e-05</v>
+        <v>5.0136807107502518e-05</v>
       </c>
       <c r="H28">
-        <v>3.4039029180815849e-05</v>
+        <v>3.4667182851725134e-05</v>
       </c>
       <c r="I28">
-        <v>-7.3287296165411089e-06</v>
+        <v>-6.5916114264355285e-06</v>
       </c>
       <c r="J28">
-        <v>3.8411332852990127e-06</v>
+        <v>3.5746262626243575e-06</v>
       </c>
       <c r="K28">
-        <v>-6.3493944229510251e-05</v>
+        <v>-6.5379825519015626e-05</v>
       </c>
       <c r="L28">
-        <v>3.9441884765833681e-06</v>
+        <v>3.866317762942793e-06</v>
       </c>
       <c r="M28">
-        <v>-5.5340363770648717e-06</v>
+        <v>-5.0858548197488004e-06</v>
       </c>
       <c r="N28">
-        <v>-0.00011200549554738826</v>
+        <v>-0.00011217044980173924</v>
       </c>
       <c r="O28">
-        <v>6.7224863809878748e-08</v>
+        <v>6.8078232379643612e-08</v>
       </c>
       <c r="P28">
-        <v>6.6184178924230008e-06</v>
+        <v>6.7775508544231446e-06</v>
       </c>
       <c r="Q28">
-        <v>1.1151586887880134e-05</v>
+        <v>1.0633462070013238e-05</v>
       </c>
       <c r="R28">
-        <v>1.9830693334169786e-05</v>
+        <v>2.0211083847265082e-05</v>
       </c>
       <c r="S28">
-        <v>8.3710665276034643e-05</v>
+        <v>8.4232763960374185e-05</v>
       </c>
       <c r="T28">
-        <v>2.9071147594358915e-05</v>
+        <v>2.9173819291400741e-05</v>
       </c>
       <c r="U28">
-        <v>-0.00042684280750269425</v>
+        <v>-0.00044183785270163201</v>
       </c>
       <c r="V28">
-        <v>-0.0004365576943273974</v>
+        <v>-0.00045312768769832732</v>
       </c>
       <c r="W28">
-        <v>-0.00041555000174634937</v>
+        <v>-0.00043202806515636435</v>
       </c>
       <c r="X28">
-        <v>-0.0001025623456676171</v>
+        <v>-0.0001020339454392385</v>
       </c>
       <c r="Y28">
-        <v>-6.6569343664000434e-05</v>
+        <v>-6.7370281808433333e-05</v>
       </c>
       <c r="Z28">
-        <v>-9.7050776052944943e-05</v>
+        <v>-9.5881723961179416e-05</v>
       </c>
       <c r="AA28">
-        <v>0.0029085033857017997</v>
+        <v>0.002901000262001698</v>
       </c>
       <c r="AB28">
-        <v>0.0029216686038496913</v>
+        <v>0.0029140377497693087</v>
       </c>
       <c r="AC28">
-        <v>0.0037686949155632948</v>
+        <v>0.003761140206710195</v>
       </c>
       <c r="AD28">
-        <v>0.0029101001154186691</v>
+        <v>0.0029025408304503494</v>
       </c>
       <c r="AE28">
-        <v>0.0029185591438347729</v>
+        <v>0.0029110942020365151</v>
       </c>
       <c r="AF28">
-        <v>0.0029115119018080456</v>
+        <v>0.0029041079820278982</v>
       </c>
       <c r="AG28">
-        <v>-6.639213141441388e-06</v>
+        <v>-6.6175940120593565e-06</v>
       </c>
       <c r="AH28">
-        <v>-0.00015229613577247584</v>
+        <v>-0.00015212615683393369</v>
       </c>
       <c r="AI28">
-        <v>-0.00010316146593031673</v>
+        <v>-0.0001036977166143387</v>
       </c>
       <c r="AJ28">
-        <v>-0.0022453718805205509</v>
+        <v>-0.0022246483183383219</v>
       </c>
     </row>
     <row r="29">
@@ -3559,109 +3559,109 @@
         <v>55</v>
       </c>
       <c r="B29">
-        <v>0.19953268158107076</v>
+        <v>0.19865261352957869</v>
       </c>
       <c r="C29">
-        <v>9.9550358277092029e-06</v>
+        <v>1.0119824896696742e-05</v>
       </c>
       <c r="D29">
-        <v>3.2431857514446849e-06</v>
+        <v>3.2796974968972556e-06</v>
       </c>
       <c r="E29">
-        <v>-3.7838868997234808e-08</v>
+        <v>-3.8147409859343333e-08</v>
       </c>
       <c r="F29">
-        <v>-0.00033621321242632862</v>
+        <v>-0.00033621873709881764</v>
       </c>
       <c r="G29">
-        <v>4.5919926953411143e-05</v>
+        <v>4.646954156561396e-05</v>
       </c>
       <c r="H29">
-        <v>3.1579243025551076e-05</v>
+        <v>3.1970297516162294e-05</v>
       </c>
       <c r="I29">
-        <v>-1.6400313896113033e-05</v>
+        <v>-1.5896844646890568e-05</v>
       </c>
       <c r="J29">
-        <v>3.582330656313413e-07</v>
+        <v>6.8099845108449441e-08</v>
       </c>
       <c r="K29">
-        <v>-6.7674234959375079e-06</v>
+        <v>-7.5124868898083022e-06</v>
       </c>
       <c r="L29">
-        <v>3.5712211650880036e-06</v>
+        <v>3.6237078676050022e-06</v>
       </c>
       <c r="M29">
-        <v>-4.717933822105455e-06</v>
+        <v>-4.3034677956591379e-06</v>
       </c>
       <c r="N29">
-        <v>-8.7585297829528234e-05</v>
+        <v>-8.7723857067682938e-05</v>
       </c>
       <c r="O29">
-        <v>-2.8464340596502083e-07</v>
+        <v>-2.8313884517011309e-07</v>
       </c>
       <c r="P29">
-        <v>2.4974489775260748e-05</v>
+        <v>2.5225174432318663e-05</v>
       </c>
       <c r="Q29">
-        <v>1.3065401879147837e-05</v>
+        <v>1.2598573094939293e-05</v>
       </c>
       <c r="R29">
-        <v>-0.00021070400319908589</v>
+        <v>-0.00020992014986082747</v>
       </c>
       <c r="S29">
-        <v>-8.9978529541907826e-05</v>
+        <v>-8.9349235680963313e-05</v>
       </c>
       <c r="T29">
-        <v>-0.00013469766881531176</v>
+        <v>-0.00013456539808588686</v>
       </c>
       <c r="U29">
-        <v>3.0242113666888171e-05</v>
+        <v>2.5111280528497537e-05</v>
       </c>
       <c r="V29">
-        <v>1.0262788959360114e-05</v>
+        <v>3.7972442476913448e-06</v>
       </c>
       <c r="W29">
-        <v>4.0257242717714123e-05</v>
+        <v>3.4204621375849564e-05</v>
       </c>
       <c r="X29">
-        <v>-8.1845277992750713e-05</v>
+        <v>-8.0919734234278183e-05</v>
       </c>
       <c r="Y29">
-        <v>-3.4827249257180079e-05</v>
+        <v>-3.5315141041959751e-05</v>
       </c>
       <c r="Z29">
-        <v>-7.5280938311871721e-05</v>
+        <v>-7.3710678641835596e-05</v>
       </c>
       <c r="AA29">
-        <v>0.0029060405772065173</v>
+        <v>0.0028987171562500471</v>
       </c>
       <c r="AB29">
-        <v>0.0029052706475953551</v>
+        <v>0.0028976281791675191</v>
       </c>
       <c r="AC29">
-        <v>0.0029101001154186691</v>
+        <v>0.0029025408304503494</v>
       </c>
       <c r="AD29">
-        <v>0.0033873501817333592</v>
+        <v>0.0033798322413862514</v>
       </c>
       <c r="AE29">
-        <v>0.0029144264479919156</v>
+        <v>0.0029070680837618591</v>
       </c>
       <c r="AF29">
-        <v>0.0029144657171838707</v>
+        <v>0.0029071022719746199</v>
       </c>
       <c r="AG29">
-        <v>-2.4475277782291051e-06</v>
+        <v>-2.4123937405018218e-06</v>
       </c>
       <c r="AH29">
-        <v>-0.0002167506171987469</v>
+        <v>-0.00021652827104453936</v>
       </c>
       <c r="AI29">
-        <v>-0.00010420829566168258</v>
+        <v>-0.00010494867171692259</v>
       </c>
       <c r="AJ29">
-        <v>-0.0026899104053870653</v>
+        <v>-0.0026794477424517179</v>
       </c>
     </row>
     <row r="30">
@@ -3669,109 +3669,109 @@
         <v>56</v>
       </c>
       <c r="B30">
-        <v>0.28878556231026104</v>
+        <v>0.2877197686956528</v>
       </c>
       <c r="C30">
-        <v>1.8740201872788885e-05</v>
+        <v>1.8933072447856352e-05</v>
       </c>
       <c r="D30">
-        <v>-8.2469178198846168e-07</v>
+        <v>-7.8189918378808134e-07</v>
       </c>
       <c r="E30">
-        <v>5.3965842930057215e-09</v>
+        <v>5.1737164344847225e-09</v>
       </c>
       <c r="F30">
-        <v>-0.00033238896329270599</v>
+        <v>-0.00033220243341828973</v>
       </c>
       <c r="G30">
-        <v>6.1274752174575741e-05</v>
+        <v>6.2051039214802662e-05</v>
       </c>
       <c r="H30">
-        <v>5.5209910383559709e-05</v>
+        <v>5.5802811006823383e-05</v>
       </c>
       <c r="I30">
-        <v>7.8808003916201817e-07</v>
+        <v>1.4989926946922406e-06</v>
       </c>
       <c r="J30">
-        <v>5.711689207059639e-06</v>
+        <v>5.4088922260687786e-06</v>
       </c>
       <c r="K30">
-        <v>-3.2184299087756286e-05</v>
+        <v>-3.3859203520010322e-05</v>
       </c>
       <c r="L30">
-        <v>2.9579091092853315e-06</v>
+        <v>3.0357571961333704e-06</v>
       </c>
       <c r="M30">
-        <v>-6.538428092497768e-06</v>
+        <v>-6.1215711150157103e-06</v>
       </c>
       <c r="N30">
-        <v>-0.0001014477349346528</v>
+        <v>-0.00010165862295907183</v>
       </c>
       <c r="O30">
-        <v>-2.2703670235616047e-07</v>
+        <v>-2.2422821792017136e-07</v>
       </c>
       <c r="P30">
-        <v>5.4294317632951387e-06</v>
+        <v>5.7037174097784301e-06</v>
       </c>
       <c r="Q30">
-        <v>2.6647312627876472e-05</v>
+        <v>2.6173973083163467e-05</v>
       </c>
       <c r="R30">
-        <v>-0.0001713867178525768</v>
+        <v>-0.00017012548983189046</v>
       </c>
       <c r="S30">
-        <v>-7.7348360760081183e-05</v>
+        <v>-7.6229307958565473e-05</v>
       </c>
       <c r="T30">
-        <v>-0.00011938335773575316</v>
+        <v>-0.00011863249829174166</v>
       </c>
       <c r="U30">
-        <v>-0.00018854380716434079</v>
+        <v>-0.00020073732666149764</v>
       </c>
       <c r="V30">
-        <v>-0.00018557136633158295</v>
+        <v>-0.00019975503862872807</v>
       </c>
       <c r="W30">
-        <v>-0.00019909139433911278</v>
+        <v>-0.00021289182875552579</v>
       </c>
       <c r="X30">
-        <v>-7.9303566415632899e-05</v>
+        <v>-7.7961844058088649e-05</v>
       </c>
       <c r="Y30">
-        <v>-2.9747572854813415e-05</v>
+        <v>-3.0264781551167134e-05</v>
       </c>
       <c r="Z30">
-        <v>-7.5616856199937069e-05</v>
+        <v>-7.1108276546815623e-05</v>
       </c>
       <c r="AA30">
-        <v>0.0029087243273573822</v>
+        <v>0.002901398655199513</v>
       </c>
       <c r="AB30">
-        <v>0.0029154973797012431</v>
+        <v>0.0029080038048700002</v>
       </c>
       <c r="AC30">
-        <v>0.0029185591438347729</v>
+        <v>0.0029110942020365151</v>
       </c>
       <c r="AD30">
-        <v>0.0029144264479919156</v>
+        <v>0.0029070680837618591</v>
       </c>
       <c r="AE30">
-        <v>0.003313065612739129</v>
+        <v>0.0033057329895809029</v>
       </c>
       <c r="AF30">
-        <v>0.0029152380562523788</v>
+        <v>0.002907965865561721</v>
       </c>
       <c r="AG30">
-        <v>-4.2143116683275095e-06</v>
+        <v>-4.1873184370279728e-06</v>
       </c>
       <c r="AH30">
-        <v>-0.00013314379931529544</v>
+        <v>-0.00013278413501111898</v>
       </c>
       <c r="AI30">
-        <v>-6.5950887269362532e-05</v>
+        <v>-6.644597786878675e-05</v>
       </c>
       <c r="AJ30">
-        <v>-0.0024311174448058094</v>
+        <v>-0.0024145160689995251</v>
       </c>
     </row>
     <row r="31">
@@ -3779,109 +3779,109 @@
         <v>57</v>
       </c>
       <c r="B31">
-        <v>0.16224224554125677</v>
+        <v>0.16144997363877731</v>
       </c>
       <c r="C31">
-        <v>1.6236824556625044e-05</v>
+        <v>1.6187612961458784e-05</v>
       </c>
       <c r="D31">
-        <v>-1.0605696990893357e-06</v>
+        <v>-1.042311372228119e-06</v>
       </c>
       <c r="E31">
-        <v>-7.9962469026845007e-10</v>
+        <v>-1.064809383806628e-09</v>
       </c>
       <c r="F31">
-        <v>-0.00033821930018997277</v>
+        <v>-0.00033806807430963762</v>
       </c>
       <c r="G31">
-        <v>6.3162003885449379e-05</v>
+        <v>6.3854481917491782e-05</v>
       </c>
       <c r="H31">
-        <v>4.0949210002263745e-05</v>
+        <v>4.1433461054875513e-05</v>
       </c>
       <c r="I31">
-        <v>-1.0023184592857515e-05</v>
+        <v>-9.3011282859750245e-06</v>
       </c>
       <c r="J31">
-        <v>1.2897999056349304e-05</v>
+        <v>1.2543127161724476e-05</v>
       </c>
       <c r="K31">
-        <v>-2.8043883466234308e-05</v>
+        <v>-3.0170302346778518e-05</v>
       </c>
       <c r="L31">
-        <v>3.1652168661934511e-06</v>
+        <v>3.2406817488013394e-06</v>
       </c>
       <c r="M31">
-        <v>-2.9057213094194881e-06</v>
+        <v>-2.3852948837333645e-06</v>
       </c>
       <c r="N31">
-        <v>-0.0001261852041956013</v>
+        <v>-0.00012612118486749618</v>
       </c>
       <c r="O31">
-        <v>-3.4574382276464022e-08</v>
+        <v>-3.5245553032679024e-08</v>
       </c>
       <c r="P31">
-        <v>2.8341475067845799e-05</v>
+        <v>2.8610057892047004e-05</v>
       </c>
       <c r="Q31">
-        <v>3.0591265652514424e-06</v>
+        <v>2.4875571624396304e-06</v>
       </c>
       <c r="R31">
-        <v>-0.00010334947615037171</v>
+        <v>-0.00010322925820934435</v>
       </c>
       <c r="S31">
-        <v>1.6882261361857685e-05</v>
+        <v>1.6836283824382507e-05</v>
       </c>
       <c r="T31">
-        <v>-3.5312369631867666e-05</v>
+        <v>-3.5722352160293298e-05</v>
       </c>
       <c r="U31">
-        <v>-0.00020352959101305667</v>
+        <v>-0.00021985978950927326</v>
       </c>
       <c r="V31">
-        <v>-0.00021021413701004374</v>
+        <v>-0.00022840052681100077</v>
       </c>
       <c r="W31">
-        <v>-0.00015975550368417177</v>
+        <v>-0.00017745958410599234</v>
       </c>
       <c r="X31">
-        <v>-9.2811942185132366e-05</v>
+        <v>-9.3829830660649205e-05</v>
       </c>
       <c r="Y31">
-        <v>-4.2999107983410516e-05</v>
+        <v>-4.4527193572601581e-05</v>
       </c>
       <c r="Z31">
-        <v>-0.00016097100158499842</v>
+        <v>-0.00016207797794405823</v>
       </c>
       <c r="AA31">
-        <v>0.0029070270264578901</v>
+        <v>0.0028997381361196848</v>
       </c>
       <c r="AB31">
-        <v>0.0029077053027501297</v>
+        <v>0.0029003232849200127</v>
       </c>
       <c r="AC31">
-        <v>0.0029115119018080456</v>
+        <v>0.0029041079820278982</v>
       </c>
       <c r="AD31">
-        <v>0.0029144657171838707</v>
+        <v>0.0029071022719746199</v>
       </c>
       <c r="AE31">
-        <v>0.0029152380562523788</v>
+        <v>0.002907965865561721</v>
       </c>
       <c r="AF31">
-        <v>0.0034389348138001174</v>
+        <v>0.0034319837776265452</v>
       </c>
       <c r="AG31">
-        <v>-2.9793961509160124e-06</v>
+        <v>-2.9657888275970835e-06</v>
       </c>
       <c r="AH31">
-        <v>-0.00016166259147393789</v>
+        <v>-0.00016101421203997771</v>
       </c>
       <c r="AI31">
-        <v>-9.908780070286982e-05</v>
+        <v>-9.9495306737855339e-05</v>
       </c>
       <c r="AJ31">
-        <v>-0.0025057044599426648</v>
+        <v>-0.0024813814254905997</v>
       </c>
     </row>
     <row r="32">
@@ -3889,109 +3889,109 @@
         <v>58</v>
       </c>
       <c r="B32">
-        <v>-0.048669337576933626</v>
+        <v>-0.048689209973775051</v>
       </c>
       <c r="C32">
-        <v>4.5706930769845149e-07</v>
+        <v>4.685086402398406e-07</v>
       </c>
       <c r="D32">
-        <v>-1.2611444277851479e-08</v>
+        <v>-1.7128619020336376e-08</v>
       </c>
       <c r="E32">
-        <v>-2.1088776176912062e-09</v>
+        <v>-2.0780692991291288e-09</v>
       </c>
       <c r="F32">
-        <v>-1.0847629299590987e-06</v>
+        <v>-1.0993353286844086e-06</v>
       </c>
       <c r="G32">
-        <v>-7.7394332615398398e-07</v>
+        <v>-7.7939584630807104e-07</v>
       </c>
       <c r="H32">
-        <v>-3.6728508684652067e-06</v>
+        <v>-3.674586900181292e-06</v>
       </c>
       <c r="I32">
-        <v>-2.2712442873387257e-06</v>
+        <v>-2.2756531562364967e-06</v>
       </c>
       <c r="J32">
-        <v>9.7116927496613578e-07</v>
+        <v>9.7408680415872816e-07</v>
       </c>
       <c r="K32">
-        <v>-5.0741236670478877e-07</v>
+        <v>-4.2931440931529312e-07</v>
       </c>
       <c r="L32">
-        <v>-2.2299980491866647e-07</v>
+        <v>-2.0092746265654915e-07</v>
       </c>
       <c r="M32">
-        <v>1.4247585618967477e-06</v>
+        <v>1.423080122863651e-06</v>
       </c>
       <c r="N32">
-        <v>-6.4342264269657049e-07</v>
+        <v>-6.4948030421008705e-07</v>
       </c>
       <c r="O32">
-        <v>-1.2076834283234572e-08</v>
+        <v>-1.1950083090177597e-08</v>
       </c>
       <c r="P32">
-        <v>-4.0507905806822829e-07</v>
+        <v>-4.0725713930974466e-07</v>
       </c>
       <c r="Q32">
-        <v>-5.597041323916139e-07</v>
+        <v>-5.5825187629298588e-07</v>
       </c>
       <c r="R32">
-        <v>-4.650223596836282e-06</v>
+        <v>-4.613170688084426e-06</v>
       </c>
       <c r="S32">
-        <v>-1.1098044695567527e-05</v>
+        <v>-1.1071130271835504e-05</v>
       </c>
       <c r="T32">
-        <v>-1.5124170488833594e-05</v>
+        <v>-1.5086855361954969e-05</v>
       </c>
       <c r="U32">
-        <v>-1.2037901713926298e-05</v>
+        <v>-1.1265101323157758e-05</v>
       </c>
       <c r="V32">
-        <v>3.298568482878279e-07</v>
+        <v>1.1891398285518049e-06</v>
       </c>
       <c r="W32">
-        <v>3.6350820467926336e-07</v>
+        <v>1.2072349175609124e-06</v>
       </c>
       <c r="X32">
-        <v>2.8892275891271729e-06</v>
+        <v>2.8039958578033729e-06</v>
       </c>
       <c r="Y32">
-        <v>7.0353498413279949e-07</v>
+        <v>6.5366012054694141e-07</v>
       </c>
       <c r="Z32">
-        <v>-4.461270944023758e-06</v>
+        <v>-4.3156808805736786e-06</v>
       </c>
       <c r="AA32">
-        <v>-1.4313372219291668e-06</v>
+        <v>-1.4020876682834243e-06</v>
       </c>
       <c r="AB32">
-        <v>-1.0244352968129001e-06</v>
+        <v>-9.9832694210193781e-07</v>
       </c>
       <c r="AC32">
-        <v>-6.639213141441388e-06</v>
+        <v>-6.6175940120593565e-06</v>
       </c>
       <c r="AD32">
-        <v>-2.4475277782291051e-06</v>
+        <v>-2.4123937405018218e-06</v>
       </c>
       <c r="AE32">
-        <v>-4.2143116683275095e-06</v>
+        <v>-4.1873184370279728e-06</v>
       </c>
       <c r="AF32">
-        <v>-2.9793961509160124e-06</v>
+        <v>-2.9657888275970835e-06</v>
       </c>
       <c r="AG32">
-        <v>5.6533435071966701e-06</v>
+        <v>5.6546642146720387e-06</v>
       </c>
       <c r="AH32">
-        <v>-5.997998105176366e-06</v>
+        <v>-6.0347853562116668e-06</v>
       </c>
       <c r="AI32">
-        <v>-1.2444182098481972e-05</v>
+        <v>-1.2447866846030128e-05</v>
       </c>
       <c r="AJ32">
-        <v>-8.371642391915619e-05</v>
+        <v>-8.4465594120187006e-05</v>
       </c>
     </row>
     <row r="33">
@@ -3999,109 +3999,109 @@
         <v>59</v>
       </c>
       <c r="B33">
-        <v>0.0015405392933348944</v>
+        <v>0.0015851389673334302</v>
       </c>
       <c r="C33">
-        <v>-1.1395694809765368e-05</v>
+        <v>-1.1473847005678611e-05</v>
       </c>
       <c r="D33">
-        <v>-1.7413413081221549e-06</v>
+        <v>-1.6847001325930749e-06</v>
       </c>
       <c r="E33">
-        <v>2.52249146753247e-10</v>
+        <v>-8.1730982407672239e-11</v>
       </c>
       <c r="F33">
-        <v>0.0001415248638067281</v>
+        <v>0.00014236051972801872</v>
       </c>
       <c r="G33">
-        <v>-2.2030612711127417e-05</v>
+        <v>-2.1333762626362404e-05</v>
       </c>
       <c r="H33">
-        <v>-2.6350577141604002e-06</v>
+        <v>-2.2220081230308599e-06</v>
       </c>
       <c r="I33">
-        <v>-2.4612296879961913e-05</v>
+        <v>-2.4201914548092619e-05</v>
       </c>
       <c r="J33">
-        <v>-1.5609354672070172e-06</v>
+        <v>-1.6489243343083217e-06</v>
       </c>
       <c r="K33">
-        <v>-1.4728989282367707e-05</v>
+        <v>-1.4824104831611794e-05</v>
       </c>
       <c r="L33">
-        <v>-1.2428005193927032e-06</v>
+        <v>-1.9726154642598932e-06</v>
       </c>
       <c r="M33">
-        <v>-2.2626364425119899e-06</v>
+        <v>-2.1417966548243286e-06</v>
       </c>
       <c r="N33">
-        <v>-2.2164138048162176e-05</v>
+        <v>-2.2028666156672684e-05</v>
       </c>
       <c r="O33">
-        <v>-5.7196816117010857e-07</v>
+        <v>-5.6983902704059431e-07</v>
       </c>
       <c r="P33">
-        <v>1.1604885549131006e-05</v>
+        <v>1.1781240804482353e-05</v>
       </c>
       <c r="Q33">
-        <v>1.9939508548757427e-05</v>
+        <v>1.9853810276576752e-05</v>
       </c>
       <c r="R33">
-        <v>-0.0001895486371505592</v>
+        <v>-0.00018856615181738617</v>
       </c>
       <c r="S33">
-        <v>-0.00018796882303842577</v>
+        <v>-0.00018733853906845871</v>
       </c>
       <c r="T33">
-        <v>-0.0002140049657082671</v>
+        <v>-0.00021340453470937437</v>
       </c>
       <c r="U33">
-        <v>-0.0001512338373518933</v>
+        <v>-0.00015787462477048764</v>
       </c>
       <c r="V33">
-        <v>-0.0001359753622682848</v>
+        <v>-0.00014501762955623776</v>
       </c>
       <c r="W33">
-        <v>-0.00011810315069277558</v>
+        <v>-0.00012588171197223594</v>
       </c>
       <c r="X33">
-        <v>2.3279697372624348e-05</v>
+        <v>2.3317861304507446e-05</v>
       </c>
       <c r="Y33">
-        <v>4.3654792742303509e-05</v>
+        <v>4.3362025318772384e-05</v>
       </c>
       <c r="Z33">
-        <v>0.00018554183225410093</v>
+        <v>0.00019335347703999676</v>
       </c>
       <c r="AA33">
-        <v>-0.00023490624061426506</v>
+        <v>-0.00023463508191903359</v>
       </c>
       <c r="AB33">
-        <v>-0.00021127524913756943</v>
+        <v>-0.00021092997712584584</v>
       </c>
       <c r="AC33">
-        <v>-0.00015229613577247584</v>
+        <v>-0.00015212615683393369</v>
       </c>
       <c r="AD33">
-        <v>-0.0002167506171987469</v>
+        <v>-0.00021652827104453936</v>
       </c>
       <c r="AE33">
-        <v>-0.00013314379931529544</v>
+        <v>-0.00013278413501111898</v>
       </c>
       <c r="AF33">
-        <v>-0.00016166259147393789</v>
+        <v>-0.00016101421203997771</v>
       </c>
       <c r="AG33">
-        <v>-5.997998105176366e-06</v>
+        <v>-6.0347853562116668e-06</v>
       </c>
       <c r="AH33">
-        <v>0.001799609755040728</v>
+        <v>0.0018000039348756462</v>
       </c>
       <c r="AI33">
-        <v>0.00019303518533604131</v>
+        <v>0.00019289250734157588</v>
       </c>
       <c r="AJ33">
-        <v>0.00060398840478209724</v>
+        <v>0.00060857861923649891</v>
       </c>
     </row>
     <row r="34">
@@ -4109,109 +4109,109 @@
         <v>60</v>
       </c>
       <c r="B34">
-        <v>-0.46934929547261428</v>
+        <v>-0.46924294593023502</v>
       </c>
       <c r="C34">
-        <v>7.7841352484640314e-07</v>
+        <v>6.2958735926880365e-07</v>
       </c>
       <c r="D34">
-        <v>-5.8608815061820762e-06</v>
+        <v>-5.8392477553168619e-06</v>
       </c>
       <c r="E34">
-        <v>5.1451634562556878e-08</v>
+        <v>5.1166537494513596e-08</v>
       </c>
       <c r="F34">
-        <v>9.6796122039921882e-05</v>
+        <v>9.7074715787209397e-05</v>
       </c>
       <c r="G34">
-        <v>3.1578757810894997e-05</v>
+        <v>3.1445221417489129e-05</v>
       </c>
       <c r="H34">
-        <v>1.7121646091136532e-05</v>
+        <v>1.696137444533167e-05</v>
       </c>
       <c r="I34">
-        <v>3.2512755883705105e-06</v>
+        <v>3.1194738703972828e-06</v>
       </c>
       <c r="J34">
-        <v>-1.3730403899072507e-05</v>
+        <v>-1.3764479233565625e-05</v>
       </c>
       <c r="K34">
-        <v>6.3375947813017154e-06</v>
+        <v>6.6164744494148471e-06</v>
       </c>
       <c r="L34">
-        <v>-2.4194662693187976e-06</v>
+        <v>-2.6014107358379848e-06</v>
       </c>
       <c r="M34">
-        <v>-2.5026242273638586e-06</v>
+        <v>-2.4784653892905579e-06</v>
       </c>
       <c r="N34">
-        <v>5.4763436536255702e-05</v>
+        <v>5.4917609153452753e-05</v>
       </c>
       <c r="O34">
-        <v>8.8186565686442837e-08</v>
+        <v>8.643054992173987e-08</v>
       </c>
       <c r="P34">
-        <v>1.0604849255206464e-05</v>
+        <v>1.0623709512893069e-05</v>
       </c>
       <c r="Q34">
-        <v>-2.0131342377696995e-05</v>
+        <v>-2.0149280674294963e-05</v>
       </c>
       <c r="R34">
-        <v>6.374556169201108e-05</v>
+        <v>6.3385690700804714e-05</v>
       </c>
       <c r="S34">
-        <v>5.0209324960333659e-05</v>
+        <v>4.9853689155833839e-05</v>
       </c>
       <c r="T34">
-        <v>6.5692277114502359e-05</v>
+        <v>6.5039223023342224e-05</v>
       </c>
       <c r="U34">
-        <v>-3.2714931552187479e-05</v>
+        <v>-3.2008186709652116e-05</v>
       </c>
       <c r="V34">
-        <v>1.7109776470275624e-05</v>
+        <v>1.7419839376479201e-05</v>
       </c>
       <c r="W34">
-        <v>4.4973636718738733e-06</v>
+        <v>5.1264841992903001e-06</v>
       </c>
       <c r="X34">
-        <v>-4.8265097263521076e-06</v>
+        <v>-5.5474953689810301e-06</v>
       </c>
       <c r="Y34">
-        <v>8.7640245386980315e-06</v>
+        <v>8.5938831198583462e-06</v>
       </c>
       <c r="Z34">
-        <v>8.7218874822208697e-05</v>
+        <v>8.3855991784810449e-05</v>
       </c>
       <c r="AA34">
-        <v>-0.00010769817196022084</v>
+        <v>-0.00010827397067764713</v>
       </c>
       <c r="AB34">
-        <v>-8.7048774519841922e-05</v>
+        <v>-8.7623671190626947e-05</v>
       </c>
       <c r="AC34">
-        <v>-0.00010316146593031673</v>
+        <v>-0.0001036977166143387</v>
       </c>
       <c r="AD34">
-        <v>-0.00010420829566168258</v>
+        <v>-0.00010494867171692259</v>
       </c>
       <c r="AE34">
-        <v>-6.5950887269362532e-05</v>
+        <v>-6.644597786878675e-05</v>
       </c>
       <c r="AF34">
-        <v>-9.908780070286982e-05</v>
+        <v>-9.9495306737855339e-05</v>
       </c>
       <c r="AG34">
-        <v>-1.2444182098481972e-05</v>
+        <v>-1.2447866846030128e-05</v>
       </c>
       <c r="AH34">
-        <v>0.00019303518533604131</v>
+        <v>0.00019289250734157588</v>
       </c>
       <c r="AI34">
-        <v>0.0013755066770988658</v>
+        <v>0.0013755773438137004</v>
       </c>
       <c r="AJ34">
-        <v>0.00029855710082384284</v>
+        <v>0.00029926324117401275</v>
       </c>
     </row>
     <row r="35">
@@ -4219,109 +4219,109 @@
         <v>61</v>
       </c>
       <c r="B35">
-        <v>0.30558455146641017</v>
+        <v>0.31174716819066239</v>
       </c>
       <c r="C35">
-        <v>0.00034627450460851311</v>
+        <v>0.0003356742477047146</v>
       </c>
       <c r="D35">
-        <v>-0.00029159833162855969</v>
+        <v>-0.00029112257386346889</v>
       </c>
       <c r="E35">
-        <v>2.7453203057273422e-06</v>
+        <v>2.740662570786367e-06</v>
       </c>
       <c r="F35">
-        <v>-0.00011587260424335971</v>
+        <v>-0.00011186756021824623</v>
       </c>
       <c r="G35">
-        <v>-0.00034392369399797193</v>
+        <v>-0.00033968865995608174</v>
       </c>
       <c r="H35">
-        <v>-0.00028215220952928924</v>
+        <v>-0.00027024954788798375</v>
       </c>
       <c r="I35">
-        <v>-0.00014186833008786152</v>
+        <v>-0.00013200696768560455</v>
       </c>
       <c r="J35">
-        <v>3.89467405004832e-05</v>
+        <v>3.9220754620448019e-05</v>
       </c>
       <c r="K35">
-        <v>-0.0029244195253660971</v>
+        <v>-0.0029969009466277357</v>
       </c>
       <c r="L35">
-        <v>0.00011265633956514313</v>
+        <v>0.00011415001739169365</v>
       </c>
       <c r="M35">
-        <v>-2.8201969746309123e-05</v>
+        <v>-2.6998152560893485e-05</v>
       </c>
       <c r="N35">
-        <v>-0.0051345458324562228</v>
+        <v>-0.0051239555920228677</v>
       </c>
       <c r="O35">
-        <v>-9.666866067589903e-05</v>
+        <v>-9.6764647735694614e-05</v>
       </c>
       <c r="P35">
-        <v>-0.00045274442340696415</v>
+        <v>-0.00045285693650963738</v>
       </c>
       <c r="Q35">
-        <v>0.0023562528910354447</v>
+        <v>0.0023564039702391984</v>
       </c>
       <c r="R35">
-        <v>-0.048628395941666985</v>
+        <v>-0.048664961998171108</v>
       </c>
       <c r="S35">
-        <v>-0.048269432432185289</v>
+        <v>-0.048299124947391303</v>
       </c>
       <c r="T35">
-        <v>-0.047652712381011209</v>
+        <v>-0.047677452669036363</v>
       </c>
       <c r="U35">
-        <v>-0.026942780966095696</v>
+        <v>-0.027517145322816634</v>
       </c>
       <c r="V35">
-        <v>-0.022981610082609877</v>
+        <v>-0.023565759690329612</v>
       </c>
       <c r="W35">
-        <v>-0.023842405045704632</v>
+        <v>-0.024436653697039588</v>
       </c>
       <c r="X35">
-        <v>-0.00074773814662214711</v>
+        <v>-0.00076972963302752388</v>
       </c>
       <c r="Y35">
-        <v>-0.00082784343779009561</v>
+        <v>-0.0008372696049304179</v>
       </c>
       <c r="Z35">
-        <v>-0.0014865553221428342</v>
+        <v>-0.0015484547893658395</v>
       </c>
       <c r="AA35">
-        <v>-0.0026099034608096233</v>
+        <v>-0.0025970306508298147</v>
       </c>
       <c r="AB35">
-        <v>-0.0024873590331442085</v>
+        <v>-0.0024655060688184112</v>
       </c>
       <c r="AC35">
-        <v>-0.0022453718805205509</v>
+        <v>-0.0022246483183383219</v>
       </c>
       <c r="AD35">
-        <v>-0.0026899104053870653</v>
+        <v>-0.0026794477424517179</v>
       </c>
       <c r="AE35">
-        <v>-0.0024311174448058094</v>
+        <v>-0.0024145160689995251</v>
       </c>
       <c r="AF35">
-        <v>-0.0025057044599426648</v>
+        <v>-0.0024813814254905997</v>
       </c>
       <c r="AG35">
-        <v>-8.371642391915619e-05</v>
+        <v>-8.4465594120187006e-05</v>
       </c>
       <c r="AH35">
-        <v>0.00060398840478209724</v>
+        <v>0.00060857861923649891</v>
       </c>
       <c r="AI35">
-        <v>0.00029855710082384284</v>
+        <v>0.00029926324117401275</v>
       </c>
       <c r="AJ35">
-        <v>0.082699131413959515</v>
+        <v>0.083312196675912192</v>
       </c>
     </row>
   </sheetData>
@@ -4445,106 +4445,106 @@
         <v>28</v>
       </c>
       <c r="B2">
-        <v>-0.017140229570873192</v>
+        <v>-0.016530073157209738</v>
       </c>
       <c r="C2">
-        <v>0.00033806938097501703</v>
+        <v>0.00033800478518149576</v>
       </c>
       <c r="D2">
-        <v>-1.1778298065185433e-06</v>
+        <v>-1.1595262593671678e-06</v>
       </c>
       <c r="E2">
-        <v>3.3006838742514826e-08</v>
+        <v>3.2797749563823646e-08</v>
       </c>
       <c r="F2">
-        <v>2.3502177242822334e-05</v>
+        <v>2.3514888390001136e-05</v>
       </c>
       <c r="G2">
-        <v>-2.1957961697634844e-05</v>
+        <v>-2.1657825642411691e-05</v>
       </c>
       <c r="H2">
-        <v>-1.4483117365472833e-05</v>
+        <v>-1.4229050579139729e-05</v>
       </c>
       <c r="I2">
-        <v>-6.721971269187937e-05</v>
+        <v>-6.7355800366263385e-05</v>
       </c>
       <c r="J2">
-        <v>4.1213408368018641e-05</v>
+        <v>4.159705099024866e-05</v>
       </c>
       <c r="K2">
-        <v>-2.226764468905269e-05</v>
+        <v>-2.1122839431273256e-05</v>
       </c>
       <c r="L2">
-        <v>-5.8287437428686758e-07</v>
+        <v>-7.1611176054830783e-07</v>
       </c>
       <c r="M2">
-        <v>-3.1723494920810533e-05</v>
+        <v>-3.2212234831237209e-05</v>
       </c>
       <c r="N2">
-        <v>-0.00032721101553160996</v>
+        <v>-0.00032709392055204717</v>
       </c>
       <c r="O2">
-        <v>-5.2190345536982111e-05</v>
+        <v>-5.2614115386368898e-05</v>
       </c>
       <c r="P2">
-        <v>3.3053013638421755e-05</v>
+        <v>3.3549356567971337e-05</v>
       </c>
       <c r="Q2">
-        <v>-0.0002335383041085244</v>
+        <v>-0.00023316230487734562</v>
       </c>
       <c r="R2">
-        <v>-0.0002303058251058735</v>
+        <v>-0.00023008438428831932</v>
       </c>
       <c r="S2">
-        <v>-0.00019378965804275452</v>
+        <v>-0.00019367918701796553</v>
       </c>
       <c r="T2">
-        <v>-0.00011173905231292986</v>
+        <v>-0.0001027422881938953</v>
       </c>
       <c r="U2">
-        <v>-6.1625668049730789e-05</v>
+        <v>-5.2265305761841304e-05</v>
       </c>
       <c r="V2">
-        <v>-0.00021239483960761732</v>
+        <v>-0.00020319985945792786</v>
       </c>
       <c r="W2">
-        <v>3.9564821483017843e-05</v>
+        <v>4.0345429562238022e-05</v>
       </c>
       <c r="X2">
-        <v>-8.9443228905280233e-07</v>
+        <v>-3.6891271348568258e-07</v>
       </c>
       <c r="Y2">
-        <v>0.00013778405085550639</v>
+        <v>0.00013694080783844886</v>
       </c>
       <c r="Z2">
-        <v>5.7221913230602833e-06</v>
+        <v>5.7425833494780031e-06</v>
       </c>
       <c r="AA2">
-        <v>1.0577578694776009e-05</v>
+        <v>1.0743021050413368e-05</v>
       </c>
       <c r="AB2">
-        <v>7.2822143498292637e-06</v>
+        <v>6.9760191377979161e-06</v>
       </c>
       <c r="AC2">
-        <v>4.2572345110106642e-06</v>
+        <v>4.37177101838762e-06</v>
       </c>
       <c r="AD2">
-        <v>-1.8895805004206254e-05</v>
+        <v>-1.8893322566322499e-05</v>
       </c>
       <c r="AE2">
-        <v>9.3130314107987875e-06</v>
+        <v>9.078395632183029e-06</v>
       </c>
       <c r="AF2">
-        <v>-1.1801453572122004e-07</v>
+        <v>-1.1713617503157034e-07</v>
       </c>
       <c r="AG2">
-        <v>-7.8303737241919042e-05</v>
+        <v>-7.8348589206558112e-05</v>
       </c>
       <c r="AH2">
-        <v>-2.8586673719581114e-05</v>
+        <v>-2.871086252514396e-05</v>
       </c>
       <c r="AI2">
-        <v>0.00018030146354133222</v>
+        <v>0.00017048838167084109</v>
       </c>
     </row>
     <row r="3">
@@ -4552,106 +4552,106 @@
         <v>29</v>
       </c>
       <c r="B3">
-        <v>0.016935458362687471</v>
+        <v>0.016860101326262086</v>
       </c>
       <c r="C3">
-        <v>-1.1778298065185433e-06</v>
+        <v>-1.1595262593671678e-06</v>
       </c>
       <c r="D3">
-        <v>1.6416486361387738e-05</v>
+        <v>1.6420423126666384e-05</v>
       </c>
       <c r="E3">
-        <v>-1.4363105323651625e-07</v>
+        <v>-1.4365460726144509e-07</v>
       </c>
       <c r="F3">
-        <v>-1.112691849875408e-05</v>
+        <v>-1.1131506836735371e-05</v>
       </c>
       <c r="G3">
-        <v>-1.049610769144287e-05</v>
+        <v>-1.0449882433668442e-05</v>
       </c>
       <c r="H3">
-        <v>-1.2277270060586291e-05</v>
+        <v>-1.2208783486304137e-05</v>
       </c>
       <c r="I3">
-        <v>5.0313548365215613e-06</v>
+        <v>5.1034531149174217e-06</v>
       </c>
       <c r="J3">
-        <v>-4.5307554241174784e-06</v>
+        <v>-4.4936032629895562e-06</v>
       </c>
       <c r="K3">
-        <v>-3.0609639437874859e-06</v>
+        <v>-2.9196896116809199e-06</v>
       </c>
       <c r="L3">
-        <v>-6.4280215891314599e-07</v>
+        <v>-6.6962297367110984e-07</v>
       </c>
       <c r="M3">
-        <v>1.6638624846267825e-06</v>
+        <v>1.6047034429475957e-06</v>
       </c>
       <c r="N3">
-        <v>1.6105749166989508e-06</v>
+        <v>1.587768351397972e-06</v>
       </c>
       <c r="O3">
-        <v>4.7435608756717042e-06</v>
+        <v>4.7129042874799443e-06</v>
       </c>
       <c r="P3">
-        <v>-2.2758995772888545e-06</v>
+        <v>-2.2156869189074688e-06</v>
       </c>
       <c r="Q3">
-        <v>-2.4673197894813532e-05</v>
+        <v>-2.4718436714475417e-05</v>
       </c>
       <c r="R3">
-        <v>-3.6716647217242154e-05</v>
+        <v>-3.6741172482691127e-05</v>
       </c>
       <c r="S3">
-        <v>-2.7617825972556318e-05</v>
+        <v>-2.7618385373603016e-05</v>
       </c>
       <c r="T3">
-        <v>5.5278619335626046e-05</v>
+        <v>5.6327917884880805e-05</v>
       </c>
       <c r="U3">
-        <v>-2.9886890183150925e-05</v>
+        <v>-2.8715351058527014e-05</v>
       </c>
       <c r="V3">
-        <v>-4.4623759993101366e-06</v>
+        <v>-3.3873129909836963e-06</v>
       </c>
       <c r="W3">
-        <v>8.9429306130692885e-06</v>
+        <v>8.9916027705526815e-06</v>
       </c>
       <c r="X3">
-        <v>3.4881524734780984e-05</v>
+        <v>3.4925405800941836e-05</v>
       </c>
       <c r="Y3">
-        <v>1.0546391990252503e-05</v>
+        <v>1.0265266595365681e-05</v>
       </c>
       <c r="Z3">
-        <v>-3.5955745998582085e-07</v>
+        <v>-3.6890395435922214e-07</v>
       </c>
       <c r="AA3">
-        <v>2.7308923763493925e-06</v>
+        <v>2.7230093151540838e-06</v>
       </c>
       <c r="AB3">
-        <v>2.697070694620193e-06</v>
+        <v>2.6496366877957415e-06</v>
       </c>
       <c r="AC3">
-        <v>3.3111745535957895e-06</v>
+        <v>3.3060123068474884e-06</v>
       </c>
       <c r="AD3">
-        <v>2.7098451452058439e-06</v>
+        <v>2.7000313798056935e-06</v>
       </c>
       <c r="AE3">
-        <v>-3.7182472273433852e-06</v>
+        <v>-3.7432941115907417e-06</v>
       </c>
       <c r="AF3">
-        <v>-1.0517234437267577e-07</v>
+        <v>-1.1073115482207998e-07</v>
       </c>
       <c r="AG3">
-        <v>6.7792657439162902e-07</v>
+        <v>7.2371231071046956e-07</v>
       </c>
       <c r="AH3">
-        <v>-2.1025786509196349e-06</v>
+        <v>-2.0665980981459645e-06</v>
       </c>
       <c r="AI3">
-        <v>-0.00037727989086930693</v>
+        <v>-0.00037840922310119454</v>
       </c>
     </row>
     <row r="4">
@@ -4659,106 +4659,106 @@
         <v>30</v>
       </c>
       <c r="B4">
-        <v>-0.00013172557719345085</v>
+        <v>-0.00013073152915414545</v>
       </c>
       <c r="C4">
-        <v>3.3006838742514826e-08</v>
+        <v>3.2797749563823646e-08</v>
       </c>
       <c r="D4">
-        <v>-1.4363105323651625e-07</v>
+        <v>-1.4365460726144509e-07</v>
       </c>
       <c r="E4">
-        <v>1.329093588220942e-09</v>
+        <v>1.3292996372632669e-09</v>
       </c>
       <c r="F4">
-        <v>1.3257966234866214e-07</v>
+        <v>1.3253998648093149e-07</v>
       </c>
       <c r="G4">
-        <v>1.1876124015754986e-07</v>
+        <v>1.187290474665369e-07</v>
       </c>
       <c r="H4">
-        <v>1.6483488710737124e-07</v>
+        <v>1.6448313864879601e-07</v>
       </c>
       <c r="I4">
-        <v>3.1801700551144731e-08</v>
+        <v>3.1527165226505297e-08</v>
       </c>
       <c r="J4">
-        <v>3.9366403143661224e-08</v>
+        <v>3.932745064176556e-08</v>
       </c>
       <c r="K4">
-        <v>6.937684904624332e-09</v>
+        <v>5.446914133081583e-09</v>
       </c>
       <c r="L4">
-        <v>8.3378763345040892e-09</v>
+        <v>8.5263708724293891e-09</v>
       </c>
       <c r="M4">
-        <v>-2.1655739911599938e-08</v>
+        <v>-2.1576164477011495e-08</v>
       </c>
       <c r="N4">
-        <v>-3.5207519034754194e-08</v>
+        <v>-3.4959148584785588e-08</v>
       </c>
       <c r="O4">
-        <v>-3.8195828957995975e-08</v>
+        <v>-3.8211111394579369e-08</v>
       </c>
       <c r="P4">
-        <v>2.457048710279807e-08</v>
+        <v>2.4471266978375564e-08</v>
       </c>
       <c r="Q4">
-        <v>1.5643170299260902e-07</v>
+        <v>1.5717468542467302e-07</v>
       </c>
       <c r="R4">
-        <v>2.9063490963525747e-07</v>
+        <v>2.9121799219837417e-07</v>
       </c>
       <c r="S4">
-        <v>2.294840276284424e-07</v>
+        <v>2.2981023190497959e-07</v>
       </c>
       <c r="T4">
-        <v>-5.2139548909216559e-07</v>
+        <v>-5.3255137979159031e-07</v>
       </c>
       <c r="U4">
-        <v>1.0555085868033711e-07</v>
+        <v>9.3323005600879071e-08</v>
       </c>
       <c r="V4">
-        <v>-2.9672922183350712e-07</v>
+        <v>-3.0831760440807579e-07</v>
       </c>
       <c r="W4">
-        <v>-2.5885828971758204e-08</v>
+        <v>-2.5385119997845615e-08</v>
       </c>
       <c r="X4">
-        <v>-2.8117749342473678e-07</v>
+        <v>-2.8087293733730018e-07</v>
       </c>
       <c r="Y4">
-        <v>-1.9302764471890355e-08</v>
+        <v>-1.8130713169339472e-08</v>
       </c>
       <c r="Z4">
-        <v>-5.5699364489547746e-09</v>
+        <v>-5.5115163241112756e-09</v>
       </c>
       <c r="AA4">
-        <v>-4.0956090897983854e-08</v>
+        <v>-4.0942454040429362e-08</v>
       </c>
       <c r="AB4">
-        <v>-4.0279910068181208e-08</v>
+        <v>-3.9895281830393476e-08</v>
       </c>
       <c r="AC4">
-        <v>-4.6066599677972516e-08</v>
+        <v>-4.6005625474448603e-08</v>
       </c>
       <c r="AD4">
-        <v>-3.3901780022848824e-08</v>
+        <v>-3.3621964339694341e-08</v>
       </c>
       <c r="AE4">
-        <v>1.8326230847159117e-08</v>
+        <v>1.8196754478072829e-08</v>
       </c>
       <c r="AF4">
-        <v>-7.9769449682427677e-10</v>
+        <v>-7.6469376919826121e-10</v>
       </c>
       <c r="AG4">
-        <v>-2.0616752399827562e-08</v>
+        <v>-2.1061352079788054e-08</v>
       </c>
       <c r="AH4">
-        <v>9.7628222075587755e-09</v>
+        <v>9.6154898530007683e-09</v>
       </c>
       <c r="AI4">
-        <v>3.2579248682791623e-06</v>
+        <v>3.2688604033339336e-06</v>
       </c>
     </row>
     <row r="5">
@@ -4766,106 +4766,106 @@
         <v>32</v>
       </c>
       <c r="B5">
-        <v>0.035394831601462694</v>
+        <v>0.03569393055445818</v>
       </c>
       <c r="C5">
-        <v>2.3502177242822334e-05</v>
+        <v>2.3514888390001136e-05</v>
       </c>
       <c r="D5">
-        <v>-1.112691849875408e-05</v>
+        <v>-1.1131506836735371e-05</v>
       </c>
       <c r="E5">
-        <v>1.3257966234866214e-07</v>
+        <v>1.3253998648093149e-07</v>
       </c>
       <c r="F5">
-        <v>0.0043205698248378628</v>
+        <v>0.004318747431300919</v>
       </c>
       <c r="G5">
-        <v>0.003331974742639575</v>
+        <v>0.0033302585050640609</v>
       </c>
       <c r="H5">
-        <v>0.0033508516809490014</v>
+        <v>0.0033491861273780496</v>
       </c>
       <c r="I5">
-        <v>0.0033348456927829056</v>
+        <v>0.0033330570069508318</v>
       </c>
       <c r="J5">
-        <v>5.4545645044529537e-06</v>
+        <v>5.5261577523229785e-06</v>
       </c>
       <c r="K5">
-        <v>1.9796338654559292e-05</v>
+        <v>1.9946374018930971e-05</v>
       </c>
       <c r="L5">
-        <v>-5.7405188505130732e-06</v>
+        <v>-5.5644572274199299e-06</v>
       </c>
       <c r="M5">
-        <v>-6.8646367053233843e-05</v>
+        <v>-6.8724727429687058e-05</v>
       </c>
       <c r="N5">
-        <v>-2.2211741921381923e-05</v>
+        <v>-2.221052676966873e-05</v>
       </c>
       <c r="O5">
-        <v>-2.542835841340494e-06</v>
+        <v>-2.6264729022641535e-06</v>
       </c>
       <c r="P5">
-        <v>6.2499291838728137e-05</v>
+        <v>6.2568237371362192e-05</v>
       </c>
       <c r="Q5">
-        <v>3.4178594085720882e-05</v>
+        <v>3.4086789976513036e-05</v>
       </c>
       <c r="R5">
-        <v>9.2978855768374204e-05</v>
+        <v>9.2686772673516125e-05</v>
       </c>
       <c r="S5">
-        <v>7.2527720131985041e-05</v>
+        <v>7.234623004049234e-05</v>
       </c>
       <c r="T5">
-        <v>0.0001052124654547246</v>
+        <v>0.00010735315558156209</v>
       </c>
       <c r="U5">
-        <v>0.00013217582648960798</v>
+        <v>0.00013435923948253528</v>
       </c>
       <c r="V5">
-        <v>3.4050800023753395e-05</v>
+        <v>3.649228354062322e-05</v>
       </c>
       <c r="W5">
-        <v>2.3762492316839416e-06</v>
+        <v>1.396123948230936e-06</v>
       </c>
       <c r="X5">
-        <v>-1.119198441620786e-05</v>
+        <v>-1.148587195645874e-05</v>
       </c>
       <c r="Y5">
-        <v>5.7622309281317365e-05</v>
+        <v>5.9715548943519012e-05</v>
       </c>
       <c r="Z5">
-        <v>-5.5970222525287064e-05</v>
+        <v>-5.6077131279566074e-05</v>
       </c>
       <c r="AA5">
-        <v>-3.256235592747638e-05</v>
+        <v>-3.2613800962478764e-05</v>
       </c>
       <c r="AB5">
-        <v>-4.3692492921836609e-05</v>
+        <v>-4.3719027208413697e-05</v>
       </c>
       <c r="AC5">
-        <v>-9.425875026856283e-05</v>
+        <v>-9.434248749252863e-05</v>
       </c>
       <c r="AD5">
-        <v>1.0258616395554358e-05</v>
+        <v>1.0024030448895545e-05</v>
       </c>
       <c r="AE5">
-        <v>-5.2922973063558609e-06</v>
+        <v>-5.3170062463804915e-06</v>
       </c>
       <c r="AF5">
-        <v>-2.1242813873393685e-06</v>
+        <v>-2.1296604221588067e-06</v>
       </c>
       <c r="AG5">
-        <v>1.3254611324652228e-05</v>
+        <v>1.3101660560370029e-05</v>
       </c>
       <c r="AH5">
-        <v>-8.3220067583281154e-07</v>
+        <v>-1.1459651114999712e-06</v>
       </c>
       <c r="AI5">
-        <v>-0.0031909959915158394</v>
+        <v>-0.0031907660066190684</v>
       </c>
     </row>
     <row r="6">
@@ -4873,106 +4873,106 @@
         <v>33</v>
       </c>
       <c r="B6">
-        <v>0.075078818242933027</v>
+        <v>0.075534146507023808</v>
       </c>
       <c r="C6">
-        <v>-2.1957961697634844e-05</v>
+        <v>-2.1657825642411691e-05</v>
       </c>
       <c r="D6">
-        <v>-1.049610769144287e-05</v>
+        <v>-1.0449882433668442e-05</v>
       </c>
       <c r="E6">
-        <v>1.1876124015754986e-07</v>
+        <v>1.187290474665369e-07</v>
       </c>
       <c r="F6">
-        <v>0.003331974742639575</v>
+        <v>0.0033302585050640609</v>
       </c>
       <c r="G6">
-        <v>0.0036920244587947296</v>
+        <v>0.0036905918227806895</v>
       </c>
       <c r="H6">
-        <v>0.0034464926035572812</v>
+        <v>0.0034448815958518669</v>
       </c>
       <c r="I6">
-        <v>0.0034460096641565387</v>
+        <v>0.003444307874982767</v>
       </c>
       <c r="J6">
-        <v>-3.8075677654614542e-05</v>
+        <v>-3.7918598515992476e-05</v>
       </c>
       <c r="K6">
-        <v>1.6986230532526804e-05</v>
+        <v>1.6091835103031221e-05</v>
       </c>
       <c r="L6">
-        <v>-6.3799710366713535e-06</v>
+        <v>-6.328648311897491e-06</v>
       </c>
       <c r="M6">
-        <v>-2.4006494258163938e-05</v>
+        <v>-2.4333501048798886e-05</v>
       </c>
       <c r="N6">
-        <v>1.2710445295975419e-05</v>
+        <v>1.2426357628698525e-05</v>
       </c>
       <c r="O6">
-        <v>2.7578659373188319e-05</v>
+        <v>2.7402438157772373e-05</v>
       </c>
       <c r="P6">
-        <v>3.0300963965835246e-05</v>
+        <v>3.0600985372090765e-05</v>
       </c>
       <c r="Q6">
-        <v>0.00011240303205274291</v>
+        <v>0.00011215392557799037</v>
       </c>
       <c r="R6">
-        <v>0.00010714980149372465</v>
+        <v>0.00010674103557494451</v>
       </c>
       <c r="S6">
-        <v>0.00010556458696630135</v>
+        <v>0.00010523337934325834</v>
       </c>
       <c r="T6">
-        <v>7.074332874305346e-05</v>
+        <v>6.506798789906185e-05</v>
       </c>
       <c r="U6">
-        <v>0.0001212270011351161</v>
+        <v>0.00011380341857671148</v>
       </c>
       <c r="V6">
-        <v>7.4130549102363239e-05</v>
+        <v>6.7121795603022763e-05</v>
       </c>
       <c r="W6">
-        <v>2.933742301836893e-05</v>
+        <v>3.240480365034445e-05</v>
       </c>
       <c r="X6">
-        <v>3.5010963706506772e-05</v>
+        <v>3.6184796380715366e-05</v>
       </c>
       <c r="Y6">
-        <v>0.00011082359073710498</v>
+        <v>0.00011715946216607118</v>
       </c>
       <c r="Z6">
-        <v>-3.2237887984472476e-05</v>
+        <v>-3.2391368146266614e-05</v>
       </c>
       <c r="AA6">
-        <v>-3.3365374743733918e-05</v>
+        <v>-3.342869865768038e-05</v>
       </c>
       <c r="AB6">
-        <v>-3.4721204415569468e-05</v>
+        <v>-3.4709028774606351e-05</v>
       </c>
       <c r="AC6">
-        <v>-9.5267496664021333e-05</v>
+        <v>-9.5431062887091789e-05</v>
       </c>
       <c r="AD6">
-        <v>-3.6770110894328648e-07</v>
+        <v>-4.4670324184873517e-07</v>
       </c>
       <c r="AE6">
-        <v>1.7840588211187744e-06</v>
+        <v>1.5892475574857154e-06</v>
       </c>
       <c r="AF6">
-        <v>-4.9769320234327978e-06</v>
+        <v>-4.9904075742537298e-06</v>
       </c>
       <c r="AG6">
-        <v>2.3653988487843877e-05</v>
+        <v>2.3560435616849611e-05</v>
       </c>
       <c r="AH6">
-        <v>5.0810295743719102e-05</v>
+        <v>5.04504162779848e-05</v>
       </c>
       <c r="AI6">
-        <v>-0.003270466191866302</v>
+        <v>-0.003264930078864586</v>
       </c>
     </row>
     <row r="7">
@@ -4980,106 +4980,106 @@
         <v>34</v>
       </c>
       <c r="B7">
-        <v>0.09944830669733494</v>
+        <v>0.099579576065623399</v>
       </c>
       <c r="C7">
-        <v>-1.4483117365472833e-05</v>
+        <v>-1.4229050579139729e-05</v>
       </c>
       <c r="D7">
-        <v>-1.2277270060586291e-05</v>
+        <v>-1.2208783486304137e-05</v>
       </c>
       <c r="E7">
-        <v>1.6483488710737124e-07</v>
+        <v>1.6448313864879601e-07</v>
       </c>
       <c r="F7">
-        <v>0.0033508516809490014</v>
+        <v>0.0033491861273780496</v>
       </c>
       <c r="G7">
-        <v>0.0034464926035572812</v>
+        <v>0.0034448815958518669</v>
       </c>
       <c r="H7">
-        <v>0.0036653828547718171</v>
+        <v>0.0036636700724075187</v>
       </c>
       <c r="I7">
-        <v>0.0035791111171026052</v>
+        <v>0.0035773197663790421</v>
       </c>
       <c r="J7">
-        <v>-4.4592238851128528e-05</v>
+        <v>-4.4606874437227474e-05</v>
       </c>
       <c r="K7">
-        <v>1.3464568744444205e-05</v>
+        <v>1.3292267483377781e-05</v>
       </c>
       <c r="L7">
-        <v>-4.661062151143344e-06</v>
+        <v>-4.6114483418551445e-06</v>
       </c>
       <c r="M7">
-        <v>-5.4427010099697242e-06</v>
+        <v>-5.4849531344481478e-06</v>
       </c>
       <c r="N7">
-        <v>1.7016537144485373e-05</v>
+        <v>1.6768692062677903e-05</v>
       </c>
       <c r="O7">
-        <v>5.8140799589011683e-05</v>
+        <v>5.8139325118979502e-05</v>
       </c>
       <c r="P7">
-        <v>-6.9123038476550216e-06</v>
+        <v>-6.8756435468558244e-06</v>
       </c>
       <c r="Q7">
-        <v>0.00012205513947016397</v>
+        <v>0.00012172266110459327</v>
       </c>
       <c r="R7">
-        <v>9.5082755675074404e-05</v>
+        <v>9.4734495009401488e-05</v>
       </c>
       <c r="S7">
-        <v>7.4378963457746687e-05</v>
+        <v>7.388652170449081e-05</v>
       </c>
       <c r="T7">
-        <v>6.3200722583111636e-05</v>
+        <v>6.3292858309631217e-05</v>
       </c>
       <c r="U7">
-        <v>0.0001504576395539274</v>
+        <v>0.00014956025952320585</v>
       </c>
       <c r="V7">
-        <v>6.15511025975745e-05</v>
+        <v>6.0869248048411742e-05</v>
       </c>
       <c r="W7">
-        <v>1.1349132512395238e-05</v>
+        <v>1.4386862176733667e-05</v>
       </c>
       <c r="X7">
-        <v>2.826723158468286e-05</v>
+        <v>2.9644530535361414e-05</v>
       </c>
       <c r="Y7">
-        <v>0.00014103812543211003</v>
+        <v>0.00014344774122373918</v>
       </c>
       <c r="Z7">
-        <v>-7.1696895795612167e-05</v>
+        <v>-7.1874354112027878e-05</v>
       </c>
       <c r="AA7">
-        <v>-8.9513114637770463e-05</v>
+        <v>-8.9556933801142932e-05</v>
       </c>
       <c r="AB7">
-        <v>-9.6464399529598956e-05</v>
+        <v>-9.6477235923793717e-05</v>
       </c>
       <c r="AC7">
-        <v>-0.00014677624567278631</v>
+        <v>-0.00014693418837219137</v>
       </c>
       <c r="AD7">
-        <v>-5.7995603966465303e-05</v>
+        <v>-5.8249228400782897e-05</v>
       </c>
       <c r="AE7">
-        <v>-4.1755144483655708e-05</v>
+        <v>-4.207361399925628e-05</v>
       </c>
       <c r="AF7">
-        <v>-3.812822218944009e-06</v>
+        <v>-3.8069441577882174e-06</v>
       </c>
       <c r="AG7">
-        <v>-9.4182418717767002e-07</v>
+        <v>-1.3115123110637311e-06</v>
       </c>
       <c r="AH7">
-        <v>1.1790754280966483e-05</v>
+        <v>1.1186649182695282e-05</v>
       </c>
       <c r="AI7">
-        <v>-0.003381134787782597</v>
+        <v>-0.0033820336201729473</v>
       </c>
     </row>
     <row r="8">
@@ -5087,106 +5087,106 @@
         <v>63</v>
       </c>
       <c r="B8">
-        <v>0.10173563395839548</v>
+        <v>0.10191902942700919</v>
       </c>
       <c r="C8">
-        <v>-6.721971269187937e-05</v>
+        <v>-6.7355800366263385e-05</v>
       </c>
       <c r="D8">
-        <v>5.0313548365215613e-06</v>
+        <v>5.1034531149174217e-06</v>
       </c>
       <c r="E8">
-        <v>3.1801700551144731e-08</v>
+        <v>3.1527165226505297e-08</v>
       </c>
       <c r="F8">
-        <v>0.0033348456927829056</v>
+        <v>0.0033330570069508318</v>
       </c>
       <c r="G8">
-        <v>0.0034460096641565387</v>
+        <v>0.003444307874982767</v>
       </c>
       <c r="H8">
-        <v>0.0035791111171026052</v>
+        <v>0.0035773197663790421</v>
       </c>
       <c r="I8">
-        <v>0.0041393192982061922</v>
+        <v>0.0041372324445851458</v>
       </c>
       <c r="J8">
-        <v>-0.00015800051402928067</v>
+        <v>-0.00015795130210541613</v>
       </c>
       <c r="K8">
-        <v>6.5553985238626469e-06</v>
+        <v>5.6290379254348058e-06</v>
       </c>
       <c r="L8">
-        <v>-1.7084432362418025e-05</v>
+        <v>-1.7160491198794399e-05</v>
       </c>
       <c r="M8">
-        <v>8.2796029395649866e-05</v>
+        <v>8.2831097415042186e-05</v>
       </c>
       <c r="N8">
-        <v>6.0961084983034175e-05</v>
+        <v>6.1195803712241507e-05</v>
       </c>
       <c r="O8">
-        <v>0.00019340393619652913</v>
+        <v>0.00019333505088077983</v>
       </c>
       <c r="P8">
-        <v>-0.00010385536595319497</v>
+        <v>-0.00010390538640871693</v>
       </c>
       <c r="Q8">
-        <v>0.00022570642505646658</v>
+        <v>0.0002252244350126123</v>
       </c>
       <c r="R8">
-        <v>0.00022836685530649645</v>
+        <v>0.00022811049602714829</v>
       </c>
       <c r="S8">
-        <v>0.0001324128404685404</v>
+        <v>0.00013170444398262395</v>
       </c>
       <c r="T8">
-        <v>-0.00012814723418749568</v>
+        <v>-0.00013543921931975181</v>
       </c>
       <c r="U8">
-        <v>-5.159543964531753e-05</v>
+        <v>-6.0851686910935905e-05</v>
       </c>
       <c r="V8">
-        <v>-0.00011983592278242523</v>
+        <v>-0.00012846647571950452</v>
       </c>
       <c r="W8">
-        <v>-1.2675792881725387e-07</v>
+        <v>2.8852205235416919e-06</v>
       </c>
       <c r="X8">
-        <v>7.4293942289223444e-05</v>
+        <v>7.5507397100281742e-05</v>
       </c>
       <c r="Y8">
-        <v>0.00013772907671989266</v>
+        <v>0.00013852717240664609</v>
       </c>
       <c r="Z8">
-        <v>-5.7447948003091359e-06</v>
+        <v>-6.0315393916438552e-06</v>
       </c>
       <c r="AA8">
-        <v>-5.5462795353136696e-05</v>
+        <v>-5.561515106820218e-05</v>
       </c>
       <c r="AB8">
-        <v>-7.5872728060489116e-05</v>
+        <v>-7.6338942696981579e-05</v>
       </c>
       <c r="AC8">
-        <v>-9.1320964737238216e-05</v>
+        <v>-9.1646211952361393e-05</v>
       </c>
       <c r="AD8">
-        <v>4.7570217411091985e-05</v>
+        <v>4.7353825128320683e-05</v>
       </c>
       <c r="AE8">
-        <v>-1.0998181087716835e-05</v>
+        <v>-1.1162008556380321e-05</v>
       </c>
       <c r="AF8">
-        <v>-1.5225029826202927e-06</v>
+        <v>-1.5413697275998045e-06</v>
       </c>
       <c r="AG8">
-        <v>0.00017677745986703283</v>
+        <v>0.00017685683753167463</v>
       </c>
       <c r="AH8">
-        <v>6.4729527955960983e-05</v>
+        <v>6.4684847934265953e-05</v>
       </c>
       <c r="AI8">
-        <v>-0.0039087046616684516</v>
+        <v>-0.0039016022318896365</v>
       </c>
     </row>
     <row r="9">
@@ -5194,106 +5194,106 @@
         <v>64</v>
       </c>
       <c r="B9">
-        <v>1.5183111231000272</v>
+        <v>1.5180195216091639</v>
       </c>
       <c r="C9">
-        <v>4.1213408368018641e-05</v>
+        <v>4.159705099024866e-05</v>
       </c>
       <c r="D9">
-        <v>-4.5307554241174784e-06</v>
+        <v>-4.4936032629895562e-06</v>
       </c>
       <c r="E9">
-        <v>3.9366403143661224e-08</v>
+        <v>3.932745064176556e-08</v>
       </c>
       <c r="F9">
-        <v>5.4545645044529537e-06</v>
+        <v>5.5261577523229785e-06</v>
       </c>
       <c r="G9">
-        <v>-3.8075677654614542e-05</v>
+        <v>-3.7918598515992476e-05</v>
       </c>
       <c r="H9">
-        <v>-4.4592238851128528e-05</v>
+        <v>-4.4606874437227474e-05</v>
       </c>
       <c r="I9">
-        <v>-0.00015800051402928067</v>
+        <v>-0.00015795130210541613</v>
       </c>
       <c r="J9">
-        <v>0.00064210866217899898</v>
+        <v>0.00064178782738026142</v>
       </c>
       <c r="K9">
-        <v>-2.2350172380330125e-05</v>
+        <v>-2.3086048402090315e-05</v>
       </c>
       <c r="L9">
-        <v>7.4984738807742944e-06</v>
+        <v>7.3811694050690362e-06</v>
       </c>
       <c r="M9">
-        <v>-0.00045996963522548811</v>
+        <v>-0.00045982538474761628</v>
       </c>
       <c r="N9">
-        <v>-2.2946718541055334e-05</v>
+        <v>-2.3347955927411466e-05</v>
       </c>
       <c r="O9">
-        <v>-0.00063948629735780839</v>
+        <v>-0.00063916565257824678</v>
       </c>
       <c r="P9">
-        <v>0.00044001378139978126</v>
+        <v>0.00043986487685248341</v>
       </c>
       <c r="Q9">
-        <v>-0.00028142695421273859</v>
+        <v>-0.00028121560836039735</v>
       </c>
       <c r="R9">
-        <v>-0.00028114959275801315</v>
+        <v>-0.00028120091219737076</v>
       </c>
       <c r="S9">
-        <v>-0.00024195772820361438</v>
+        <v>-0.00024159070326182217</v>
       </c>
       <c r="T9">
-        <v>-5.427711514046656e-05</v>
+        <v>-5.9662954073992389e-05</v>
       </c>
       <c r="U9">
-        <v>-8.684763448134892e-05</v>
+        <v>-9.3223257890432193e-05</v>
       </c>
       <c r="V9">
-        <v>-0.00011456626608425207</v>
+        <v>-0.00012104402601295762</v>
       </c>
       <c r="W9">
-        <v>1.8842634774256128e-05</v>
+        <v>2.2253769112660799e-05</v>
       </c>
       <c r="X9">
-        <v>-6.1086821669755975e-05</v>
+        <v>-5.9665466520087527e-05</v>
       </c>
       <c r="Y9">
-        <v>-6.0210898848725486e-05</v>
+        <v>-5.816469041652558e-05</v>
       </c>
       <c r="Z9">
-        <v>8.5311790844845093e-06</v>
+        <v>8.5149803357657992e-06</v>
       </c>
       <c r="AA9">
-        <v>7.6920219427976225e-06</v>
+        <v>7.7232169495954248e-06</v>
       </c>
       <c r="AB9">
-        <v>-1.024119070579583e-05</v>
+        <v>-9.9065126713600744e-06</v>
       </c>
       <c r="AC9">
-        <v>9.4274848582951993e-06</v>
+        <v>9.5318444476418823e-06</v>
       </c>
       <c r="AD9">
-        <v>-7.4113146721242862e-05</v>
+        <v>-7.4128590388704578e-05</v>
       </c>
       <c r="AE9">
-        <v>-3.34843595512793e-06</v>
+        <v>-3.4362991330363968e-06</v>
       </c>
       <c r="AF9">
-        <v>-1.2766501460807108e-06</v>
+        <v>-1.2655894037201618e-06</v>
       </c>
       <c r="AG9">
-        <v>-0.00016867270152082627</v>
+        <v>-0.00016898574867744656</v>
       </c>
       <c r="AH9">
-        <v>-8.3141777482098215e-05</v>
+        <v>-8.3200465864430545e-05</v>
       </c>
       <c r="AI9">
-        <v>0.00037117144109132753</v>
+        <v>0.00037411143719150966</v>
       </c>
     </row>
     <row r="10">
@@ -5301,106 +5301,106 @@
         <v>36</v>
       </c>
       <c r="B10">
-        <v>0.019507095327876152</v>
+        <v>0.019864871028473223</v>
       </c>
       <c r="C10">
-        <v>-2.226764468905269e-05</v>
+        <v>-2.1122839431273256e-05</v>
       </c>
       <c r="D10">
-        <v>-3.0609639437874859e-06</v>
+        <v>-2.9196896116809199e-06</v>
       </c>
       <c r="E10">
-        <v>6.937684904624332e-09</v>
+        <v>5.446914133081583e-09</v>
       </c>
       <c r="F10">
-        <v>1.9796338654559292e-05</v>
+        <v>1.9946374018930971e-05</v>
       </c>
       <c r="G10">
-        <v>1.6986230532526804e-05</v>
+        <v>1.6091835103031221e-05</v>
       </c>
       <c r="H10">
-        <v>1.3464568744444205e-05</v>
+        <v>1.3292267483377781e-05</v>
       </c>
       <c r="I10">
-        <v>6.5553985238626469e-06</v>
+        <v>5.6290379254348058e-06</v>
       </c>
       <c r="J10">
-        <v>-2.2350172380330125e-05</v>
+        <v>-2.3086048402090315e-05</v>
       </c>
       <c r="K10">
-        <v>0.00032887685903156271</v>
+        <v>0.00033512445474611854</v>
       </c>
       <c r="L10">
-        <v>-2.4770403754243677e-05</v>
+        <v>-2.5254455305878726e-05</v>
       </c>
       <c r="M10">
-        <v>9.7229906533740165e-06</v>
+        <v>1.0395485362990614e-05</v>
       </c>
       <c r="N10">
-        <v>1.9103405061938144e-05</v>
+        <v>1.7986021986654278e-05</v>
       </c>
       <c r="O10">
-        <v>2.2991581508446522e-05</v>
+        <v>2.3619129366459282e-05</v>
       </c>
       <c r="P10">
-        <v>-8.8130101792035479e-06</v>
+        <v>-9.4033853972996361e-06</v>
       </c>
       <c r="Q10">
-        <v>0.00011345800635159751</v>
+        <v>0.00011245365347632881</v>
       </c>
       <c r="R10">
-        <v>8.5593527860833296e-05</v>
+        <v>8.4701074168258951e-05</v>
       </c>
       <c r="S10">
-        <v>1.4060996713626765e-05</v>
+        <v>1.2075251853831039e-05</v>
       </c>
       <c r="T10">
-        <v>0.0024487103081431687</v>
+        <v>0.0024972211811194393</v>
       </c>
       <c r="U10">
-        <v>0.0024932705477126752</v>
+        <v>0.0025423143104802422</v>
       </c>
       <c r="V10">
-        <v>0.0025184652257739613</v>
+        <v>0.002568404299279205</v>
       </c>
       <c r="W10">
-        <v>-2.956393193700654e-05</v>
+        <v>-2.8229001594775981e-05</v>
       </c>
       <c r="X10">
-        <v>1.522582992835868e-06</v>
+        <v>2.2909570554582198e-06</v>
       </c>
       <c r="Y10">
-        <v>4.4895728899750978e-05</v>
+        <v>4.6191887562013366e-05</v>
       </c>
       <c r="Z10">
-        <v>9.5288826796151305e-06</v>
+        <v>9.418187349832124e-06</v>
       </c>
       <c r="AA10">
-        <v>-1.9570131783865075e-05</v>
+        <v>-1.9276415664130865e-05</v>
       </c>
       <c r="AB10">
-        <v>-2.6616656722436446e-05</v>
+        <v>-2.7012175418189175e-05</v>
       </c>
       <c r="AC10">
-        <v>8.045076416849338e-06</v>
+        <v>7.8577577430050637e-06</v>
       </c>
       <c r="AD10">
-        <v>-1.6211091124791006e-05</v>
+        <v>-1.7723351807230679e-05</v>
       </c>
       <c r="AE10">
-        <v>1.2277340705570843e-05</v>
+        <v>1.1960281701943796e-05</v>
       </c>
       <c r="AF10">
-        <v>7.6871471711810675e-07</v>
+        <v>8.2590497641914012e-07</v>
       </c>
       <c r="AG10">
-        <v>1.6656694351073042e-05</v>
+        <v>1.6152553236027049e-05</v>
       </c>
       <c r="AH10">
-        <v>3.2264897530520989e-05</v>
+        <v>3.0176125816626896e-05</v>
       </c>
       <c r="AI10">
-        <v>-0.002408534962640044</v>
+        <v>-0.0024598768867113464</v>
       </c>
     </row>
     <row r="11">
@@ -5408,106 +5408,106 @@
         <v>37</v>
       </c>
       <c r="B11">
-        <v>0.0067365302942258513</v>
+        <v>0.0067999473075663905</v>
       </c>
       <c r="C11">
-        <v>-5.8287437428686758e-07</v>
+        <v>-7.1611176054830783e-07</v>
       </c>
       <c r="D11">
-        <v>-6.4280215891314599e-07</v>
+        <v>-6.6962297367110984e-07</v>
       </c>
       <c r="E11">
-        <v>8.3378763345040892e-09</v>
+        <v>8.5263708724293891e-09</v>
       </c>
       <c r="F11">
-        <v>-5.7405188505130732e-06</v>
+        <v>-5.5644572274199299e-06</v>
       </c>
       <c r="G11">
-        <v>-6.3799710366713535e-06</v>
+        <v>-6.328648311897491e-06</v>
       </c>
       <c r="H11">
-        <v>-4.661062151143344e-06</v>
+        <v>-4.6114483418551445e-06</v>
       </c>
       <c r="I11">
-        <v>-1.7084432362418025e-05</v>
+        <v>-1.7160491198794399e-05</v>
       </c>
       <c r="J11">
-        <v>7.4984738807742944e-06</v>
+        <v>7.3811694050690362e-06</v>
       </c>
       <c r="K11">
-        <v>-2.4770403754243677e-05</v>
+        <v>-2.5254455305878726e-05</v>
       </c>
       <c r="L11">
-        <v>2.175116941829289e-05</v>
+        <v>2.1754716653805837e-05</v>
       </c>
       <c r="M11">
-        <v>-4.2656021039700153e-06</v>
+        <v>-4.0715320172183104e-06</v>
       </c>
       <c r="N11">
-        <v>7.0522282635133661e-07</v>
+        <v>8.4221969913879455e-07</v>
       </c>
       <c r="O11">
-        <v>-8.5357450856608926e-06</v>
+        <v>-8.418638274399032e-06</v>
       </c>
       <c r="P11">
-        <v>4.8322519843575747e-06</v>
+        <v>4.6374156606388902e-06</v>
       </c>
       <c r="Q11">
-        <v>-9.1853752335519542e-06</v>
+        <v>-8.4233950044148215e-06</v>
       </c>
       <c r="R11">
-        <v>-2.5537299756361466e-05</v>
+        <v>-2.4807567488618741e-05</v>
       </c>
       <c r="S11">
-        <v>-1.2851763871653474e-05</v>
+        <v>-1.1985930145395562e-05</v>
       </c>
       <c r="T11">
-        <v>-4.5785419642202534e-05</v>
+        <v>-4.933522852928612e-05</v>
       </c>
       <c r="U11">
-        <v>-6.2587876562417014e-05</v>
+        <v>-6.637102713381732e-05</v>
       </c>
       <c r="V11">
-        <v>-5.4942421264625129e-05</v>
+        <v>-5.8997845047084071e-05</v>
       </c>
       <c r="W11">
-        <v>3.9323988728646681e-07</v>
+        <v>2.1549592304919692e-07</v>
       </c>
       <c r="X11">
-        <v>2.8840996153256368e-06</v>
+        <v>2.8208978696641841e-06</v>
       </c>
       <c r="Y11">
-        <v>9.6987525820311322e-06</v>
+        <v>8.6033118555267458e-06</v>
       </c>
       <c r="Z11">
-        <v>-6.0049578820980547e-06</v>
+        <v>-5.8983953549960456e-06</v>
       </c>
       <c r="AA11">
-        <v>-8.3258245848905986e-06</v>
+        <v>-8.370704189693698e-06</v>
       </c>
       <c r="AB11">
-        <v>-4.5104831088476339e-06</v>
+        <v>-4.4093195581566065e-06</v>
       </c>
       <c r="AC11">
-        <v>-7.3148628605913319e-06</v>
+        <v>-7.1575627419663402e-06</v>
       </c>
       <c r="AD11">
-        <v>-1.1032005505418663e-05</v>
+        <v>-1.0905681299324917e-05</v>
       </c>
       <c r="AE11">
-        <v>-5.3927727825969897e-06</v>
+        <v>-5.2561162497527967e-06</v>
       </c>
       <c r="AF11">
-        <v>-2.8400275670942545e-07</v>
+        <v>-2.708817252856624e-07</v>
       </c>
       <c r="AG11">
-        <v>-4.7572744028242836e-06</v>
+        <v>-5.157916866126524e-06</v>
       </c>
       <c r="AH11">
-        <v>-7.4010554880799231e-06</v>
+        <v>-7.1369518895646625e-06</v>
       </c>
       <c r="AI11">
-        <v>7.7037032292740965e-05</v>
+        <v>8.0841463138480685e-05</v>
       </c>
     </row>
     <row r="12">
@@ -5515,106 +5515,106 @@
         <v>65</v>
       </c>
       <c r="B12">
-        <v>0.65327016067453847</v>
+        <v>0.6531478238810513</v>
       </c>
       <c r="C12">
-        <v>-3.1723494920810533e-05</v>
+        <v>-3.2212234831237209e-05</v>
       </c>
       <c r="D12">
-        <v>1.6638624846267825e-06</v>
+        <v>1.6047034429475957e-06</v>
       </c>
       <c r="E12">
-        <v>-2.1655739911599938e-08</v>
+        <v>-2.1576164477011495e-08</v>
       </c>
       <c r="F12">
-        <v>-6.8646367053233843e-05</v>
+        <v>-6.8724727429687058e-05</v>
       </c>
       <c r="G12">
-        <v>-2.4006494258163938e-05</v>
+        <v>-2.4333501048798886e-05</v>
       </c>
       <c r="H12">
-        <v>-5.4427010099697242e-06</v>
+        <v>-5.4849531344481478e-06</v>
       </c>
       <c r="I12">
-        <v>8.2796029395649866e-05</v>
+        <v>8.2831097415042186e-05</v>
       </c>
       <c r="J12">
-        <v>-0.00045996963522548811</v>
+        <v>-0.00045982538474761628</v>
       </c>
       <c r="K12">
-        <v>9.7229906533740165e-06</v>
+        <v>1.0395485362990614e-05</v>
       </c>
       <c r="L12">
-        <v>-4.2656021039700153e-06</v>
+        <v>-4.0715320172183104e-06</v>
       </c>
       <c r="M12">
-        <v>0.00063890354726480261</v>
+        <v>0.00063883565286701439</v>
       </c>
       <c r="N12">
-        <v>8.9759368205663441e-06</v>
+        <v>9.4608499921825426e-06</v>
       </c>
       <c r="O12">
-        <v>0.00045450976423457522</v>
+        <v>0.00045438385070667529</v>
       </c>
       <c r="P12">
-        <v>-0.00061150762929524315</v>
+        <v>-0.00061142475532724656</v>
       </c>
       <c r="Q12">
-        <v>-0.00019879542569420361</v>
+        <v>-0.00019866227728903326</v>
       </c>
       <c r="R12">
-        <v>-0.00018439082620359744</v>
+        <v>-0.00018411001790500124</v>
       </c>
       <c r="S12">
-        <v>-0.0002258836783469497</v>
+        <v>-0.0002257750330859217</v>
       </c>
       <c r="T12">
-        <v>-4.0859574182594242e-05</v>
+        <v>-3.6088427002290925e-05</v>
       </c>
       <c r="U12">
-        <v>1.5597952882382601e-05</v>
+        <v>2.1954280476577358e-05</v>
       </c>
       <c r="V12">
-        <v>3.051233833794083e-05</v>
+        <v>3.6938012733061165e-05</v>
       </c>
       <c r="W12">
-        <v>-1.8682077194645524e-05</v>
+        <v>-2.3776958373916191e-05</v>
       </c>
       <c r="X12">
-        <v>3.8780828261938898e-05</v>
+        <v>3.6866996768808093e-05</v>
       </c>
       <c r="Y12">
-        <v>-0.00018981797359741528</v>
+        <v>-0.00019737655532720032</v>
       </c>
       <c r="Z12">
-        <v>-5.2738991774779885e-05</v>
+        <v>-5.2793343367700959e-05</v>
       </c>
       <c r="AA12">
-        <v>-8.1565824726875994e-05</v>
+        <v>-8.174737975831258e-05</v>
       </c>
       <c r="AB12">
-        <v>-7.4531000168357822e-05</v>
+        <v>-7.4798169395010197e-05</v>
       </c>
       <c r="AC12">
-        <v>-6.6399652958953561e-05</v>
+        <v>-6.6566042929599653e-05</v>
       </c>
       <c r="AD12">
-        <v>-5.2142528327796093e-05</v>
+        <v>-5.2188146467307259e-05</v>
       </c>
       <c r="AE12">
-        <v>-5.4684359378744815e-05</v>
+        <v>-5.4707719815161954e-05</v>
       </c>
       <c r="AF12">
-        <v>4.5341083384152171e-06</v>
+        <v>4.5140438765156904e-06</v>
       </c>
       <c r="AG12">
-        <v>7.9370531799451678e-05</v>
+        <v>7.9398350037771e-05</v>
       </c>
       <c r="AH12">
-        <v>5.013149121636935e-05</v>
+        <v>5.0290009126370559e-05</v>
       </c>
       <c r="AI12">
-        <v>-0.00010796927102515791</v>
+        <v>-0.00010912148249779828</v>
       </c>
     </row>
     <row r="13">
@@ -5622,106 +5622,106 @@
         <v>39</v>
       </c>
       <c r="B13">
-        <v>0.076266537637629681</v>
+        <v>0.075677520889658234</v>
       </c>
       <c r="C13">
-        <v>-0.00032721101553160996</v>
+        <v>-0.00032709392055204717</v>
       </c>
       <c r="D13">
-        <v>1.6105749166989508e-06</v>
+        <v>1.587768351397972e-06</v>
       </c>
       <c r="E13">
-        <v>-3.5207519034754194e-08</v>
+        <v>-3.4959148584785588e-08</v>
       </c>
       <c r="F13">
-        <v>-2.2211741921381923e-05</v>
+        <v>-2.221052676966873e-05</v>
       </c>
       <c r="G13">
-        <v>1.2710445295975419e-05</v>
+        <v>1.2426357628698525e-05</v>
       </c>
       <c r="H13">
-        <v>1.7016537144485373e-05</v>
+        <v>1.6768692062677903e-05</v>
       </c>
       <c r="I13">
-        <v>6.0961084983034175e-05</v>
+        <v>6.1195803712241507e-05</v>
       </c>
       <c r="J13">
-        <v>-2.2946718541055334e-05</v>
+        <v>-2.3347955927411466e-05</v>
       </c>
       <c r="K13">
-        <v>1.9103405061938144e-05</v>
+        <v>1.7986021986654278e-05</v>
       </c>
       <c r="L13">
-        <v>7.0522282635133661e-07</v>
+        <v>8.4221969913879455e-07</v>
       </c>
       <c r="M13">
-        <v>8.9759368205663441e-06</v>
+        <v>9.4608499921825426e-06</v>
       </c>
       <c r="N13">
-        <v>0.0074391994945310841</v>
+        <v>0.0074385457061766948</v>
       </c>
       <c r="O13">
-        <v>0.00012093042132118714</v>
+        <v>0.00012130999266770541</v>
       </c>
       <c r="P13">
-        <v>0.00057843243999440694</v>
+        <v>0.0005783430327398031</v>
       </c>
       <c r="Q13">
-        <v>0.0044503371439920062</v>
+        <v>0.0044497253950711198</v>
       </c>
       <c r="R13">
-        <v>0.0044446210162897761</v>
+        <v>0.0044441537076495424</v>
       </c>
       <c r="S13">
-        <v>0.0044155113288065658</v>
+        <v>0.0044151738506471444</v>
       </c>
       <c r="T13">
-        <v>0.0001269330852393532</v>
+        <v>0.00011822182869630467</v>
       </c>
       <c r="U13">
-        <v>4.2134927435865614e-05</v>
+        <v>3.3146942100654173e-05</v>
       </c>
       <c r="V13">
-        <v>0.00019110709000858057</v>
+        <v>0.00018222348271810547</v>
       </c>
       <c r="W13">
-        <v>-4.1771402812106916e-05</v>
+        <v>-4.2543583907250739e-05</v>
       </c>
       <c r="X13">
-        <v>1.1926379245470742e-07</v>
+        <v>-4.7090840577933713e-07</v>
       </c>
       <c r="Y13">
-        <v>-0.00012504007718881338</v>
+        <v>-0.00012331938187331941</v>
       </c>
       <c r="Z13">
-        <v>6.3903171694334451e-05</v>
+        <v>6.3892697498914601e-05</v>
       </c>
       <c r="AA13">
-        <v>0.00011456175015991151</v>
+        <v>0.00011439383984365313</v>
       </c>
       <c r="AB13">
-        <v>0.00013430757200705204</v>
+        <v>0.00013461317724291501</v>
       </c>
       <c r="AC13">
-        <v>9.8039917483482919e-05</v>
+        <v>9.7898026577931821e-05</v>
       </c>
       <c r="AD13">
-        <v>7.1475371197587522e-05</v>
+        <v>7.1443082540535198e-05</v>
       </c>
       <c r="AE13">
-        <v>0.00012324085976339047</v>
+        <v>0.00012350157466021208</v>
       </c>
       <c r="AF13">
-        <v>-1.6854814070528881e-06</v>
+        <v>-1.6835123396858036e-06</v>
       </c>
       <c r="AG13">
-        <v>6.7198161181713026e-05</v>
+        <v>6.7252230678467063e-05</v>
       </c>
       <c r="AH13">
-        <v>3.4162190225686239e-05</v>
+        <v>3.4368224754767647e-05</v>
       </c>
       <c r="AI13">
-        <v>-0.004452135442681469</v>
+        <v>-0.0044423224796542029</v>
       </c>
     </row>
     <row r="14">
@@ -5729,106 +5729,106 @@
         <v>66</v>
       </c>
       <c r="B14">
-        <v>-0.13691387330468932</v>
+        <v>-0.13662494003012624</v>
       </c>
       <c r="C14">
-        <v>-5.2190345536982111e-05</v>
+        <v>-5.2614115386368898e-05</v>
       </c>
       <c r="D14">
-        <v>4.7435608756717042e-06</v>
+        <v>4.7129042874799443e-06</v>
       </c>
       <c r="E14">
-        <v>-3.8195828957995975e-08</v>
+        <v>-3.8211111394579369e-08</v>
       </c>
       <c r="F14">
-        <v>-2.542835841340494e-06</v>
+        <v>-2.6264729022641535e-06</v>
       </c>
       <c r="G14">
-        <v>2.7578659373188319e-05</v>
+        <v>2.7402438157772373e-05</v>
       </c>
       <c r="H14">
-        <v>5.8140799589011683e-05</v>
+        <v>5.8139325118979502e-05</v>
       </c>
       <c r="I14">
-        <v>0.00019340393619652913</v>
+        <v>0.00019333505088077983</v>
       </c>
       <c r="J14">
-        <v>-0.00063948629735780839</v>
+        <v>-0.00063916565257824678</v>
       </c>
       <c r="K14">
-        <v>2.2991581508446522e-05</v>
+        <v>2.3619129366459282e-05</v>
       </c>
       <c r="L14">
-        <v>-8.5357450856608926e-06</v>
+        <v>-8.418638274399032e-06</v>
       </c>
       <c r="M14">
-        <v>0.00045450976423457522</v>
+        <v>0.00045438385070667529</v>
       </c>
       <c r="N14">
-        <v>0.00012093042132118714</v>
+        <v>0.00012130999266770541</v>
       </c>
       <c r="O14">
-        <v>0.010574454106923811</v>
+        <v>0.01057464469854366</v>
       </c>
       <c r="P14">
-        <v>-0.0074843242081282972</v>
+        <v>-0.0074848957076368372</v>
       </c>
       <c r="Q14">
-        <v>0.003772712901295393</v>
+        <v>0.0037722655307442371</v>
       </c>
       <c r="R14">
-        <v>0.0037718232656827151</v>
+        <v>0.0037716578152304607</v>
       </c>
       <c r="S14">
-        <v>0.0037332183932664458</v>
+        <v>0.0037326038703194338</v>
       </c>
       <c r="T14">
-        <v>6.3569120295488822e-05</v>
+        <v>6.799584020791556e-05</v>
       </c>
       <c r="U14">
-        <v>7.7539521417399929e-05</v>
+        <v>8.2907278544705921e-05</v>
       </c>
       <c r="V14">
-        <v>0.00010938102572210823</v>
+        <v>0.00011489318579543873</v>
       </c>
       <c r="W14">
-        <v>-2.182191783004425e-05</v>
+        <v>-2.5224057276764082e-05</v>
       </c>
       <c r="X14">
-        <v>6.1591036288373402e-05</v>
+        <v>6.0222017016385771e-05</v>
       </c>
       <c r="Y14">
-        <v>6.0157633434816129e-05</v>
+        <v>5.7313670718088842e-05</v>
       </c>
       <c r="Z14">
-        <v>-0.00011543975939217192</v>
+        <v>-0.00011547568708166747</v>
       </c>
       <c r="AA14">
-        <v>-9.5444848122407241e-05</v>
+        <v>-9.553782629575147e-05</v>
       </c>
       <c r="AB14">
-        <v>-9.9987714929009334e-05</v>
+        <v>-0.00010038128288236559</v>
       </c>
       <c r="AC14">
-        <v>-0.00012832431907419813</v>
+        <v>-0.00012848653550902875</v>
       </c>
       <c r="AD14">
-        <v>-4.7235486771416541e-05</v>
+        <v>-4.7242070389820132e-05</v>
       </c>
       <c r="AE14">
-        <v>-9.5000747710684023e-05</v>
+        <v>-9.497152143127203e-05</v>
       </c>
       <c r="AF14">
-        <v>-2.9715070134869425e-06</v>
+        <v>-2.9833865790864454e-06</v>
       </c>
       <c r="AG14">
-        <v>0.0001750698952145773</v>
+        <v>0.00017536319512749359</v>
       </c>
       <c r="AH14">
-        <v>0.00022189868718456023</v>
+        <v>0.00022196014127580637</v>
       </c>
       <c r="AI14">
-        <v>-0.0037005242288102864</v>
+        <v>-0.0037023871339994029</v>
       </c>
     </row>
     <row r="15">
@@ -5836,106 +5836,106 @@
         <v>67</v>
       </c>
       <c r="B15">
-        <v>0.042525396567240963</v>
+        <v>0.042579154919832565</v>
       </c>
       <c r="C15">
-        <v>3.3053013638421755e-05</v>
+        <v>3.3549356567971337e-05</v>
       </c>
       <c r="D15">
-        <v>-2.2758995772888545e-06</v>
+        <v>-2.2156869189074688e-06</v>
       </c>
       <c r="E15">
-        <v>2.457048710279807e-08</v>
+        <v>2.4471266978375564e-08</v>
       </c>
       <c r="F15">
-        <v>6.2499291838728137e-05</v>
+        <v>6.2568237371362192e-05</v>
       </c>
       <c r="G15">
-        <v>3.0300963965835246e-05</v>
+        <v>3.0600985372090765e-05</v>
       </c>
       <c r="H15">
-        <v>-6.9123038476550216e-06</v>
+        <v>-6.8756435468558244e-06</v>
       </c>
       <c r="I15">
-        <v>-0.00010385536595319497</v>
+        <v>-0.00010390538640871693</v>
       </c>
       <c r="J15">
-        <v>0.00044001378139978126</v>
+        <v>0.00043986487685248341</v>
       </c>
       <c r="K15">
-        <v>-8.8130101792035479e-06</v>
+        <v>-9.4033853972996361e-06</v>
       </c>
       <c r="L15">
-        <v>4.8322519843575747e-06</v>
+        <v>4.6374156606388902e-06</v>
       </c>
       <c r="M15">
-        <v>-0.00061150762929524315</v>
+        <v>-0.00061142475532724656</v>
       </c>
       <c r="N15">
-        <v>0.00057843243999440694</v>
+        <v>0.0005783430327398031</v>
       </c>
       <c r="O15">
-        <v>-0.0074843242081282972</v>
+        <v>-0.0074848957076368372</v>
       </c>
       <c r="P15">
-        <v>0.0096880455925068675</v>
+        <v>0.009688435520830695</v>
       </c>
       <c r="Q15">
-        <v>0.0034901810177060716</v>
+        <v>0.0034900312782587726</v>
       </c>
       <c r="R15">
-        <v>0.0034801524514338385</v>
+        <v>0.0034798574403264483</v>
       </c>
       <c r="S15">
-        <v>0.0035208298416822166</v>
+        <v>0.0035207377562913172</v>
       </c>
       <c r="T15">
-        <v>-2.4394633965528793e-05</v>
+        <v>-2.8474912227118834e-05</v>
       </c>
       <c r="U15">
-        <v>-4.4100356099130694e-06</v>
+        <v>-1.0017500246774203e-05</v>
       </c>
       <c r="V15">
-        <v>-1.8891590283882259e-05</v>
+        <v>-2.4610251780634695e-05</v>
       </c>
       <c r="W15">
-        <v>1.8707009413747772e-05</v>
+        <v>2.3697218473121755e-05</v>
       </c>
       <c r="X15">
-        <v>-3.9132342708521708e-05</v>
+        <v>-3.7255878129687707e-05</v>
       </c>
       <c r="Y15">
-        <v>0.00015936702076296003</v>
+        <v>0.00016661892369636234</v>
       </c>
       <c r="Z15">
-        <v>8.6421126252416661e-05</v>
+        <v>8.6525314375642546e-05</v>
       </c>
       <c r="AA15">
-        <v>0.00010814157455045134</v>
+        <v>0.00010835578757822277</v>
       </c>
       <c r="AB15">
-        <v>8.854105528242098e-05</v>
+        <v>8.8851153156342948e-05</v>
       </c>
       <c r="AC15">
-        <v>0.00010920062210723416</v>
+        <v>0.00010941218739209991</v>
       </c>
       <c r="AD15">
-        <v>6.8460209244772773e-05</v>
+        <v>6.8524030885496129e-05</v>
       </c>
       <c r="AE15">
-        <v>5.8168987783405678e-05</v>
+        <v>5.8228554816225743e-05</v>
       </c>
       <c r="AF15">
-        <v>-4.8550016487323321e-06</v>
+        <v>-4.835728867982459e-06</v>
       </c>
       <c r="AG15">
-        <v>-4.5373912749079905e-05</v>
+        <v>-4.5397950292241571e-05</v>
       </c>
       <c r="AH15">
-        <v>-0.00015097457733100018</v>
+        <v>-0.00015119055836303815</v>
       </c>
       <c r="AI15">
-        <v>-0.0031854452860888309</v>
+        <v>-0.0031849625751416287</v>
       </c>
     </row>
     <row r="16">
@@ -5943,106 +5943,106 @@
         <v>43</v>
       </c>
       <c r="B16">
-        <v>-0.27907468457175877</v>
+        <v>-0.27858390856768867</v>
       </c>
       <c r="C16">
-        <v>-0.0002335383041085244</v>
+        <v>-0.00023316230487734562</v>
       </c>
       <c r="D16">
-        <v>-2.4673197894813532e-05</v>
+        <v>-2.4718436714475417e-05</v>
       </c>
       <c r="E16">
-        <v>1.5643170299260902e-07</v>
+        <v>1.5717468542467302e-07</v>
       </c>
       <c r="F16">
-        <v>3.4178594085720882e-05</v>
+        <v>3.4086789976513036e-05</v>
       </c>
       <c r="G16">
-        <v>0.00011240303205274291</v>
+        <v>0.00011215392557799037</v>
       </c>
       <c r="H16">
-        <v>0.00012205513947016397</v>
+        <v>0.00012172266110459327</v>
       </c>
       <c r="I16">
-        <v>0.00022570642505646658</v>
+        <v>0.0002252244350126123</v>
       </c>
       <c r="J16">
-        <v>-0.00028142695421273859</v>
+        <v>-0.00028121560836039735</v>
       </c>
       <c r="K16">
-        <v>0.00011345800635159751</v>
+        <v>0.00011245365347632881</v>
       </c>
       <c r="L16">
-        <v>-9.1853752335519542e-06</v>
+        <v>-8.4233950044148215e-06</v>
       </c>
       <c r="M16">
-        <v>-0.00019879542569420361</v>
+        <v>-0.00019866227728903326</v>
       </c>
       <c r="N16">
-        <v>0.0044503371439920062</v>
+        <v>0.0044497253950711198</v>
       </c>
       <c r="O16">
-        <v>0.003772712901295393</v>
+        <v>0.0037722655307442371</v>
       </c>
       <c r="P16">
-        <v>0.0034901810177060716</v>
+        <v>0.0034900312782587726</v>
       </c>
       <c r="Q16">
-        <v>0.016758042712536586</v>
+        <v>0.016755690848965166</v>
       </c>
       <c r="R16">
-        <v>0.016323141568697592</v>
+        <v>0.016320488162909159</v>
       </c>
       <c r="S16">
-        <v>0.016302657286524705</v>
+        <v>0.016299966950468654</v>
       </c>
       <c r="T16">
-        <v>0.0036031776442228642</v>
+        <v>0.003600202638976196</v>
       </c>
       <c r="U16">
-        <v>0.00067996828917176746</v>
+        <v>0.00067584595036841548</v>
       </c>
       <c r="V16">
-        <v>0.0008445104196873538</v>
+        <v>0.00084114758004532491</v>
       </c>
       <c r="W16">
-        <v>-4.6238094873402381e-05</v>
+        <v>-4.4052120864641406e-05</v>
       </c>
       <c r="X16">
-        <v>2.9497718223016941e-05</v>
+        <v>2.9757273650001578e-05</v>
       </c>
       <c r="Y16">
-        <v>0.00021911050133918177</v>
+        <v>0.00023147393001431062</v>
       </c>
       <c r="Z16">
-        <v>-1.4042573154109811e-05</v>
+        <v>-1.4248406050923479e-05</v>
       </c>
       <c r="AA16">
-        <v>4.6668522205139517e-05</v>
+        <v>4.6359194890806775e-05</v>
       </c>
       <c r="AB16">
-        <v>9.9448226390481693e-05</v>
+        <v>9.9282122083284253e-05</v>
       </c>
       <c r="AC16">
-        <v>-3.4255856849454633e-05</v>
+        <v>-3.4653852526901445e-05</v>
       </c>
       <c r="AD16">
-        <v>6.6467335825516442e-05</v>
+        <v>6.5856619127423362e-05</v>
       </c>
       <c r="AE16">
-        <v>-5.7145689075200311e-07</v>
+        <v>-4.8637700066664173e-07</v>
       </c>
       <c r="AF16">
-        <v>-4.2520489844773894e-06</v>
+        <v>-4.2407887498384193e-06</v>
       </c>
       <c r="AG16">
-        <v>0.00031607126843852251</v>
+        <v>0.00031659723868952827</v>
       </c>
       <c r="AH16">
-        <v>0.00019648143661476526</v>
+        <v>0.00019594872205736056</v>
       </c>
       <c r="AI16">
-        <v>-0.015830166702359098</v>
+        <v>-0.015825749025517082</v>
       </c>
     </row>
     <row r="17">
@@ -6050,106 +6050,106 @@
         <v>44</v>
       </c>
       <c r="B17">
-        <v>-0.21399226506175684</v>
+        <v>-0.21378754484854434</v>
       </c>
       <c r="C17">
-        <v>-0.0002303058251058735</v>
+        <v>-0.00023008438428831932</v>
       </c>
       <c r="D17">
-        <v>-3.6716647217242154e-05</v>
+        <v>-3.6741172482691127e-05</v>
       </c>
       <c r="E17">
-        <v>2.9063490963525747e-07</v>
+        <v>2.9121799219837417e-07</v>
       </c>
       <c r="F17">
-        <v>9.2978855768374204e-05</v>
+        <v>9.2686772673516125e-05</v>
       </c>
       <c r="G17">
-        <v>0.00010714980149372465</v>
+        <v>0.00010674103557494451</v>
       </c>
       <c r="H17">
-        <v>9.5082755675074404e-05</v>
+        <v>9.4734495009401488e-05</v>
       </c>
       <c r="I17">
-        <v>0.00022836685530649645</v>
+        <v>0.00022811049602714829</v>
       </c>
       <c r="J17">
-        <v>-0.00028114959275801315</v>
+        <v>-0.00028120091219737076</v>
       </c>
       <c r="K17">
-        <v>8.5593527860833296e-05</v>
+        <v>8.4701074168258951e-05</v>
       </c>
       <c r="L17">
-        <v>-2.5537299756361466e-05</v>
+        <v>-2.4807567488618741e-05</v>
       </c>
       <c r="M17">
-        <v>-0.00018439082620359744</v>
+        <v>-0.00018411001790500124</v>
       </c>
       <c r="N17">
-        <v>0.0044446210162897761</v>
+        <v>0.0044441537076495424</v>
       </c>
       <c r="O17">
-        <v>0.0037718232656827151</v>
+        <v>0.0037716578152304607</v>
       </c>
       <c r="P17">
-        <v>0.0034801524514338385</v>
+        <v>0.0034798574403264483</v>
       </c>
       <c r="Q17">
-        <v>0.016323141568697592</v>
+        <v>0.016320488162909159</v>
       </c>
       <c r="R17">
-        <v>0.016585533691270422</v>
+        <v>0.016582958235566887</v>
       </c>
       <c r="S17">
-        <v>0.016168166483734661</v>
+        <v>0.016165211278795173</v>
       </c>
       <c r="T17">
-        <v>0.0031028692919028824</v>
+        <v>0.0030999572069719526</v>
       </c>
       <c r="U17">
-        <v>0.00040633665604698299</v>
+        <v>0.00040240943404083913</v>
       </c>
       <c r="V17">
-        <v>0.00052868522768988624</v>
+        <v>0.0005256087312728345</v>
       </c>
       <c r="W17">
-        <v>-6.2072318204642253e-05</v>
+        <v>-6.0744806840123128e-05</v>
       </c>
       <c r="X17">
-        <v>-5.0913165239407747e-06</v>
+        <v>-5.1193897151529874e-06</v>
       </c>
       <c r="Y17">
-        <v>8.2035876236467332e-05</v>
+        <v>9.3570909470648382e-05</v>
       </c>
       <c r="Z17">
-        <v>9.9292650511473638e-06</v>
+        <v>9.9286993257364023e-06</v>
       </c>
       <c r="AA17">
-        <v>6.579859296115256e-05</v>
+        <v>6.572844696292211e-05</v>
       </c>
       <c r="AB17">
-        <v>7.9745894430414922e-05</v>
+        <v>7.9839508586744285e-05</v>
       </c>
       <c r="AC17">
-        <v>1.0732254452152333e-05</v>
+        <v>1.0444425434076934e-05</v>
       </c>
       <c r="AD17">
-        <v>8.7401855542785893e-05</v>
+        <v>8.7148450729574757e-05</v>
       </c>
       <c r="AE17">
-        <v>3.5825910529381022e-05</v>
+        <v>3.6249155061806844e-05</v>
       </c>
       <c r="AF17">
-        <v>-8.6593109527509067e-06</v>
+        <v>-8.6701134686602592e-06</v>
       </c>
       <c r="AG17">
-        <v>0.00028715676090059969</v>
+        <v>0.0002879989900816636</v>
       </c>
       <c r="AH17">
-        <v>0.00018711060073023714</v>
+        <v>0.0001867011565983975</v>
       </c>
       <c r="AI17">
-        <v>-0.015025821244958616</v>
+        <v>-0.01502158810750011</v>
       </c>
     </row>
     <row r="18">
@@ -6157,106 +6157,106 @@
         <v>45</v>
       </c>
       <c r="B18">
-        <v>-0.12513703312581384</v>
+        <v>-0.1249114686515805</v>
       </c>
       <c r="C18">
-        <v>-0.00019378965804275452</v>
+        <v>-0.00019367918701796553</v>
       </c>
       <c r="D18">
-        <v>-2.7617825972556318e-05</v>
+        <v>-2.7618385373603016e-05</v>
       </c>
       <c r="E18">
-        <v>2.294840276284424e-07</v>
+        <v>2.2981023190497959e-07</v>
       </c>
       <c r="F18">
-        <v>7.2527720131985041e-05</v>
+        <v>7.234623004049234e-05</v>
       </c>
       <c r="G18">
-        <v>0.00010556458696630135</v>
+        <v>0.00010523337934325834</v>
       </c>
       <c r="H18">
-        <v>7.4378963457746687e-05</v>
+        <v>7.388652170449081e-05</v>
       </c>
       <c r="I18">
-        <v>0.0001324128404685404</v>
+        <v>0.00013170444398262395</v>
       </c>
       <c r="J18">
-        <v>-0.00024195772820361438</v>
+        <v>-0.00024159070326182217</v>
       </c>
       <c r="K18">
-        <v>1.4060996713626765e-05</v>
+        <v>1.2075251853831039e-05</v>
       </c>
       <c r="L18">
-        <v>-1.2851763871653474e-05</v>
+        <v>-1.1985930145395562e-05</v>
       </c>
       <c r="M18">
-        <v>-0.0002258836783469497</v>
+        <v>-0.0002257750330859217</v>
       </c>
       <c r="N18">
-        <v>0.0044155113288065658</v>
+        <v>0.0044151738506471444</v>
       </c>
       <c r="O18">
-        <v>0.0037332183932664458</v>
+        <v>0.0037326038703194338</v>
       </c>
       <c r="P18">
-        <v>0.0035208298416822166</v>
+        <v>0.0035207377562913172</v>
       </c>
       <c r="Q18">
-        <v>0.016302657286524705</v>
+        <v>0.016299966950468654</v>
       </c>
       <c r="R18">
-        <v>0.016168166483734661</v>
+        <v>0.016165211278795173</v>
       </c>
       <c r="S18">
-        <v>0.016411463768413431</v>
+        <v>0.016408465661292653</v>
       </c>
       <c r="T18">
-        <v>0.002830381218431534</v>
+        <v>0.0028197971898799128</v>
       </c>
       <c r="U18">
-        <v>-1.3807853405045645e-05</v>
+        <v>-2.5275215848472726e-05</v>
       </c>
       <c r="V18">
-        <v>4.3320037314492762e-05</v>
+        <v>3.2504609520023686e-05</v>
       </c>
       <c r="W18">
-        <v>-6.9648624537904256e-05</v>
+        <v>-6.731041884144413e-05</v>
       </c>
       <c r="X18">
-        <v>-2.2127136224194943e-05</v>
+        <v>-2.1592972747274189e-05</v>
       </c>
       <c r="Y18">
-        <v>0.0002056334237344401</v>
+        <v>0.00021078688298528658</v>
       </c>
       <c r="Z18">
-        <v>-1.6775914302801127e-05</v>
+        <v>-1.6892185388245676e-05</v>
       </c>
       <c r="AA18">
-        <v>4.3098241443089141e-05</v>
+        <v>4.3026856138298538e-05</v>
       </c>
       <c r="AB18">
-        <v>7.1132001372349076e-05</v>
+        <v>7.0954999775664626e-05</v>
       </c>
       <c r="AC18">
-        <v>-6.5461614596439011e-06</v>
+        <v>-6.8574665755454303e-06</v>
       </c>
       <c r="AD18">
-        <v>5.932915766124116e-05</v>
+        <v>5.9035760047622746e-05</v>
       </c>
       <c r="AE18">
-        <v>1.7578409182146797e-05</v>
+        <v>1.7587982876780405e-05</v>
       </c>
       <c r="AF18">
-        <v>-1.1463604557539225e-05</v>
+        <v>-1.1447210369927276e-05</v>
       </c>
       <c r="AG18">
-        <v>0.00020059819423439221</v>
+        <v>0.0002006316169769623</v>
       </c>
       <c r="AH18">
-        <v>0.00014551465158310021</v>
+        <v>0.00014512875049894208</v>
       </c>
       <c r="AI18">
-        <v>-0.014774351112696028</v>
+        <v>-0.014763368816508946</v>
       </c>
     </row>
     <row r="19">
@@ -6264,106 +6264,106 @@
         <v>46</v>
       </c>
       <c r="B19">
-        <v>0.30175223928742079</v>
+        <v>0.30689102994222972</v>
       </c>
       <c r="C19">
-        <v>-0.00011173905231292986</v>
+        <v>-0.0001027422881938953</v>
       </c>
       <c r="D19">
-        <v>5.5278619335626046e-05</v>
+        <v>5.6327917884880805e-05</v>
       </c>
       <c r="E19">
-        <v>-5.2139548909216559e-07</v>
+        <v>-5.3255137979159031e-07</v>
       </c>
       <c r="F19">
-        <v>0.0001052124654547246</v>
+        <v>0.00010735315558156209</v>
       </c>
       <c r="G19">
-        <v>7.074332874305346e-05</v>
+        <v>6.506798789906185e-05</v>
       </c>
       <c r="H19">
-        <v>6.3200722583111636e-05</v>
+        <v>6.3292858309631217e-05</v>
       </c>
       <c r="I19">
-        <v>-0.00012814723418749568</v>
+        <v>-0.00013543921931975181</v>
       </c>
       <c r="J19">
-        <v>-5.427711514046656e-05</v>
+        <v>-5.9662954073992389e-05</v>
       </c>
       <c r="K19">
-        <v>0.0024487103081431687</v>
+        <v>0.0024972211811194393</v>
       </c>
       <c r="L19">
-        <v>-4.5785419642202534e-05</v>
+        <v>-4.933522852928612e-05</v>
       </c>
       <c r="M19">
-        <v>-4.0859574182594242e-05</v>
+        <v>-3.6088427002290925e-05</v>
       </c>
       <c r="N19">
-        <v>0.0001269330852393532</v>
+        <v>0.00011822182869630467</v>
       </c>
       <c r="O19">
-        <v>6.3569120295488822e-05</v>
+        <v>6.799584020791556e-05</v>
       </c>
       <c r="P19">
-        <v>-2.4394633965528793e-05</v>
+        <v>-2.8474912227118834e-05</v>
       </c>
       <c r="Q19">
-        <v>0.0036031776442228642</v>
+        <v>0.003600202638976196</v>
       </c>
       <c r="R19">
-        <v>0.0031028692919028824</v>
+        <v>0.0030999572069719526</v>
       </c>
       <c r="S19">
-        <v>0.002830381218431534</v>
+        <v>0.0028197971898799128</v>
       </c>
       <c r="T19">
-        <v>0.023335704424347504</v>
+        <v>0.023718959018883545</v>
       </c>
       <c r="U19">
-        <v>0.019628108190124963</v>
+        <v>0.020014447954107284</v>
       </c>
       <c r="V19">
-        <v>0.019757722921737629</v>
+        <v>0.020148993634667056</v>
       </c>
       <c r="W19">
-        <v>2.1100730272364903e-05</v>
+        <v>3.4522939287826981e-05</v>
       </c>
       <c r="X19">
-        <v>1.2912768528288224e-05</v>
+        <v>2.190562178820514e-05</v>
       </c>
       <c r="Y19">
-        <v>0.00072054389331477169</v>
+        <v>0.0007232136229608525</v>
       </c>
       <c r="Z19">
-        <v>-1.7703820299388301e-06</v>
+        <v>-2.1245397239001707e-06</v>
       </c>
       <c r="AA19">
-        <v>-0.0002391107342234371</v>
+        <v>-0.00023697175779435059</v>
       </c>
       <c r="AB19">
-        <v>-0.00023331829453876549</v>
+        <v>-0.00023627816261422669</v>
       </c>
       <c r="AC19">
-        <v>-4.9629513844086891e-05</v>
+        <v>-4.9982022240475585e-05</v>
       </c>
       <c r="AD19">
-        <v>-0.00028632919040400863</v>
+        <v>-0.00029799213440012858</v>
       </c>
       <c r="AE19">
-        <v>-6.6982911648969141e-05</v>
+        <v>-6.9971695066448243e-05</v>
       </c>
       <c r="AF19">
-        <v>-2.9561829437222678e-07</v>
+        <v>2.1528153876205439e-07</v>
       </c>
       <c r="AG19">
-        <v>-4.8286190883990721e-05</v>
+        <v>-5.5994886211566119e-05</v>
       </c>
       <c r="AH19">
-        <v>0.00016431300235473373</v>
+        <v>0.00014858609909701621</v>
       </c>
       <c r="AI19">
-        <v>-0.024007797661731684</v>
+        <v>-0.024416804220154135</v>
       </c>
     </row>
     <row r="20">
@@ -6371,106 +6371,106 @@
         <v>47</v>
       </c>
       <c r="B20">
-        <v>0.25746884824837424</v>
+        <v>0.26153167700082769</v>
       </c>
       <c r="C20">
-        <v>-6.1625668049730789e-05</v>
+        <v>-5.2265305761841304e-05</v>
       </c>
       <c r="D20">
-        <v>-2.9886890183150925e-05</v>
+        <v>-2.8715351058527014e-05</v>
       </c>
       <c r="E20">
-        <v>1.0555085868033711e-07</v>
+        <v>9.3323005600879071e-08</v>
       </c>
       <c r="F20">
-        <v>0.00013217582648960798</v>
+        <v>0.00013435923948253528</v>
       </c>
       <c r="G20">
-        <v>0.0001212270011351161</v>
+        <v>0.00011380341857671148</v>
       </c>
       <c r="H20">
-        <v>0.0001504576395539274</v>
+        <v>0.00014956025952320585</v>
       </c>
       <c r="I20">
-        <v>-5.159543964531753e-05</v>
+        <v>-6.0851686910935905e-05</v>
       </c>
       <c r="J20">
-        <v>-8.684763448134892e-05</v>
+        <v>-9.3223257890432193e-05</v>
       </c>
       <c r="K20">
-        <v>0.0024932705477126752</v>
+        <v>0.0025423143104802422</v>
       </c>
       <c r="L20">
-        <v>-6.2587876562417014e-05</v>
+        <v>-6.637102713381732e-05</v>
       </c>
       <c r="M20">
-        <v>1.5597952882382601e-05</v>
+        <v>2.1954280476577358e-05</v>
       </c>
       <c r="N20">
-        <v>4.2134927435865614e-05</v>
+        <v>3.3146942100654173e-05</v>
       </c>
       <c r="O20">
-        <v>7.7539521417399929e-05</v>
+        <v>8.2907278544705921e-05</v>
       </c>
       <c r="P20">
-        <v>-4.4100356099130694e-06</v>
+        <v>-1.0017500246774203e-05</v>
       </c>
       <c r="Q20">
-        <v>0.00067996828917176746</v>
+        <v>0.00067584595036841548</v>
       </c>
       <c r="R20">
-        <v>0.00040633665604698299</v>
+        <v>0.00040240943404083913</v>
       </c>
       <c r="S20">
-        <v>-1.3807853405045645e-05</v>
+        <v>-2.5275215848472726e-05</v>
       </c>
       <c r="T20">
-        <v>0.019628108190124963</v>
+        <v>0.020014447954107284</v>
       </c>
       <c r="U20">
-        <v>0.020330161876498044</v>
+        <v>0.020715823942641615</v>
       </c>
       <c r="V20">
-        <v>0.020263020209561857</v>
+        <v>0.020655427483198725</v>
       </c>
       <c r="W20">
-        <v>-0.00013911405428177116</v>
+        <v>-0.00012790703301523485</v>
       </c>
       <c r="X20">
-        <v>2.0679287143843435e-05</v>
+        <v>2.8191657824618455e-05</v>
       </c>
       <c r="Y20">
-        <v>0.00051600613871761233</v>
+        <v>0.00051999392204682676</v>
       </c>
       <c r="Z20">
-        <v>6.6596775726588363e-05</v>
+        <v>6.6557231107324325e-05</v>
       </c>
       <c r="AA20">
-        <v>-0.0001612216177934913</v>
+        <v>-0.00015827837842209442</v>
       </c>
       <c r="AB20">
-        <v>-0.000213103502907863</v>
+        <v>-0.00021599875091771149</v>
       </c>
       <c r="AC20">
-        <v>5.6877917379005542e-05</v>
+        <v>5.6598753435136047e-05</v>
       </c>
       <c r="AD20">
-        <v>-0.00019822358007756495</v>
+        <v>-0.00021078048529140064</v>
       </c>
       <c r="AE20">
-        <v>6.8994809937670707e-05</v>
+        <v>6.7585007183653626e-05</v>
       </c>
       <c r="AF20">
-        <v>6.434105305371939e-06</v>
+        <v>6.9688415398830176e-06</v>
       </c>
       <c r="AG20">
-        <v>3.5529327898728424e-05</v>
+        <v>2.6878304278842719e-05</v>
       </c>
       <c r="AH20">
-        <v>0.00016931722591211236</v>
+        <v>0.00015217774312469186</v>
       </c>
       <c r="AI20">
-        <v>-0.019144972698791899</v>
+        <v>-0.019556821768951863</v>
       </c>
     </row>
     <row r="21">
@@ -6478,106 +6478,106 @@
         <v>48</v>
       </c>
       <c r="B21">
-        <v>0.31264245698831505</v>
+        <v>0.31668596663367216</v>
       </c>
       <c r="C21">
-        <v>-0.00021239483960761732</v>
+        <v>-0.00020319985945792786</v>
       </c>
       <c r="D21">
-        <v>-4.4623759993101366e-06</v>
+        <v>-3.3873129909836963e-06</v>
       </c>
       <c r="E21">
-        <v>-2.9672922183350712e-07</v>
+        <v>-3.0831760440807579e-07</v>
       </c>
       <c r="F21">
-        <v>3.4050800023753395e-05</v>
+        <v>3.649228354062322e-05</v>
       </c>
       <c r="G21">
-        <v>7.4130549102363239e-05</v>
+        <v>6.7121795603022763e-05</v>
       </c>
       <c r="H21">
-        <v>6.15511025975745e-05</v>
+        <v>6.0869248048411742e-05</v>
       </c>
       <c r="I21">
-        <v>-0.00011983592278242523</v>
+        <v>-0.00012846647571950452</v>
       </c>
       <c r="J21">
-        <v>-0.00011456626608425207</v>
+        <v>-0.00012104402601295762</v>
       </c>
       <c r="K21">
-        <v>0.0025184652257739613</v>
+        <v>0.002568404299279205</v>
       </c>
       <c r="L21">
-        <v>-5.4942421264625129e-05</v>
+        <v>-5.8997845047084071e-05</v>
       </c>
       <c r="M21">
-        <v>3.051233833794083e-05</v>
+        <v>3.6938012733061165e-05</v>
       </c>
       <c r="N21">
-        <v>0.00019110709000858057</v>
+        <v>0.00018222348271810547</v>
       </c>
       <c r="O21">
-        <v>0.00010938102572210823</v>
+        <v>0.00011489318579543873</v>
       </c>
       <c r="P21">
-        <v>-1.8891590283882259e-05</v>
+        <v>-2.4610251780634695e-05</v>
       </c>
       <c r="Q21">
-        <v>0.0008445104196873538</v>
+        <v>0.00084114758004532491</v>
       </c>
       <c r="R21">
-        <v>0.00052868522768988624</v>
+        <v>0.0005256087312728345</v>
       </c>
       <c r="S21">
-        <v>4.3320037314492762e-05</v>
+        <v>3.2504609520023686e-05</v>
       </c>
       <c r="T21">
-        <v>0.019757722921737629</v>
+        <v>0.020148993634667056</v>
       </c>
       <c r="U21">
-        <v>0.020263020209561857</v>
+        <v>0.020655427483198725</v>
       </c>
       <c r="V21">
-        <v>0.021314650250681227</v>
+        <v>0.021712917151899276</v>
       </c>
       <c r="W21">
-        <v>-0.00017066564095262157</v>
+        <v>-0.00015955138939490609</v>
       </c>
       <c r="X21">
-        <v>1.6094479887793483e-05</v>
+        <v>2.2910447972973938e-05</v>
       </c>
       <c r="Y21">
-        <v>0.00048255718139797454</v>
+        <v>0.00049063200750470645</v>
       </c>
       <c r="Z21">
-        <v>3.234588801504304e-05</v>
+        <v>3.2379196705672499e-05</v>
       </c>
       <c r="AA21">
-        <v>-0.00019776480947328486</v>
+        <v>-0.00019517041910760771</v>
       </c>
       <c r="AB21">
-        <v>-0.000228015592020864</v>
+        <v>-0.0002307304293205051</v>
       </c>
       <c r="AC21">
-        <v>5.064178824815916e-05</v>
+        <v>5.0429980654251652e-05</v>
       </c>
       <c r="AD21">
-        <v>-0.00022346204295744382</v>
+        <v>-0.00023556963315815062</v>
       </c>
       <c r="AE21">
-        <v>6.0863052053493219e-05</v>
+        <v>5.9506652066179883e-05</v>
       </c>
       <c r="AF21">
-        <v>6.5462480586167397e-06</v>
+        <v>7.0868702618841553e-06</v>
       </c>
       <c r="AG21">
-        <v>0.00010284722603032259</v>
+        <v>9.5301536831786382e-05</v>
       </c>
       <c r="AH21">
-        <v>0.00021353528251407371</v>
+        <v>0.00019727308075736388</v>
       </c>
       <c r="AI21">
-        <v>-0.019555278136735209</v>
+        <v>-0.019970339422381342</v>
       </c>
     </row>
     <row r="22">
@@ -6585,106 +6585,106 @@
         <v>49</v>
       </c>
       <c r="B22">
-        <v>0.0054815085061861984</v>
+        <v>0.0094792007980459142</v>
       </c>
       <c r="C22">
-        <v>3.9564821483017843e-05</v>
+        <v>4.0345429562238022e-05</v>
       </c>
       <c r="D22">
-        <v>8.9429306130692885e-06</v>
+        <v>8.9916027705526815e-06</v>
       </c>
       <c r="E22">
-        <v>-2.5885828971758204e-08</v>
+        <v>-2.5385119997845615e-08</v>
       </c>
       <c r="F22">
-        <v>2.3762492316839416e-06</v>
+        <v>1.396123948230936e-06</v>
       </c>
       <c r="G22">
-        <v>2.933742301836893e-05</v>
+        <v>3.240480365034445e-05</v>
       </c>
       <c r="H22">
-        <v>1.1349132512395238e-05</v>
+        <v>1.4386862176733667e-05</v>
       </c>
       <c r="I22">
-        <v>-1.2675792881725387e-07</v>
+        <v>2.8852205235416919e-06</v>
       </c>
       <c r="J22">
-        <v>1.8842634774256128e-05</v>
+        <v>2.2253769112660799e-05</v>
       </c>
       <c r="K22">
-        <v>-2.956393193700654e-05</v>
+        <v>-2.8229001594775981e-05</v>
       </c>
       <c r="L22">
-        <v>3.9323988728646681e-07</v>
+        <v>2.1549592304919692e-07</v>
       </c>
       <c r="M22">
-        <v>-1.8682077194645524e-05</v>
+        <v>-2.3776958373916191e-05</v>
       </c>
       <c r="N22">
-        <v>-4.1771402812106916e-05</v>
+        <v>-4.2543583907250739e-05</v>
       </c>
       <c r="O22">
-        <v>-2.182191783004425e-05</v>
+        <v>-2.5224057276764082e-05</v>
       </c>
       <c r="P22">
-        <v>1.8707009413747772e-05</v>
+        <v>2.3697218473121755e-05</v>
       </c>
       <c r="Q22">
-        <v>-4.6238094873402381e-05</v>
+        <v>-4.4052120864641406e-05</v>
       </c>
       <c r="R22">
-        <v>-6.2072318204642253e-05</v>
+        <v>-6.0744806840123128e-05</v>
       </c>
       <c r="S22">
-        <v>-6.9648624537904256e-05</v>
+        <v>-6.731041884144413e-05</v>
       </c>
       <c r="T22">
-        <v>2.1100730272364903e-05</v>
+        <v>3.4522939287826981e-05</v>
       </c>
       <c r="U22">
-        <v>-0.00013911405428177116</v>
+        <v>-0.00012790703301523485</v>
       </c>
       <c r="V22">
-        <v>-0.00017066564095262157</v>
+        <v>-0.00015955138939490609</v>
       </c>
       <c r="W22">
-        <v>0.00063084839585771145</v>
+        <v>0.00063219260239416608</v>
       </c>
       <c r="X22">
-        <v>0.00020733605832726429</v>
+        <v>0.00021111983175499925</v>
       </c>
       <c r="Y22">
-        <v>0.00031608076664480216</v>
+        <v>0.00032374727392850693</v>
       </c>
       <c r="Z22">
-        <v>-3.0080707959581621e-07</v>
+        <v>-2.8259794567796529e-07</v>
       </c>
       <c r="AA22">
-        <v>-1.2805140901900563e-05</v>
+        <v>-1.2850461832927804e-05</v>
       </c>
       <c r="AB22">
-        <v>1.2864131794275286e-06</v>
+        <v>8.9035697779476348e-07</v>
       </c>
       <c r="AC22">
-        <v>-6.3322716246603925e-06</v>
+        <v>-6.1956261635208589e-06</v>
       </c>
       <c r="AD22">
-        <v>7.5633144020334964e-06</v>
+        <v>7.9580214339586058e-06</v>
       </c>
       <c r="AE22">
-        <v>-4.9954516738316636e-05</v>
+        <v>-5.1787848250889523e-05</v>
       </c>
       <c r="AF22">
-        <v>2.6429877657229862e-07</v>
+        <v>-1.6556312024076805e-08</v>
       </c>
       <c r="AG22">
-        <v>3.383842085780478e-05</v>
+        <v>3.3973305414521386e-05</v>
       </c>
       <c r="AH22">
-        <v>-1.1683104600936545e-05</v>
+        <v>-1.182606046036495e-05</v>
       </c>
       <c r="AI22">
-        <v>-0.00041100116851545585</v>
+        <v>-0.00042718926414069328</v>
       </c>
     </row>
     <row r="23">
@@ -6692,106 +6692,106 @@
         <v>50</v>
       </c>
       <c r="B23">
-        <v>0.075606241716321951</v>
+        <v>0.076294703820031354</v>
       </c>
       <c r="C23">
-        <v>-8.9443228905280233e-07</v>
+        <v>-3.6891271348568258e-07</v>
       </c>
       <c r="D23">
-        <v>3.4881524734780984e-05</v>
+        <v>3.4925405800941836e-05</v>
       </c>
       <c r="E23">
-        <v>-2.8117749342473678e-07</v>
+        <v>-2.8087293733730018e-07</v>
       </c>
       <c r="F23">
-        <v>-1.119198441620786e-05</v>
+        <v>-1.148587195645874e-05</v>
       </c>
       <c r="G23">
-        <v>3.5010963706506772e-05</v>
+        <v>3.6184796380715366e-05</v>
       </c>
       <c r="H23">
-        <v>2.826723158468286e-05</v>
+        <v>2.9644530535361414e-05</v>
       </c>
       <c r="I23">
-        <v>7.4293942289223444e-05</v>
+        <v>7.5507397100281742e-05</v>
       </c>
       <c r="J23">
-        <v>-6.1086821669755975e-05</v>
+        <v>-5.9665466520087527e-05</v>
       </c>
       <c r="K23">
-        <v>1.522582992835868e-06</v>
+        <v>2.2909570554582198e-06</v>
       </c>
       <c r="L23">
-        <v>2.8840996153256368e-06</v>
+        <v>2.8208978696641841e-06</v>
       </c>
       <c r="M23">
-        <v>3.8780828261938898e-05</v>
+        <v>3.6866996768808093e-05</v>
       </c>
       <c r="N23">
-        <v>1.1926379245470742e-07</v>
+        <v>-4.7090840577933713e-07</v>
       </c>
       <c r="O23">
-        <v>6.1591036288373402e-05</v>
+        <v>6.0222017016385771e-05</v>
       </c>
       <c r="P23">
-        <v>-3.9132342708521708e-05</v>
+        <v>-3.7255878129687707e-05</v>
       </c>
       <c r="Q23">
-        <v>2.9497718223016941e-05</v>
+        <v>2.9757273650001578e-05</v>
       </c>
       <c r="R23">
-        <v>-5.0913165239407747e-06</v>
+        <v>-5.1193897151529874e-06</v>
       </c>
       <c r="S23">
-        <v>-2.2127136224194943e-05</v>
+        <v>-2.1592972747274189e-05</v>
       </c>
       <c r="T23">
-        <v>1.2912768528288224e-05</v>
+        <v>2.190562178820514e-05</v>
       </c>
       <c r="U23">
-        <v>2.0679287143843435e-05</v>
+        <v>2.8191657824618455e-05</v>
       </c>
       <c r="V23">
-        <v>1.6094479887793483e-05</v>
+        <v>2.2910447972973938e-05</v>
       </c>
       <c r="W23">
-        <v>0.00020733605832726429</v>
+        <v>0.00021111983175499925</v>
       </c>
       <c r="X23">
-        <v>0.00053786741536874085</v>
+        <v>0.00053996478025711053</v>
       </c>
       <c r="Y23">
-        <v>0.00022308529666843194</v>
+        <v>0.00022623288523965224</v>
       </c>
       <c r="Z23">
-        <v>9.9461068469423614e-06</v>
+        <v>1.0090656048973535e-05</v>
       </c>
       <c r="AA23">
-        <v>1.5265079848251746e-05</v>
+        <v>1.5038794390850993e-05</v>
       </c>
       <c r="AB23">
-        <v>2.4269044024923377e-05</v>
+        <v>2.395369186708842e-05</v>
       </c>
       <c r="AC23">
-        <v>1.8885996400031121e-05</v>
+        <v>1.8834833522594766e-05</v>
       </c>
       <c r="AD23">
-        <v>5.9731947545477453e-05</v>
+        <v>5.9793821400408779e-05</v>
       </c>
       <c r="AE23">
-        <v>1.2268955093169197e-05</v>
+        <v>1.1611884530182302e-05</v>
       </c>
       <c r="AF23">
-        <v>-1.2264595303643813e-07</v>
+        <v>-2.6925762539104889e-07</v>
       </c>
       <c r="AG23">
-        <v>0.00011583449999951964</v>
+        <v>0.00011623267111935905</v>
       </c>
       <c r="AH23">
-        <v>1.5224501182161082e-05</v>
+        <v>1.5389163367935809e-05</v>
       </c>
       <c r="AI23">
-        <v>-0.0012675766661341425</v>
+        <v>-0.0012783098564462269</v>
       </c>
     </row>
     <row r="24">
@@ -6799,106 +6799,106 @@
         <v>51</v>
       </c>
       <c r="B24">
-        <v>0.58030121769813392</v>
+        <v>0.60155594803663481</v>
       </c>
       <c r="C24">
-        <v>0.00013778405085550639</v>
+        <v>0.00013694080783844886</v>
       </c>
       <c r="D24">
-        <v>1.0546391990252503e-05</v>
+        <v>1.0265266595365681e-05</v>
       </c>
       <c r="E24">
-        <v>-1.9302764471890355e-08</v>
+        <v>-1.8130713169339472e-08</v>
       </c>
       <c r="F24">
-        <v>5.7622309281317365e-05</v>
+        <v>5.9715548943519012e-05</v>
       </c>
       <c r="G24">
-        <v>0.00011082359073710498</v>
+        <v>0.00011715946216607118</v>
       </c>
       <c r="H24">
-        <v>0.00014103812543211003</v>
+        <v>0.00014344774122373918</v>
       </c>
       <c r="I24">
-        <v>0.00013772907671989266</v>
+        <v>0.00013852717240664609</v>
       </c>
       <c r="J24">
-        <v>-6.0210898848725486e-05</v>
+        <v>-5.816469041652558e-05</v>
       </c>
       <c r="K24">
-        <v>4.4895728899750978e-05</v>
+        <v>4.6191887562013366e-05</v>
       </c>
       <c r="L24">
-        <v>9.6987525820311322e-06</v>
+        <v>8.6033118555267458e-06</v>
       </c>
       <c r="M24">
-        <v>-0.00018981797359741528</v>
+        <v>-0.00019737655532720032</v>
       </c>
       <c r="N24">
-        <v>-0.00012504007718881338</v>
+        <v>-0.00012331938187331941</v>
       </c>
       <c r="O24">
-        <v>6.0157633434816129e-05</v>
+        <v>5.7313670718088842e-05</v>
       </c>
       <c r="P24">
-        <v>0.00015936702076296003</v>
+        <v>0.00016661892369636234</v>
       </c>
       <c r="Q24">
-        <v>0.00021911050133918177</v>
+        <v>0.00023147393001431062</v>
       </c>
       <c r="R24">
-        <v>8.2035876236467332e-05</v>
+        <v>9.3570909470648382e-05</v>
       </c>
       <c r="S24">
-        <v>0.0002056334237344401</v>
+        <v>0.00021078688298528658</v>
       </c>
       <c r="T24">
-        <v>0.00072054389331477169</v>
+        <v>0.0007232136229608525</v>
       </c>
       <c r="U24">
-        <v>0.00051600613871761233</v>
+        <v>0.00051999392204682676</v>
       </c>
       <c r="V24">
-        <v>0.00048255718139797454</v>
+        <v>0.00049063200750470645</v>
       </c>
       <c r="W24">
-        <v>0.00031608076664480216</v>
+        <v>0.00032374727392850693</v>
       </c>
       <c r="X24">
-        <v>0.00022308529666843194</v>
+        <v>0.00022623288523965224</v>
       </c>
       <c r="Y24">
-        <v>0.0049127713774817644</v>
+        <v>0.0049391707950833235</v>
       </c>
       <c r="Z24">
-        <v>4.544531451682553e-05</v>
+        <v>4.1001920201236318e-05</v>
       </c>
       <c r="AA24">
-        <v>6.0082731177777028e-05</v>
+        <v>5.8546293138214242e-05</v>
       </c>
       <c r="AB24">
-        <v>9.2823550993128756e-05</v>
+        <v>8.9294459759380824e-05</v>
       </c>
       <c r="AC24">
-        <v>3.3394181581054242e-05</v>
+        <v>3.0241719546356469e-05</v>
       </c>
       <c r="AD24">
-        <v>9.2201178753770717e-05</v>
+        <v>9.1352888362737433e-05</v>
       </c>
       <c r="AE24">
-        <v>-2.3088192576370845e-05</v>
+        <v>-3.5884440126575035e-05</v>
       </c>
       <c r="AF24">
-        <v>-9.1016462402966812e-06</v>
+        <v>-8.8393577961908054e-06</v>
       </c>
       <c r="AG24">
-        <v>7.3739496584565752e-05</v>
+        <v>6.0175165015133813e-05</v>
       </c>
       <c r="AH24">
-        <v>1.185222418444978e-05</v>
+        <v>1.0711515924385082e-05</v>
       </c>
       <c r="AI24">
-        <v>-0.0011978237530955954</v>
+        <v>-0.0011984065111760687</v>
       </c>
     </row>
     <row r="25">
@@ -6906,106 +6906,106 @@
         <v>52</v>
       </c>
       <c r="B25">
-        <v>-0.17691015112612518</v>
+        <v>-0.17667000773885255</v>
       </c>
       <c r="C25">
-        <v>5.7221913230602833e-06</v>
+        <v>5.7425833494780031e-06</v>
       </c>
       <c r="D25">
-        <v>-3.5955745998582085e-07</v>
+        <v>-3.6890395435922214e-07</v>
       </c>
       <c r="E25">
-        <v>-5.5699364489547746e-09</v>
+        <v>-5.5115163241112756e-09</v>
       </c>
       <c r="F25">
-        <v>-5.5970222525287064e-05</v>
+        <v>-5.6077131279566074e-05</v>
       </c>
       <c r="G25">
-        <v>-3.2237887984472476e-05</v>
+        <v>-3.2391368146266614e-05</v>
       </c>
       <c r="H25">
-        <v>-7.1696895795612167e-05</v>
+        <v>-7.1874354112027878e-05</v>
       </c>
       <c r="I25">
-        <v>-5.7447948003091359e-06</v>
+        <v>-6.0315393916438552e-06</v>
       </c>
       <c r="J25">
-        <v>8.5311790844845093e-06</v>
+        <v>8.5149803357657992e-06</v>
       </c>
       <c r="K25">
-        <v>9.5288826796151305e-06</v>
+        <v>9.418187349832124e-06</v>
       </c>
       <c r="L25">
-        <v>-6.0049578820980547e-06</v>
+        <v>-5.8983953549960456e-06</v>
       </c>
       <c r="M25">
-        <v>-5.2738991774779885e-05</v>
+        <v>-5.2793343367700959e-05</v>
       </c>
       <c r="N25">
-        <v>6.3903171694334451e-05</v>
+        <v>6.3892697498914601e-05</v>
       </c>
       <c r="O25">
-        <v>-0.00011543975939217192</v>
+        <v>-0.00011547568708166747</v>
       </c>
       <c r="P25">
-        <v>8.6421126252416661e-05</v>
+        <v>8.6525314375642546e-05</v>
       </c>
       <c r="Q25">
-        <v>-1.4042573154109811e-05</v>
+        <v>-1.4248406050923479e-05</v>
       </c>
       <c r="R25">
-        <v>9.9292650511473638e-06</v>
+        <v>9.9286993257364023e-06</v>
       </c>
       <c r="S25">
-        <v>-1.6775914302801127e-05</v>
+        <v>-1.6892185388245676e-05</v>
       </c>
       <c r="T25">
-        <v>-1.7703820299388301e-06</v>
+        <v>-2.1245397239001707e-06</v>
       </c>
       <c r="U25">
-        <v>6.6596775726588363e-05</v>
+        <v>6.6557231107324325e-05</v>
       </c>
       <c r="V25">
-        <v>3.234588801504304e-05</v>
+        <v>3.2379196705672499e-05</v>
       </c>
       <c r="W25">
-        <v>-3.0080707959581621e-07</v>
+        <v>-2.8259794567796529e-07</v>
       </c>
       <c r="X25">
-        <v>9.9461068469423614e-06</v>
+        <v>1.0090656048973535e-05</v>
       </c>
       <c r="Y25">
-        <v>4.544531451682553e-05</v>
+        <v>4.1001920201236318e-05</v>
       </c>
       <c r="Z25">
-        <v>0.0027353329559316282</v>
+        <v>0.0027368841041138471</v>
       </c>
       <c r="AA25">
-        <v>0.0024019470371932561</v>
+        <v>0.002403550398369916</v>
       </c>
       <c r="AB25">
-        <v>0.0024003706698320004</v>
+        <v>0.0024018384466925175</v>
       </c>
       <c r="AC25">
-        <v>0.0024053124015353117</v>
+        <v>0.0024068293784165707</v>
       </c>
       <c r="AD25">
-        <v>0.0024130635737536028</v>
+        <v>0.0024144940450831001</v>
       </c>
       <c r="AE25">
-        <v>0.0023943327021205148</v>
+        <v>0.0023958525996362438</v>
       </c>
       <c r="AF25">
-        <v>6.8855059488431573e-06</v>
+        <v>6.8893600317669401e-06</v>
       </c>
       <c r="AG25">
-        <v>3.9008417406748153e-05</v>
+        <v>3.8664036657134679e-05</v>
       </c>
       <c r="AH25">
-        <v>6.6071984716610348e-06</v>
+        <v>6.6604240827844267e-06</v>
       </c>
       <c r="AI25">
-        <v>-0.0024091914813475467</v>
+        <v>-0.0024100460320740777</v>
       </c>
     </row>
     <row r="26">
@@ -7013,106 +7013,106 @@
         <v>53</v>
       </c>
       <c r="B26">
-        <v>-0.041780170364350111</v>
+        <v>-0.041384073498688286</v>
       </c>
       <c r="C26">
-        <v>1.0577578694776009e-05</v>
+        <v>1.0743021050413368e-05</v>
       </c>
       <c r="D26">
-        <v>2.7308923763493925e-06</v>
+        <v>2.7230093151540838e-06</v>
       </c>
       <c r="E26">
-        <v>-4.0956090897983854e-08</v>
+        <v>-4.0942454040429362e-08</v>
       </c>
       <c r="F26">
-        <v>-3.256235592747638e-05</v>
+        <v>-3.2613800962478764e-05</v>
       </c>
       <c r="G26">
-        <v>-3.3365374743733918e-05</v>
+        <v>-3.342869865768038e-05</v>
       </c>
       <c r="H26">
-        <v>-8.9513114637770463e-05</v>
+        <v>-8.9556933801142932e-05</v>
       </c>
       <c r="I26">
-        <v>-5.5462795353136696e-05</v>
+        <v>-5.561515106820218e-05</v>
       </c>
       <c r="J26">
-        <v>7.6920219427976225e-06</v>
+        <v>7.7232169495954248e-06</v>
       </c>
       <c r="K26">
-        <v>-1.9570131783865075e-05</v>
+        <v>-1.9276415664130865e-05</v>
       </c>
       <c r="L26">
-        <v>-8.3258245848905986e-06</v>
+        <v>-8.370704189693698e-06</v>
       </c>
       <c r="M26">
-        <v>-8.1565824726875994e-05</v>
+        <v>-8.174737975831258e-05</v>
       </c>
       <c r="N26">
-        <v>0.00011456175015991151</v>
+        <v>0.00011439383984365313</v>
       </c>
       <c r="O26">
-        <v>-9.5444848122407241e-05</v>
+        <v>-9.553782629575147e-05</v>
       </c>
       <c r="P26">
-        <v>0.00010814157455045134</v>
+        <v>0.00010835578757822277</v>
       </c>
       <c r="Q26">
-        <v>4.6668522205139517e-05</v>
+        <v>4.6359194890806775e-05</v>
       </c>
       <c r="R26">
-        <v>6.579859296115256e-05</v>
+        <v>6.572844696292211e-05</v>
       </c>
       <c r="S26">
-        <v>4.3098241443089141e-05</v>
+        <v>4.3026856138298538e-05</v>
       </c>
       <c r="T26">
-        <v>-0.0002391107342234371</v>
+        <v>-0.00023697175779435059</v>
       </c>
       <c r="U26">
-        <v>-0.0001612216177934913</v>
+        <v>-0.00015827837842209442</v>
       </c>
       <c r="V26">
-        <v>-0.00019776480947328486</v>
+        <v>-0.00019517041910760771</v>
       </c>
       <c r="W26">
-        <v>-1.2805140901900563e-05</v>
+        <v>-1.2850461832927804e-05</v>
       </c>
       <c r="X26">
-        <v>1.5265079848251746e-05</v>
+        <v>1.5038794390850993e-05</v>
       </c>
       <c r="Y26">
-        <v>6.0082731177777028e-05</v>
+        <v>5.8546293138214242e-05</v>
       </c>
       <c r="Z26">
-        <v>0.0024019470371932561</v>
+        <v>0.002403550398369916</v>
       </c>
       <c r="AA26">
-        <v>0.0029132641563827297</v>
+        <v>0.0029148475551923816</v>
       </c>
       <c r="AB26">
-        <v>0.0024145795193169753</v>
+        <v>0.0024160957126365826</v>
       </c>
       <c r="AC26">
-        <v>0.002407777320436252</v>
+        <v>0.0024093572699213821</v>
       </c>
       <c r="AD26">
-        <v>0.0024183629461501988</v>
+        <v>0.0024199231391288829</v>
       </c>
       <c r="AE26">
-        <v>0.0023961305224088668</v>
+        <v>0.0023976319659872111</v>
       </c>
       <c r="AF26">
-        <v>5.0341015421428035e-06</v>
+        <v>5.039172834197763e-06</v>
       </c>
       <c r="AG26">
-        <v>3.5143103445039927e-05</v>
+        <v>3.4835930301661648e-05</v>
       </c>
       <c r="AH26">
-        <v>-2.8320511428704806e-05</v>
+        <v>-2.8199243767408622e-05</v>
       </c>
       <c r="AI26">
-        <v>-0.0021972512193771704</v>
+        <v>-0.0022004278612251281</v>
       </c>
     </row>
     <row r="27">
@@ -7120,106 +7120,106 @@
         <v>54</v>
       </c>
       <c r="B27">
-        <v>-0.041959917611259147</v>
+        <v>-0.041511225058046997</v>
       </c>
       <c r="C27">
-        <v>7.2822143498292637e-06</v>
+        <v>6.9760191377979161e-06</v>
       </c>
       <c r="D27">
-        <v>2.697070694620193e-06</v>
+        <v>2.6496366877957415e-06</v>
       </c>
       <c r="E27">
-        <v>-4.0279910068181208e-08</v>
+        <v>-3.9895281830393476e-08</v>
       </c>
       <c r="F27">
-        <v>-4.3692492921836609e-05</v>
+        <v>-4.3719027208413697e-05</v>
       </c>
       <c r="G27">
-        <v>-3.4721204415569468e-05</v>
+        <v>-3.4709028774606351e-05</v>
       </c>
       <c r="H27">
-        <v>-9.6464399529598956e-05</v>
+        <v>-9.6477235923793717e-05</v>
       </c>
       <c r="I27">
-        <v>-7.5872728060489116e-05</v>
+        <v>-7.6338942696981579e-05</v>
       </c>
       <c r="J27">
-        <v>-1.024119070579583e-05</v>
+        <v>-9.9065126713600744e-06</v>
       </c>
       <c r="K27">
-        <v>-2.6616656722436446e-05</v>
+        <v>-2.7012175418189175e-05</v>
       </c>
       <c r="L27">
-        <v>-4.5104831088476339e-06</v>
+        <v>-4.4093195581566065e-06</v>
       </c>
       <c r="M27">
-        <v>-7.4531000168357822e-05</v>
+        <v>-7.4798169395010197e-05</v>
       </c>
       <c r="N27">
-        <v>0.00013430757200705204</v>
+        <v>0.00013461317724291501</v>
       </c>
       <c r="O27">
-        <v>-9.9987714929009334e-05</v>
+        <v>-0.00010038128288236559</v>
       </c>
       <c r="P27">
-        <v>8.854105528242098e-05</v>
+        <v>8.8851153156342948e-05</v>
       </c>
       <c r="Q27">
-        <v>9.9448226390481693e-05</v>
+        <v>9.9282122083284253e-05</v>
       </c>
       <c r="R27">
-        <v>7.9745894430414922e-05</v>
+        <v>7.9839508586744285e-05</v>
       </c>
       <c r="S27">
-        <v>7.1132001372349076e-05</v>
+        <v>7.0954999775664626e-05</v>
       </c>
       <c r="T27">
-        <v>-0.00023331829453876549</v>
+        <v>-0.00023627816261422669</v>
       </c>
       <c r="U27">
-        <v>-0.000213103502907863</v>
+        <v>-0.00021599875091771149</v>
       </c>
       <c r="V27">
-        <v>-0.000228015592020864</v>
+        <v>-0.0002307304293205051</v>
       </c>
       <c r="W27">
-        <v>1.2864131794275286e-06</v>
+        <v>8.9035697779476348e-07</v>
       </c>
       <c r="X27">
-        <v>2.4269044024923377e-05</v>
+        <v>2.395369186708842e-05</v>
       </c>
       <c r="Y27">
-        <v>9.2823550993128756e-05</v>
+        <v>8.9294459759380824e-05</v>
       </c>
       <c r="Z27">
-        <v>0.0024003706698320004</v>
+        <v>0.0024018384466925175</v>
       </c>
       <c r="AA27">
-        <v>0.0024145795193169753</v>
+        <v>0.0024160957126365826</v>
       </c>
       <c r="AB27">
-        <v>0.0028900449380497972</v>
+        <v>0.0028912112699131546</v>
       </c>
       <c r="AC27">
-        <v>0.0024043897227105974</v>
+        <v>0.0024058644118620937</v>
       </c>
       <c r="AD27">
-        <v>0.0024166781997009002</v>
+        <v>0.0024182207010879434</v>
       </c>
       <c r="AE27">
-        <v>0.0023922319415731258</v>
+        <v>0.0023938239766845499</v>
       </c>
       <c r="AF27">
-        <v>3.9761924869891407e-06</v>
+        <v>3.9742914039158828e-06</v>
       </c>
       <c r="AG27">
-        <v>8.4925635283048407e-05</v>
+        <v>8.5101182829898977e-05</v>
       </c>
       <c r="AH27">
-        <v>1.8899554389884433e-05</v>
+        <v>1.9214496868034817e-05</v>
       </c>
       <c r="AI27">
-        <v>-0.0021741961383255994</v>
+        <v>-0.0021712246245258688</v>
       </c>
     </row>
     <row r="28">
@@ -7227,106 +7227,106 @@
         <v>55</v>
       </c>
       <c r="B28">
-        <v>-0.17308448932077908</v>
+        <v>-0.17274750090494068</v>
       </c>
       <c r="C28">
-        <v>4.2572345110106642e-06</v>
+        <v>4.37177101838762e-06</v>
       </c>
       <c r="D28">
-        <v>3.3111745535957895e-06</v>
+        <v>3.3060123068474884e-06</v>
       </c>
       <c r="E28">
-        <v>-4.6066599677972516e-08</v>
+        <v>-4.6005625474448603e-08</v>
       </c>
       <c r="F28">
-        <v>-9.425875026856283e-05</v>
+        <v>-9.434248749252863e-05</v>
       </c>
       <c r="G28">
-        <v>-9.5267496664021333e-05</v>
+        <v>-9.5431062887091789e-05</v>
       </c>
       <c r="H28">
-        <v>-0.00014677624567278631</v>
+        <v>-0.00014693418837219137</v>
       </c>
       <c r="I28">
-        <v>-9.1320964737238216e-05</v>
+        <v>-9.1646211952361393e-05</v>
       </c>
       <c r="J28">
-        <v>9.4274848582951993e-06</v>
+        <v>9.5318444476418823e-06</v>
       </c>
       <c r="K28">
-        <v>8.045076416849338e-06</v>
+        <v>7.8577577430050637e-06</v>
       </c>
       <c r="L28">
-        <v>-7.3148628605913319e-06</v>
+        <v>-7.1575627419663402e-06</v>
       </c>
       <c r="M28">
-        <v>-6.6399652958953561e-05</v>
+        <v>-6.6566042929599653e-05</v>
       </c>
       <c r="N28">
-        <v>9.8039917483482919e-05</v>
+        <v>9.7898026577931821e-05</v>
       </c>
       <c r="O28">
-        <v>-0.00012832431907419813</v>
+        <v>-0.00012848653550902875</v>
       </c>
       <c r="P28">
-        <v>0.00010920062210723416</v>
+        <v>0.00010941218739209991</v>
       </c>
       <c r="Q28">
-        <v>-3.4255856849454633e-05</v>
+        <v>-3.4653852526901445e-05</v>
       </c>
       <c r="R28">
-        <v>1.0732254452152333e-05</v>
+        <v>1.0444425434076934e-05</v>
       </c>
       <c r="S28">
-        <v>-6.5461614596439011e-06</v>
+        <v>-6.8574665755454303e-06</v>
       </c>
       <c r="T28">
-        <v>-4.9629513844086891e-05</v>
+        <v>-4.9982022240475585e-05</v>
       </c>
       <c r="U28">
-        <v>5.6877917379005542e-05</v>
+        <v>5.6598753435136047e-05</v>
       </c>
       <c r="V28">
-        <v>5.064178824815916e-05</v>
+        <v>5.0429980654251652e-05</v>
       </c>
       <c r="W28">
-        <v>-6.3322716246603925e-06</v>
+        <v>-6.1956261635208589e-06</v>
       </c>
       <c r="X28">
-        <v>1.8885996400031121e-05</v>
+        <v>1.8834833522594766e-05</v>
       </c>
       <c r="Y28">
-        <v>3.3394181581054242e-05</v>
+        <v>3.0241719546356469e-05</v>
       </c>
       <c r="Z28">
-        <v>0.0024053124015353117</v>
+        <v>0.0024068293784165707</v>
       </c>
       <c r="AA28">
-        <v>0.002407777320436252</v>
+        <v>0.0024093572699213821</v>
       </c>
       <c r="AB28">
-        <v>0.0024043897227105974</v>
+        <v>0.0024058644118620937</v>
       </c>
       <c r="AC28">
-        <v>0.002736857499425413</v>
+        <v>0.0027382482436391796</v>
       </c>
       <c r="AD28">
-        <v>0.0024153830837603122</v>
+        <v>0.0024168318782956813</v>
       </c>
       <c r="AE28">
-        <v>0.0023988742628119177</v>
+        <v>0.0024003266541567266</v>
       </c>
       <c r="AF28">
-        <v>7.3288350495538185e-06</v>
+        <v>7.3384980026480068e-06</v>
       </c>
       <c r="AG28">
-        <v>3.0846391880545981e-05</v>
+        <v>3.0650755195742868e-05</v>
       </c>
       <c r="AH28">
-        <v>-1.8176728307583035e-05</v>
+        <v>-1.8159970944595571e-05</v>
       </c>
       <c r="AI28">
-        <v>-0.0023874069787615457</v>
+        <v>-0.0023882160995456758</v>
       </c>
     </row>
     <row r="29">
@@ -7334,106 +7334,106 @@
         <v>56</v>
       </c>
       <c r="B29">
-        <v>-0.059777586583149328</v>
+        <v>-0.059646042206067167</v>
       </c>
       <c r="C29">
-        <v>-1.8895805004206254e-05</v>
+        <v>-1.8893322566322499e-05</v>
       </c>
       <c r="D29">
-        <v>2.7098451452058439e-06</v>
+        <v>2.7000313798056935e-06</v>
       </c>
       <c r="E29">
-        <v>-3.3901780022848824e-08</v>
+        <v>-3.3621964339694341e-08</v>
       </c>
       <c r="F29">
-        <v>1.0258616395554358e-05</v>
+        <v>1.0024030448895545e-05</v>
       </c>
       <c r="G29">
-        <v>-3.6770110894328648e-07</v>
+        <v>-4.4670324184873517e-07</v>
       </c>
       <c r="H29">
-        <v>-5.7995603966465303e-05</v>
+        <v>-5.8249228400782897e-05</v>
       </c>
       <c r="I29">
-        <v>4.7570217411091985e-05</v>
+        <v>4.7353825128320683e-05</v>
       </c>
       <c r="J29">
-        <v>-7.4113146721242862e-05</v>
+        <v>-7.4128590388704578e-05</v>
       </c>
       <c r="K29">
-        <v>-1.6211091124791006e-05</v>
+        <v>-1.7723351807230679e-05</v>
       </c>
       <c r="L29">
-        <v>-1.1032005505418663e-05</v>
+        <v>-1.0905681299324917e-05</v>
       </c>
       <c r="M29">
-        <v>-5.2142528327796093e-05</v>
+        <v>-5.2188146467307259e-05</v>
       </c>
       <c r="N29">
-        <v>7.1475371197587522e-05</v>
+        <v>7.1443082540535198e-05</v>
       </c>
       <c r="O29">
-        <v>-4.7235486771416541e-05</v>
+        <v>-4.7242070389820132e-05</v>
       </c>
       <c r="P29">
-        <v>6.8460209244772773e-05</v>
+        <v>6.8524030885496129e-05</v>
       </c>
       <c r="Q29">
-        <v>6.6467335825516442e-05</v>
+        <v>6.5856619127423362e-05</v>
       </c>
       <c r="R29">
-        <v>8.7401855542785893e-05</v>
+        <v>8.7148450729574757e-05</v>
       </c>
       <c r="S29">
-        <v>5.932915766124116e-05</v>
+        <v>5.9035760047622746e-05</v>
       </c>
       <c r="T29">
-        <v>-0.00028632919040400863</v>
+        <v>-0.00029799213440012858</v>
       </c>
       <c r="U29">
-        <v>-0.00019822358007756495</v>
+        <v>-0.00021078048529140064</v>
       </c>
       <c r="V29">
-        <v>-0.00022346204295744382</v>
+        <v>-0.00023556963315815062</v>
       </c>
       <c r="W29">
-        <v>7.5633144020334964e-06</v>
+        <v>7.9580214339586058e-06</v>
       </c>
       <c r="X29">
-        <v>5.9731947545477453e-05</v>
+        <v>5.9793821400408779e-05</v>
       </c>
       <c r="Y29">
-        <v>9.2201178753770717e-05</v>
+        <v>9.1352888362737433e-05</v>
       </c>
       <c r="Z29">
-        <v>0.0024130635737536028</v>
+        <v>0.0024144940450831001</v>
       </c>
       <c r="AA29">
-        <v>0.0024183629461501988</v>
+        <v>0.0024199231391288829</v>
       </c>
       <c r="AB29">
-        <v>0.0024166781997009002</v>
+        <v>0.0024182207010879434</v>
       </c>
       <c r="AC29">
-        <v>0.0024153830837603122</v>
+        <v>0.0024168318782956813</v>
       </c>
       <c r="AD29">
-        <v>0.002741044324812615</v>
+        <v>0.0027426640374758997</v>
       </c>
       <c r="AE29">
-        <v>0.002399823517029775</v>
+        <v>0.0024013860735255625</v>
       </c>
       <c r="AF29">
-        <v>6.7432536734442293e-06</v>
+        <v>6.7317510321905603e-06</v>
       </c>
       <c r="AG29">
-        <v>0.0002488530751332714</v>
+        <v>0.00024879189554570264</v>
       </c>
       <c r="AH29">
-        <v>-2.8456481678028681e-07</v>
+        <v>5.4293743339964631e-08</v>
       </c>
       <c r="AI29">
-        <v>-0.0022674087277131556</v>
+        <v>-0.0022567947157818703</v>
       </c>
     </row>
     <row r="30">
@@ -7441,106 +7441,106 @@
         <v>57</v>
       </c>
       <c r="B30">
-        <v>-0.15103280478580675</v>
+        <v>-0.15083426778561873</v>
       </c>
       <c r="C30">
-        <v>9.3130314107987875e-06</v>
+        <v>9.078395632183029e-06</v>
       </c>
       <c r="D30">
-        <v>-3.7182472273433852e-06</v>
+        <v>-3.7432941115907417e-06</v>
       </c>
       <c r="E30">
-        <v>1.8326230847159117e-08</v>
+        <v>1.8196754478072829e-08</v>
       </c>
       <c r="F30">
-        <v>-5.2922973063558609e-06</v>
+        <v>-5.3170062463804915e-06</v>
       </c>
       <c r="G30">
-        <v>1.7840588211187744e-06</v>
+        <v>1.5892475574857154e-06</v>
       </c>
       <c r="H30">
-        <v>-4.1755144483655708e-05</v>
+        <v>-4.207361399925628e-05</v>
       </c>
       <c r="I30">
-        <v>-1.0998181087716835e-05</v>
+        <v>-1.1162008556380321e-05</v>
       </c>
       <c r="J30">
-        <v>-3.34843595512793e-06</v>
+        <v>-3.4362991330363968e-06</v>
       </c>
       <c r="K30">
-        <v>1.2277340705570843e-05</v>
+        <v>1.1960281701943796e-05</v>
       </c>
       <c r="L30">
-        <v>-5.3927727825969897e-06</v>
+        <v>-5.2561162497527967e-06</v>
       </c>
       <c r="M30">
-        <v>-5.4684359378744815e-05</v>
+        <v>-5.4707719815161954e-05</v>
       </c>
       <c r="N30">
-        <v>0.00012324085976339047</v>
+        <v>0.00012350157466021208</v>
       </c>
       <c r="O30">
-        <v>-9.5000747710684023e-05</v>
+        <v>-9.497152143127203e-05</v>
       </c>
       <c r="P30">
-        <v>5.8168987783405678e-05</v>
+        <v>5.8228554816225743e-05</v>
       </c>
       <c r="Q30">
-        <v>-5.7145689075200311e-07</v>
+        <v>-4.8637700066664173e-07</v>
       </c>
       <c r="R30">
-        <v>3.5825910529381022e-05</v>
+        <v>3.6249155061806844e-05</v>
       </c>
       <c r="S30">
-        <v>1.7578409182146797e-05</v>
+        <v>1.7587982876780405e-05</v>
       </c>
       <c r="T30">
-        <v>-6.6982911648969141e-05</v>
+        <v>-6.9971695066448243e-05</v>
       </c>
       <c r="U30">
-        <v>6.8994809937670707e-05</v>
+        <v>6.7585007183653626e-05</v>
       </c>
       <c r="V30">
-        <v>6.0863052053493219e-05</v>
+        <v>5.9506652066179883e-05</v>
       </c>
       <c r="W30">
-        <v>-4.9954516738316636e-05</v>
+        <v>-5.1787848250889523e-05</v>
       </c>
       <c r="X30">
-        <v>1.2268955093169197e-05</v>
+        <v>1.1611884530182302e-05</v>
       </c>
       <c r="Y30">
-        <v>-2.3088192576370845e-05</v>
+        <v>-3.5884440126575035e-05</v>
       </c>
       <c r="Z30">
-        <v>0.0023943327021205148</v>
+        <v>0.0023958525996362438</v>
       </c>
       <c r="AA30">
-        <v>0.0023961305224088668</v>
+        <v>0.0023976319659872111</v>
       </c>
       <c r="AB30">
-        <v>0.0023922319415731258</v>
+        <v>0.0023938239766845499</v>
       </c>
       <c r="AC30">
-        <v>0.0023988742628119177</v>
+        <v>0.0024003266541567266</v>
       </c>
       <c r="AD30">
-        <v>0.002399823517029775</v>
+        <v>0.0024013860735255625</v>
       </c>
       <c r="AE30">
-        <v>0.0028590045554329315</v>
+        <v>0.0028600629481484534</v>
       </c>
       <c r="AF30">
-        <v>4.640559718731578e-06</v>
+        <v>4.6628558613332784e-06</v>
       </c>
       <c r="AG30">
-        <v>2.7589194120178871e-05</v>
+        <v>2.6252214162212316e-05</v>
       </c>
       <c r="AH30">
-        <v>-3.89107080160404e-05</v>
+        <v>-3.8857779376191403e-05</v>
       </c>
       <c r="AI30">
-        <v>-0.0022996381816512762</v>
+        <v>-0.0022968007437127974</v>
       </c>
     </row>
     <row r="31">
@@ -7548,106 +7548,106 @@
         <v>58</v>
       </c>
       <c r="B31">
-        <v>0.022623976220380211</v>
+        <v>0.022661376593080655</v>
       </c>
       <c r="C31">
-        <v>-1.1801453572122004e-07</v>
+        <v>-1.1713617503157034e-07</v>
       </c>
       <c r="D31">
-        <v>-1.0517234437267577e-07</v>
+        <v>-1.1073115482207998e-07</v>
       </c>
       <c r="E31">
-        <v>-7.9769449682427677e-10</v>
+        <v>-7.6469376919826121e-10</v>
       </c>
       <c r="F31">
-        <v>-2.1242813873393685e-06</v>
+        <v>-2.1296604221588067e-06</v>
       </c>
       <c r="G31">
-        <v>-4.9769320234327978e-06</v>
+        <v>-4.9904075742537298e-06</v>
       </c>
       <c r="H31">
-        <v>-3.812822218944009e-06</v>
+        <v>-3.8069441577882174e-06</v>
       </c>
       <c r="I31">
-        <v>-1.5225029826202927e-06</v>
+        <v>-1.5413697275998045e-06</v>
       </c>
       <c r="J31">
-        <v>-1.2766501460807108e-06</v>
+        <v>-1.2655894037201618e-06</v>
       </c>
       <c r="K31">
-        <v>7.6871471711810675e-07</v>
+        <v>8.2590497641914012e-07</v>
       </c>
       <c r="L31">
-        <v>-2.8400275670942545e-07</v>
+        <v>-2.708817252856624e-07</v>
       </c>
       <c r="M31">
-        <v>4.5341083384152171e-06</v>
+        <v>4.5140438765156904e-06</v>
       </c>
       <c r="N31">
-        <v>-1.6854814070528881e-06</v>
+        <v>-1.6835123396858036e-06</v>
       </c>
       <c r="O31">
-        <v>-2.9715070134869425e-06</v>
+        <v>-2.9833865790864454e-06</v>
       </c>
       <c r="P31">
-        <v>-4.8550016487323321e-06</v>
+        <v>-4.835728867982459e-06</v>
       </c>
       <c r="Q31">
-        <v>-4.2520489844773894e-06</v>
+        <v>-4.2407887498384193e-06</v>
       </c>
       <c r="R31">
-        <v>-8.6593109527509067e-06</v>
+        <v>-8.6701134686602592e-06</v>
       </c>
       <c r="S31">
-        <v>-1.1463604557539225e-05</v>
+        <v>-1.1447210369927276e-05</v>
       </c>
       <c r="T31">
-        <v>-2.9561829437222678e-07</v>
+        <v>2.1528153876205439e-07</v>
       </c>
       <c r="U31">
-        <v>6.434105305371939e-06</v>
+        <v>6.9688415398830176e-06</v>
       </c>
       <c r="V31">
-        <v>6.5462480586167397e-06</v>
+        <v>7.0868702618841553e-06</v>
       </c>
       <c r="W31">
-        <v>2.6429877657229862e-07</v>
+        <v>-1.6556312024076805e-08</v>
       </c>
       <c r="X31">
-        <v>-1.2264595303643813e-07</v>
+        <v>-2.6925762539104889e-07</v>
       </c>
       <c r="Y31">
-        <v>-9.1016462402966812e-06</v>
+        <v>-8.8393577961908054e-06</v>
       </c>
       <c r="Z31">
-        <v>6.8855059488431573e-06</v>
+        <v>6.8893600317669401e-06</v>
       </c>
       <c r="AA31">
-        <v>5.0341015421428035e-06</v>
+        <v>5.039172834197763e-06</v>
       </c>
       <c r="AB31">
-        <v>3.9761924869891407e-06</v>
+        <v>3.9742914039158828e-06</v>
       </c>
       <c r="AC31">
-        <v>7.3288350495538185e-06</v>
+        <v>7.3384980026480068e-06</v>
       </c>
       <c r="AD31">
-        <v>6.7432536734442293e-06</v>
+        <v>6.7317510321905603e-06</v>
       </c>
       <c r="AE31">
-        <v>4.640559718731578e-06</v>
+        <v>4.6628558613332784e-06</v>
       </c>
       <c r="AF31">
-        <v>3.8262559738154043e-06</v>
+        <v>3.8250915107269126e-06</v>
       </c>
       <c r="AG31">
-        <v>-6.0272775925399258e-06</v>
+        <v>-6.0227971973546426e-06</v>
       </c>
       <c r="AH31">
-        <v>-1.1944329663813337e-05</v>
+        <v>-1.1946887292048473e-05</v>
       </c>
       <c r="AI31">
-        <v>-6.1229541170580211e-05</v>
+        <v>-6.1465698923922151e-05</v>
       </c>
     </row>
     <row r="32">
@@ -7655,106 +7655,106 @@
         <v>59</v>
       </c>
       <c r="B32">
-        <v>-0.20141914495740831</v>
+        <v>-0.20132120976842946</v>
       </c>
       <c r="C32">
-        <v>-7.8303737241919042e-05</v>
+        <v>-7.8348589206558112e-05</v>
       </c>
       <c r="D32">
-        <v>6.7792657439162902e-07</v>
+        <v>7.2371231071046956e-07</v>
       </c>
       <c r="E32">
-        <v>-2.0616752399827562e-08</v>
+        <v>-2.1061352079788054e-08</v>
       </c>
       <c r="F32">
-        <v>1.3254611324652228e-05</v>
+        <v>1.3101660560370029e-05</v>
       </c>
       <c r="G32">
-        <v>2.3653988487843877e-05</v>
+        <v>2.3560435616849611e-05</v>
       </c>
       <c r="H32">
-        <v>-9.4182418717767002e-07</v>
+        <v>-1.3115123110637311e-06</v>
       </c>
       <c r="I32">
-        <v>0.00017677745986703283</v>
+        <v>0.00017685683753167463</v>
       </c>
       <c r="J32">
-        <v>-0.00016867270152082627</v>
+        <v>-0.00016898574867744656</v>
       </c>
       <c r="K32">
-        <v>1.6656694351073042e-05</v>
+        <v>1.6152553236027049e-05</v>
       </c>
       <c r="L32">
-        <v>-4.7572744028242836e-06</v>
+        <v>-5.157916866126524e-06</v>
       </c>
       <c r="M32">
-        <v>7.9370531799451678e-05</v>
+        <v>7.9398350037771e-05</v>
       </c>
       <c r="N32">
-        <v>6.7198161181713026e-05</v>
+        <v>6.7252230678467063e-05</v>
       </c>
       <c r="O32">
-        <v>0.0001750698952145773</v>
+        <v>0.00017536319512749359</v>
       </c>
       <c r="P32">
-        <v>-4.5373912749079905e-05</v>
+        <v>-4.5397950292241571e-05</v>
       </c>
       <c r="Q32">
-        <v>0.00031607126843852251</v>
+        <v>0.00031659723868952827</v>
       </c>
       <c r="R32">
-        <v>0.00028715676090059969</v>
+        <v>0.0002879989900816636</v>
       </c>
       <c r="S32">
-        <v>0.00020059819423439221</v>
+        <v>0.0002006316169769623</v>
       </c>
       <c r="T32">
-        <v>-4.8286190883990721e-05</v>
+        <v>-5.5994886211566119e-05</v>
       </c>
       <c r="U32">
-        <v>3.5529327898728424e-05</v>
+        <v>2.6878304278842719e-05</v>
       </c>
       <c r="V32">
-        <v>0.00010284722603032259</v>
+        <v>9.5301536831786382e-05</v>
       </c>
       <c r="W32">
-        <v>3.383842085780478e-05</v>
+        <v>3.3973305414521386e-05</v>
       </c>
       <c r="X32">
-        <v>0.00011583449999951964</v>
+        <v>0.00011623267111935905</v>
       </c>
       <c r="Y32">
-        <v>7.3739496584565752e-05</v>
+        <v>6.0175165015133813e-05</v>
       </c>
       <c r="Z32">
-        <v>3.9008417406748153e-05</v>
+        <v>3.8664036657134679e-05</v>
       </c>
       <c r="AA32">
-        <v>3.5143103445039927e-05</v>
+        <v>3.4835930301661648e-05</v>
       </c>
       <c r="AB32">
-        <v>8.4925635283048407e-05</v>
+        <v>8.5101182829898977e-05</v>
       </c>
       <c r="AC32">
-        <v>3.0846391880545981e-05</v>
+        <v>3.0650755195742868e-05</v>
       </c>
       <c r="AD32">
-        <v>0.0002488530751332714</v>
+        <v>0.00024879189554570264</v>
       </c>
       <c r="AE32">
-        <v>2.7589194120178871e-05</v>
+        <v>2.6252214162212316e-05</v>
       </c>
       <c r="AF32">
-        <v>-6.0272775925399258e-06</v>
+        <v>-6.0227971973546426e-06</v>
       </c>
       <c r="AG32">
-        <v>0.0017435790274805698</v>
+        <v>0.0017412523813394669</v>
       </c>
       <c r="AH32">
-        <v>0.0002839342265336464</v>
+        <v>0.00028408191679715956</v>
       </c>
       <c r="AI32">
-        <v>-0.00031764632932575275</v>
+        <v>-0.00031052205956822116</v>
       </c>
     </row>
     <row r="33">
@@ -7762,106 +7762,106 @@
         <v>60</v>
       </c>
       <c r="B33">
-        <v>-0.12567371101174948</v>
+        <v>-0.12610477213348631</v>
       </c>
       <c r="C33">
-        <v>-2.8586673719581114e-05</v>
+        <v>-2.871086252514396e-05</v>
       </c>
       <c r="D33">
-        <v>-2.1025786509196349e-06</v>
+        <v>-2.0665980981459645e-06</v>
       </c>
       <c r="E33">
-        <v>9.7628222075587755e-09</v>
+        <v>9.6154898530007683e-09</v>
       </c>
       <c r="F33">
-        <v>-8.3220067583281154e-07</v>
+        <v>-1.1459651114999712e-06</v>
       </c>
       <c r="G33">
-        <v>5.0810295743719102e-05</v>
+        <v>5.04504162779848e-05</v>
       </c>
       <c r="H33">
-        <v>1.1790754280966483e-05</v>
+        <v>1.1186649182695282e-05</v>
       </c>
       <c r="I33">
-        <v>6.4729527955960983e-05</v>
+        <v>6.4684847934265953e-05</v>
       </c>
       <c r="J33">
-        <v>-8.3141777482098215e-05</v>
+        <v>-8.3200465864430545e-05</v>
       </c>
       <c r="K33">
-        <v>3.2264897530520989e-05</v>
+        <v>3.0176125816626896e-05</v>
       </c>
       <c r="L33">
-        <v>-7.4010554880799231e-06</v>
+        <v>-7.1369518895646625e-06</v>
       </c>
       <c r="M33">
-        <v>5.013149121636935e-05</v>
+        <v>5.0290009126370559e-05</v>
       </c>
       <c r="N33">
-        <v>3.4162190225686239e-05</v>
+        <v>3.4368224754767647e-05</v>
       </c>
       <c r="O33">
-        <v>0.00022189868718456023</v>
+        <v>0.00022196014127580637</v>
       </c>
       <c r="P33">
-        <v>-0.00015097457733100018</v>
+        <v>-0.00015119055836303815</v>
       </c>
       <c r="Q33">
-        <v>0.00019648143661476526</v>
+        <v>0.00019594872205736056</v>
       </c>
       <c r="R33">
-        <v>0.00018711060073023714</v>
+        <v>0.0001867011565983975</v>
       </c>
       <c r="S33">
-        <v>0.00014551465158310021</v>
+        <v>0.00014512875049894208</v>
       </c>
       <c r="T33">
-        <v>0.00016431300235473373</v>
+        <v>0.00014858609909701621</v>
       </c>
       <c r="U33">
-        <v>0.00016931722591211236</v>
+        <v>0.00015217774312469186</v>
       </c>
       <c r="V33">
-        <v>0.00021353528251407371</v>
+        <v>0.00019727308075736388</v>
       </c>
       <c r="W33">
-        <v>-1.1683104600936545e-05</v>
+        <v>-1.182606046036495e-05</v>
       </c>
       <c r="X33">
-        <v>1.5224501182161082e-05</v>
+        <v>1.5389163367935809e-05</v>
       </c>
       <c r="Y33">
-        <v>1.185222418444978e-05</v>
+        <v>1.0711515924385082e-05</v>
       </c>
       <c r="Z33">
-        <v>6.6071984716610348e-06</v>
+        <v>6.6604240827844267e-06</v>
       </c>
       <c r="AA33">
-        <v>-2.8320511428704806e-05</v>
+        <v>-2.8199243767408622e-05</v>
       </c>
       <c r="AB33">
-        <v>1.8899554389884433e-05</v>
+        <v>1.9214496868034817e-05</v>
       </c>
       <c r="AC33">
-        <v>-1.8176728307583035e-05</v>
+        <v>-1.8159970944595571e-05</v>
       </c>
       <c r="AD33">
-        <v>-2.8456481678028681e-07</v>
+        <v>5.4293743339964631e-08</v>
       </c>
       <c r="AE33">
-        <v>-3.89107080160404e-05</v>
+        <v>-3.8857779376191403e-05</v>
       </c>
       <c r="AF33">
-        <v>-1.1944329663813337e-05</v>
+        <v>-1.1946887292048473e-05</v>
       </c>
       <c r="AG33">
-        <v>0.0002839342265336464</v>
+        <v>0.00028408191679715956</v>
       </c>
       <c r="AH33">
-        <v>0.0014619434463006196</v>
+        <v>0.0014618430071155078</v>
       </c>
       <c r="AI33">
-        <v>-0.00011722674572657436</v>
+        <v>-0.00010223603091888482</v>
       </c>
     </row>
     <row r="34">
@@ -7869,106 +7869,106 @@
         <v>61</v>
       </c>
       <c r="B34">
-        <v>-0.4431631749946896</v>
+        <v>-0.44886908162203287</v>
       </c>
       <c r="C34">
-        <v>0.00018030146354133222</v>
+        <v>0.00017048838167084109</v>
       </c>
       <c r="D34">
-        <v>-0.00037727989086930693</v>
+        <v>-0.00037840922310119454</v>
       </c>
       <c r="E34">
-        <v>3.2579248682791623e-06</v>
+        <v>3.2688604033339336e-06</v>
       </c>
       <c r="F34">
-        <v>-0.0031909959915158394</v>
+        <v>-0.0031907660066190684</v>
       </c>
       <c r="G34">
-        <v>-0.003270466191866302</v>
+        <v>-0.003264930078864586</v>
       </c>
       <c r="H34">
-        <v>-0.003381134787782597</v>
+        <v>-0.0033820336201729473</v>
       </c>
       <c r="I34">
-        <v>-0.0039087046616684516</v>
+        <v>-0.0039016022318896365</v>
       </c>
       <c r="J34">
-        <v>0.00037117144109132753</v>
+        <v>0.00037411143719150966</v>
       </c>
       <c r="K34">
-        <v>-0.002408534962640044</v>
+        <v>-0.0024598768867113464</v>
       </c>
       <c r="L34">
-        <v>7.7037032292740965e-05</v>
+        <v>8.0841463138480685e-05</v>
       </c>
       <c r="M34">
-        <v>-0.00010796927102515791</v>
+        <v>-0.00010912148249779828</v>
       </c>
       <c r="N34">
-        <v>-0.004452135442681469</v>
+        <v>-0.0044423224796542029</v>
       </c>
       <c r="O34">
-        <v>-0.0037005242288102864</v>
+        <v>-0.0037023871339994029</v>
       </c>
       <c r="P34">
-        <v>-0.0031854452860888309</v>
+        <v>-0.0031849625751416287</v>
       </c>
       <c r="Q34">
-        <v>-0.015830166702359098</v>
+        <v>-0.015825749025517082</v>
       </c>
       <c r="R34">
-        <v>-0.015025821244958616</v>
+        <v>-0.01502158810750011</v>
       </c>
       <c r="S34">
-        <v>-0.014774351112696028</v>
+        <v>-0.014763368816508946</v>
       </c>
       <c r="T34">
-        <v>-0.024007797661731684</v>
+        <v>-0.024416804220154135</v>
       </c>
       <c r="U34">
-        <v>-0.019144972698791899</v>
+        <v>-0.019556821768951863</v>
       </c>
       <c r="V34">
-        <v>-0.019555278136735209</v>
+        <v>-0.019970339422381342</v>
       </c>
       <c r="W34">
-        <v>-0.00041100116851545585</v>
+        <v>-0.00042718926414069328</v>
       </c>
       <c r="X34">
-        <v>-0.0012675766661341425</v>
+        <v>-0.0012783098564462269</v>
       </c>
       <c r="Y34">
-        <v>-0.0011978237530955954</v>
+        <v>-0.0011984065111760687</v>
       </c>
       <c r="Z34">
-        <v>-0.0024091914813475467</v>
+        <v>-0.0024100460320740777</v>
       </c>
       <c r="AA34">
-        <v>-0.0021972512193771704</v>
+        <v>-0.0022004278612251281</v>
       </c>
       <c r="AB34">
-        <v>-0.0021741961383255994</v>
+        <v>-0.0021712246245258688</v>
       </c>
       <c r="AC34">
-        <v>-0.0023874069787615457</v>
+        <v>-0.0023882160995456758</v>
       </c>
       <c r="AD34">
-        <v>-0.0022674087277131556</v>
+        <v>-0.0022567947157818703</v>
       </c>
       <c r="AE34">
-        <v>-0.0022996381816512762</v>
+        <v>-0.0022968007437127974</v>
       </c>
       <c r="AF34">
-        <v>-6.1229541170580211e-05</v>
+        <v>-6.1465698923922151e-05</v>
       </c>
       <c r="AG34">
-        <v>-0.00031764632932575275</v>
+        <v>-0.00031052205956822116</v>
       </c>
       <c r="AH34">
-        <v>-0.00011722674572657436</v>
+        <v>-0.00010223603091888482</v>
       </c>
       <c r="AI34">
-        <v>0.051332128838372015</v>
+        <v>0.051766342372952509</v>
       </c>
     </row>
   </sheetData>

--- a/input/ES/reg_income.xlsx
+++ b/input/ES/reg_income.xlsx
@@ -448,7 +448,7 @@
         <v>19</v>
       </c>
       <c r="B13">
-        <v>0.54362013493723471</v>
+        <v>0.63405729156306156</v>
       </c>
       <c r="C13"/>
       <c r="D13"/>
@@ -459,7 +459,7 @@
         <v>17</v>
       </c>
       <c r="B14">
-        <v>52275</v>
+        <v>53223</v>
       </c>
       <c r="C14"/>
       <c r="D14"/>
@@ -4445,106 +4445,106 @@
         <v>28</v>
       </c>
       <c r="B2">
-        <v>-0.016530073157209738</v>
+        <v>-0.0099465674818788388</v>
       </c>
       <c r="C2">
-        <v>0.00033800478518149576</v>
+        <v>0.00024411009917686062</v>
       </c>
       <c r="D2">
-        <v>-1.1595262593671678e-06</v>
+        <v>-1.2664761897858985e-06</v>
       </c>
       <c r="E2">
-        <v>3.2797749563823646e-08</v>
+        <v>2.6287358297690028e-08</v>
       </c>
       <c r="F2">
-        <v>2.3514888390001136e-05</v>
+        <v>1.7601772434195182e-05</v>
       </c>
       <c r="G2">
-        <v>-2.1657825642411691e-05</v>
+        <v>-1.490817548300548e-05</v>
       </c>
       <c r="H2">
-        <v>-1.4229050579139729e-05</v>
+        <v>-2.8763485953285989e-06</v>
       </c>
       <c r="I2">
-        <v>-6.7355800366263385e-05</v>
+        <v>-4.6281657879378537e-05</v>
       </c>
       <c r="J2">
-        <v>4.159705099024866e-05</v>
+        <v>7.4873669564022607e-06</v>
       </c>
       <c r="K2">
-        <v>-2.1122839431273256e-05</v>
+        <v>-1.5208566547023861e-05</v>
       </c>
       <c r="L2">
-        <v>-7.1611176054830783e-07</v>
+        <v>-4.0111230732168969e-07</v>
       </c>
       <c r="M2">
-        <v>-3.2212234831237209e-05</v>
+        <v>-4.2896352715254841e-06</v>
       </c>
       <c r="N2">
-        <v>-0.00032709392055204717</v>
+        <v>-0.00024034260259612488</v>
       </c>
       <c r="O2">
-        <v>-5.2614115386368898e-05</v>
+        <v>-1.0223419842135619e-05</v>
       </c>
       <c r="P2">
-        <v>3.3549356567971337e-05</v>
+        <v>4.576667820430703e-06</v>
       </c>
       <c r="Q2">
-        <v>-0.00023316230487734562</v>
+        <v>-0.00018675253873414515</v>
       </c>
       <c r="R2">
-        <v>-0.00023008438428831932</v>
+        <v>-0.00018151597747181135</v>
       </c>
       <c r="S2">
-        <v>-0.00019367918701796553</v>
+        <v>-0.00015507529010086275</v>
       </c>
       <c r="T2">
-        <v>-0.0001027422881938953</v>
+        <v>-9.5660569266283366e-05</v>
       </c>
       <c r="U2">
-        <v>-5.2265305761841304e-05</v>
+        <v>-2.95200541884232e-05</v>
       </c>
       <c r="V2">
-        <v>-0.00020319985945792786</v>
+        <v>-0.00014176747662271859</v>
       </c>
       <c r="W2">
-        <v>4.0345429562238022e-05</v>
+        <v>2.9154778942572579e-05</v>
       </c>
       <c r="X2">
-        <v>-3.6891271348568258e-07</v>
+        <v>6.1134543296815869e-06</v>
       </c>
       <c r="Y2">
-        <v>0.00013694080783844886</v>
+        <v>0.00010297790051462028</v>
       </c>
       <c r="Z2">
-        <v>5.7425833494780031e-06</v>
+        <v>-9.335864421748392e-06</v>
       </c>
       <c r="AA2">
-        <v>1.0743021050413368e-05</v>
+        <v>-5.8546447618001047e-06</v>
       </c>
       <c r="AB2">
-        <v>6.9760191377979161e-06</v>
+        <v>-1.0585656419178065e-05</v>
       </c>
       <c r="AC2">
-        <v>4.37177101838762e-06</v>
+        <v>-8.7572897623118122e-06</v>
       </c>
       <c r="AD2">
-        <v>-1.8893322566322499e-05</v>
+        <v>-2.4432389547118601e-05</v>
       </c>
       <c r="AE2">
-        <v>9.078395632183029e-06</v>
+        <v>-4.4127055464639188e-06</v>
       </c>
       <c r="AF2">
-        <v>-1.1713617503157034e-07</v>
+        <v>-1.3817237429177379e-07</v>
       </c>
       <c r="AG2">
-        <v>-7.8348589206558112e-05</v>
+        <v>-4.6110191547671093e-05</v>
       </c>
       <c r="AH2">
-        <v>-2.871086252514396e-05</v>
+        <v>-1.7785141546052447e-05</v>
       </c>
       <c r="AI2">
-        <v>0.00017048838167084109</v>
+        <v>0.00015577358027267209</v>
       </c>
     </row>
     <row r="3">
@@ -4552,106 +4552,106 @@
         <v>29</v>
       </c>
       <c r="B3">
-        <v>0.016860101326262086</v>
+        <v>0.0080688654942652569</v>
       </c>
       <c r="C3">
-        <v>-1.1595262593671678e-06</v>
+        <v>-1.2664761897858985e-06</v>
       </c>
       <c r="D3">
-        <v>1.6420423126666384e-05</v>
+        <v>1.197965394310739e-05</v>
       </c>
       <c r="E3">
-        <v>-1.4365460726144509e-07</v>
+        <v>-1.0292787588158636e-07</v>
       </c>
       <c r="F3">
-        <v>-1.1131506836735371e-05</v>
+        <v>-4.8322411429239144e-06</v>
       </c>
       <c r="G3">
-        <v>-1.0449882433668442e-05</v>
+        <v>-4.5870197709802075e-06</v>
       </c>
       <c r="H3">
-        <v>-1.2208783486304137e-05</v>
+        <v>-7.855583864556253e-06</v>
       </c>
       <c r="I3">
-        <v>5.1034531149174217e-06</v>
+        <v>8.1667961682356852e-06</v>
       </c>
       <c r="J3">
-        <v>-4.4936032629895562e-06</v>
+        <v>-4.8127730407201622e-07</v>
       </c>
       <c r="K3">
-        <v>-2.9196896116809199e-06</v>
+        <v>-2.1040436555915697e-06</v>
       </c>
       <c r="L3">
-        <v>-6.6962297367110984e-07</v>
+        <v>-8.6176110047960581e-07</v>
       </c>
       <c r="M3">
-        <v>1.6047034429475957e-06</v>
+        <v>-3.8982039267731415e-07</v>
       </c>
       <c r="N3">
-        <v>1.587768351397972e-06</v>
+        <v>3.1532069630658345e-07</v>
       </c>
       <c r="O3">
-        <v>4.7129042874799443e-06</v>
+        <v>-7.4091149670805026e-08</v>
       </c>
       <c r="P3">
-        <v>-2.2156869189074688e-06</v>
+        <v>2.7184789103790458e-07</v>
       </c>
       <c r="Q3">
-        <v>-2.4718436714475417e-05</v>
+        <v>-2.0730517857023458e-05</v>
       </c>
       <c r="R3">
-        <v>-3.6741172482691127e-05</v>
+        <v>-2.9683770745107406e-05</v>
       </c>
       <c r="S3">
-        <v>-2.7618385373603016e-05</v>
+        <v>-2.1545048505077787e-05</v>
       </c>
       <c r="T3">
-        <v>5.6327917884880805e-05</v>
+        <v>4.1911041234563763e-05</v>
       </c>
       <c r="U3">
-        <v>-2.8715351058527014e-05</v>
+        <v>-2.4552717071218503e-05</v>
       </c>
       <c r="V3">
-        <v>-3.3873129909836963e-06</v>
+        <v>-8.3669400091756764e-06</v>
       </c>
       <c r="W3">
-        <v>8.9916027705526815e-06</v>
+        <v>1.0149484608886576e-05</v>
       </c>
       <c r="X3">
-        <v>3.4925405800941836e-05</v>
+        <v>2.6659730312490085e-05</v>
       </c>
       <c r="Y3">
-        <v>1.0265266595365681e-05</v>
+        <v>9.8901673089887138e-06</v>
       </c>
       <c r="Z3">
-        <v>-3.6890395435922214e-07</v>
+        <v>9.1350952081012903e-07</v>
       </c>
       <c r="AA3">
-        <v>2.7230093151540838e-06</v>
+        <v>3.6215784504039074e-06</v>
       </c>
       <c r="AB3">
-        <v>2.6496366877957415e-06</v>
+        <v>4.3609333452371355e-06</v>
       </c>
       <c r="AC3">
-        <v>3.3060123068474884e-06</v>
+        <v>3.6727555877707108e-06</v>
       </c>
       <c r="AD3">
-        <v>2.7000313798056935e-06</v>
+        <v>3.6196768917586006e-06</v>
       </c>
       <c r="AE3">
-        <v>-3.7432941115907417e-06</v>
+        <v>-4.014368705582283e-06</v>
       </c>
       <c r="AF3">
-        <v>-1.1073115482207998e-07</v>
+        <v>-1.3660476020046644e-07</v>
       </c>
       <c r="AG3">
-        <v>7.2371231071046956e-07</v>
+        <v>1.1014417681391481e-06</v>
       </c>
       <c r="AH3">
-        <v>-2.0665980981459645e-06</v>
+        <v>-1.6190327647853096e-07</v>
       </c>
       <c r="AI3">
-        <v>-0.00037840922310119454</v>
+        <v>-0.00027957227949393528</v>
       </c>
     </row>
     <row r="4">
@@ -4659,106 +4659,106 @@
         <v>30</v>
       </c>
       <c r="B4">
-        <v>-0.00013073152915414545</v>
+        <v>-7.1974103601231976e-05</v>
       </c>
       <c r="C4">
-        <v>3.2797749563823646e-08</v>
+        <v>2.6287358297690028e-08</v>
       </c>
       <c r="D4">
-        <v>-1.4365460726144509e-07</v>
+        <v>-1.0292787588158636e-07</v>
       </c>
       <c r="E4">
-        <v>1.3292996372632669e-09</v>
+        <v>9.3671921542464885e-10</v>
       </c>
       <c r="F4">
-        <v>1.3253998648093149e-07</v>
+        <v>5.4897828747911303e-08</v>
       </c>
       <c r="G4">
-        <v>1.187290474665369e-07</v>
+        <v>4.8509377529350295e-08</v>
       </c>
       <c r="H4">
-        <v>1.6448313864879601e-07</v>
+        <v>1.0103065565266212e-07</v>
       </c>
       <c r="I4">
-        <v>3.1527165226505297e-08</v>
+        <v>-2.2507369047811773e-08</v>
       </c>
       <c r="J4">
-        <v>3.932745064176556e-08</v>
+        <v>3.3314865379650852e-09</v>
       </c>
       <c r="K4">
-        <v>5.446914133081583e-09</v>
+        <v>2.6175745309641719e-09</v>
       </c>
       <c r="L4">
-        <v>8.5263708724293891e-09</v>
+        <v>9.4811688437675025e-09</v>
       </c>
       <c r="M4">
-        <v>-2.1576164477011495e-08</v>
+        <v>2.4439494548659494e-09</v>
       </c>
       <c r="N4">
-        <v>-3.4959148584785588e-08</v>
+        <v>-1.7725946010885246e-08</v>
       </c>
       <c r="O4">
-        <v>-3.8211111394579369e-08</v>
+        <v>2.2688116442150717e-09</v>
       </c>
       <c r="P4">
-        <v>2.4471266978375564e-08</v>
+        <v>-2.0261303533115006e-09</v>
       </c>
       <c r="Q4">
-        <v>1.5717468542467302e-07</v>
+        <v>1.345105398685577e-07</v>
       </c>
       <c r="R4">
-        <v>2.9121799219837417e-07</v>
+        <v>2.3201903387752886e-07</v>
       </c>
       <c r="S4">
-        <v>2.2981023190497959e-07</v>
+        <v>1.7713008708386214e-07</v>
       </c>
       <c r="T4">
-        <v>-5.3255137979159031e-07</v>
+        <v>-3.9850582766799807e-07</v>
       </c>
       <c r="U4">
-        <v>9.3323005600879071e-08</v>
+        <v>8.5366265271832758e-08</v>
       </c>
       <c r="V4">
-        <v>-3.0831760440807579e-07</v>
+        <v>-1.8236208065779914e-07</v>
       </c>
       <c r="W4">
-        <v>-2.5385119997845615e-08</v>
+        <v>-4.687240301874925e-08</v>
       </c>
       <c r="X4">
-        <v>-2.8087293733730018e-07</v>
+        <v>-2.0757740691395408e-07</v>
       </c>
       <c r="Y4">
-        <v>-1.8130713169339472e-08</v>
+        <v>-3.7547868734137601e-08</v>
       </c>
       <c r="Z4">
-        <v>-5.5115163241112756e-09</v>
+        <v>-3.6069770294001315e-08</v>
       </c>
       <c r="AA4">
-        <v>-4.0942454040429362e-08</v>
+        <v>-6.8712749839840212e-08</v>
       </c>
       <c r="AB4">
-        <v>-3.9895281830393476e-08</v>
+        <v>-7.3442178562350164e-08</v>
       </c>
       <c r="AC4">
-        <v>-4.6005625474448603e-08</v>
+        <v>-6.6999920756369802e-08</v>
       </c>
       <c r="AD4">
-        <v>-3.3621964339694341e-08</v>
+        <v>-6.1898072402069532e-08</v>
       </c>
       <c r="AE4">
-        <v>1.8196754478072829e-08</v>
+        <v>-8.3402859556666785e-10</v>
       </c>
       <c r="AF4">
-        <v>-7.6469376919826121e-10</v>
+        <v>-9.5757793863241551e-11</v>
       </c>
       <c r="AG4">
-        <v>-2.1061352079788054e-08</v>
+        <v>-2.3560282270735233e-08</v>
       </c>
       <c r="AH4">
-        <v>9.6154898530007683e-09</v>
+        <v>-9.8789553017018076e-09</v>
       </c>
       <c r="AI4">
-        <v>3.2688604033339336e-06</v>
+        <v>2.4101841408793162e-06</v>
       </c>
     </row>
     <row r="5">
@@ -4766,106 +4766,106 @@
         <v>32</v>
       </c>
       <c r="B5">
-        <v>0.03569393055445818</v>
+        <v>0.016990081193109886</v>
       </c>
       <c r="C5">
-        <v>2.3514888390001136e-05</v>
+        <v>1.7601772434195182e-05</v>
       </c>
       <c r="D5">
-        <v>-1.1131506836735371e-05</v>
+        <v>-4.8322411429239144e-06</v>
       </c>
       <c r="E5">
-        <v>1.3253998648093149e-07</v>
+        <v>5.4897828747911303e-08</v>
       </c>
       <c r="F5">
-        <v>0.004318747431300919</v>
+        <v>0.0032753876282476087</v>
       </c>
       <c r="G5">
-        <v>0.0033302585050640609</v>
+        <v>0.0025060621319671411</v>
       </c>
       <c r="H5">
-        <v>0.0033491861273780496</v>
+        <v>0.0025183613321627194</v>
       </c>
       <c r="I5">
-        <v>0.0033330570069508318</v>
+        <v>0.0025078561469495286</v>
       </c>
       <c r="J5">
-        <v>5.5261577523229785e-06</v>
+        <v>1.0441632202006488e-05</v>
       </c>
       <c r="K5">
-        <v>1.9946374018930971e-05</v>
+        <v>1.2780744562305172e-05</v>
       </c>
       <c r="L5">
-        <v>-5.5644572274199299e-06</v>
+        <v>-4.1921918042736863e-06</v>
       </c>
       <c r="M5">
-        <v>-6.8724727429687058e-05</v>
+        <v>-1.6654925238770426e-05</v>
       </c>
       <c r="N5">
-        <v>-2.221052676966873e-05</v>
+        <v>-1.7393331160956826e-05</v>
       </c>
       <c r="O5">
-        <v>-2.6264729022641535e-06</v>
+        <v>-1.0381919715457988e-05</v>
       </c>
       <c r="P5">
-        <v>6.2568237371362192e-05</v>
+        <v>1.5451374548412723e-05</v>
       </c>
       <c r="Q5">
-        <v>3.4086789976513036e-05</v>
+        <v>-1.6462071217785649e-05</v>
       </c>
       <c r="R5">
-        <v>9.2686772673516125e-05</v>
+        <v>2.7511439242178248e-05</v>
       </c>
       <c r="S5">
-        <v>7.234623004049234e-05</v>
+        <v>1.4456196281646683e-05</v>
       </c>
       <c r="T5">
-        <v>0.00010735315558156209</v>
+        <v>7.2319497612602108e-05</v>
       </c>
       <c r="U5">
-        <v>0.00013435923948253528</v>
+        <v>8.6116183005344616e-05</v>
       </c>
       <c r="V5">
-        <v>3.649228354062322e-05</v>
+        <v>3.9381120078241195e-05</v>
       </c>
       <c r="W5">
-        <v>1.396123948230936e-06</v>
+        <v>-2.3705830900374821e-05</v>
       </c>
       <c r="X5">
-        <v>-1.148587195645874e-05</v>
+        <v>-3.3536093379019387e-05</v>
       </c>
       <c r="Y5">
-        <v>5.9715548943519012e-05</v>
+        <v>3.1718669050096599e-05</v>
       </c>
       <c r="Z5">
-        <v>-5.6077131279566074e-05</v>
+        <v>-5.1834310924630395e-05</v>
       </c>
       <c r="AA5">
-        <v>-3.2613800962478764e-05</v>
+        <v>-3.7256828155836277e-05</v>
       </c>
       <c r="AB5">
-        <v>-4.3719027208413697e-05</v>
+        <v>-4.3119877050201987e-05</v>
       </c>
       <c r="AC5">
-        <v>-9.434248749252863e-05</v>
+        <v>-7.7778989518010634e-05</v>
       </c>
       <c r="AD5">
-        <v>1.0024030448895545e-05</v>
+        <v>-1.8384535306178919e-06</v>
       </c>
       <c r="AE5">
-        <v>-5.3170062463804915e-06</v>
+        <v>-1.8419200261227565e-05</v>
       </c>
       <c r="AF5">
-        <v>-2.1296604221588067e-06</v>
+        <v>-1.2536112130698041e-07</v>
       </c>
       <c r="AG5">
-        <v>1.3101660560370029e-05</v>
+        <v>-1.6968138335860146e-05</v>
       </c>
       <c r="AH5">
-        <v>-1.1459651114999712e-06</v>
+        <v>-3.163277299217046e-06</v>
       </c>
       <c r="AI5">
-        <v>-0.0031907660066190684</v>
+        <v>-0.0024347903066560409</v>
       </c>
     </row>
     <row r="6">
@@ -4873,106 +4873,106 @@
         <v>33</v>
       </c>
       <c r="B6">
-        <v>0.075534146507023808</v>
+        <v>0.023034392710275145</v>
       </c>
       <c r="C6">
-        <v>-2.1657825642411691e-05</v>
+        <v>-1.490817548300548e-05</v>
       </c>
       <c r="D6">
-        <v>-1.0449882433668442e-05</v>
+        <v>-4.5870197709802075e-06</v>
       </c>
       <c r="E6">
-        <v>1.187290474665369e-07</v>
+        <v>4.8509377529350295e-08</v>
       </c>
       <c r="F6">
-        <v>0.0033302585050640609</v>
+        <v>0.0025060621319671411</v>
       </c>
       <c r="G6">
-        <v>0.0036905918227806895</v>
+        <v>0.0027737642581545921</v>
       </c>
       <c r="H6">
-        <v>0.0034448815958518669</v>
+        <v>0.0025800678806974053</v>
       </c>
       <c r="I6">
-        <v>0.003444307874982767</v>
+        <v>0.0025837486740412129</v>
       </c>
       <c r="J6">
-        <v>-3.7918598515992476e-05</v>
+        <v>-8.3244767404608939e-06</v>
       </c>
       <c r="K6">
-        <v>1.6091835103031221e-05</v>
+        <v>1.2346989523060137e-05</v>
       </c>
       <c r="L6">
-        <v>-6.328648311897491e-06</v>
+        <v>-4.5552460465075425e-06</v>
       </c>
       <c r="M6">
-        <v>-2.4333501048798886e-05</v>
+        <v>2.6813406474502808e-07</v>
       </c>
       <c r="N6">
-        <v>1.2426357628698525e-05</v>
+        <v>9.3865545268970109e-06</v>
       </c>
       <c r="O6">
-        <v>2.7402438157772373e-05</v>
+        <v>5.0526528036755011e-06</v>
       </c>
       <c r="P6">
-        <v>3.0600985372090765e-05</v>
+        <v>1.6942264189230539e-06</v>
       </c>
       <c r="Q6">
-        <v>0.00011215392557799037</v>
+        <v>5.0933515410422209e-05</v>
       </c>
       <c r="R6">
-        <v>0.00010674103557494451</v>
+        <v>4.1964274798717439e-05</v>
       </c>
       <c r="S6">
-        <v>0.00010523337934325834</v>
+        <v>4.6691616419018874e-05</v>
       </c>
       <c r="T6">
-        <v>6.506798789906185e-05</v>
+        <v>6.1135750738960503e-05</v>
       </c>
       <c r="U6">
-        <v>0.00011380341857671148</v>
+        <v>9.7678731807014207e-05</v>
       </c>
       <c r="V6">
-        <v>6.7121795603022763e-05</v>
+        <v>8.3261361007281199e-05</v>
       </c>
       <c r="W6">
-        <v>3.240480365034445e-05</v>
+        <v>9.8725724469550351e-06</v>
       </c>
       <c r="X6">
-        <v>3.6184796380715366e-05</v>
+        <v>1.1602479155745776e-05</v>
       </c>
       <c r="Y6">
-        <v>0.00011715946216607118</v>
+        <v>8.6282675976143792e-05</v>
       </c>
       <c r="Z6">
-        <v>-3.2391368146266614e-05</v>
+        <v>-2.3694207330035404e-05</v>
       </c>
       <c r="AA6">
-        <v>-3.342869865768038e-05</v>
+        <v>-2.6420656955067042e-05</v>
       </c>
       <c r="AB6">
-        <v>-3.4709028774606351e-05</v>
+        <v>-2.4660131683162771e-05</v>
       </c>
       <c r="AC6">
-        <v>-9.5431062887091789e-05</v>
+        <v>-7.3953676822698881e-05</v>
       </c>
       <c r="AD6">
-        <v>-4.4670324184873517e-07</v>
+        <v>-1.3619129778063492e-05</v>
       </c>
       <c r="AE6">
-        <v>1.5892475574857154e-06</v>
+        <v>-4.6261090988816548e-06</v>
       </c>
       <c r="AF6">
-        <v>-4.9904075742537298e-06</v>
+        <v>-2.8987659844247721e-06</v>
       </c>
       <c r="AG6">
-        <v>2.3560435616849611e-05</v>
+        <v>2.3488971895614663e-06</v>
       </c>
       <c r="AH6">
-        <v>5.04504162779848e-05</v>
+        <v>5.6548310784992374e-05</v>
       </c>
       <c r="AI6">
-        <v>-0.003264930078864586</v>
+        <v>-0.0025068716653706587</v>
       </c>
     </row>
     <row r="7">
@@ -4980,106 +4980,106 @@
         <v>34</v>
       </c>
       <c r="B7">
-        <v>0.099579576065623399</v>
+        <v>0.044455828266261953</v>
       </c>
       <c r="C7">
-        <v>-1.4229050579139729e-05</v>
+        <v>-2.8763485953285989e-06</v>
       </c>
       <c r="D7">
-        <v>-1.2208783486304137e-05</v>
+        <v>-7.855583864556253e-06</v>
       </c>
       <c r="E7">
-        <v>1.6448313864879601e-07</v>
+        <v>1.0103065565266212e-07</v>
       </c>
       <c r="F7">
-        <v>0.0033491861273780496</v>
+        <v>0.0025183613321627194</v>
       </c>
       <c r="G7">
-        <v>0.0034448815958518669</v>
+        <v>0.0025800678806974053</v>
       </c>
       <c r="H7">
-        <v>0.0036636700724075187</v>
+        <v>0.002737060003854637</v>
       </c>
       <c r="I7">
-        <v>0.0035773197663790421</v>
+        <v>0.0026671012710242741</v>
       </c>
       <c r="J7">
-        <v>-4.4606874437227474e-05</v>
+        <v>-1.5508708249053821e-05</v>
       </c>
       <c r="K7">
-        <v>1.3292267483377781e-05</v>
+        <v>6.2938293980314443e-06</v>
       </c>
       <c r="L7">
-        <v>-4.6114483418551445e-06</v>
+        <v>-2.4100736421399857e-06</v>
       </c>
       <c r="M7">
-        <v>-5.4849531344481478e-06</v>
+        <v>7.655752822538595e-06</v>
       </c>
       <c r="N7">
-        <v>1.6768692062677903e-05</v>
+        <v>4.2859539845740394e-06</v>
       </c>
       <c r="O7">
-        <v>5.8139325118979502e-05</v>
+        <v>2.0651020696011693e-05</v>
       </c>
       <c r="P7">
-        <v>-6.8756435468558244e-06</v>
+        <v>-1.0737971898872799e-05</v>
       </c>
       <c r="Q7">
-        <v>0.00012172266110459327</v>
+        <v>6.7345411768237901e-05</v>
       </c>
       <c r="R7">
-        <v>9.4734495009401488e-05</v>
+        <v>4.35244828016065e-05</v>
       </c>
       <c r="S7">
-        <v>7.388652170449081e-05</v>
+        <v>3.690571616251628e-05</v>
       </c>
       <c r="T7">
-        <v>6.3292858309631217e-05</v>
+        <v>1.7097488510219461e-05</v>
       </c>
       <c r="U7">
-        <v>0.00014956025952320585</v>
+        <v>9.7737619638381271e-05</v>
       </c>
       <c r="V7">
-        <v>6.0869248048411742e-05</v>
+        <v>3.8233718438623193e-05</v>
       </c>
       <c r="W7">
-        <v>1.4386862176733667e-05</v>
+        <v>-8.5563527611985386e-06</v>
       </c>
       <c r="X7">
-        <v>2.9644530535361414e-05</v>
+        <v>6.5853044540289691e-06</v>
       </c>
       <c r="Y7">
-        <v>0.00014344774122373918</v>
+        <v>9.836435578030071e-05</v>
       </c>
       <c r="Z7">
-        <v>-7.1874354112027878e-05</v>
+        <v>-7.6247231313643794e-05</v>
       </c>
       <c r="AA7">
-        <v>-8.9556933801142932e-05</v>
+        <v>-9.1057264796521155e-05</v>
       </c>
       <c r="AB7">
-        <v>-9.6477235923793717e-05</v>
+        <v>-9.1372038908214153e-05</v>
       </c>
       <c r="AC7">
-        <v>-0.00014693418837219137</v>
+        <v>-0.00013429476518331436</v>
       </c>
       <c r="AD7">
-        <v>-5.8249228400782897e-05</v>
+        <v>-6.8257765771505079e-05</v>
       </c>
       <c r="AE7">
-        <v>-4.207361399925628e-05</v>
+        <v>-4.7055995359580351e-05</v>
       </c>
       <c r="AF7">
-        <v>-3.8069441577882174e-06</v>
+        <v>-2.1202340239441037e-06</v>
       </c>
       <c r="AG7">
-        <v>-1.3115123110637311e-06</v>
+        <v>-2.752301032101466e-05</v>
       </c>
       <c r="AH7">
-        <v>1.1186649182695282e-05</v>
+        <v>6.1610761025077295e-06</v>
       </c>
       <c r="AI7">
-        <v>-0.0033820336201729473</v>
+        <v>-0.0024907840804877122</v>
       </c>
     </row>
     <row r="8">
@@ -5087,106 +5087,106 @@
         <v>63</v>
       </c>
       <c r="B8">
-        <v>0.10191902942700919</v>
+        <v>0.04749721078508385</v>
       </c>
       <c r="C8">
-        <v>-6.7355800366263385e-05</v>
+        <v>-4.6281657879378537e-05</v>
       </c>
       <c r="D8">
-        <v>5.1034531149174217e-06</v>
+        <v>8.1667961682356852e-06</v>
       </c>
       <c r="E8">
-        <v>3.1527165226505297e-08</v>
+        <v>-2.2507369047811773e-08</v>
       </c>
       <c r="F8">
-        <v>0.0033330570069508318</v>
+        <v>0.0025078561469495286</v>
       </c>
       <c r="G8">
-        <v>0.003444307874982767</v>
+        <v>0.0025837486740412129</v>
       </c>
       <c r="H8">
-        <v>0.0035773197663790421</v>
+        <v>0.0026671012710242741</v>
       </c>
       <c r="I8">
-        <v>0.0041372324445851458</v>
+        <v>0.0031113251052543884</v>
       </c>
       <c r="J8">
-        <v>-0.00015795130210541613</v>
+        <v>-4.0007141896878035e-05</v>
       </c>
       <c r="K8">
-        <v>5.6290379254348058e-06</v>
+        <v>1.1836322680258097e-06</v>
       </c>
       <c r="L8">
-        <v>-1.7160491198794399e-05</v>
+        <v>-1.0576376631313277e-05</v>
       </c>
       <c r="M8">
-        <v>8.2831097415042186e-05</v>
+        <v>2.3057124559346988e-05</v>
       </c>
       <c r="N8">
-        <v>6.1195803712241507e-05</v>
+        <v>4.1849089375644254e-05</v>
       </c>
       <c r="O8">
-        <v>0.00019333505088077983</v>
+        <v>3.8196819185115681e-05</v>
       </c>
       <c r="P8">
-        <v>-0.00010390538640871693</v>
+        <v>-2.4508959900644691e-05</v>
       </c>
       <c r="Q8">
-        <v>0.0002252244350126123</v>
+        <v>0.00013209345152957091</v>
       </c>
       <c r="R8">
-        <v>0.00022811049602714829</v>
+        <v>0.00012728769464689796</v>
       </c>
       <c r="S8">
-        <v>0.00013170444398262395</v>
+        <v>6.5374092568053471e-05</v>
       </c>
       <c r="T8">
-        <v>-0.00013543921931975181</v>
+        <v>-8.2717081325280224e-05</v>
       </c>
       <c r="U8">
-        <v>-6.0851686910935905e-05</v>
+        <v>-5.4794783141643485e-05</v>
       </c>
       <c r="V8">
-        <v>-0.00012846647571950452</v>
+        <v>-9.1353798657312774e-05</v>
       </c>
       <c r="W8">
-        <v>2.8852205235416919e-06</v>
+        <v>-1.1666824654228198e-05</v>
       </c>
       <c r="X8">
-        <v>7.5507397100281742e-05</v>
+        <v>4.6188312691185078e-05</v>
       </c>
       <c r="Y8">
-        <v>0.00013852717240664609</v>
+        <v>0.00010371067588002786</v>
       </c>
       <c r="Z8">
-        <v>-6.0315393916438552e-06</v>
+        <v>1.1164296909034824e-05</v>
       </c>
       <c r="AA8">
-        <v>-5.561515106820218e-05</v>
+        <v>-2.9495735676815082e-05</v>
       </c>
       <c r="AB8">
-        <v>-7.6338942696981579e-05</v>
+        <v>-4.0220255936107693e-05</v>
       </c>
       <c r="AC8">
-        <v>-9.1646211952361393e-05</v>
+        <v>-5.789279880685479e-05</v>
       </c>
       <c r="AD8">
-        <v>4.7353825128320683e-05</v>
+        <v>4.768166417012964e-05</v>
       </c>
       <c r="AE8">
-        <v>-1.1162008556380321e-05</v>
+        <v>6.7545297397632689e-06</v>
       </c>
       <c r="AF8">
-        <v>-1.5413697275998045e-06</v>
+        <v>-2.5183170442093184e-07</v>
       </c>
       <c r="AG8">
-        <v>0.00017685683753167463</v>
+        <v>9.3093959670792308e-05</v>
       </c>
       <c r="AH8">
-        <v>6.4684847934265953e-05</v>
+        <v>3.5675842478548499e-05</v>
       </c>
       <c r="AI8">
-        <v>-0.0039016022318896365</v>
+        <v>-0.0029982245594123175</v>
       </c>
     </row>
     <row r="9">
@@ -5194,106 +5194,106 @@
         <v>64</v>
       </c>
       <c r="B9">
-        <v>1.5180195216091639</v>
+        <v>0.6248277955240169</v>
       </c>
       <c r="C9">
-        <v>4.159705099024866e-05</v>
+        <v>7.4873669564022607e-06</v>
       </c>
       <c r="D9">
-        <v>-4.4936032629895562e-06</v>
+        <v>-4.8127730407201622e-07</v>
       </c>
       <c r="E9">
-        <v>3.932745064176556e-08</v>
+        <v>3.3314865379650852e-09</v>
       </c>
       <c r="F9">
-        <v>5.5261577523229785e-06</v>
+        <v>1.0441632202006488e-05</v>
       </c>
       <c r="G9">
-        <v>-3.7918598515992476e-05</v>
+        <v>-8.3244767404608939e-06</v>
       </c>
       <c r="H9">
-        <v>-4.4606874437227474e-05</v>
+        <v>-1.5508708249053821e-05</v>
       </c>
       <c r="I9">
-        <v>-0.00015795130210541613</v>
+        <v>-4.0007141896878035e-05</v>
       </c>
       <c r="J9">
-        <v>0.00064178782738026142</v>
+        <v>7.7042335273389833e-05</v>
       </c>
       <c r="K9">
-        <v>-2.3086048402090315e-05</v>
+        <v>-2.4442730153099527e-06</v>
       </c>
       <c r="L9">
-        <v>7.3811694050690362e-06</v>
+        <v>-1.2438598104645486e-06</v>
       </c>
       <c r="M9">
-        <v>-0.00045982538474761628</v>
+        <v>-6.5096680805900128e-05</v>
       </c>
       <c r="N9">
-        <v>-2.3347955927411466e-05</v>
+        <v>-3.122888310336402e-06</v>
       </c>
       <c r="O9">
-        <v>-0.00063916565257824678</v>
+        <v>-7.5920632807978535e-05</v>
       </c>
       <c r="P9">
-        <v>0.00043986487685248341</v>
+        <v>6.3305209309768443e-05</v>
       </c>
       <c r="Q9">
-        <v>-0.00028121560836039735</v>
+        <v>-4.53730621217587e-05</v>
       </c>
       <c r="R9">
-        <v>-0.00028120091219737076</v>
+        <v>-4.4683056230358801e-05</v>
       </c>
       <c r="S9">
-        <v>-0.00024159070326182217</v>
+        <v>-4.337675529428107e-05</v>
       </c>
       <c r="T9">
-        <v>-5.9662954073992389e-05</v>
+        <v>-1.2158462172536947e-05</v>
       </c>
       <c r="U9">
-        <v>-9.3223257890432193e-05</v>
+        <v>-2.7260263517076077e-05</v>
       </c>
       <c r="V9">
-        <v>-0.00012104402601295762</v>
+        <v>-2.7004610335824979e-05</v>
       </c>
       <c r="W9">
-        <v>2.2253769112660799e-05</v>
+        <v>2.7620788434536656e-06</v>
       </c>
       <c r="X9">
-        <v>-5.9665466520087527e-05</v>
+        <v>-1.8224339906499334e-05</v>
       </c>
       <c r="Y9">
-        <v>-5.816469041652558e-05</v>
+        <v>-2.1306315218930899e-05</v>
       </c>
       <c r="Z9">
-        <v>8.5149803357657992e-06</v>
+        <v>7.2757498058676063e-06</v>
       </c>
       <c r="AA9">
-        <v>7.7232169495954248e-06</v>
+        <v>6.9017503300158681e-06</v>
       </c>
       <c r="AB9">
-        <v>-9.9065126713600744e-06</v>
+        <v>2.632259753434833e-06</v>
       </c>
       <c r="AC9">
-        <v>9.5318444476418823e-06</v>
+        <v>8.3152163847382398e-06</v>
       </c>
       <c r="AD9">
-        <v>-7.4128590388704578e-05</v>
+        <v>-9.1512358603782229e-06</v>
       </c>
       <c r="AE9">
-        <v>-3.4362991330363968e-06</v>
+        <v>8.0240392261744832e-06</v>
       </c>
       <c r="AF9">
-        <v>-1.2655894037201618e-06</v>
+        <v>-6.6831626087156612e-07</v>
       </c>
       <c r="AG9">
-        <v>-0.00016898574867744656</v>
+        <v>-3.0264472768573137e-05</v>
       </c>
       <c r="AH9">
-        <v>-8.3200465864430545e-05</v>
+        <v>-2.1851970220350368e-05</v>
       </c>
       <c r="AI9">
-        <v>0.00037411143719150966</v>
+        <v>8.019374920288896e-05</v>
       </c>
     </row>
     <row r="10">
@@ -5301,106 +5301,106 @@
         <v>36</v>
       </c>
       <c r="B10">
-        <v>0.019864871028473223</v>
+        <v>0.021324138692213734</v>
       </c>
       <c r="C10">
-        <v>-2.1122839431273256e-05</v>
+        <v>-1.5208566547023861e-05</v>
       </c>
       <c r="D10">
-        <v>-2.9196896116809199e-06</v>
+        <v>-2.1040436555915697e-06</v>
       </c>
       <c r="E10">
-        <v>5.446914133081583e-09</v>
+        <v>2.6175745309641719e-09</v>
       </c>
       <c r="F10">
-        <v>1.9946374018930971e-05</v>
+        <v>1.2780744562305172e-05</v>
       </c>
       <c r="G10">
-        <v>1.6091835103031221e-05</v>
+        <v>1.2346989523060137e-05</v>
       </c>
       <c r="H10">
-        <v>1.3292267483377781e-05</v>
+        <v>6.2938293980314443e-06</v>
       </c>
       <c r="I10">
-        <v>5.6290379254348058e-06</v>
+        <v>1.1836322680258097e-06</v>
       </c>
       <c r="J10">
-        <v>-2.3086048402090315e-05</v>
+        <v>-2.4442730153099527e-06</v>
       </c>
       <c r="K10">
-        <v>0.00033512445474611854</v>
+        <v>0.0002541622921735693</v>
       </c>
       <c r="L10">
-        <v>-2.5254455305878726e-05</v>
+        <v>-2.0429203728817576e-05</v>
       </c>
       <c r="M10">
-        <v>1.0395485362990614e-05</v>
+        <v>-1.3639714086494223e-06</v>
       </c>
       <c r="N10">
-        <v>1.7986021986654278e-05</v>
+        <v>1.3463637768981388e-05</v>
       </c>
       <c r="O10">
-        <v>2.3619129366459282e-05</v>
+        <v>2.7466930257796166e-06</v>
       </c>
       <c r="P10">
-        <v>-9.4033853972996361e-06</v>
+        <v>1.2614631502436618e-06</v>
       </c>
       <c r="Q10">
-        <v>0.00011245365347632881</v>
+        <v>8.8838302483919577e-05</v>
       </c>
       <c r="R10">
-        <v>8.4701074168258951e-05</v>
+        <v>6.2896581643416809e-05</v>
       </c>
       <c r="S10">
-        <v>1.2075251853831039e-05</v>
+        <v>9.5007338137436705e-06</v>
       </c>
       <c r="T10">
-        <v>0.0024972211811194393</v>
+        <v>0.0018872080951591495</v>
       </c>
       <c r="U10">
-        <v>0.0025423143104802422</v>
+        <v>0.0019220082482929528</v>
       </c>
       <c r="V10">
-        <v>0.002568404299279205</v>
+        <v>0.0019437705410297766</v>
       </c>
       <c r="W10">
-        <v>-2.8229001594775981e-05</v>
+        <v>-1.9221651197954986e-05</v>
       </c>
       <c r="X10">
-        <v>2.2909570554582198e-06</v>
+        <v>7.4496682716483891e-06</v>
       </c>
       <c r="Y10">
-        <v>4.6191887562013366e-05</v>
+        <v>5.5120278635650984e-05</v>
       </c>
       <c r="Z10">
-        <v>9.418187349832124e-06</v>
+        <v>2.1383848145603915e-05</v>
       </c>
       <c r="AA10">
-        <v>-1.9276415664130865e-05</v>
+        <v>4.0595445390421633e-06</v>
       </c>
       <c r="AB10">
-        <v>-2.7012175418189175e-05</v>
+        <v>-2.5227767774379725e-06</v>
       </c>
       <c r="AC10">
-        <v>7.8577577430050637e-06</v>
+        <v>2.1739266659929926e-05</v>
       </c>
       <c r="AD10">
-        <v>-1.7723351807230679e-05</v>
+        <v>2.4285883841762448e-06</v>
       </c>
       <c r="AE10">
-        <v>1.1960281701943796e-05</v>
+        <v>1.3038864400544787e-05</v>
       </c>
       <c r="AF10">
-        <v>8.2590497641914012e-07</v>
+        <v>8.397996004587753e-07</v>
       </c>
       <c r="AG10">
-        <v>1.6152553236027049e-05</v>
+        <v>8.9231783656214085e-06</v>
       </c>
       <c r="AH10">
-        <v>3.0176125816626896e-05</v>
+        <v>9.3125405626924085e-06</v>
       </c>
       <c r="AI10">
-        <v>-0.0024598768867113464</v>
+        <v>-0.00187831800198429</v>
       </c>
     </row>
     <row r="11">
@@ -5408,106 +5408,106 @@
         <v>37</v>
       </c>
       <c r="B11">
-        <v>0.0067999473075663905</v>
+        <v>0.0074296143127429177</v>
       </c>
       <c r="C11">
-        <v>-7.1611176054830783e-07</v>
+        <v>-4.0111230732168969e-07</v>
       </c>
       <c r="D11">
-        <v>-6.6962297367110984e-07</v>
+        <v>-8.6176110047960581e-07</v>
       </c>
       <c r="E11">
-        <v>8.5263708724293891e-09</v>
+        <v>9.4811688437675025e-09</v>
       </c>
       <c r="F11">
-        <v>-5.5644572274199299e-06</v>
+        <v>-4.1921918042736863e-06</v>
       </c>
       <c r="G11">
-        <v>-6.328648311897491e-06</v>
+        <v>-4.5552460465075425e-06</v>
       </c>
       <c r="H11">
-        <v>-4.6114483418551445e-06</v>
+        <v>-2.4100736421399857e-06</v>
       </c>
       <c r="I11">
-        <v>-1.7160491198794399e-05</v>
+        <v>-1.0576376631313277e-05</v>
       </c>
       <c r="J11">
-        <v>7.3811694050690362e-06</v>
+        <v>-1.2438598104645486e-06</v>
       </c>
       <c r="K11">
-        <v>-2.5254455305878726e-05</v>
+        <v>-2.0429203728817576e-05</v>
       </c>
       <c r="L11">
-        <v>2.1754716653805837e-05</v>
+        <v>1.7527365325024938e-05</v>
       </c>
       <c r="M11">
-        <v>-4.0715320172183104e-06</v>
+        <v>2.2714633045317487e-06</v>
       </c>
       <c r="N11">
-        <v>8.4221969913879455e-07</v>
+        <v>5.0481052890735936e-07</v>
       </c>
       <c r="O11">
-        <v>-8.418638274399032e-06</v>
+        <v>1.094630901900406e-06</v>
       </c>
       <c r="P11">
-        <v>4.6374156606388902e-06</v>
+        <v>-2.1465462890232318e-06</v>
       </c>
       <c r="Q11">
-        <v>-8.4233950044148215e-06</v>
+        <v>-5.2446072122630411e-06</v>
       </c>
       <c r="R11">
-        <v>-2.4807567488618741e-05</v>
+        <v>-1.8481287009426216e-05</v>
       </c>
       <c r="S11">
-        <v>-1.1985930145395562e-05</v>
+        <v>-6.0486556435260163e-06</v>
       </c>
       <c r="T11">
-        <v>-4.933522852928612e-05</v>
+        <v>-4.1690923457297036e-05</v>
       </c>
       <c r="U11">
-        <v>-6.637102713381732e-05</v>
+        <v>-4.9678699126256522e-05</v>
       </c>
       <c r="V11">
-        <v>-5.8997845047084071e-05</v>
+        <v>-4.723236331971339e-05</v>
       </c>
       <c r="W11">
-        <v>2.1549592304919692e-07</v>
+        <v>9.2883273672897568e-09</v>
       </c>
       <c r="X11">
-        <v>2.8208978696641841e-06</v>
+        <v>3.5352631715359018e-06</v>
       </c>
       <c r="Y11">
-        <v>8.6033118555267458e-06</v>
+        <v>3.9968723023051736e-06</v>
       </c>
       <c r="Z11">
-        <v>-5.8983953549960456e-06</v>
+        <v>-9.6109704479998775e-06</v>
       </c>
       <c r="AA11">
-        <v>-8.370704189693698e-06</v>
+        <v>-1.1695178700563376e-05</v>
       </c>
       <c r="AB11">
-        <v>-4.4093195581566065e-06</v>
+        <v>-8.7266002255603918e-06</v>
       </c>
       <c r="AC11">
-        <v>-7.1575627419663402e-06</v>
+        <v>-1.0450915284128772e-05</v>
       </c>
       <c r="AD11">
-        <v>-1.0905681299324917e-05</v>
+        <v>-1.2277464137015223e-05</v>
       </c>
       <c r="AE11">
-        <v>-5.2561162497527967e-06</v>
+        <v>-9.1444009299757552e-06</v>
       </c>
       <c r="AF11">
-        <v>-2.708817252856624e-07</v>
+        <v>-1.7756947047362303e-07</v>
       </c>
       <c r="AG11">
-        <v>-5.157916866126524e-06</v>
+        <v>2.7865441998081248e-06</v>
       </c>
       <c r="AH11">
-        <v>-7.1369518895646625e-06</v>
+        <v>-4.8713737517581206e-06</v>
       </c>
       <c r="AI11">
-        <v>8.0841463138480685e-05</v>
+        <v>7.2341622901808439e-05</v>
       </c>
     </row>
     <row r="12">
@@ -5515,106 +5515,106 @@
         <v>65</v>
       </c>
       <c r="B12">
-        <v>0.6531478238810513</v>
+        <v>0.23595020672705081</v>
       </c>
       <c r="C12">
-        <v>-3.2212234831237209e-05</v>
+        <v>-4.2896352715254841e-06</v>
       </c>
       <c r="D12">
-        <v>1.6047034429475957e-06</v>
+        <v>-3.8982039267731415e-07</v>
       </c>
       <c r="E12">
-        <v>-2.1576164477011495e-08</v>
+        <v>2.4439494548659494e-09</v>
       </c>
       <c r="F12">
-        <v>-6.8724727429687058e-05</v>
+        <v>-1.6654925238770426e-05</v>
       </c>
       <c r="G12">
-        <v>-2.4333501048798886e-05</v>
+        <v>2.6813406474502808e-07</v>
       </c>
       <c r="H12">
-        <v>-5.4849531344481478e-06</v>
+        <v>7.655752822538595e-06</v>
       </c>
       <c r="I12">
-        <v>8.2831097415042186e-05</v>
+        <v>2.3057124559346988e-05</v>
       </c>
       <c r="J12">
-        <v>-0.00045982538474761628</v>
+        <v>-6.5096680805900128e-05</v>
       </c>
       <c r="K12">
-        <v>1.0395485362990614e-05</v>
+        <v>-1.3639714086494223e-06</v>
       </c>
       <c r="L12">
-        <v>-4.0715320172183104e-06</v>
+        <v>2.2714633045317487e-06</v>
       </c>
       <c r="M12">
-        <v>0.00063883565286701439</v>
+        <v>7.5307071760238352e-05</v>
       </c>
       <c r="N12">
-        <v>9.4608499921825426e-06</v>
+        <v>-3.6634439352818961e-07</v>
       </c>
       <c r="O12">
-        <v>0.00045438385070667529</v>
+        <v>6.3710702773932295e-05</v>
       </c>
       <c r="P12">
-        <v>-0.00061142475532724656</v>
+        <v>-7.298279095239436e-05</v>
       </c>
       <c r="Q12">
-        <v>-0.00019866227728903326</v>
+        <v>-3.0928753385423572e-05</v>
       </c>
       <c r="R12">
-        <v>-0.00018411001790500124</v>
+        <v>-3.2786319386836512e-05</v>
       </c>
       <c r="S12">
-        <v>-0.0002257750330859217</v>
+        <v>-3.2591179853449747e-05</v>
       </c>
       <c r="T12">
-        <v>-3.6088427002290925e-05</v>
+        <v>-8.2752868392882915e-06</v>
       </c>
       <c r="U12">
-        <v>2.1954280476577358e-05</v>
+        <v>5.4532147123851329e-06</v>
       </c>
       <c r="V12">
-        <v>3.6938012733061165e-05</v>
+        <v>2.1209010254739871e-06</v>
       </c>
       <c r="W12">
-        <v>-2.3776958373916191e-05</v>
+        <v>-4.3790451813930481e-06</v>
       </c>
       <c r="X12">
-        <v>3.6866996768808093e-05</v>
+        <v>1.0492823791332157e-05</v>
       </c>
       <c r="Y12">
-        <v>-0.00019737655532720032</v>
+        <v>-3.5140046851827511e-05</v>
       </c>
       <c r="Z12">
-        <v>-5.2793343367700959e-05</v>
+        <v>-1.0553378979036472e-05</v>
       </c>
       <c r="AA12">
-        <v>-8.174737975831258e-05</v>
+        <v>-1.5697155095718355e-05</v>
       </c>
       <c r="AB12">
-        <v>-7.4798169395010197e-05</v>
+        <v>-1.7947351872157482e-05</v>
       </c>
       <c r="AC12">
-        <v>-6.6566042929599653e-05</v>
+        <v>-1.3303158559206591e-05</v>
       </c>
       <c r="AD12">
-        <v>-5.2188146467307259e-05</v>
+        <v>-1.1053181640752294e-05</v>
       </c>
       <c r="AE12">
-        <v>-5.4707719815161954e-05</v>
+        <v>-1.2242476380704357e-05</v>
       </c>
       <c r="AF12">
-        <v>4.5140438765156904e-06</v>
+        <v>1.1087454115216786e-06</v>
       </c>
       <c r="AG12">
-        <v>7.9398350037771e-05</v>
+        <v>1.290950570694912e-05</v>
       </c>
       <c r="AH12">
-        <v>5.0290009126370559e-05</v>
+        <v>1.3523503522019133e-05</v>
       </c>
       <c r="AI12">
-        <v>-0.00010912148249779828</v>
+        <v>-1.905461139721737e-05</v>
       </c>
     </row>
     <row r="13">
@@ -5622,106 +5622,106 @@
         <v>39</v>
       </c>
       <c r="B13">
-        <v>0.075677520889658234</v>
+        <v>0.045696865127133238</v>
       </c>
       <c r="C13">
-        <v>-0.00032709392055204717</v>
+        <v>-0.00024034260259612488</v>
       </c>
       <c r="D13">
-        <v>1.587768351397972e-06</v>
+        <v>3.1532069630658345e-07</v>
       </c>
       <c r="E13">
-        <v>-3.4959148584785588e-08</v>
+        <v>-1.7725946010885246e-08</v>
       </c>
       <c r="F13">
-        <v>-2.221052676966873e-05</v>
+        <v>-1.7393331160956826e-05</v>
       </c>
       <c r="G13">
-        <v>1.2426357628698525e-05</v>
+        <v>9.3865545268970109e-06</v>
       </c>
       <c r="H13">
-        <v>1.6768692062677903e-05</v>
+        <v>4.2859539845740394e-06</v>
       </c>
       <c r="I13">
-        <v>6.1195803712241507e-05</v>
+        <v>4.1849089375644254e-05</v>
       </c>
       <c r="J13">
-        <v>-2.3347955927411466e-05</v>
+        <v>-3.122888310336402e-06</v>
       </c>
       <c r="K13">
-        <v>1.7986021986654278e-05</v>
+        <v>1.3463637768981388e-05</v>
       </c>
       <c r="L13">
-        <v>8.4221969913879455e-07</v>
+        <v>5.0481052890735936e-07</v>
       </c>
       <c r="M13">
-        <v>9.4608499921825426e-06</v>
+        <v>-3.6634439352818961e-07</v>
       </c>
       <c r="N13">
-        <v>0.0074385457061766948</v>
+        <v>0.0054023609774367194</v>
       </c>
       <c r="O13">
-        <v>0.00012130999266770541</v>
+        <v>-0.00011392201719039749</v>
       </c>
       <c r="P13">
-        <v>0.0005783430327398031</v>
+        <v>0.00025355586642840188</v>
       </c>
       <c r="Q13">
-        <v>0.0044497253950711198</v>
+        <v>0.003143876566568251</v>
       </c>
       <c r="R13">
-        <v>0.0044441537076495424</v>
+        <v>0.0031367564315206318</v>
       </c>
       <c r="S13">
-        <v>0.0044151738506471444</v>
+        <v>0.0031138684658133182</v>
       </c>
       <c r="T13">
-        <v>0.00011822182869630467</v>
+        <v>0.00013469517750868939</v>
       </c>
       <c r="U13">
-        <v>3.3146942100654173e-05</v>
+        <v>2.0021917693776713e-05</v>
       </c>
       <c r="V13">
-        <v>0.00018222348271810547</v>
+        <v>0.00013139748255474302</v>
       </c>
       <c r="W13">
-        <v>-4.2543583907250739e-05</v>
+        <v>-3.3220939055277261e-05</v>
       </c>
       <c r="X13">
-        <v>-4.7090840577933713e-07</v>
+        <v>-9.1130213531504141e-06</v>
       </c>
       <c r="Y13">
-        <v>-0.00012331938187331941</v>
+        <v>-9.8619098376432311e-05</v>
       </c>
       <c r="Z13">
-        <v>6.3892697498914601e-05</v>
+        <v>0.00012401814429304544</v>
       </c>
       <c r="AA13">
-        <v>0.00011439383984365313</v>
+        <v>0.00016044528123872084</v>
       </c>
       <c r="AB13">
-        <v>0.00013461317724291501</v>
+        <v>0.00019725792838860698</v>
       </c>
       <c r="AC13">
-        <v>9.7898026577931821e-05</v>
+        <v>0.00014651550897268654</v>
       </c>
       <c r="AD13">
-        <v>7.1443082540535198e-05</v>
+        <v>0.00012474930381014453</v>
       </c>
       <c r="AE13">
-        <v>0.00012350157466021208</v>
+        <v>0.0001852813442095532</v>
       </c>
       <c r="AF13">
-        <v>-1.6835123396858036e-06</v>
+        <v>-5.421617844185672e-07</v>
       </c>
       <c r="AG13">
-        <v>6.7252230678467063e-05</v>
+        <v>3.2833001582458464e-05</v>
       </c>
       <c r="AH13">
-        <v>3.4368224754767647e-05</v>
+        <v>2.8941215185435436e-05</v>
       </c>
       <c r="AI13">
-        <v>-0.0044423224796542029</v>
+        <v>-0.003199411113164013</v>
       </c>
     </row>
     <row r="14">
@@ -5729,106 +5729,106 @@
         <v>66</v>
       </c>
       <c r="B14">
-        <v>-0.13662494003012624</v>
+        <v>-0.021116651853919446</v>
       </c>
       <c r="C14">
-        <v>-5.2614115386368898e-05</v>
+        <v>-1.0223419842135619e-05</v>
       </c>
       <c r="D14">
-        <v>4.7129042874799443e-06</v>
+        <v>-7.4091149670805026e-08</v>
       </c>
       <c r="E14">
-        <v>-3.8211111394579369e-08</v>
+        <v>2.2688116442150717e-09</v>
       </c>
       <c r="F14">
-        <v>-2.6264729022641535e-06</v>
+        <v>-1.0381919715457988e-05</v>
       </c>
       <c r="G14">
-        <v>2.7402438157772373e-05</v>
+        <v>5.0526528036755011e-06</v>
       </c>
       <c r="H14">
-        <v>5.8139325118979502e-05</v>
+        <v>2.0651020696011693e-05</v>
       </c>
       <c r="I14">
-        <v>0.00019333505088077983</v>
+        <v>3.8196819185115681e-05</v>
       </c>
       <c r="J14">
-        <v>-0.00063916565257824678</v>
+        <v>-7.5920632807978535e-05</v>
       </c>
       <c r="K14">
-        <v>2.3619129366459282e-05</v>
+        <v>2.7466930257796166e-06</v>
       </c>
       <c r="L14">
-        <v>-8.418638274399032e-06</v>
+        <v>1.094630901900406e-06</v>
       </c>
       <c r="M14">
-        <v>0.00045438385070667529</v>
+        <v>6.3710702773932295e-05</v>
       </c>
       <c r="N14">
-        <v>0.00012130999266770541</v>
+        <v>-0.00011392201719039749</v>
       </c>
       <c r="O14">
-        <v>0.01057464469854366</v>
+        <v>0.0012769543957204432</v>
       </c>
       <c r="P14">
-        <v>-0.0074848957076368372</v>
+        <v>-0.0010403094967339445</v>
       </c>
       <c r="Q14">
-        <v>0.0037722655307442371</v>
+        <v>0.00070658237498762351</v>
       </c>
       <c r="R14">
-        <v>0.0037716578152304607</v>
+        <v>0.00070660488532476575</v>
       </c>
       <c r="S14">
-        <v>0.0037326038703194338</v>
+        <v>0.00070660489949130642</v>
       </c>
       <c r="T14">
-        <v>6.799584020791556e-05</v>
+        <v>2.0022371290431254e-05</v>
       </c>
       <c r="U14">
-        <v>8.2907278544705921e-05</v>
+        <v>2.595289062499854e-05</v>
       </c>
       <c r="V14">
-        <v>0.00011489318579543873</v>
+        <v>2.6230948615721508e-05</v>
       </c>
       <c r="W14">
-        <v>-2.5224057276764082e-05</v>
+        <v>-3.8825774180729108e-06</v>
       </c>
       <c r="X14">
-        <v>6.0222017016385771e-05</v>
+        <v>1.7266261719943712e-05</v>
       </c>
       <c r="Y14">
-        <v>5.7313670718088842e-05</v>
+        <v>2.2703858386491338e-05</v>
       </c>
       <c r="Z14">
-        <v>-0.00011547568708166747</v>
+        <v>-4.1741491435329258e-05</v>
       </c>
       <c r="AA14">
-        <v>-9.553782629575147e-05</v>
+        <v>-3.7558632074420238e-05</v>
       </c>
       <c r="AB14">
-        <v>-0.00010038128288236559</v>
+        <v>-3.7989180969422463e-05</v>
       </c>
       <c r="AC14">
-        <v>-0.00012848653550902875</v>
+        <v>-4.6037538605574115e-05</v>
       </c>
       <c r="AD14">
-        <v>-4.7242070389820132e-05</v>
+        <v>-3.7540151969539556e-05</v>
       </c>
       <c r="AE14">
-        <v>-9.497152143127203e-05</v>
+        <v>-4.3420541572997698e-05</v>
       </c>
       <c r="AF14">
-        <v>-2.9833865790864454e-06</v>
+        <v>-7.1055333476091166e-07</v>
       </c>
       <c r="AG14">
-        <v>0.00017536319512749359</v>
+        <v>2.9504140180518852e-05</v>
       </c>
       <c r="AH14">
-        <v>0.00022196014127580637</v>
+        <v>3.4805187773936431e-05</v>
       </c>
       <c r="AI14">
-        <v>-0.0037023871339994029</v>
+        <v>-0.00066844723513465412</v>
       </c>
     </row>
     <row r="15">
@@ -5836,106 +5836,106 @@
         <v>67</v>
       </c>
       <c r="B15">
-        <v>0.042579154919832565</v>
+        <v>0.039770997714112993</v>
       </c>
       <c r="C15">
-        <v>3.3549356567971337e-05</v>
+        <v>4.576667820430703e-06</v>
       </c>
       <c r="D15">
-        <v>-2.2156869189074688e-06</v>
+        <v>2.7184789103790458e-07</v>
       </c>
       <c r="E15">
-        <v>2.4471266978375564e-08</v>
+        <v>-2.0261303533115006e-09</v>
       </c>
       <c r="F15">
-        <v>6.2568237371362192e-05</v>
+        <v>1.5451374548412723e-05</v>
       </c>
       <c r="G15">
-        <v>3.0600985372090765e-05</v>
+        <v>1.6942264189230539e-06</v>
       </c>
       <c r="H15">
-        <v>-6.8756435468558244e-06</v>
+        <v>-1.0737971898872799e-05</v>
       </c>
       <c r="I15">
-        <v>-0.00010390538640871693</v>
+        <v>-2.4508959900644691e-05</v>
       </c>
       <c r="J15">
-        <v>0.00043986487685248341</v>
+        <v>6.3305209309768443e-05</v>
       </c>
       <c r="K15">
-        <v>-9.4033853972996361e-06</v>
+        <v>1.2614631502436618e-06</v>
       </c>
       <c r="L15">
-        <v>4.6374156606388902e-06</v>
+        <v>-2.1465462890232318e-06</v>
       </c>
       <c r="M15">
-        <v>-0.00061142475532724656</v>
+        <v>-7.298279095239436e-05</v>
       </c>
       <c r="N15">
-        <v>0.0005783430327398031</v>
+        <v>0.00025355586642840188</v>
       </c>
       <c r="O15">
-        <v>-0.0074848957076368372</v>
+        <v>-0.0010403094967339445</v>
       </c>
       <c r="P15">
-        <v>0.009688435520830695</v>
+        <v>0.0012488559653919963</v>
       </c>
       <c r="Q15">
-        <v>0.0034900312782587726</v>
+        <v>0.0010167608927740242</v>
       </c>
       <c r="R15">
-        <v>0.0034798574403264483</v>
+        <v>0.001019554288409</v>
       </c>
       <c r="S15">
-        <v>0.0035207377562913172</v>
+        <v>0.001018056860376293</v>
       </c>
       <c r="T15">
-        <v>-2.8474912227118834e-05</v>
+        <v>-1.8396627539396591e-05</v>
       </c>
       <c r="U15">
-        <v>-1.0017500246774203e-05</v>
+        <v>-5.3823427814128568e-06</v>
       </c>
       <c r="V15">
-        <v>-2.4610251780634695e-05</v>
+        <v>-1.8199951561626254e-06</v>
       </c>
       <c r="W15">
-        <v>2.3697218473121755e-05</v>
+        <v>3.9921339113148423e-06</v>
       </c>
       <c r="X15">
-        <v>-3.7255878129687707e-05</v>
+        <v>-1.0195612902429526e-05</v>
       </c>
       <c r="Y15">
-        <v>0.00016661892369636234</v>
+        <v>2.316996492159111e-05</v>
       </c>
       <c r="Z15">
-        <v>8.6525314375642546e-05</v>
+        <v>2.8500856413521142e-05</v>
       </c>
       <c r="AA15">
-        <v>0.00010835578757822277</v>
+        <v>3.1628420065588504e-05</v>
       </c>
       <c r="AB15">
-        <v>8.8851153156342948e-05</v>
+        <v>3.4950511344949709e-05</v>
       </c>
       <c r="AC15">
-        <v>0.00010941218739209991</v>
+        <v>3.1764693548203232e-05</v>
       </c>
       <c r="AD15">
-        <v>6.8524030885496129e-05</v>
+        <v>2.9113856266219703e-05</v>
       </c>
       <c r="AE15">
-        <v>5.8228554816225743e-05</v>
+        <v>2.6371509084704827e-05</v>
       </c>
       <c r="AF15">
-        <v>-4.835728867982459e-06</v>
+        <v>-1.0920358114035344e-06</v>
       </c>
       <c r="AG15">
-        <v>-4.5397950292241571e-05</v>
+        <v>-5.9418637690063832e-06</v>
       </c>
       <c r="AH15">
-        <v>-0.00015119055836303815</v>
+        <v>-2.8616771146732921e-05</v>
       </c>
       <c r="AI15">
-        <v>-0.0031849625751416287</v>
+        <v>-0.00097849154912832176</v>
       </c>
     </row>
     <row r="16">
@@ -5943,106 +5943,106 @@
         <v>43</v>
       </c>
       <c r="B16">
-        <v>-0.27858390856768867</v>
+        <v>-0.041524420204073466</v>
       </c>
       <c r="C16">
-        <v>-0.00023316230487734562</v>
+        <v>-0.00018675253873414515</v>
       </c>
       <c r="D16">
-        <v>-2.4718436714475417e-05</v>
+        <v>-2.0730517857023458e-05</v>
       </c>
       <c r="E16">
-        <v>1.5717468542467302e-07</v>
+        <v>1.345105398685577e-07</v>
       </c>
       <c r="F16">
-        <v>3.4086789976513036e-05</v>
+        <v>-1.6462071217785649e-05</v>
       </c>
       <c r="G16">
-        <v>0.00011215392557799037</v>
+        <v>5.0933515410422209e-05</v>
       </c>
       <c r="H16">
-        <v>0.00012172266110459327</v>
+        <v>6.7345411768237901e-05</v>
       </c>
       <c r="I16">
-        <v>0.0002252244350126123</v>
+        <v>0.00013209345152957091</v>
       </c>
       <c r="J16">
-        <v>-0.00028121560836039735</v>
+        <v>-4.53730621217587e-05</v>
       </c>
       <c r="K16">
-        <v>0.00011245365347632881</v>
+        <v>8.8838302483919577e-05</v>
       </c>
       <c r="L16">
-        <v>-8.4233950044148215e-06</v>
+        <v>-5.2446072122630411e-06</v>
       </c>
       <c r="M16">
-        <v>-0.00019866227728903326</v>
+        <v>-3.0928753385423572e-05</v>
       </c>
       <c r="N16">
-        <v>0.0044497253950711198</v>
+        <v>0.003143876566568251</v>
       </c>
       <c r="O16">
-        <v>0.0037722655307442371</v>
+        <v>0.00070658237498762351</v>
       </c>
       <c r="P16">
-        <v>0.0034900312782587726</v>
+        <v>0.0010167608927740242</v>
       </c>
       <c r="Q16">
-        <v>0.016755690848965166</v>
+        <v>0.012008777553138766</v>
       </c>
       <c r="R16">
-        <v>0.016320488162909159</v>
+        <v>0.011695797723531931</v>
       </c>
       <c r="S16">
-        <v>0.016299966950468654</v>
+        <v>0.011669206246228572</v>
       </c>
       <c r="T16">
-        <v>0.003600202638976196</v>
+        <v>0.0029771787142031441</v>
       </c>
       <c r="U16">
-        <v>0.00067584595036841548</v>
+        <v>0.00054304833169308182</v>
       </c>
       <c r="V16">
-        <v>0.00084114758004532491</v>
+        <v>0.0006671776916946379</v>
       </c>
       <c r="W16">
-        <v>-4.4052120864641406e-05</v>
+        <v>-3.5816147462752225e-05</v>
       </c>
       <c r="X16">
-        <v>2.9757273650001578e-05</v>
+        <v>1.7291944555928923e-05</v>
       </c>
       <c r="Y16">
-        <v>0.00023147393001431062</v>
+        <v>0.0001220726888068787</v>
       </c>
       <c r="Z16">
-        <v>-1.4248406050923479e-05</v>
+        <v>6.6182500210149042e-05</v>
       </c>
       <c r="AA16">
-        <v>4.6359194890806775e-05</v>
+        <v>9.487294352295006e-05</v>
       </c>
       <c r="AB16">
-        <v>9.9282122083284253e-05</v>
+        <v>0.00015783475030169613</v>
       </c>
       <c r="AC16">
-        <v>-3.4653852526901445e-05</v>
+        <v>3.0762400758397104e-05</v>
       </c>
       <c r="AD16">
-        <v>6.5856619127423362e-05</v>
+        <v>0.00011287110516250659</v>
       </c>
       <c r="AE16">
-        <v>-4.8637700066664173e-07</v>
+        <v>7.3446356314997813e-05</v>
       </c>
       <c r="AF16">
-        <v>-4.2407887498384193e-06</v>
+        <v>-4.8402692097325375e-07</v>
       </c>
       <c r="AG16">
-        <v>0.00031659723868952827</v>
+        <v>0.00019026094556276463</v>
       </c>
       <c r="AH16">
-        <v>0.00019594872205736056</v>
+        <v>9.7376897196153021e-05</v>
       </c>
       <c r="AI16">
-        <v>-0.015825749025517082</v>
+        <v>-0.011551297423127107</v>
       </c>
     </row>
     <row r="17">
@@ -6050,106 +6050,106 @@
         <v>44</v>
       </c>
       <c r="B17">
-        <v>-0.21378754484854434</v>
+        <v>-0.0089967538258947082</v>
       </c>
       <c r="C17">
-        <v>-0.00023008438428831932</v>
+        <v>-0.00018151597747181135</v>
       </c>
       <c r="D17">
-        <v>-3.6741172482691127e-05</v>
+        <v>-2.9683770745107406e-05</v>
       </c>
       <c r="E17">
-        <v>2.9121799219837417e-07</v>
+        <v>2.3201903387752886e-07</v>
       </c>
       <c r="F17">
-        <v>9.2686772673516125e-05</v>
+        <v>2.7511439242178248e-05</v>
       </c>
       <c r="G17">
-        <v>0.00010674103557494451</v>
+        <v>4.1964274798717439e-05</v>
       </c>
       <c r="H17">
-        <v>9.4734495009401488e-05</v>
+        <v>4.35244828016065e-05</v>
       </c>
       <c r="I17">
-        <v>0.00022811049602714829</v>
+        <v>0.00012728769464689796</v>
       </c>
       <c r="J17">
-        <v>-0.00028120091219737076</v>
+        <v>-4.4683056230358801e-05</v>
       </c>
       <c r="K17">
-        <v>8.4701074168258951e-05</v>
+        <v>6.2896581643416809e-05</v>
       </c>
       <c r="L17">
-        <v>-2.4807567488618741e-05</v>
+        <v>-1.8481287009426216e-05</v>
       </c>
       <c r="M17">
-        <v>-0.00018411001790500124</v>
+        <v>-3.2786319386836512e-05</v>
       </c>
       <c r="N17">
-        <v>0.0044441537076495424</v>
+        <v>0.0031367564315206318</v>
       </c>
       <c r="O17">
-        <v>0.0037716578152304607</v>
+        <v>0.00070660488532476575</v>
       </c>
       <c r="P17">
-        <v>0.0034798574403264483</v>
+        <v>0.001019554288409</v>
       </c>
       <c r="Q17">
-        <v>0.016320488162909159</v>
+        <v>0.011695797723531931</v>
       </c>
       <c r="R17">
-        <v>0.016582958235566887</v>
+        <v>0.011894305970167749</v>
       </c>
       <c r="S17">
-        <v>0.016165211278795173</v>
+        <v>0.011579020506819346</v>
       </c>
       <c r="T17">
-        <v>0.0030999572069719526</v>
+        <v>0.0025435265004966432</v>
       </c>
       <c r="U17">
-        <v>0.00040240943404083913</v>
+        <v>0.00028300368417480751</v>
       </c>
       <c r="V17">
-        <v>0.0005256087312728345</v>
+        <v>0.00038790812345809115</v>
       </c>
       <c r="W17">
-        <v>-6.0744806840123128e-05</v>
+        <v>-5.1554931737010667e-05</v>
       </c>
       <c r="X17">
-        <v>-5.1193897151529874e-06</v>
+        <v>-1.7823892669612852e-05</v>
       </c>
       <c r="Y17">
-        <v>9.3570909470648382e-05</v>
+        <v>5.2840393465285705e-06</v>
       </c>
       <c r="Z17">
-        <v>9.9286993257364023e-06</v>
+        <v>6.7856582924429899e-05</v>
       </c>
       <c r="AA17">
-        <v>6.572844696292211e-05</v>
+        <v>0.00010159802617199822</v>
       </c>
       <c r="AB17">
-        <v>7.9839508586744285e-05</v>
+        <v>0.00013175722019482779</v>
       </c>
       <c r="AC17">
-        <v>1.0444425434076934e-05</v>
+        <v>5.4821079419653182e-05</v>
       </c>
       <c r="AD17">
-        <v>8.7148450729574757e-05</v>
+        <v>0.00011607455231191243</v>
       </c>
       <c r="AE17">
-        <v>3.6249155061806844e-05</v>
+        <v>9.5597050472739378e-05</v>
       </c>
       <c r="AF17">
-        <v>-8.6701134686602592e-06</v>
+        <v>-3.8478896559055505e-06</v>
       </c>
       <c r="AG17">
-        <v>0.0002879989900816636</v>
+        <v>0.00016438269767595284</v>
       </c>
       <c r="AH17">
-        <v>0.0001867011565983975</v>
+        <v>9.4695687023475111e-05</v>
       </c>
       <c r="AI17">
-        <v>-0.01502158810750011</v>
+        <v>-0.0108666916165113</v>
       </c>
     </row>
     <row r="18">
@@ -6157,106 +6157,106 @@
         <v>45</v>
       </c>
       <c r="B18">
-        <v>-0.1249114686515805</v>
+        <v>0.047190442355942955</v>
       </c>
       <c r="C18">
-        <v>-0.00019367918701796553</v>
+        <v>-0.00015507529010086275</v>
       </c>
       <c r="D18">
-        <v>-2.7618385373603016e-05</v>
+        <v>-2.1545048505077787e-05</v>
       </c>
       <c r="E18">
-        <v>2.2981023190497959e-07</v>
+        <v>1.7713008708386214e-07</v>
       </c>
       <c r="F18">
-        <v>7.234623004049234e-05</v>
+        <v>1.4456196281646683e-05</v>
       </c>
       <c r="G18">
-        <v>0.00010523337934325834</v>
+        <v>4.6691616419018874e-05</v>
       </c>
       <c r="H18">
-        <v>7.388652170449081e-05</v>
+        <v>3.690571616251628e-05</v>
       </c>
       <c r="I18">
-        <v>0.00013170444398262395</v>
+        <v>6.5374092568053471e-05</v>
       </c>
       <c r="J18">
-        <v>-0.00024159070326182217</v>
+        <v>-4.337675529428107e-05</v>
       </c>
       <c r="K18">
-        <v>1.2075251853831039e-05</v>
+        <v>9.5007338137436705e-06</v>
       </c>
       <c r="L18">
-        <v>-1.1985930145395562e-05</v>
+        <v>-6.0486556435260163e-06</v>
       </c>
       <c r="M18">
-        <v>-0.0002257750330859217</v>
+        <v>-3.2591179853449747e-05</v>
       </c>
       <c r="N18">
-        <v>0.0044151738506471444</v>
+        <v>0.0031138684658133182</v>
       </c>
       <c r="O18">
-        <v>0.0037326038703194338</v>
+        <v>0.00070660489949130642</v>
       </c>
       <c r="P18">
-        <v>0.0035207377562913172</v>
+        <v>0.001018056860376293</v>
       </c>
       <c r="Q18">
-        <v>0.016299966950468654</v>
+        <v>0.011669206246228572</v>
       </c>
       <c r="R18">
-        <v>0.016165211278795173</v>
+        <v>0.011579020506819346</v>
       </c>
       <c r="S18">
-        <v>0.016408465661292653</v>
+        <v>0.011747020299627424</v>
       </c>
       <c r="T18">
-        <v>0.0028197971898799128</v>
+        <v>0.002365847834919511</v>
       </c>
       <c r="U18">
-        <v>-2.5275215848472726e-05</v>
+        <v>-9.3612752841117433e-06</v>
       </c>
       <c r="V18">
-        <v>3.2504609520023686e-05</v>
+        <v>4.1114775312971023e-05</v>
       </c>
       <c r="W18">
-        <v>-6.731041884144413e-05</v>
+        <v>-5.4361942385244334e-05</v>
       </c>
       <c r="X18">
-        <v>-2.1592972747274189e-05</v>
+        <v>-1.6540941160553139e-05</v>
       </c>
       <c r="Y18">
-        <v>0.00021078688298528658</v>
+        <v>0.0001029112026425011</v>
       </c>
       <c r="Z18">
-        <v>-1.6892185388245676e-05</v>
+        <v>1.5977289439899484e-05</v>
       </c>
       <c r="AA18">
-        <v>4.3026856138298538e-05</v>
+        <v>4.9367833054357949e-05</v>
       </c>
       <c r="AB18">
-        <v>7.0954999775664626e-05</v>
+        <v>8.5799646120243581e-05</v>
       </c>
       <c r="AC18">
-        <v>-6.8574665755454303e-06</v>
+        <v>6.352830463492512e-06</v>
       </c>
       <c r="AD18">
-        <v>5.9035760047622746e-05</v>
+        <v>5.9201836919625228e-05</v>
       </c>
       <c r="AE18">
-        <v>1.7587982876780405e-05</v>
+        <v>4.3467628110373442e-05</v>
       </c>
       <c r="AF18">
-        <v>-1.1447210369927276e-05</v>
+        <v>-6.1333967309722153e-06</v>
       </c>
       <c r="AG18">
-        <v>0.0002006316169769623</v>
+        <v>0.0001026237763215327</v>
       </c>
       <c r="AH18">
-        <v>0.00014512875049894208</v>
+        <v>7.1503295263667353e-05</v>
       </c>
       <c r="AI18">
-        <v>-0.014763368816508946</v>
+        <v>-0.010715118799295528</v>
       </c>
     </row>
     <row r="19">
@@ -6264,106 +6264,106 @@
         <v>46</v>
       </c>
       <c r="B19">
-        <v>0.30689102994222972</v>
+        <v>0.22675041138778157</v>
       </c>
       <c r="C19">
-        <v>-0.0001027422881938953</v>
+        <v>-9.5660569266283366e-05</v>
       </c>
       <c r="D19">
-        <v>5.6327917884880805e-05</v>
+        <v>4.1911041234563763e-05</v>
       </c>
       <c r="E19">
-        <v>-5.3255137979159031e-07</v>
+        <v>-3.9850582766799807e-07</v>
       </c>
       <c r="F19">
-        <v>0.00010735315558156209</v>
+        <v>7.2319497612602108e-05</v>
       </c>
       <c r="G19">
-        <v>6.506798789906185e-05</v>
+        <v>6.1135750738960503e-05</v>
       </c>
       <c r="H19">
-        <v>6.3292858309631217e-05</v>
+        <v>1.7097488510219461e-05</v>
       </c>
       <c r="I19">
-        <v>-0.00013543921931975181</v>
+        <v>-8.2717081325280224e-05</v>
       </c>
       <c r="J19">
-        <v>-5.9662954073992389e-05</v>
+        <v>-1.2158462172536947e-05</v>
       </c>
       <c r="K19">
-        <v>0.0024972211811194393</v>
+        <v>0.0018872080951591495</v>
       </c>
       <c r="L19">
-        <v>-4.933522852928612e-05</v>
+        <v>-4.1690923457297036e-05</v>
       </c>
       <c r="M19">
-        <v>-3.6088427002290925e-05</v>
+        <v>-8.2752868392882915e-06</v>
       </c>
       <c r="N19">
-        <v>0.00011822182869630467</v>
+        <v>0.00013469517750868939</v>
       </c>
       <c r="O19">
-        <v>6.799584020791556e-05</v>
+        <v>2.0022371290431254e-05</v>
       </c>
       <c r="P19">
-        <v>-2.8474912227118834e-05</v>
+        <v>-1.8396627539396591e-05</v>
       </c>
       <c r="Q19">
-        <v>0.003600202638976196</v>
+        <v>0.0029771787142031441</v>
       </c>
       <c r="R19">
-        <v>0.0030999572069719526</v>
+        <v>0.0025435265004966432</v>
       </c>
       <c r="S19">
-        <v>0.0028197971898799128</v>
+        <v>0.002365847834919511</v>
       </c>
       <c r="T19">
-        <v>0.023718959018883545</v>
+        <v>0.018073448140702914</v>
       </c>
       <c r="U19">
-        <v>0.020014447954107284</v>
+        <v>0.01511653657210689</v>
       </c>
       <c r="V19">
-        <v>0.020148993634667056</v>
+        <v>0.015229920627762718</v>
       </c>
       <c r="W19">
-        <v>3.4522939287826981e-05</v>
+        <v>7.0611643962856284e-05</v>
       </c>
       <c r="X19">
-        <v>2.190562178820514e-05</v>
+        <v>9.8248452292374992e-05</v>
       </c>
       <c r="Y19">
-        <v>0.0007232136229608525</v>
+        <v>0.00070207492734455923</v>
       </c>
       <c r="Z19">
-        <v>-2.1245397239001707e-06</v>
+        <v>8.1796134884655827e-05</v>
       </c>
       <c r="AA19">
-        <v>-0.00023697175779435059</v>
+        <v>-6.5977748268545265e-05</v>
       </c>
       <c r="AB19">
-        <v>-0.00023627816261422669</v>
+        <v>-8.1554675259494763e-05</v>
       </c>
       <c r="AC19">
-        <v>-4.9982022240475585e-05</v>
+        <v>5.5011388798308428e-05</v>
       </c>
       <c r="AD19">
-        <v>-0.00029799213440012858</v>
+        <v>-0.00010304340954919852</v>
       </c>
       <c r="AE19">
-        <v>-6.9971695066448243e-05</v>
+        <v>-8.9685666702423459e-05</v>
       </c>
       <c r="AF19">
-        <v>2.1528153876205439e-07</v>
+        <v>2.9647257412071418e-06</v>
       </c>
       <c r="AG19">
-        <v>-5.5994886211566119e-05</v>
+        <v>-6.2888099250091312e-06</v>
       </c>
       <c r="AH19">
-        <v>0.00014858609909701621</v>
+        <v>1.4120930301418644e-05</v>
       </c>
       <c r="AI19">
-        <v>-0.024416804220154135</v>
+        <v>-0.018831810835430202</v>
       </c>
     </row>
     <row r="20">
@@ -6371,106 +6371,106 @@
         <v>47</v>
       </c>
       <c r="B20">
-        <v>0.26153167700082769</v>
+        <v>0.24438362484980597</v>
       </c>
       <c r="C20">
-        <v>-5.2265305761841304e-05</v>
+        <v>-2.95200541884232e-05</v>
       </c>
       <c r="D20">
-        <v>-2.8715351058527014e-05</v>
+        <v>-2.4552717071218503e-05</v>
       </c>
       <c r="E20">
-        <v>9.3323005600879071e-08</v>
+        <v>8.5366265271832758e-08</v>
       </c>
       <c r="F20">
-        <v>0.00013435923948253528</v>
+        <v>8.6116183005344616e-05</v>
       </c>
       <c r="G20">
-        <v>0.00011380341857671148</v>
+        <v>9.7678731807014207e-05</v>
       </c>
       <c r="H20">
-        <v>0.00014956025952320585</v>
+        <v>9.7737619638381271e-05</v>
       </c>
       <c r="I20">
-        <v>-6.0851686910935905e-05</v>
+        <v>-5.4794783141643485e-05</v>
       </c>
       <c r="J20">
-        <v>-9.3223257890432193e-05</v>
+        <v>-2.7260263517076077e-05</v>
       </c>
       <c r="K20">
-        <v>0.0025423143104802422</v>
+        <v>0.0019220082482929528</v>
       </c>
       <c r="L20">
-        <v>-6.637102713381732e-05</v>
+        <v>-4.9678699126256522e-05</v>
       </c>
       <c r="M20">
-        <v>2.1954280476577358e-05</v>
+        <v>5.4532147123851329e-06</v>
       </c>
       <c r="N20">
-        <v>3.3146942100654173e-05</v>
+        <v>2.0021917693776713e-05</v>
       </c>
       <c r="O20">
-        <v>8.2907278544705921e-05</v>
+        <v>2.595289062499854e-05</v>
       </c>
       <c r="P20">
-        <v>-1.0017500246774203e-05</v>
+        <v>-5.3823427814128568e-06</v>
       </c>
       <c r="Q20">
-        <v>0.00067584595036841548</v>
+        <v>0.00054304833169308182</v>
       </c>
       <c r="R20">
-        <v>0.00040240943404083913</v>
+        <v>0.00028300368417480751</v>
       </c>
       <c r="S20">
-        <v>-2.5275215848472726e-05</v>
+        <v>-9.3612752841117433e-06</v>
       </c>
       <c r="T20">
-        <v>0.020014447954107284</v>
+        <v>0.01511653657210689</v>
       </c>
       <c r="U20">
-        <v>0.020715823942641615</v>
+        <v>0.015723565725514799</v>
       </c>
       <c r="V20">
-        <v>0.020655427483198725</v>
+        <v>0.015679695076591789</v>
       </c>
       <c r="W20">
-        <v>-0.00012790703301523485</v>
+        <v>-6.8321306906789572e-05</v>
       </c>
       <c r="X20">
-        <v>2.8191657824618455e-05</v>
+        <v>9.1066052044852259e-05</v>
       </c>
       <c r="Y20">
-        <v>0.00051999392204682676</v>
+        <v>0.00057607957093675508</v>
       </c>
       <c r="Z20">
-        <v>6.6557231107324325e-05</v>
+        <v>0.00018260500360920383</v>
       </c>
       <c r="AA20">
-        <v>-0.00015827837842209442</v>
+        <v>4.8086735575649138e-05</v>
       </c>
       <c r="AB20">
-        <v>-0.00021599875091771149</v>
+        <v>-5.1239361966075401e-06</v>
       </c>
       <c r="AC20">
-        <v>5.6598753435136047e-05</v>
+        <v>0.00019026714922081717</v>
       </c>
       <c r="AD20">
-        <v>-0.00021078048529140064</v>
+        <v>3.853106959384768e-07</v>
       </c>
       <c r="AE20">
-        <v>6.7585007183653626e-05</v>
+        <v>9.3167404871446384e-05</v>
       </c>
       <c r="AF20">
-        <v>6.9688415398830176e-06</v>
+        <v>7.4139764138646432e-06</v>
       </c>
       <c r="AG20">
-        <v>2.6878304278842719e-05</v>
+        <v>7.9994971644315252e-05</v>
       </c>
       <c r="AH20">
-        <v>0.00015217774312469186</v>
+        <v>1.3543670851434708e-05</v>
       </c>
       <c r="AI20">
-        <v>-0.019556821768951863</v>
+        <v>-0.014929297964842797</v>
       </c>
     </row>
     <row r="21">
@@ -6478,106 +6478,106 @@
         <v>48</v>
       </c>
       <c r="B21">
-        <v>0.31668596663367216</v>
+        <v>0.2819906190925453</v>
       </c>
       <c r="C21">
-        <v>-0.00020319985945792786</v>
+        <v>-0.00014176747662271859</v>
       </c>
       <c r="D21">
-        <v>-3.3873129909836963e-06</v>
+        <v>-8.3669400091756764e-06</v>
       </c>
       <c r="E21">
-        <v>-3.0831760440807579e-07</v>
+        <v>-1.8236208065779914e-07</v>
       </c>
       <c r="F21">
-        <v>3.649228354062322e-05</v>
+        <v>3.9381120078241195e-05</v>
       </c>
       <c r="G21">
-        <v>6.7121795603022763e-05</v>
+        <v>8.3261361007281199e-05</v>
       </c>
       <c r="H21">
-        <v>6.0869248048411742e-05</v>
+        <v>3.8233718438623193e-05</v>
       </c>
       <c r="I21">
-        <v>-0.00012846647571950452</v>
+        <v>-9.1353798657312774e-05</v>
       </c>
       <c r="J21">
-        <v>-0.00012104402601295762</v>
+        <v>-2.7004610335824979e-05</v>
       </c>
       <c r="K21">
-        <v>0.002568404299279205</v>
+        <v>0.0019437705410297766</v>
       </c>
       <c r="L21">
-        <v>-5.8997845047084071e-05</v>
+        <v>-4.723236331971339e-05</v>
       </c>
       <c r="M21">
-        <v>3.6938012733061165e-05</v>
+        <v>2.1209010254739871e-06</v>
       </c>
       <c r="N21">
-        <v>0.00018222348271810547</v>
+        <v>0.00013139748255474302</v>
       </c>
       <c r="O21">
-        <v>0.00011489318579543873</v>
+        <v>2.6230948615721508e-05</v>
       </c>
       <c r="P21">
-        <v>-2.4610251780634695e-05</v>
+        <v>-1.8199951561626254e-06</v>
       </c>
       <c r="Q21">
-        <v>0.00084114758004532491</v>
+        <v>0.0006671776916946379</v>
       </c>
       <c r="R21">
-        <v>0.0005256087312728345</v>
+        <v>0.00038790812345809115</v>
       </c>
       <c r="S21">
-        <v>3.2504609520023686e-05</v>
+        <v>4.1114775312971023e-05</v>
       </c>
       <c r="T21">
-        <v>0.020148993634667056</v>
+        <v>0.015229920627762718</v>
       </c>
       <c r="U21">
-        <v>0.020655427483198725</v>
+        <v>0.015679695076591789</v>
       </c>
       <c r="V21">
-        <v>0.021712917151899276</v>
+        <v>0.016426119721242243</v>
       </c>
       <c r="W21">
-        <v>-0.00015955138939490609</v>
+        <v>-0.00010476350483751729</v>
       </c>
       <c r="X21">
-        <v>2.2910447972973938e-05</v>
+        <v>5.8590977754004788e-05</v>
       </c>
       <c r="Y21">
-        <v>0.00049063200750470645</v>
+        <v>0.00053790788706125064</v>
       </c>
       <c r="Z21">
-        <v>3.2379196705672499e-05</v>
+        <v>0.00020058416387127957</v>
       </c>
       <c r="AA21">
-        <v>-0.00019517041910760771</v>
+        <v>7.8774566333253936e-05</v>
       </c>
       <c r="AB21">
-        <v>-0.0002307304293205051</v>
+        <v>3.6505203233518167e-05</v>
       </c>
       <c r="AC21">
-        <v>5.0429980654251652e-05</v>
+        <v>0.00023111009227154682</v>
       </c>
       <c r="AD21">
-        <v>-0.00023556963315815062</v>
+        <v>2.4134375351770807e-05</v>
       </c>
       <c r="AE21">
-        <v>5.9506652066179883e-05</v>
+        <v>0.0001348805627858201</v>
       </c>
       <c r="AF21">
-        <v>7.0868702618841553e-06</v>
+        <v>7.1148461006115976e-06</v>
       </c>
       <c r="AG21">
-        <v>9.5301536831786382e-05</v>
+        <v>0.00010872160819264814</v>
       </c>
       <c r="AH21">
-        <v>0.00019727308075736388</v>
+        <v>7.3259343357217656e-05</v>
       </c>
       <c r="AI21">
-        <v>-0.019970339422381342</v>
+        <v>-0.015225895337582101</v>
       </c>
     </row>
     <row r="22">
@@ -6585,106 +6585,106 @@
         <v>49</v>
       </c>
       <c r="B22">
-        <v>0.0094792007980459142</v>
+        <v>-0.0055814200925311695</v>
       </c>
       <c r="C22">
-        <v>4.0345429562238022e-05</v>
+        <v>2.9154778942572579e-05</v>
       </c>
       <c r="D22">
-        <v>8.9916027705526815e-06</v>
+        <v>1.0149484608886576e-05</v>
       </c>
       <c r="E22">
-        <v>-2.5385119997845615e-08</v>
+        <v>-4.687240301874925e-08</v>
       </c>
       <c r="F22">
-        <v>1.396123948230936e-06</v>
+        <v>-2.3705830900374821e-05</v>
       </c>
       <c r="G22">
-        <v>3.240480365034445e-05</v>
+        <v>9.8725724469550351e-06</v>
       </c>
       <c r="H22">
-        <v>1.4386862176733667e-05</v>
+        <v>-8.5563527611985386e-06</v>
       </c>
       <c r="I22">
-        <v>2.8852205235416919e-06</v>
+        <v>-1.1666824654228198e-05</v>
       </c>
       <c r="J22">
-        <v>2.2253769112660799e-05</v>
+        <v>2.7620788434536656e-06</v>
       </c>
       <c r="K22">
-        <v>-2.8229001594775981e-05</v>
+        <v>-1.9221651197954986e-05</v>
       </c>
       <c r="L22">
-        <v>2.1549592304919692e-07</v>
+        <v>9.2883273672897568e-09</v>
       </c>
       <c r="M22">
-        <v>-2.3776958373916191e-05</v>
+        <v>-4.3790451813930481e-06</v>
       </c>
       <c r="N22">
-        <v>-4.2543583907250739e-05</v>
+        <v>-3.3220939055277261e-05</v>
       </c>
       <c r="O22">
-        <v>-2.5224057276764082e-05</v>
+        <v>-3.8825774180729108e-06</v>
       </c>
       <c r="P22">
-        <v>2.3697218473121755e-05</v>
+        <v>3.9921339113148423e-06</v>
       </c>
       <c r="Q22">
-        <v>-4.4052120864641406e-05</v>
+        <v>-3.5816147462752225e-05</v>
       </c>
       <c r="R22">
-        <v>-6.0744806840123128e-05</v>
+        <v>-5.1554931737010667e-05</v>
       </c>
       <c r="S22">
-        <v>-6.731041884144413e-05</v>
+        <v>-5.4361942385244334e-05</v>
       </c>
       <c r="T22">
-        <v>3.4522939287826981e-05</v>
+        <v>7.0611643962856284e-05</v>
       </c>
       <c r="U22">
-        <v>-0.00012790703301523485</v>
+        <v>-6.8321306906789572e-05</v>
       </c>
       <c r="V22">
-        <v>-0.00015955138939490609</v>
+        <v>-0.00010476350483751729</v>
       </c>
       <c r="W22">
-        <v>0.00063219260239416608</v>
+        <v>0.00047555179875446426</v>
       </c>
       <c r="X22">
-        <v>0.00021111983175499925</v>
+        <v>0.00016636127862838999</v>
       </c>
       <c r="Y22">
-        <v>0.00032374727392850693</v>
+        <v>0.00025073862351095399</v>
       </c>
       <c r="Z22">
-        <v>-2.8259794567796529e-07</v>
+        <v>1.1209677716053802e-05</v>
       </c>
       <c r="AA22">
-        <v>-1.2850461832927804e-05</v>
+        <v>3.0164766362266756e-06</v>
       </c>
       <c r="AB22">
-        <v>8.9035697779476348e-07</v>
+        <v>1.6215172945386385e-05</v>
       </c>
       <c r="AC22">
-        <v>-6.1956261635208589e-06</v>
+        <v>8.347343052448163e-06</v>
       </c>
       <c r="AD22">
-        <v>7.9580214339586058e-06</v>
+        <v>1.8218598874120664e-05</v>
       </c>
       <c r="AE22">
-        <v>-5.1787848250889523e-05</v>
+        <v>-4.794041635996373e-05</v>
       </c>
       <c r="AF22">
-        <v>-1.6556312024076805e-08</v>
+        <v>-3.8638261772101368e-07</v>
       </c>
       <c r="AG22">
-        <v>3.3973305414521386e-05</v>
+        <v>3.4010345848732202e-05</v>
       </c>
       <c r="AH22">
-        <v>-1.182606046036495e-05</v>
+        <v>-1.6129807065460138e-05</v>
       </c>
       <c r="AI22">
-        <v>-0.00042718926414069328</v>
+        <v>-0.00041631372711569385</v>
       </c>
     </row>
     <row r="23">
@@ -6692,106 +6692,106 @@
         <v>50</v>
       </c>
       <c r="B23">
-        <v>0.076294703820031354</v>
+        <v>0.042900599829082231</v>
       </c>
       <c r="C23">
-        <v>-3.6891271348568258e-07</v>
+        <v>6.1134543296815869e-06</v>
       </c>
       <c r="D23">
-        <v>3.4925405800941836e-05</v>
+        <v>2.6659730312490085e-05</v>
       </c>
       <c r="E23">
-        <v>-2.8087293733730018e-07</v>
+        <v>-2.0757740691395408e-07</v>
       </c>
       <c r="F23">
-        <v>-1.148587195645874e-05</v>
+        <v>-3.3536093379019387e-05</v>
       </c>
       <c r="G23">
-        <v>3.6184796380715366e-05</v>
+        <v>1.1602479155745776e-05</v>
       </c>
       <c r="H23">
-        <v>2.9644530535361414e-05</v>
+        <v>6.5853044540289691e-06</v>
       </c>
       <c r="I23">
-        <v>7.5507397100281742e-05</v>
+        <v>4.6188312691185078e-05</v>
       </c>
       <c r="J23">
-        <v>-5.9665466520087527e-05</v>
+        <v>-1.8224339906499334e-05</v>
       </c>
       <c r="K23">
-        <v>2.2909570554582198e-06</v>
+        <v>7.4496682716483891e-06</v>
       </c>
       <c r="L23">
-        <v>2.8208978696641841e-06</v>
+        <v>3.5352631715359018e-06</v>
       </c>
       <c r="M23">
-        <v>3.6866996768808093e-05</v>
+        <v>1.0492823791332157e-05</v>
       </c>
       <c r="N23">
-        <v>-4.7090840577933713e-07</v>
+        <v>-9.1130213531504141e-06</v>
       </c>
       <c r="O23">
-        <v>6.0222017016385771e-05</v>
+        <v>1.7266261719943712e-05</v>
       </c>
       <c r="P23">
-        <v>-3.7255878129687707e-05</v>
+        <v>-1.0195612902429526e-05</v>
       </c>
       <c r="Q23">
-        <v>2.9757273650001578e-05</v>
+        <v>1.7291944555928923e-05</v>
       </c>
       <c r="R23">
-        <v>-5.1193897151529874e-06</v>
+        <v>-1.7823892669612852e-05</v>
       </c>
       <c r="S23">
-        <v>-2.1592972747274189e-05</v>
+        <v>-1.6540941160553139e-05</v>
       </c>
       <c r="T23">
-        <v>2.190562178820514e-05</v>
+        <v>9.8248452292374992e-05</v>
       </c>
       <c r="U23">
-        <v>2.8191657824618455e-05</v>
+        <v>9.1066052044852259e-05</v>
       </c>
       <c r="V23">
-        <v>2.2910447972973938e-05</v>
+        <v>5.8590977754004788e-05</v>
       </c>
       <c r="W23">
-        <v>0.00021111983175499925</v>
+        <v>0.00016636127862838999</v>
       </c>
       <c r="X23">
-        <v>0.00053996478025711053</v>
+        <v>0.00040067938195212241</v>
       </c>
       <c r="Y23">
-        <v>0.00022623288523965224</v>
+        <v>0.00017854780852958842</v>
       </c>
       <c r="Z23">
-        <v>1.0090656048973535e-05</v>
+        <v>-1.4819805628393432e-05</v>
       </c>
       <c r="AA23">
-        <v>1.5038794390850993e-05</v>
+        <v>-1.5540206249952911e-05</v>
       </c>
       <c r="AB23">
-        <v>2.395369186708842e-05</v>
+        <v>-1.5218837537113125e-06</v>
       </c>
       <c r="AC23">
-        <v>1.8834833522594766e-05</v>
+        <v>-6.7203803147305443e-06</v>
       </c>
       <c r="AD23">
-        <v>5.9793821400408779e-05</v>
+        <v>1.9219754684363105e-05</v>
       </c>
       <c r="AE23">
-        <v>1.1611884530182302e-05</v>
+        <v>-2.7750565127864939e-05</v>
       </c>
       <c r="AF23">
-        <v>-2.6925762539104889e-07</v>
+        <v>-7.6999422546614844e-07</v>
       </c>
       <c r="AG23">
-        <v>0.00011623267111935905</v>
+        <v>9.5602396610584188e-05</v>
       </c>
       <c r="AH23">
-        <v>1.5389163367935809e-05</v>
+        <v>7.974738377641258e-06</v>
       </c>
       <c r="AI23">
-        <v>-0.0012783098564462269</v>
+        <v>-0.00099830234275434309</v>
       </c>
     </row>
     <row r="24">
@@ -6799,106 +6799,106 @@
         <v>51</v>
       </c>
       <c r="B24">
-        <v>0.60155594803663481</v>
+        <v>0.21517368165845735</v>
       </c>
       <c r="C24">
-        <v>0.00013694080783844886</v>
+        <v>0.00010297790051462028</v>
       </c>
       <c r="D24">
-        <v>1.0265266595365681e-05</v>
+        <v>9.8901673089887138e-06</v>
       </c>
       <c r="E24">
-        <v>-1.8130713169339472e-08</v>
+        <v>-3.7547868734137601e-08</v>
       </c>
       <c r="F24">
-        <v>5.9715548943519012e-05</v>
+        <v>3.1718669050096599e-05</v>
       </c>
       <c r="G24">
-        <v>0.00011715946216607118</v>
+        <v>8.6282675976143792e-05</v>
       </c>
       <c r="H24">
-        <v>0.00014344774122373918</v>
+        <v>9.836435578030071e-05</v>
       </c>
       <c r="I24">
-        <v>0.00013852717240664609</v>
+        <v>0.00010371067588002786</v>
       </c>
       <c r="J24">
-        <v>-5.816469041652558e-05</v>
+        <v>-2.1306315218930899e-05</v>
       </c>
       <c r="K24">
-        <v>4.6191887562013366e-05</v>
+        <v>5.5120278635650984e-05</v>
       </c>
       <c r="L24">
-        <v>8.6033118555267458e-06</v>
+        <v>3.9968723023051736e-06</v>
       </c>
       <c r="M24">
-        <v>-0.00019737655532720032</v>
+        <v>-3.5140046851827511e-05</v>
       </c>
       <c r="N24">
-        <v>-0.00012331938187331941</v>
+        <v>-9.8619098376432311e-05</v>
       </c>
       <c r="O24">
-        <v>5.7313670718088842e-05</v>
+        <v>2.2703858386491338e-05</v>
       </c>
       <c r="P24">
-        <v>0.00016661892369636234</v>
+        <v>2.316996492159111e-05</v>
       </c>
       <c r="Q24">
-        <v>0.00023147393001431062</v>
+        <v>0.0001220726888068787</v>
       </c>
       <c r="R24">
-        <v>9.3570909470648382e-05</v>
+        <v>5.2840393465285705e-06</v>
       </c>
       <c r="S24">
-        <v>0.00021078688298528658</v>
+        <v>0.0001029112026425011</v>
       </c>
       <c r="T24">
-        <v>0.0007232136229608525</v>
+        <v>0.00070207492734455923</v>
       </c>
       <c r="U24">
-        <v>0.00051999392204682676</v>
+        <v>0.00057607957093675508</v>
       </c>
       <c r="V24">
-        <v>0.00049063200750470645</v>
+        <v>0.00053790788706125064</v>
       </c>
       <c r="W24">
-        <v>0.00032374727392850693</v>
+        <v>0.00025073862351095399</v>
       </c>
       <c r="X24">
-        <v>0.00022623288523965224</v>
+        <v>0.00017854780852958842</v>
       </c>
       <c r="Y24">
-        <v>0.0049391707950833235</v>
+        <v>0.0033872444461233967</v>
       </c>
       <c r="Z24">
-        <v>4.1001920201236318e-05</v>
+        <v>2.8285800909851966e-06</v>
       </c>
       <c r="AA24">
-        <v>5.8546293138214242e-05</v>
+        <v>2.6390516142182593e-05</v>
       </c>
       <c r="AB24">
-        <v>8.9294459759380824e-05</v>
+        <v>4.8858054046928959e-05</v>
       </c>
       <c r="AC24">
-        <v>3.0241719546356469e-05</v>
+        <v>-7.622718019915215e-07</v>
       </c>
       <c r="AD24">
-        <v>9.1352888362737433e-05</v>
+        <v>3.5780002498820378e-05</v>
       </c>
       <c r="AE24">
-        <v>-3.5884440126575035e-05</v>
+        <v>-7.4989240712913642e-05</v>
       </c>
       <c r="AF24">
-        <v>-8.8393577961908054e-06</v>
+        <v>-4.8846479974168429e-06</v>
       </c>
       <c r="AG24">
-        <v>6.0175165015133813e-05</v>
+        <v>2.1838411203416522e-05</v>
       </c>
       <c r="AH24">
-        <v>1.0711515924385082e-05</v>
+        <v>1.3512546714689229e-05</v>
       </c>
       <c r="AI24">
-        <v>-0.0011984065111760687</v>
+        <v>-0.001090271946000361</v>
       </c>
     </row>
     <row r="25">
@@ -6906,106 +6906,106 @@
         <v>52</v>
       </c>
       <c r="B25">
-        <v>-0.17667000773885255</v>
+        <v>-0.10278586913875591</v>
       </c>
       <c r="C25">
-        <v>5.7425833494780031e-06</v>
+        <v>-9.335864421748392e-06</v>
       </c>
       <c r="D25">
-        <v>-3.6890395435922214e-07</v>
+        <v>9.1350952081012903e-07</v>
       </c>
       <c r="E25">
-        <v>-5.5115163241112756e-09</v>
+        <v>-3.6069770294001315e-08</v>
       </c>
       <c r="F25">
-        <v>-5.6077131279566074e-05</v>
+        <v>-5.1834310924630395e-05</v>
       </c>
       <c r="G25">
-        <v>-3.2391368146266614e-05</v>
+        <v>-2.3694207330035404e-05</v>
       </c>
       <c r="H25">
-        <v>-7.1874354112027878e-05</v>
+        <v>-7.6247231313643794e-05</v>
       </c>
       <c r="I25">
-        <v>-6.0315393916438552e-06</v>
+        <v>1.1164296909034824e-05</v>
       </c>
       <c r="J25">
-        <v>8.5149803357657992e-06</v>
+        <v>7.2757498058676063e-06</v>
       </c>
       <c r="K25">
-        <v>9.418187349832124e-06</v>
+        <v>2.1383848145603915e-05</v>
       </c>
       <c r="L25">
-        <v>-5.8983953549960456e-06</v>
+        <v>-9.6109704479998775e-06</v>
       </c>
       <c r="M25">
-        <v>-5.2793343367700959e-05</v>
+        <v>-1.0553378979036472e-05</v>
       </c>
       <c r="N25">
-        <v>6.3892697498914601e-05</v>
+        <v>0.00012401814429304544</v>
       </c>
       <c r="O25">
-        <v>-0.00011547568708166747</v>
+        <v>-4.1741491435329258e-05</v>
       </c>
       <c r="P25">
-        <v>8.6525314375642546e-05</v>
+        <v>2.8500856413521142e-05</v>
       </c>
       <c r="Q25">
-        <v>-1.4248406050923479e-05</v>
+        <v>6.6182500210149042e-05</v>
       </c>
       <c r="R25">
-        <v>9.9286993257364023e-06</v>
+        <v>6.7856582924429899e-05</v>
       </c>
       <c r="S25">
-        <v>-1.6892185388245676e-05</v>
+        <v>1.5977289439899484e-05</v>
       </c>
       <c r="T25">
-        <v>-2.1245397239001707e-06</v>
+        <v>8.1796134884655827e-05</v>
       </c>
       <c r="U25">
-        <v>6.6557231107324325e-05</v>
+        <v>0.00018260500360920383</v>
       </c>
       <c r="V25">
-        <v>3.2379196705672499e-05</v>
+        <v>0.00020058416387127957</v>
       </c>
       <c r="W25">
-        <v>-2.8259794567796529e-07</v>
+        <v>1.1209677716053802e-05</v>
       </c>
       <c r="X25">
-        <v>1.0090656048973535e-05</v>
+        <v>-1.4819805628393432e-05</v>
       </c>
       <c r="Y25">
-        <v>4.1001920201236318e-05</v>
+        <v>2.8285800909851966e-06</v>
       </c>
       <c r="Z25">
-        <v>0.0027368841041138471</v>
+        <v>0.0023639021397631331</v>
       </c>
       <c r="AA25">
-        <v>0.002403550398369916</v>
+        <v>0.0021223492808096116</v>
       </c>
       <c r="AB25">
-        <v>0.0024018384466925175</v>
+        <v>0.0021256421183058131</v>
       </c>
       <c r="AC25">
-        <v>0.0024068293784165707</v>
+        <v>0.0021240227273291684</v>
       </c>
       <c r="AD25">
-        <v>0.0024144940450831001</v>
+        <v>0.0021274580204613961</v>
       </c>
       <c r="AE25">
-        <v>0.0023958525996362438</v>
+        <v>0.002109964130242789</v>
       </c>
       <c r="AF25">
-        <v>6.8893600317669401e-06</v>
+        <v>8.2309305574250539e-06</v>
       </c>
       <c r="AG25">
-        <v>3.8664036657134679e-05</v>
+        <v>4.8591971455376384e-05</v>
       </c>
       <c r="AH25">
-        <v>6.6604240827844267e-06</v>
+        <v>-2.6220638622332726e-05</v>
       </c>
       <c r="AI25">
-        <v>-0.0024100460320740777</v>
+        <v>-0.0023158348738640863</v>
       </c>
     </row>
     <row r="26">
@@ -7013,106 +7013,106 @@
         <v>53</v>
       </c>
       <c r="B26">
-        <v>-0.041384073498688286</v>
+        <v>-0.036225405680923375</v>
       </c>
       <c r="C26">
-        <v>1.0743021050413368e-05</v>
+        <v>-5.8546447618001047e-06</v>
       </c>
       <c r="D26">
-        <v>2.7230093151540838e-06</v>
+        <v>3.6215784504039074e-06</v>
       </c>
       <c r="E26">
-        <v>-4.0942454040429362e-08</v>
+        <v>-6.8712749839840212e-08</v>
       </c>
       <c r="F26">
-        <v>-3.2613800962478764e-05</v>
+        <v>-3.7256828155836277e-05</v>
       </c>
       <c r="G26">
-        <v>-3.342869865768038e-05</v>
+        <v>-2.6420656955067042e-05</v>
       </c>
       <c r="H26">
-        <v>-8.9556933801142932e-05</v>
+        <v>-9.1057264796521155e-05</v>
       </c>
       <c r="I26">
-        <v>-5.561515106820218e-05</v>
+        <v>-2.9495735676815082e-05</v>
       </c>
       <c r="J26">
-        <v>7.7232169495954248e-06</v>
+        <v>6.9017503300158681e-06</v>
       </c>
       <c r="K26">
-        <v>-1.9276415664130865e-05</v>
+        <v>4.0595445390421633e-06</v>
       </c>
       <c r="L26">
-        <v>-8.370704189693698e-06</v>
+        <v>-1.1695178700563376e-05</v>
       </c>
       <c r="M26">
-        <v>-8.174737975831258e-05</v>
+        <v>-1.5697155095718355e-05</v>
       </c>
       <c r="N26">
-        <v>0.00011439383984365313</v>
+        <v>0.00016044528123872084</v>
       </c>
       <c r="O26">
-        <v>-9.553782629575147e-05</v>
+        <v>-3.7558632074420238e-05</v>
       </c>
       <c r="P26">
-        <v>0.00010835578757822277</v>
+        <v>3.1628420065588504e-05</v>
       </c>
       <c r="Q26">
-        <v>4.6359194890806775e-05</v>
+        <v>9.487294352295006e-05</v>
       </c>
       <c r="R26">
-        <v>6.572844696292211e-05</v>
+        <v>0.00010159802617199822</v>
       </c>
       <c r="S26">
-        <v>4.3026856138298538e-05</v>
+        <v>4.9367833054357949e-05</v>
       </c>
       <c r="T26">
-        <v>-0.00023697175779435059</v>
+        <v>-6.5977748268545265e-05</v>
       </c>
       <c r="U26">
-        <v>-0.00015827837842209442</v>
+        <v>4.8086735575649138e-05</v>
       </c>
       <c r="V26">
-        <v>-0.00019517041910760771</v>
+        <v>7.8774566333253936e-05</v>
       </c>
       <c r="W26">
-        <v>-1.2850461832927804e-05</v>
+        <v>3.0164766362266756e-06</v>
       </c>
       <c r="X26">
-        <v>1.5038794390850993e-05</v>
+        <v>-1.5540206249952911e-05</v>
       </c>
       <c r="Y26">
-        <v>5.8546293138214242e-05</v>
+        <v>2.6390516142182593e-05</v>
       </c>
       <c r="Z26">
-        <v>0.002403550398369916</v>
+        <v>0.0021223492808096116</v>
       </c>
       <c r="AA26">
-        <v>0.0029148475551923816</v>
+        <v>0.0024772697194631902</v>
       </c>
       <c r="AB26">
-        <v>0.0024160957126365826</v>
+        <v>0.0021351677875133183</v>
       </c>
       <c r="AC26">
-        <v>0.0024093572699213821</v>
+        <v>0.002125110038320336</v>
       </c>
       <c r="AD26">
-        <v>0.0024199231391288829</v>
+        <v>0.0021300649491891146</v>
       </c>
       <c r="AE26">
-        <v>0.0023976319659872111</v>
+        <v>0.0021116197683530651</v>
       </c>
       <c r="AF26">
-        <v>5.039172834197763e-06</v>
+        <v>6.9238386467466201e-06</v>
       </c>
       <c r="AG26">
-        <v>3.4835930301661648e-05</v>
+        <v>5.7692432346097104e-05</v>
       </c>
       <c r="AH26">
-        <v>-2.8199243767408622e-05</v>
+        <v>-3.7669613783008625e-05</v>
       </c>
       <c r="AI26">
-        <v>-0.0022004278612251281</v>
+        <v>-0.0021911353971823654</v>
       </c>
     </row>
     <row r="27">
@@ -7120,106 +7120,106 @@
         <v>54</v>
       </c>
       <c r="B27">
-        <v>-0.041511225058046997</v>
+        <v>-0.051789723528653145</v>
       </c>
       <c r="C27">
-        <v>6.9760191377979161e-06</v>
+        <v>-1.0585656419178065e-05</v>
       </c>
       <c r="D27">
-        <v>2.6496366877957415e-06</v>
+        <v>4.3609333452371355e-06</v>
       </c>
       <c r="E27">
-        <v>-3.9895281830393476e-08</v>
+        <v>-7.3442178562350164e-08</v>
       </c>
       <c r="F27">
-        <v>-4.3719027208413697e-05</v>
+        <v>-4.3119877050201987e-05</v>
       </c>
       <c r="G27">
-        <v>-3.4709028774606351e-05</v>
+        <v>-2.4660131683162771e-05</v>
       </c>
       <c r="H27">
-        <v>-9.6477235923793717e-05</v>
+        <v>-9.1372038908214153e-05</v>
       </c>
       <c r="I27">
-        <v>-7.6338942696981579e-05</v>
+        <v>-4.0220255936107693e-05</v>
       </c>
       <c r="J27">
-        <v>-9.9065126713600744e-06</v>
+        <v>2.632259753434833e-06</v>
       </c>
       <c r="K27">
-        <v>-2.7012175418189175e-05</v>
+        <v>-2.5227767774379725e-06</v>
       </c>
       <c r="L27">
-        <v>-4.4093195581566065e-06</v>
+        <v>-8.7266002255603918e-06</v>
       </c>
       <c r="M27">
-        <v>-7.4798169395010197e-05</v>
+        <v>-1.7947351872157482e-05</v>
       </c>
       <c r="N27">
-        <v>0.00013461317724291501</v>
+        <v>0.00019725792838860698</v>
       </c>
       <c r="O27">
-        <v>-0.00010038128288236559</v>
+        <v>-3.7989180969422463e-05</v>
       </c>
       <c r="P27">
-        <v>8.8851153156342948e-05</v>
+        <v>3.4950511344949709e-05</v>
       </c>
       <c r="Q27">
-        <v>9.9282122083284253e-05</v>
+        <v>0.00015783475030169613</v>
       </c>
       <c r="R27">
-        <v>7.9839508586744285e-05</v>
+        <v>0.00013175722019482779</v>
       </c>
       <c r="S27">
-        <v>7.0954999775664626e-05</v>
+        <v>8.5799646120243581e-05</v>
       </c>
       <c r="T27">
-        <v>-0.00023627816261422669</v>
+        <v>-8.1554675259494763e-05</v>
       </c>
       <c r="U27">
-        <v>-0.00021599875091771149</v>
+        <v>-5.1239361966075401e-06</v>
       </c>
       <c r="V27">
-        <v>-0.0002307304293205051</v>
+        <v>3.6505203233518167e-05</v>
       </c>
       <c r="W27">
-        <v>8.9035697779476348e-07</v>
+        <v>1.6215172945386385e-05</v>
       </c>
       <c r="X27">
-        <v>2.395369186708842e-05</v>
+        <v>-1.5218837537113125e-06</v>
       </c>
       <c r="Y27">
-        <v>8.9294459759380824e-05</v>
+        <v>4.8858054046928959e-05</v>
       </c>
       <c r="Z27">
-        <v>0.0024018384466925175</v>
+        <v>0.0021256421183058131</v>
       </c>
       <c r="AA27">
-        <v>0.0024160957126365826</v>
+        <v>0.0021351677875133183</v>
       </c>
       <c r="AB27">
-        <v>0.0028912112699131546</v>
+        <v>0.0024572812342327803</v>
       </c>
       <c r="AC27">
-        <v>0.0024058644118620937</v>
+        <v>0.0021270935360720982</v>
       </c>
       <c r="AD27">
-        <v>0.0024182207010879434</v>
+        <v>0.0021350028532362876</v>
       </c>
       <c r="AE27">
-        <v>0.0023938239766845499</v>
+        <v>0.0021126325070296315</v>
       </c>
       <c r="AF27">
-        <v>3.9742914039158828e-06</v>
+        <v>6.3410570567871928e-06</v>
       </c>
       <c r="AG27">
-        <v>8.5101182829898977e-05</v>
+        <v>7.1950381959264009e-05</v>
       </c>
       <c r="AH27">
-        <v>1.9214496868034817e-05</v>
+        <v>-2.2614177046242478e-05</v>
       </c>
       <c r="AI27">
-        <v>-0.0021712246245258688</v>
+        <v>-0.0022047320839206708</v>
       </c>
     </row>
     <row r="28">
@@ -7227,106 +7227,106 @@
         <v>55</v>
       </c>
       <c r="B28">
-        <v>-0.17274750090494068</v>
+        <v>-0.10264379271074485</v>
       </c>
       <c r="C28">
-        <v>4.37177101838762e-06</v>
+        <v>-8.7572897623118122e-06</v>
       </c>
       <c r="D28">
-        <v>3.3060123068474884e-06</v>
+        <v>3.6727555877707108e-06</v>
       </c>
       <c r="E28">
-        <v>-4.6005625474448603e-08</v>
+        <v>-6.6999920756369802e-08</v>
       </c>
       <c r="F28">
-        <v>-9.434248749252863e-05</v>
+        <v>-7.7778989518010634e-05</v>
       </c>
       <c r="G28">
-        <v>-9.5431062887091789e-05</v>
+        <v>-7.3953676822698881e-05</v>
       </c>
       <c r="H28">
-        <v>-0.00014693418837219137</v>
+        <v>-0.00013429476518331436</v>
       </c>
       <c r="I28">
-        <v>-9.1646211952361393e-05</v>
+        <v>-5.789279880685479e-05</v>
       </c>
       <c r="J28">
-        <v>9.5318444476418823e-06</v>
+        <v>8.3152163847382398e-06</v>
       </c>
       <c r="K28">
-        <v>7.8577577430050637e-06</v>
+        <v>2.1739266659929926e-05</v>
       </c>
       <c r="L28">
-        <v>-7.1575627419663402e-06</v>
+        <v>-1.0450915284128772e-05</v>
       </c>
       <c r="M28">
-        <v>-6.6566042929599653e-05</v>
+        <v>-1.3303158559206591e-05</v>
       </c>
       <c r="N28">
-        <v>9.7898026577931821e-05</v>
+        <v>0.00014651550897268654</v>
       </c>
       <c r="O28">
-        <v>-0.00012848653550902875</v>
+        <v>-4.6037538605574115e-05</v>
       </c>
       <c r="P28">
-        <v>0.00010941218739209991</v>
+        <v>3.1764693548203232e-05</v>
       </c>
       <c r="Q28">
-        <v>-3.4653852526901445e-05</v>
+        <v>3.0762400758397104e-05</v>
       </c>
       <c r="R28">
-        <v>1.0444425434076934e-05</v>
+        <v>5.4821079419653182e-05</v>
       </c>
       <c r="S28">
-        <v>-6.8574665755454303e-06</v>
+        <v>6.352830463492512e-06</v>
       </c>
       <c r="T28">
-        <v>-4.9982022240475585e-05</v>
+        <v>5.5011388798308428e-05</v>
       </c>
       <c r="U28">
-        <v>5.6598753435136047e-05</v>
+        <v>0.00019026714922081717</v>
       </c>
       <c r="V28">
-        <v>5.0429980654251652e-05</v>
+        <v>0.00023111009227154682</v>
       </c>
       <c r="W28">
-        <v>-6.1956261635208589e-06</v>
+        <v>8.347343052448163e-06</v>
       </c>
       <c r="X28">
-        <v>1.8834833522594766e-05</v>
+        <v>-6.7203803147305443e-06</v>
       </c>
       <c r="Y28">
-        <v>3.0241719546356469e-05</v>
+        <v>-7.622718019915215e-07</v>
       </c>
       <c r="Z28">
-        <v>0.0024068293784165707</v>
+        <v>0.0021240227273291684</v>
       </c>
       <c r="AA28">
-        <v>0.0024093572699213821</v>
+        <v>0.002125110038320336</v>
       </c>
       <c r="AB28">
-        <v>0.0024058644118620937</v>
+        <v>0.0021270935360720982</v>
       </c>
       <c r="AC28">
-        <v>0.0027382482436391796</v>
+        <v>0.0023633643182878962</v>
       </c>
       <c r="AD28">
-        <v>0.0024168318782956813</v>
+        <v>0.0021270264141845779</v>
       </c>
       <c r="AE28">
-        <v>0.0024003266541567266</v>
+        <v>0.002112266810682553</v>
       </c>
       <c r="AF28">
-        <v>7.3384980026480068e-06</v>
+        <v>8.948103966095376e-06</v>
       </c>
       <c r="AG28">
-        <v>3.0650755195742868e-05</v>
+        <v>4.8606877753752144e-05</v>
       </c>
       <c r="AH28">
-        <v>-1.8159970944595571e-05</v>
+        <v>-5.2841160719077781e-05</v>
       </c>
       <c r="AI28">
-        <v>-0.0023882160995456758</v>
+        <v>-0.0023054847195037266</v>
       </c>
     </row>
     <row r="29">
@@ -7334,106 +7334,106 @@
         <v>56</v>
       </c>
       <c r="B29">
-        <v>-0.059646042206067167</v>
+        <v>-0.048350971377519043</v>
       </c>
       <c r="C29">
-        <v>-1.8893322566322499e-05</v>
+        <v>-2.4432389547118601e-05</v>
       </c>
       <c r="D29">
-        <v>2.7000313798056935e-06</v>
+        <v>3.6196768917586006e-06</v>
       </c>
       <c r="E29">
-        <v>-3.3621964339694341e-08</v>
+        <v>-6.1898072402069532e-08</v>
       </c>
       <c r="F29">
-        <v>1.0024030448895545e-05</v>
+        <v>-1.8384535306178919e-06</v>
       </c>
       <c r="G29">
-        <v>-4.4670324184873517e-07</v>
+        <v>-1.3619129778063492e-05</v>
       </c>
       <c r="H29">
-        <v>-5.8249228400782897e-05</v>
+        <v>-6.8257765771505079e-05</v>
       </c>
       <c r="I29">
-        <v>4.7353825128320683e-05</v>
+        <v>4.768166417012964e-05</v>
       </c>
       <c r="J29">
-        <v>-7.4128590388704578e-05</v>
+        <v>-9.1512358603782229e-06</v>
       </c>
       <c r="K29">
-        <v>-1.7723351807230679e-05</v>
+        <v>2.4285883841762448e-06</v>
       </c>
       <c r="L29">
-        <v>-1.0905681299324917e-05</v>
+        <v>-1.2277464137015223e-05</v>
       </c>
       <c r="M29">
-        <v>-5.2188146467307259e-05</v>
+        <v>-1.1053181640752294e-05</v>
       </c>
       <c r="N29">
-        <v>7.1443082540535198e-05</v>
+        <v>0.00012474930381014453</v>
       </c>
       <c r="O29">
-        <v>-4.7242070389820132e-05</v>
+        <v>-3.7540151969539556e-05</v>
       </c>
       <c r="P29">
-        <v>6.8524030885496129e-05</v>
+        <v>2.9113856266219703e-05</v>
       </c>
       <c r="Q29">
-        <v>6.5856619127423362e-05</v>
+        <v>0.00011287110516250659</v>
       </c>
       <c r="R29">
-        <v>8.7148450729574757e-05</v>
+        <v>0.00011607455231191243</v>
       </c>
       <c r="S29">
-        <v>5.9035760047622746e-05</v>
+        <v>5.9201836919625228e-05</v>
       </c>
       <c r="T29">
-        <v>-0.00029799213440012858</v>
+        <v>-0.00010304340954919852</v>
       </c>
       <c r="U29">
-        <v>-0.00021078048529140064</v>
+        <v>3.853106959384768e-07</v>
       </c>
       <c r="V29">
-        <v>-0.00023556963315815062</v>
+        <v>2.4134375351770807e-05</v>
       </c>
       <c r="W29">
-        <v>7.9580214339586058e-06</v>
+        <v>1.8218598874120664e-05</v>
       </c>
       <c r="X29">
-        <v>5.9793821400408779e-05</v>
+        <v>1.9219754684363105e-05</v>
       </c>
       <c r="Y29">
-        <v>9.1352888362737433e-05</v>
+        <v>3.5780002498820378e-05</v>
       </c>
       <c r="Z29">
-        <v>0.0024144940450831001</v>
+        <v>0.0021274580204613961</v>
       </c>
       <c r="AA29">
-        <v>0.0024199231391288829</v>
+        <v>0.0021300649491891146</v>
       </c>
       <c r="AB29">
-        <v>0.0024182207010879434</v>
+        <v>0.0021350028532362876</v>
       </c>
       <c r="AC29">
-        <v>0.0024168318782956813</v>
+        <v>0.0021270264141845779</v>
       </c>
       <c r="AD29">
-        <v>0.0027426640374758997</v>
+        <v>0.0023560558506151431</v>
       </c>
       <c r="AE29">
-        <v>0.0024013860735255625</v>
+        <v>0.0021110009035527756</v>
       </c>
       <c r="AF29">
-        <v>6.7317510321905603e-06</v>
+        <v>9.1173440295177805e-06</v>
       </c>
       <c r="AG29">
-        <v>0.00024879189554570264</v>
+        <v>0.00020040793013192601</v>
       </c>
       <c r="AH29">
-        <v>5.4293743339964631e-08</v>
+        <v>-3.24299948368668e-05</v>
       </c>
       <c r="AI29">
-        <v>-0.0022567947157818703</v>
+        <v>-0.0022442484931118984</v>
       </c>
     </row>
     <row r="30">
@@ -7441,106 +7441,106 @@
         <v>57</v>
       </c>
       <c r="B30">
-        <v>-0.15083426778561873</v>
+        <v>-0.11049107609094856</v>
       </c>
       <c r="C30">
-        <v>9.078395632183029e-06</v>
+        <v>-4.4127055464639188e-06</v>
       </c>
       <c r="D30">
-        <v>-3.7432941115907417e-06</v>
+        <v>-4.014368705582283e-06</v>
       </c>
       <c r="E30">
-        <v>1.8196754478072829e-08</v>
+        <v>-8.3402859556666785e-10</v>
       </c>
       <c r="F30">
-        <v>-5.3170062463804915e-06</v>
+        <v>-1.8419200261227565e-05</v>
       </c>
       <c r="G30">
-        <v>1.5892475574857154e-06</v>
+        <v>-4.6261090988816548e-06</v>
       </c>
       <c r="H30">
-        <v>-4.207361399925628e-05</v>
+        <v>-4.7055995359580351e-05</v>
       </c>
       <c r="I30">
-        <v>-1.1162008556380321e-05</v>
+        <v>6.7545297397632689e-06</v>
       </c>
       <c r="J30">
-        <v>-3.4362991330363968e-06</v>
+        <v>8.0240392261744832e-06</v>
       </c>
       <c r="K30">
-        <v>1.1960281701943796e-05</v>
+        <v>1.3038864400544787e-05</v>
       </c>
       <c r="L30">
-        <v>-5.2561162497527967e-06</v>
+        <v>-9.1444009299757552e-06</v>
       </c>
       <c r="M30">
-        <v>-5.4707719815161954e-05</v>
+        <v>-1.2242476380704357e-05</v>
       </c>
       <c r="N30">
-        <v>0.00012350157466021208</v>
+        <v>0.0001852813442095532</v>
       </c>
       <c r="O30">
-        <v>-9.497152143127203e-05</v>
+        <v>-4.3420541572997698e-05</v>
       </c>
       <c r="P30">
-        <v>5.8228554816225743e-05</v>
+        <v>2.6371509084704827e-05</v>
       </c>
       <c r="Q30">
-        <v>-4.8637700066664173e-07</v>
+        <v>7.3446356314997813e-05</v>
       </c>
       <c r="R30">
-        <v>3.6249155061806844e-05</v>
+        <v>9.5597050472739378e-05</v>
       </c>
       <c r="S30">
-        <v>1.7587982876780405e-05</v>
+        <v>4.3467628110373442e-05</v>
       </c>
       <c r="T30">
-        <v>-6.9971695066448243e-05</v>
+        <v>-8.9685666702423459e-05</v>
       </c>
       <c r="U30">
-        <v>6.7585007183653626e-05</v>
+        <v>9.3167404871446384e-05</v>
       </c>
       <c r="V30">
-        <v>5.9506652066179883e-05</v>
+        <v>0.0001348805627858201</v>
       </c>
       <c r="W30">
-        <v>-5.1787848250889523e-05</v>
+        <v>-4.794041635996373e-05</v>
       </c>
       <c r="X30">
-        <v>1.1611884530182302e-05</v>
+        <v>-2.7750565127864939e-05</v>
       </c>
       <c r="Y30">
-        <v>-3.5884440126575035e-05</v>
+        <v>-7.4989240712913642e-05</v>
       </c>
       <c r="Z30">
-        <v>0.0023958525996362438</v>
+        <v>0.002109964130242789</v>
       </c>
       <c r="AA30">
-        <v>0.0023976319659872111</v>
+        <v>0.0021116197683530651</v>
       </c>
       <c r="AB30">
-        <v>0.0023938239766845499</v>
+        <v>0.0021126325070296315</v>
       </c>
       <c r="AC30">
-        <v>0.0024003266541567266</v>
+        <v>0.002112266810682553</v>
       </c>
       <c r="AD30">
-        <v>0.0024013860735255625</v>
+        <v>0.0021110009035527756</v>
       </c>
       <c r="AE30">
-        <v>0.0028600629481484534</v>
+        <v>0.0024564957981944922</v>
       </c>
       <c r="AF30">
-        <v>4.6628558613332784e-06</v>
+        <v>5.8879662373217137e-06</v>
       </c>
       <c r="AG30">
-        <v>2.6252214162212316e-05</v>
+        <v>3.7142461486385121e-05</v>
       </c>
       <c r="AH30">
-        <v>-3.8857779376191403e-05</v>
+        <v>-6.7257423107632409e-05</v>
       </c>
       <c r="AI30">
-        <v>-0.0022968007437127974</v>
+        <v>-0.0020547465710433234</v>
       </c>
     </row>
     <row r="31">
@@ -7548,106 +7548,106 @@
         <v>58</v>
       </c>
       <c r="B31">
-        <v>0.022661376593080655</v>
+        <v>0.012156935219847684</v>
       </c>
       <c r="C31">
-        <v>-1.1713617503157034e-07</v>
+        <v>-1.3817237429177379e-07</v>
       </c>
       <c r="D31">
-        <v>-1.1073115482207998e-07</v>
+        <v>-1.3660476020046644e-07</v>
       </c>
       <c r="E31">
-        <v>-7.6469376919826121e-10</v>
+        <v>-9.5757793863241551e-11</v>
       </c>
       <c r="F31">
-        <v>-2.1296604221588067e-06</v>
+        <v>-1.2536112130698041e-07</v>
       </c>
       <c r="G31">
-        <v>-4.9904075742537298e-06</v>
+        <v>-2.8987659844247721e-06</v>
       </c>
       <c r="H31">
-        <v>-3.8069441577882174e-06</v>
+        <v>-2.1202340239441037e-06</v>
       </c>
       <c r="I31">
-        <v>-1.5413697275998045e-06</v>
+        <v>-2.5183170442093184e-07</v>
       </c>
       <c r="J31">
-        <v>-1.2655894037201618e-06</v>
+        <v>-6.6831626087156612e-07</v>
       </c>
       <c r="K31">
-        <v>8.2590497641914012e-07</v>
+        <v>8.397996004587753e-07</v>
       </c>
       <c r="L31">
-        <v>-2.708817252856624e-07</v>
+        <v>-1.7756947047362303e-07</v>
       </c>
       <c r="M31">
-        <v>4.5140438765156904e-06</v>
+        <v>1.1087454115216786e-06</v>
       </c>
       <c r="N31">
-        <v>-1.6835123396858036e-06</v>
+        <v>-5.421617844185672e-07</v>
       </c>
       <c r="O31">
-        <v>-2.9833865790864454e-06</v>
+        <v>-7.1055333476091166e-07</v>
       </c>
       <c r="P31">
-        <v>-4.835728867982459e-06</v>
+        <v>-1.0920358114035344e-06</v>
       </c>
       <c r="Q31">
-        <v>-4.2407887498384193e-06</v>
+        <v>-4.8402692097325375e-07</v>
       </c>
       <c r="R31">
-        <v>-8.6701134686602592e-06</v>
+        <v>-3.8478896559055505e-06</v>
       </c>
       <c r="S31">
-        <v>-1.1447210369927276e-05</v>
+        <v>-6.1333967309722153e-06</v>
       </c>
       <c r="T31">
-        <v>2.1528153876205439e-07</v>
+        <v>2.9647257412071418e-06</v>
       </c>
       <c r="U31">
-        <v>6.9688415398830176e-06</v>
+        <v>7.4139764138646432e-06</v>
       </c>
       <c r="V31">
-        <v>7.0868702618841553e-06</v>
+        <v>7.1148461006115976e-06</v>
       </c>
       <c r="W31">
-        <v>-1.6556312024076805e-08</v>
+        <v>-3.8638261772101368e-07</v>
       </c>
       <c r="X31">
-        <v>-2.6925762539104889e-07</v>
+        <v>-7.6999422546614844e-07</v>
       </c>
       <c r="Y31">
-        <v>-8.8393577961908054e-06</v>
+        <v>-4.8846479974168429e-06</v>
       </c>
       <c r="Z31">
-        <v>6.8893600317669401e-06</v>
+        <v>8.2309305574250539e-06</v>
       </c>
       <c r="AA31">
-        <v>5.039172834197763e-06</v>
+        <v>6.9238386467466201e-06</v>
       </c>
       <c r="AB31">
-        <v>3.9742914039158828e-06</v>
+        <v>6.3410570567871928e-06</v>
       </c>
       <c r="AC31">
-        <v>7.3384980026480068e-06</v>
+        <v>8.948103966095376e-06</v>
       </c>
       <c r="AD31">
-        <v>6.7317510321905603e-06</v>
+        <v>9.1173440295177805e-06</v>
       </c>
       <c r="AE31">
-        <v>4.6628558613332784e-06</v>
+        <v>5.8879662373217137e-06</v>
       </c>
       <c r="AF31">
-        <v>3.8250915107269126e-06</v>
+        <v>2.8421139156941524e-06</v>
       </c>
       <c r="AG31">
-        <v>-6.0227971973546426e-06</v>
+        <v>-4.1980285272648089e-06</v>
       </c>
       <c r="AH31">
-        <v>-1.1946887292048473e-05</v>
+        <v>-9.9133810261697846e-06</v>
       </c>
       <c r="AI31">
-        <v>-6.1465698923922151e-05</v>
+        <v>-5.0810842566947293e-05</v>
       </c>
     </row>
     <row r="32">
@@ -7655,106 +7655,106 @@
         <v>59</v>
       </c>
       <c r="B32">
-        <v>-0.20132120976842946</v>
+        <v>-0.16834303349841773</v>
       </c>
       <c r="C32">
-        <v>-7.8348589206558112e-05</v>
+        <v>-4.6110191547671093e-05</v>
       </c>
       <c r="D32">
-        <v>7.2371231071046956e-07</v>
+        <v>1.1014417681391481e-06</v>
       </c>
       <c r="E32">
-        <v>-2.1061352079788054e-08</v>
+        <v>-2.3560282270735233e-08</v>
       </c>
       <c r="F32">
-        <v>1.3101660560370029e-05</v>
+        <v>-1.6968138335860146e-05</v>
       </c>
       <c r="G32">
-        <v>2.3560435616849611e-05</v>
+        <v>2.3488971895614663e-06</v>
       </c>
       <c r="H32">
-        <v>-1.3115123110637311e-06</v>
+        <v>-2.752301032101466e-05</v>
       </c>
       <c r="I32">
-        <v>0.00017685683753167463</v>
+        <v>9.3093959670792308e-05</v>
       </c>
       <c r="J32">
-        <v>-0.00016898574867744656</v>
+        <v>-3.0264472768573137e-05</v>
       </c>
       <c r="K32">
-        <v>1.6152553236027049e-05</v>
+        <v>8.9231783656214085e-06</v>
       </c>
       <c r="L32">
-        <v>-5.157916866126524e-06</v>
+        <v>2.7865441998081248e-06</v>
       </c>
       <c r="M32">
-        <v>7.9398350037771e-05</v>
+        <v>1.290950570694912e-05</v>
       </c>
       <c r="N32">
-        <v>6.7252230678467063e-05</v>
+        <v>3.2833001582458464e-05</v>
       </c>
       <c r="O32">
-        <v>0.00017536319512749359</v>
+        <v>2.9504140180518852e-05</v>
       </c>
       <c r="P32">
-        <v>-4.5397950292241571e-05</v>
+        <v>-5.9418637690063832e-06</v>
       </c>
       <c r="Q32">
-        <v>0.00031659723868952827</v>
+        <v>0.00019026094556276463</v>
       </c>
       <c r="R32">
-        <v>0.0002879989900816636</v>
+        <v>0.00016438269767595284</v>
       </c>
       <c r="S32">
-        <v>0.0002006316169769623</v>
+        <v>0.0001026237763215327</v>
       </c>
       <c r="T32">
-        <v>-5.5994886211566119e-05</v>
+        <v>-6.2888099250091312e-06</v>
       </c>
       <c r="U32">
-        <v>2.6878304278842719e-05</v>
+        <v>7.9994971644315252e-05</v>
       </c>
       <c r="V32">
-        <v>9.5301536831786382e-05</v>
+        <v>0.00010872160819264814</v>
       </c>
       <c r="W32">
-        <v>3.3973305414521386e-05</v>
+        <v>3.4010345848732202e-05</v>
       </c>
       <c r="X32">
-        <v>0.00011623267111935905</v>
+        <v>9.5602396610584188e-05</v>
       </c>
       <c r="Y32">
-        <v>6.0175165015133813e-05</v>
+        <v>2.1838411203416522e-05</v>
       </c>
       <c r="Z32">
-        <v>3.8664036657134679e-05</v>
+        <v>4.8591971455376384e-05</v>
       </c>
       <c r="AA32">
-        <v>3.4835930301661648e-05</v>
+        <v>5.7692432346097104e-05</v>
       </c>
       <c r="AB32">
-        <v>8.5101182829898977e-05</v>
+        <v>7.1950381959264009e-05</v>
       </c>
       <c r="AC32">
-        <v>3.0650755195742868e-05</v>
+        <v>4.8606877753752144e-05</v>
       </c>
       <c r="AD32">
-        <v>0.00024879189554570264</v>
+        <v>0.00020040793013192601</v>
       </c>
       <c r="AE32">
-        <v>2.6252214162212316e-05</v>
+        <v>3.7142461486385121e-05</v>
       </c>
       <c r="AF32">
-        <v>-6.0227971973546426e-06</v>
+        <v>-4.1980285272648089e-06</v>
       </c>
       <c r="AG32">
-        <v>0.0017412523813394669</v>
+        <v>0.001308767589036399</v>
       </c>
       <c r="AH32">
-        <v>0.00028408191679715956</v>
+        <v>0.00014955068993683282</v>
       </c>
       <c r="AI32">
-        <v>-0.00031052205956822116</v>
+        <v>-0.0002592194314152793</v>
       </c>
     </row>
     <row r="33">
@@ -7762,106 +7762,106 @@
         <v>60</v>
       </c>
       <c r="B33">
-        <v>-0.12610477213348631</v>
+        <v>-0.14606536816231794</v>
       </c>
       <c r="C33">
-        <v>-2.871086252514396e-05</v>
+        <v>-1.7785141546052447e-05</v>
       </c>
       <c r="D33">
-        <v>-2.0665980981459645e-06</v>
+        <v>-1.6190327647853096e-07</v>
       </c>
       <c r="E33">
-        <v>9.6154898530007683e-09</v>
+        <v>-9.8789553017018076e-09</v>
       </c>
       <c r="F33">
-        <v>-1.1459651114999712e-06</v>
+        <v>-3.163277299217046e-06</v>
       </c>
       <c r="G33">
-        <v>5.04504162779848e-05</v>
+        <v>5.6548310784992374e-05</v>
       </c>
       <c r="H33">
-        <v>1.1186649182695282e-05</v>
+        <v>6.1610761025077295e-06</v>
       </c>
       <c r="I33">
-        <v>6.4684847934265953e-05</v>
+        <v>3.5675842478548499e-05</v>
       </c>
       <c r="J33">
-        <v>-8.3200465864430545e-05</v>
+        <v>-2.1851970220350368e-05</v>
       </c>
       <c r="K33">
-        <v>3.0176125816626896e-05</v>
+        <v>9.3125405626924085e-06</v>
       </c>
       <c r="L33">
-        <v>-7.1369518895646625e-06</v>
+        <v>-4.8713737517581206e-06</v>
       </c>
       <c r="M33">
-        <v>5.0290009126370559e-05</v>
+        <v>1.3523503522019133e-05</v>
       </c>
       <c r="N33">
-        <v>3.4368224754767647e-05</v>
+        <v>2.8941215185435436e-05</v>
       </c>
       <c r="O33">
-        <v>0.00022196014127580637</v>
+        <v>3.4805187773936431e-05</v>
       </c>
       <c r="P33">
-        <v>-0.00015119055836303815</v>
+        <v>-2.8616771146732921e-05</v>
       </c>
       <c r="Q33">
-        <v>0.00019594872205736056</v>
+        <v>9.7376897196153021e-05</v>
       </c>
       <c r="R33">
-        <v>0.0001867011565983975</v>
+        <v>9.4695687023475111e-05</v>
       </c>
       <c r="S33">
-        <v>0.00014512875049894208</v>
+        <v>7.1503295263667353e-05</v>
       </c>
       <c r="T33">
-        <v>0.00014858609909701621</v>
+        <v>1.4120930301418644e-05</v>
       </c>
       <c r="U33">
-        <v>0.00015217774312469186</v>
+        <v>1.3543670851434708e-05</v>
       </c>
       <c r="V33">
-        <v>0.00019727308075736388</v>
+        <v>7.3259343357217656e-05</v>
       </c>
       <c r="W33">
-        <v>-1.182606046036495e-05</v>
+        <v>-1.6129807065460138e-05</v>
       </c>
       <c r="X33">
-        <v>1.5389163367935809e-05</v>
+        <v>7.974738377641258e-06</v>
       </c>
       <c r="Y33">
-        <v>1.0711515924385082e-05</v>
+        <v>1.3512546714689229e-05</v>
       </c>
       <c r="Z33">
-        <v>6.6604240827844267e-06</v>
+        <v>-2.6220638622332726e-05</v>
       </c>
       <c r="AA33">
-        <v>-2.8199243767408622e-05</v>
+        <v>-3.7669613783008625e-05</v>
       </c>
       <c r="AB33">
-        <v>1.9214496868034817e-05</v>
+        <v>-2.2614177046242478e-05</v>
       </c>
       <c r="AC33">
-        <v>-1.8159970944595571e-05</v>
+        <v>-5.2841160719077781e-05</v>
       </c>
       <c r="AD33">
-        <v>5.4293743339964631e-08</v>
+        <v>-3.24299948368668e-05</v>
       </c>
       <c r="AE33">
-        <v>-3.8857779376191403e-05</v>
+        <v>-6.7257423107632409e-05</v>
       </c>
       <c r="AF33">
-        <v>-1.1946887292048473e-05</v>
+        <v>-9.9133810261697846e-06</v>
       </c>
       <c r="AG33">
-        <v>0.00028408191679715956</v>
+        <v>0.00014955068993683282</v>
       </c>
       <c r="AH33">
-        <v>0.0014618430071155078</v>
+        <v>0.0012169340638983968</v>
       </c>
       <c r="AI33">
-        <v>-0.00010223603091888482</v>
+        <v>8.9426217182326411e-05</v>
       </c>
     </row>
     <row r="34">
@@ -7869,106 +7869,106 @@
         <v>61</v>
       </c>
       <c r="B34">
-        <v>-0.44886908162203287</v>
+        <v>-0.31728577352928866</v>
       </c>
       <c r="C34">
-        <v>0.00017048838167084109</v>
+        <v>0.00015577358027267209</v>
       </c>
       <c r="D34">
-        <v>-0.00037840922310119454</v>
+        <v>-0.00027957227949393528</v>
       </c>
       <c r="E34">
-        <v>3.2688604033339336e-06</v>
+        <v>2.4101841408793162e-06</v>
       </c>
       <c r="F34">
-        <v>-0.0031907660066190684</v>
+        <v>-0.0024347903066560409</v>
       </c>
       <c r="G34">
-        <v>-0.003264930078864586</v>
+        <v>-0.0025068716653706587</v>
       </c>
       <c r="H34">
-        <v>-0.0033820336201729473</v>
+        <v>-0.0024907840804877122</v>
       </c>
       <c r="I34">
-        <v>-0.0039016022318896365</v>
+        <v>-0.0029982245594123175</v>
       </c>
       <c r="J34">
-        <v>0.00037411143719150966</v>
+        <v>8.019374920288896e-05</v>
       </c>
       <c r="K34">
-        <v>-0.0024598768867113464</v>
+        <v>-0.00187831800198429</v>
       </c>
       <c r="L34">
-        <v>8.0841463138480685e-05</v>
+        <v>7.2341622901808439e-05</v>
       </c>
       <c r="M34">
-        <v>-0.00010912148249779828</v>
+        <v>-1.905461139721737e-05</v>
       </c>
       <c r="N34">
-        <v>-0.0044423224796542029</v>
+        <v>-0.003199411113164013</v>
       </c>
       <c r="O34">
-        <v>-0.0037023871339994029</v>
+        <v>-0.00066844723513465412</v>
       </c>
       <c r="P34">
-        <v>-0.0031849625751416287</v>
+        <v>-0.00097849154912832176</v>
       </c>
       <c r="Q34">
-        <v>-0.015825749025517082</v>
+        <v>-0.011551297423127107</v>
       </c>
       <c r="R34">
-        <v>-0.01502158810750011</v>
+        <v>-0.0108666916165113</v>
       </c>
       <c r="S34">
-        <v>-0.014763368816508946</v>
+        <v>-0.010715118799295528</v>
       </c>
       <c r="T34">
-        <v>-0.024416804220154135</v>
+        <v>-0.018831810835430202</v>
       </c>
       <c r="U34">
-        <v>-0.019556821768951863</v>
+        <v>-0.014929297964842797</v>
       </c>
       <c r="V34">
-        <v>-0.019970339422381342</v>
+        <v>-0.015225895337582101</v>
       </c>
       <c r="W34">
-        <v>-0.00042718926414069328</v>
+        <v>-0.00041631372711569385</v>
       </c>
       <c r="X34">
-        <v>-0.0012783098564462269</v>
+        <v>-0.00099830234275434309</v>
       </c>
       <c r="Y34">
-        <v>-0.0011984065111760687</v>
+        <v>-0.001090271946000361</v>
       </c>
       <c r="Z34">
-        <v>-0.0024100460320740777</v>
+        <v>-0.0023158348738640863</v>
       </c>
       <c r="AA34">
-        <v>-0.0022004278612251281</v>
+        <v>-0.0021911353971823654</v>
       </c>
       <c r="AB34">
-        <v>-0.0021712246245258688</v>
+        <v>-0.0022047320839206708</v>
       </c>
       <c r="AC34">
-        <v>-0.0023882160995456758</v>
+        <v>-0.0023054847195037266</v>
       </c>
       <c r="AD34">
-        <v>-0.0022567947157818703</v>
+        <v>-0.0022442484931118984</v>
       </c>
       <c r="AE34">
-        <v>-0.0022968007437127974</v>
+        <v>-0.0020547465710433234</v>
       </c>
       <c r="AF34">
-        <v>-6.1465698923922151e-05</v>
+        <v>-5.0810842566947293e-05</v>
       </c>
       <c r="AG34">
-        <v>-0.00031052205956822116</v>
+        <v>-0.0002592194314152793</v>
       </c>
       <c r="AH34">
-        <v>-0.00010223603091888482</v>
+        <v>8.9426217182326411e-05</v>
       </c>
       <c r="AI34">
-        <v>0.051766342372952509</v>
+        <v>0.039259369291388263</v>
       </c>
     </row>
   </sheetData>

--- a/input/ES/reg_income.xlsx
+++ b/input/ES/reg_income.xlsx
@@ -45,7 +45,7 @@
     <t>Ashley Burdett, Aleksandra Kolndrekaj</t>
   </si>
   <si>
-    <t>15 June 2016 AK</t>
+    <t>07 Oct. 2026 AK</t>
   </si>
   <si>
     <t>Description:</t>
@@ -63,7 +63,7 @@
     <t>Goodnessoffit</t>
   </si>
   <si>
-    <t xml:space="preserve">I1a - Receiving capital income </t>
+    <t xml:space="preserve">I1a - Receive capital income </t>
   </si>
   <si>
     <t>Pseudo R-squared</t>
@@ -72,7 +72,7 @@
     <t>N</t>
   </si>
   <si>
-    <t>I1b - Capital income amount</t>
+    <t>I1b - Amount of capital income</t>
   </si>
   <si>
     <t>R-squared</t>
@@ -328,7 +328,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -358,25 +358,45 @@
       <c r="F2"/>
     </row>
     <row r="3">
+      <c r="A3" t="s">
+        <v>15</v>
+      </c>
       <c r="B3"/>
       <c r="C3"/>
       <c r="D3"/>
       <c r="F3"/>
     </row>
     <row r="4">
-      <c r="B4"/>
+      <c r="A4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B4">
+        <v>0.32022555969286282</v>
+      </c>
       <c r="C4"/>
       <c r="D4"/>
-      <c r="F4"/>
+      <c r="E4" t="s">
+        <v>24</v>
+      </c>
+      <c r="F4">
+        <v>15120.96397464909</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>15</v>
-      </c>
-      <c r="B5"/>
+        <v>17</v>
+      </c>
+      <c r="B5">
+        <v>139917</v>
+      </c>
       <c r="C5"/>
       <c r="D5"/>
-      <c r="F5"/>
+      <c r="E5" t="s">
+        <v>25</v>
+      </c>
+      <c r="F5">
+        <v>-97413945.038870797</v>
+      </c>
     </row>
     <row r="6">
       <c r="B6"/>
@@ -386,84 +406,34 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>16</v>
-      </c>
-      <c r="B7">
-        <v>0.32022555969286282</v>
-      </c>
+        <v>18</v>
+      </c>
+      <c r="B7"/>
       <c r="C7"/>
       <c r="D7"/>
-      <c r="E7" t="s">
-        <v>24</v>
-      </c>
-      <c r="F7">
-        <v>15120.96397464909</v>
-      </c>
+      <c r="F7"/>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B8">
-        <v>139917</v>
+        <v>0.63405729156306156</v>
       </c>
       <c r="C8"/>
       <c r="D8"/>
-      <c r="E8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F8">
-        <v>-97413945.038870797</v>
-      </c>
+      <c r="F8"/>
     </row>
     <row r="9">
-      <c r="B9"/>
+      <c r="A9" t="s">
+        <v>17</v>
+      </c>
+      <c r="B9">
+        <v>53223</v>
+      </c>
       <c r="C9"/>
       <c r="D9"/>
       <c r="F9"/>
-    </row>
-    <row r="10">
-      <c r="B10"/>
-      <c r="C10"/>
-      <c r="D10"/>
-      <c r="F10"/>
-    </row>
-    <row r="11">
-      <c r="A11" t="s">
-        <v>18</v>
-      </c>
-      <c r="B11"/>
-      <c r="C11"/>
-      <c r="D11"/>
-      <c r="F11"/>
-    </row>
-    <row r="12">
-      <c r="B12"/>
-      <c r="C12"/>
-      <c r="D12"/>
-      <c r="F12"/>
-    </row>
-    <row r="13">
-      <c r="A13" t="s">
-        <v>19</v>
-      </c>
-      <c r="B13">
-        <v>0.63405729156306156</v>
-      </c>
-      <c r="C13"/>
-      <c r="D13"/>
-      <c r="F13"/>
-    </row>
-    <row r="14">
-      <c r="A14" t="s">
-        <v>17</v>
-      </c>
-      <c r="B14">
-        <v>53223</v>
-      </c>
-      <c r="C14"/>
-      <c r="D14"/>
-      <c r="F14"/>
     </row>
   </sheetData>
 </worksheet>
